--- a/data/Base_Op_Cam.xlsx
+++ b/data/Base_Op_Cam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mefp\Sergio Garnica\Documents\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD14EA0-C1E9-49FF-8896-6735E14B690C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162716B3-6300-4C5F-86B1-E29D369F2641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{D18D9BAD-78DE-4368-BCF3-29E6374A660B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D18D9BAD-78DE-4368-BCF3-29E6374A660B}"/>
   </bookViews>
   <sheets>
     <sheet name="TC" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,9 @@
   </sheets>
   <calcPr calcId="191029" concurrentCalc="0" concurrentManualCount="4"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId4"/>
-    <pivotCache cacheId="11" r:id="rId5"/>
-    <pivotCache cacheId="14" r:id="rId6"/>
+    <pivotCache cacheId="5" r:id="rId4"/>
+    <pivotCache cacheId="8" r:id="rId5"/>
+    <pivotCache cacheId="11" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="133">
   <si>
     <t>Nombre</t>
   </si>
@@ -491,6 +491,18 @@
   <si>
     <t>2026-09-04</t>
   </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
 </sst>
 </file>
 
@@ -547,14 +559,17 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46272.637042939816" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{04D15196-6A10-4FCA-A07B-7666B41B44BD}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46275.696096412037" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{9ECE6D2C-0019-46A8-93F5-B57014A573FD}">
   <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="10">
+  <cacheFields count="9">
     <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
     </cacheField>
     <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+      <sharedItems count="2">
+        <s v="[Transaccion].[Transaccion].&amp;[Compra]" c="Compra"/>
+        <s v="[Transaccion].[Transaccion].&amp;[Venta]" c="Venta"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
@@ -569,7 +584,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
     </cacheField>
     <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
-      <sharedItems count="96">
+      <sharedItems count="100">
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
@@ -666,6 +681,515 @@
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-02T00:00:00]" c="2026-09-02"/>
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-03T00:00:00]" c="2026-09-03"/>
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-04T00:00:00]" c="2026-09-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-05T00:00:00]" c="2026-09-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-06T00:00:00]" c="2026-09-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-07T00:00:00]" c="2026-09-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-08T00:00:00]" c="2026-09-08"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
+      <sharedItems count="14">
+        <s v="[Entidades].[Sigla].&amp;[BCR]" c="BCR"/>
+        <s v="[Entidades].[Sigla].&amp;[BEC]" c="BEC"/>
+        <s v="[Entidades].[Sigla].&amp;[BFO]" c="BFO"/>
+        <s v="[Entidades].[Sigla].&amp;[BGA]" c="BGA"/>
+        <s v="[Entidades].[Sigla].&amp;[BIE]" c="BIE"/>
+        <s v="[Entidades].[Sigla].&amp;[BIS]" c="BIS"/>
+        <s v="[Entidades].[Sigla].&amp;[BME]" c="BME"/>
+        <s v="[Entidades].[Sigla].&amp;[BNA]" c="BNA"/>
+        <s v="[Entidades].[Sigla].&amp;[BNB]" c="BNB"/>
+        <s v="[Entidades].[Sigla].&amp;[BPR]" c="BPR"/>
+        <s v="[Entidades].[Sigla].&amp;[BSO]" c="BSO"/>
+        <s v="[Entidades].[Sigla].&amp;[BUN]" c="BUN"/>
+        <s v="[Entidades].[Sigla].&amp;[PCO]" c="PCO"/>
+        <s v="[Entidades].[Sigla].&amp;[PEF]" c="PEF"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Numero Operaciones]" caption="Numero Operaciones" numFmtId="0" hierarchy="28" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="29">
+    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Categoria]" caption="Cod Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Categoria].[All]" allUniqueName="[Actividad Economica].[Cod Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Sector Actividad]" caption="Cod Sector Actividad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" allUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion].[All]" allUniqueName="[Actividad Economica].[Descripcion].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion Categoria]" caption="Descripcion Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" allUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Concepto].[Cod Concepto]" caption="Cod Concepto" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Concepto].[Cod Concepto].[All]" allUniqueName="[Concepto].[Cod Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Concepto].[Concepto]" caption="Concepto" attribute="1" defaultMemberUniqueName="[Concepto].[Concepto].[All]" allUniqueName="[Concepto].[Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Entidades].[Cod Entidad]" caption="Cod Entidad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Entidades].[Cod Entidad].[All]" allUniqueName="[Entidades].[Cod Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Entidades].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Entidades].[Nombre].[All]" allUniqueName="[Entidades].[Nombre].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Entidades].[Sigla]" caption="Sigla" attribute="1" defaultMemberUniqueName="[Entidades].[Sigla].[All]" allUniqueName="[Entidades].[Sigla].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="7"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Entidades].[Tipo Entidad]" caption="Tipo Entidad" attribute="1" defaultMemberUniqueName="[Entidades].[Tipo Entidad].[All]" allUniqueName="[Entidades].[Tipo Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Estrato].[Cod Estrato]" caption="Cod Estrato" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Estrato].[Cod Estrato].[All]" allUniqueName="[Estrato].[Cod Estrato].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Estrato].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Estrato].[Descripcion].[All]" allUniqueName="[Estrato].[Descripcion].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Moneda Cambio].[Cod Moneda]" caption="Cod Moneda" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Moneda Cambio].[Cod Moneda].[All]" allUniqueName="[Moneda Cambio].[Cod Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Moneda Cambio].[Moneda]" caption="Moneda" attribute="1" defaultMemberUniqueName="[Moneda Cambio].[Moneda].[All]" allUniqueName="[Moneda Cambio].[Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Monto Menor].[Cod Monto Menor]" caption="Cod Monto Menor" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Monto Menor].[Cod Monto Menor].[All]" allUniqueName="[Monto Menor].[Cod Monto Menor].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Monto Menor].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Monto Menor].[Descripcion].[All]" allUniqueName="[Monto Menor].[Descripcion].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="5"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Subsistema].[Cod Subsistema]" caption="Cod Subsistema" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Subsistema].[Cod Subsistema].[All]" allUniqueName="[Subsistema].[Cod Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Subsistema].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Subsistema].[Nombre].[All]" allUniqueName="[Subsistema].[Nombre].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Subsistema].[Sigla Subsistema]" caption="Sigla Subsistema" attribute="1" defaultMemberUniqueName="[Subsistema].[Sigla Subsistema].[All]" allUniqueName="[Subsistema].[Sigla Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha]" caption="Cod Fecha" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Fecha]" caption="Fecha" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="6"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes]" caption="Ultimo Dia Mes" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transaccion].[Cod Transaccion]" caption="Cod Transaccion" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Transaccion].[Cod Transaccion].[All]" allUniqueName="[Transaccion].[Cod Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transaccion].[Transaccion]" caption="Transaccion" attribute="1" defaultMemberUniqueName="[Transaccion].[Transaccion].[All]" allUniqueName="[Transaccion].[Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Monto Usd]" caption="Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Usd]" caption="Tipo Cambio Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Mm Usd]" caption="Tipo Cambio Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Numero Operaciones]" caption="Numero Operaciones" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="8"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="10">
+    <dimension name="Actividad Economica" uniqueName="[Actividad Economica]" caption="Actividad Economica"/>
+    <dimension name="Concepto" uniqueName="[Concepto]" caption="Concepto"/>
+    <dimension name="Entidades" uniqueName="[Entidades]" caption="Entidades"/>
+    <dimension name="Estrato" uniqueName="[Estrato]" caption="Estrato"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Moneda Cambio" uniqueName="[Moneda Cambio]" caption="Moneda Cambio"/>
+    <dimension name="Monto Menor" uniqueName="[Monto Menor]" caption="Monto Menor"/>
+    <dimension name="Subsistema" uniqueName="[Subsistema]" caption="Subsistema"/>
+    <dimension name="Tipo Cambio Fecha Dia" uniqueName="[Tipo Cambio Fecha Dia]" caption="Tipo Cambio Fecha Dia"/>
+    <dimension name="Transaccion" uniqueName="[Transaccion]" caption="Transaccion"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Operaciones Cambiarias" caption="Fact Operaciones Cambiarias"/>
+  </measureGroups>
+  <maps count="9">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+    <map measureGroup="0" dimension="8"/>
+    <map measureGroup="0" dimension="9"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46275.696365046293" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{F7995ADC-F0B3-4CE9-B66F-D51574EF46B6}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="9">
+    <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
+      <sharedItems count="2">
+        <s v="[Transaccion].[Transaccion].&amp;[Compra]" c="Compra"/>
+        <s v="[Transaccion].[Transaccion].&amp;[Venta]" c="Venta"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda]" caption="Cod Moneda" numFmtId="0" hierarchy="12" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda].[Moneda]" caption="Moneda" propertyName="Moneda" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Monto Menor].[Descripcion].[Descripcion]" caption="Descripcion" numFmtId="0" hierarchy="15" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
+      <sharedItems count="100">
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-04T00:00:00]" c="2026-06-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-05T00:00:00]" c="2026-06-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-06T00:00:00]" c="2026-06-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-07T00:00:00]" c="2026-06-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-08T00:00:00]" c="2026-06-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-09T00:00:00]" c="2026-06-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-10T00:00:00]" c="2026-06-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-11T00:00:00]" c="2026-06-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-12T00:00:00]" c="2026-06-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-13T00:00:00]" c="2026-06-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-14T00:00:00]" c="2026-06-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-15T00:00:00]" c="2026-06-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-16T00:00:00]" c="2026-06-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-17T00:00:00]" c="2026-06-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-18T00:00:00]" c="2026-06-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-19T00:00:00]" c="2026-06-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-20T00:00:00]" c="2026-06-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-21T00:00:00]" c="2026-06-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-22T00:00:00]" c="2026-06-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-23T00:00:00]" c="2026-06-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-24T00:00:00]" c="2026-06-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-25T00:00:00]" c="2026-06-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-26T00:00:00]" c="2026-06-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-27T00:00:00]" c="2026-06-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-28T00:00:00]" c="2026-06-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-29T00:00:00]" c="2026-06-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-30T00:00:00]" c="2026-06-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-01T00:00:00]" c="2026-07-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-02T00:00:00]" c="2026-07-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-03T00:00:00]" c="2026-07-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-04T00:00:00]" c="2026-07-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-05T00:00:00]" c="2026-07-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-06T00:00:00]" c="2026-07-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-07T00:00:00]" c="2026-07-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-08T00:00:00]" c="2026-07-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-09T00:00:00]" c="2026-07-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-10T00:00:00]" c="2026-07-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-11T00:00:00]" c="2026-07-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-12T00:00:00]" c="2026-07-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-13T00:00:00]" c="2026-07-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-14T00:00:00]" c="2026-07-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-15T00:00:00]" c="2026-07-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-16T00:00:00]" c="2026-07-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-17T00:00:00]" c="2026-07-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-18T00:00:00]" c="2026-07-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-19T00:00:00]" c="2026-07-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-20T00:00:00]" c="2026-07-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-21T00:00:00]" c="2026-07-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-22T00:00:00]" c="2026-07-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-23T00:00:00]" c="2026-07-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-24T00:00:00]" c="2026-07-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-25T00:00:00]" c="2026-07-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-26T00:00:00]" c="2026-07-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-27T00:00:00]" c="2026-07-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-28T00:00:00]" c="2026-07-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-29T00:00:00]" c="2026-07-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-30T00:00:00]" c="2026-07-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-31T00:00:00]" c="2026-07-31"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-01T00:00:00]" c="2026-08-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-02T00:00:00]" c="2026-08-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-03T00:00:00]" c="2026-08-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-04T00:00:00]" c="2026-08-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-05T00:00:00]" c="2026-08-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-06T00:00:00]" c="2026-08-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-07T00:00:00]" c="2026-08-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-08T00:00:00]" c="2026-08-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-09T00:00:00]" c="2026-08-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-10T00:00:00]" c="2026-08-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-11T00:00:00]" c="2026-08-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-12T00:00:00]" c="2026-08-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-13T00:00:00]" c="2026-08-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-14T00:00:00]" c="2026-08-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-15T00:00:00]" c="2026-08-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-16T00:00:00]" c="2026-08-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-17T00:00:00]" c="2026-08-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-18T00:00:00]" c="2026-08-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-19T00:00:00]" c="2026-08-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-20T00:00:00]" c="2026-08-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-21T00:00:00]" c="2026-08-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-22T00:00:00]" c="2026-08-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-23T00:00:00]" c="2026-08-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-24T00:00:00]" c="2026-08-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-25T00:00:00]" c="2026-08-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-26T00:00:00]" c="2026-08-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-27T00:00:00]" c="2026-08-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-28T00:00:00]" c="2026-08-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-29T00:00:00]" c="2026-08-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-30T00:00:00]" c="2026-08-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-31T00:00:00]" c="2026-08-31"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-01T00:00:00]" c="2026-09-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-02T00:00:00]" c="2026-09-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-03T00:00:00]" c="2026-09-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-04T00:00:00]" c="2026-09-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-05T00:00:00]" c="2026-09-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-06T00:00:00]" c="2026-09-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-07T00:00:00]" c="2026-09-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-08T00:00:00]" c="2026-09-08"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
+      <sharedItems count="14">
+        <s v="[Entidades].[Sigla].&amp;[BCR]" c="BCR"/>
+        <s v="[Entidades].[Sigla].&amp;[BEC]" c="BEC"/>
+        <s v="[Entidades].[Sigla].&amp;[BFO]" c="BFO"/>
+        <s v="[Entidades].[Sigla].&amp;[BGA]" c="BGA"/>
+        <s v="[Entidades].[Sigla].&amp;[BIE]" c="BIE"/>
+        <s v="[Entidades].[Sigla].&amp;[BIS]" c="BIS"/>
+        <s v="[Entidades].[Sigla].&amp;[BME]" c="BME"/>
+        <s v="[Entidades].[Sigla].&amp;[BNA]" c="BNA"/>
+        <s v="[Entidades].[Sigla].&amp;[BNB]" c="BNB"/>
+        <s v="[Entidades].[Sigla].&amp;[BPR]" c="BPR"/>
+        <s v="[Entidades].[Sigla].&amp;[BSO]" c="BSO"/>
+        <s v="[Entidades].[Sigla].&amp;[BUN]" c="BUN"/>
+        <s v="[Entidades].[Sigla].&amp;[PCO]" c="PCO"/>
+        <s v="[Entidades].[Sigla].&amp;[PEF]" c="PEF"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" numFmtId="0" hierarchy="26" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="29">
+    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Categoria]" caption="Cod Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Categoria].[All]" allUniqueName="[Actividad Economica].[Cod Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Sector Actividad]" caption="Cod Sector Actividad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" allUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion].[All]" allUniqueName="[Actividad Economica].[Descripcion].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion Categoria]" caption="Descripcion Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" allUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Concepto].[Cod Concepto]" caption="Cod Concepto" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Concepto].[Cod Concepto].[All]" allUniqueName="[Concepto].[Cod Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Concepto].[Concepto]" caption="Concepto" attribute="1" defaultMemberUniqueName="[Concepto].[Concepto].[All]" allUniqueName="[Concepto].[Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Entidades].[Cod Entidad]" caption="Cod Entidad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Entidades].[Cod Entidad].[All]" allUniqueName="[Entidades].[Cod Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Entidades].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Entidades].[Nombre].[All]" allUniqueName="[Entidades].[Nombre].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Entidades].[Sigla]" caption="Sigla" attribute="1" defaultMemberUniqueName="[Entidades].[Sigla].[All]" allUniqueName="[Entidades].[Sigla].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="7"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Entidades].[Tipo Entidad]" caption="Tipo Entidad" attribute="1" defaultMemberUniqueName="[Entidades].[Tipo Entidad].[All]" allUniqueName="[Entidades].[Tipo Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Estrato].[Cod Estrato]" caption="Cod Estrato" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Estrato].[Cod Estrato].[All]" allUniqueName="[Estrato].[Cod Estrato].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Estrato].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Estrato].[Descripcion].[All]" allUniqueName="[Estrato].[Descripcion].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Moneda Cambio].[Cod Moneda]" caption="Cod Moneda" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Moneda Cambio].[Cod Moneda].[All]" allUniqueName="[Moneda Cambio].[Cod Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Moneda Cambio].[Moneda]" caption="Moneda" attribute="1" defaultMemberUniqueName="[Moneda Cambio].[Moneda].[All]" allUniqueName="[Moneda Cambio].[Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Monto Menor].[Cod Monto Menor]" caption="Cod Monto Menor" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Monto Menor].[Cod Monto Menor].[All]" allUniqueName="[Monto Menor].[Cod Monto Menor].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Monto Menor].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Monto Menor].[Descripcion].[All]" allUniqueName="[Monto Menor].[Descripcion].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="5"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Subsistema].[Cod Subsistema]" caption="Cod Subsistema" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Subsistema].[Cod Subsistema].[All]" allUniqueName="[Subsistema].[Cod Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Subsistema].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Subsistema].[Nombre].[All]" allUniqueName="[Subsistema].[Nombre].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Subsistema].[Sigla Subsistema]" caption="Sigla Subsistema" attribute="1" defaultMemberUniqueName="[Subsistema].[Sigla Subsistema].[All]" allUniqueName="[Subsistema].[Sigla Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha]" caption="Cod Fecha" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Fecha]" caption="Fecha" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="6"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes]" caption="Ultimo Dia Mes" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transaccion].[Cod Transaccion]" caption="Cod Transaccion" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Transaccion].[Cod Transaccion].[All]" allUniqueName="[Transaccion].[Cod Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transaccion].[Transaccion]" caption="Transaccion" attribute="1" defaultMemberUniqueName="[Transaccion].[Transaccion].[All]" allUniqueName="[Transaccion].[Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Monto Usd]" caption="Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Usd]" caption="Tipo Cambio Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="8"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Mm Usd]" caption="Tipo Cambio Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Numero Operaciones]" caption="Numero Operaciones" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="10">
+    <dimension name="Actividad Economica" uniqueName="[Actividad Economica]" caption="Actividad Economica"/>
+    <dimension name="Concepto" uniqueName="[Concepto]" caption="Concepto"/>
+    <dimension name="Entidades" uniqueName="[Entidades]" caption="Entidades"/>
+    <dimension name="Estrato" uniqueName="[Estrato]" caption="Estrato"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Moneda Cambio" uniqueName="[Moneda Cambio]" caption="Moneda Cambio"/>
+    <dimension name="Monto Menor" uniqueName="[Monto Menor]" caption="Monto Menor"/>
+    <dimension name="Subsistema" uniqueName="[Subsistema]" caption="Subsistema"/>
+    <dimension name="Tipo Cambio Fecha Dia" uniqueName="[Tipo Cambio Fecha Dia]" caption="Tipo Cambio Fecha Dia"/>
+    <dimension name="Transaccion" uniqueName="[Transaccion]" caption="Transaccion"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Operaciones Cambiarias" caption="Fact Operaciones Cambiarias"/>
+  </measureGroups>
+  <maps count="9">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+    <map measureGroup="0" dimension="8"/>
+    <map measureGroup="0" dimension="9"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46275.696549768516" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{04D15196-6A10-4FCA-A07B-7666B41B44BD}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="10">
+    <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda]" caption="Cod Moneda" numFmtId="0" hierarchy="12" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda].[Moneda]" caption="Moneda" propertyName="Moneda" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Monto Menor].[Descripcion].[Descripcion]" caption="Descripcion" numFmtId="0" hierarchy="15" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
+      <sharedItems count="100">
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-04T00:00:00]" c="2026-06-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-05T00:00:00]" c="2026-06-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-06T00:00:00]" c="2026-06-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-07T00:00:00]" c="2026-06-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-08T00:00:00]" c="2026-06-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-09T00:00:00]" c="2026-06-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-10T00:00:00]" c="2026-06-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-11T00:00:00]" c="2026-06-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-12T00:00:00]" c="2026-06-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-13T00:00:00]" c="2026-06-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-14T00:00:00]" c="2026-06-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-15T00:00:00]" c="2026-06-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-16T00:00:00]" c="2026-06-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-17T00:00:00]" c="2026-06-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-18T00:00:00]" c="2026-06-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-19T00:00:00]" c="2026-06-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-20T00:00:00]" c="2026-06-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-21T00:00:00]" c="2026-06-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-22T00:00:00]" c="2026-06-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-23T00:00:00]" c="2026-06-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-24T00:00:00]" c="2026-06-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-25T00:00:00]" c="2026-06-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-26T00:00:00]" c="2026-06-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-27T00:00:00]" c="2026-06-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-28T00:00:00]" c="2026-06-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-29T00:00:00]" c="2026-06-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-30T00:00:00]" c="2026-06-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-01T00:00:00]" c="2026-07-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-02T00:00:00]" c="2026-07-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-03T00:00:00]" c="2026-07-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-04T00:00:00]" c="2026-07-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-05T00:00:00]" c="2026-07-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-06T00:00:00]" c="2026-07-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-07T00:00:00]" c="2026-07-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-08T00:00:00]" c="2026-07-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-09T00:00:00]" c="2026-07-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-10T00:00:00]" c="2026-07-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-11T00:00:00]" c="2026-07-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-12T00:00:00]" c="2026-07-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-13T00:00:00]" c="2026-07-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-14T00:00:00]" c="2026-07-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-15T00:00:00]" c="2026-07-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-16T00:00:00]" c="2026-07-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-17T00:00:00]" c="2026-07-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-18T00:00:00]" c="2026-07-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-19T00:00:00]" c="2026-07-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-20T00:00:00]" c="2026-07-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-21T00:00:00]" c="2026-07-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-22T00:00:00]" c="2026-07-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-23T00:00:00]" c="2026-07-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-24T00:00:00]" c="2026-07-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-25T00:00:00]" c="2026-07-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-26T00:00:00]" c="2026-07-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-27T00:00:00]" c="2026-07-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-28T00:00:00]" c="2026-07-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-29T00:00:00]" c="2026-07-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-30T00:00:00]" c="2026-07-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-31T00:00:00]" c="2026-07-31"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-01T00:00:00]" c="2026-08-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-02T00:00:00]" c="2026-08-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-03T00:00:00]" c="2026-08-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-04T00:00:00]" c="2026-08-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-05T00:00:00]" c="2026-08-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-06T00:00:00]" c="2026-08-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-07T00:00:00]" c="2026-08-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-08T00:00:00]" c="2026-08-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-09T00:00:00]" c="2026-08-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-10T00:00:00]" c="2026-08-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-11T00:00:00]" c="2026-08-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-12T00:00:00]" c="2026-08-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-13T00:00:00]" c="2026-08-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-14T00:00:00]" c="2026-08-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-15T00:00:00]" c="2026-08-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-16T00:00:00]" c="2026-08-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-17T00:00:00]" c="2026-08-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-18T00:00:00]" c="2026-08-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-19T00:00:00]" c="2026-08-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-20T00:00:00]" c="2026-08-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-21T00:00:00]" c="2026-08-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-22T00:00:00]" c="2026-08-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-23T00:00:00]" c="2026-08-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-24T00:00:00]" c="2026-08-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-25T00:00:00]" c="2026-08-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-26T00:00:00]" c="2026-08-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-27T00:00:00]" c="2026-08-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-28T00:00:00]" c="2026-08-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-29T00:00:00]" c="2026-08-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-30T00:00:00]" c="2026-08-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-31T00:00:00]" c="2026-08-31"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-01T00:00:00]" c="2026-09-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-02T00:00:00]" c="2026-09-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-03T00:00:00]" c="2026-09-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-04T00:00:00]" c="2026-09-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-05T00:00:00]" c="2026-09-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-06T00:00:00]" c="2026-09-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-07T00:00:00]" c="2026-09-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-08T00:00:00]" c="2026-09-08"/>
       </sharedItems>
     </cacheField>
     <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
@@ -798,509 +1322,9 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46272.637262384262" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{F7995ADC-F0B3-4CE9-B66F-D51574EF46B6}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="9">
-    <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
-      <sharedItems count="2">
-        <s v="[Transaccion].[Transaccion].&amp;[Compra]" c="Compra"/>
-        <s v="[Transaccion].[Transaccion].&amp;[Venta]" c="Venta"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda]" caption="Cod Moneda" numFmtId="0" hierarchy="12" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda].[Moneda]" caption="Moneda" propertyName="Moneda" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Monto Menor].[Descripcion].[Descripcion]" caption="Descripcion" numFmtId="0" hierarchy="15" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
-      <sharedItems count="96">
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-04T00:00:00]" c="2026-06-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-05T00:00:00]" c="2026-06-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-06T00:00:00]" c="2026-06-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-07T00:00:00]" c="2026-06-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-08T00:00:00]" c="2026-06-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-09T00:00:00]" c="2026-06-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-10T00:00:00]" c="2026-06-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-11T00:00:00]" c="2026-06-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-12T00:00:00]" c="2026-06-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-13T00:00:00]" c="2026-06-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-14T00:00:00]" c="2026-06-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-15T00:00:00]" c="2026-06-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-16T00:00:00]" c="2026-06-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-17T00:00:00]" c="2026-06-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-18T00:00:00]" c="2026-06-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-19T00:00:00]" c="2026-06-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-20T00:00:00]" c="2026-06-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-21T00:00:00]" c="2026-06-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-22T00:00:00]" c="2026-06-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-23T00:00:00]" c="2026-06-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-24T00:00:00]" c="2026-06-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-25T00:00:00]" c="2026-06-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-26T00:00:00]" c="2026-06-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-27T00:00:00]" c="2026-06-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-28T00:00:00]" c="2026-06-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-29T00:00:00]" c="2026-06-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-30T00:00:00]" c="2026-06-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-01T00:00:00]" c="2026-07-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-02T00:00:00]" c="2026-07-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-03T00:00:00]" c="2026-07-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-04T00:00:00]" c="2026-07-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-05T00:00:00]" c="2026-07-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-06T00:00:00]" c="2026-07-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-07T00:00:00]" c="2026-07-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-08T00:00:00]" c="2026-07-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-09T00:00:00]" c="2026-07-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-10T00:00:00]" c="2026-07-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-11T00:00:00]" c="2026-07-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-12T00:00:00]" c="2026-07-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-13T00:00:00]" c="2026-07-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-14T00:00:00]" c="2026-07-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-15T00:00:00]" c="2026-07-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-16T00:00:00]" c="2026-07-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-17T00:00:00]" c="2026-07-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-18T00:00:00]" c="2026-07-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-19T00:00:00]" c="2026-07-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-20T00:00:00]" c="2026-07-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-21T00:00:00]" c="2026-07-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-22T00:00:00]" c="2026-07-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-23T00:00:00]" c="2026-07-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-24T00:00:00]" c="2026-07-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-25T00:00:00]" c="2026-07-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-26T00:00:00]" c="2026-07-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-27T00:00:00]" c="2026-07-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-28T00:00:00]" c="2026-07-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-29T00:00:00]" c="2026-07-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-30T00:00:00]" c="2026-07-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-31T00:00:00]" c="2026-07-31"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-01T00:00:00]" c="2026-08-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-02T00:00:00]" c="2026-08-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-03T00:00:00]" c="2026-08-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-04T00:00:00]" c="2026-08-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-05T00:00:00]" c="2026-08-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-06T00:00:00]" c="2026-08-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-07T00:00:00]" c="2026-08-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-08T00:00:00]" c="2026-08-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-09T00:00:00]" c="2026-08-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-10T00:00:00]" c="2026-08-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-11T00:00:00]" c="2026-08-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-12T00:00:00]" c="2026-08-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-13T00:00:00]" c="2026-08-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-14T00:00:00]" c="2026-08-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-15T00:00:00]" c="2026-08-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-16T00:00:00]" c="2026-08-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-17T00:00:00]" c="2026-08-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-18T00:00:00]" c="2026-08-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-19T00:00:00]" c="2026-08-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-20T00:00:00]" c="2026-08-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-21T00:00:00]" c="2026-08-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-22T00:00:00]" c="2026-08-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-23T00:00:00]" c="2026-08-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-24T00:00:00]" c="2026-08-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-25T00:00:00]" c="2026-08-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-26T00:00:00]" c="2026-08-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-27T00:00:00]" c="2026-08-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-28T00:00:00]" c="2026-08-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-29T00:00:00]" c="2026-08-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-30T00:00:00]" c="2026-08-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-31T00:00:00]" c="2026-08-31"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-01T00:00:00]" c="2026-09-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-02T00:00:00]" c="2026-09-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-03T00:00:00]" c="2026-09-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-04T00:00:00]" c="2026-09-04"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
-      <sharedItems count="14">
-        <s v="[Entidades].[Sigla].&amp;[BCR]" c="BCR"/>
-        <s v="[Entidades].[Sigla].&amp;[BEC]" c="BEC"/>
-        <s v="[Entidades].[Sigla].&amp;[BFO]" c="BFO"/>
-        <s v="[Entidades].[Sigla].&amp;[BGA]" c="BGA"/>
-        <s v="[Entidades].[Sigla].&amp;[BIE]" c="BIE"/>
-        <s v="[Entidades].[Sigla].&amp;[BIS]" c="BIS"/>
-        <s v="[Entidades].[Sigla].&amp;[BME]" c="BME"/>
-        <s v="[Entidades].[Sigla].&amp;[BNA]" c="BNA"/>
-        <s v="[Entidades].[Sigla].&amp;[BNB]" c="BNB"/>
-        <s v="[Entidades].[Sigla].&amp;[BPR]" c="BPR"/>
-        <s v="[Entidades].[Sigla].&amp;[BSO]" c="BSO"/>
-        <s v="[Entidades].[Sigla].&amp;[BUN]" c="BUN"/>
-        <s v="[Entidades].[Sigla].&amp;[PCO]" c="PCO"/>
-        <s v="[Entidades].[Sigla].&amp;[PEF]" c="PEF"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" numFmtId="0" hierarchy="26" level="32767"/>
-  </cacheFields>
-  <cacheHierarchies count="29">
-    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Categoria]" caption="Cod Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Categoria].[All]" allUniqueName="[Actividad Economica].[Cod Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Sector Actividad]" caption="Cod Sector Actividad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" allUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion].[All]" allUniqueName="[Actividad Economica].[Descripcion].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion Categoria]" caption="Descripcion Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" allUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Concepto].[Cod Concepto]" caption="Cod Concepto" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Concepto].[Cod Concepto].[All]" allUniqueName="[Concepto].[Cod Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Concepto].[Concepto]" caption="Concepto" attribute="1" defaultMemberUniqueName="[Concepto].[Concepto].[All]" allUniqueName="[Concepto].[Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Entidades].[Cod Entidad]" caption="Cod Entidad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Entidades].[Cod Entidad].[All]" allUniqueName="[Entidades].[Cod Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Entidades].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Entidades].[Nombre].[All]" allUniqueName="[Entidades].[Nombre].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Entidades].[Sigla]" caption="Sigla" attribute="1" defaultMemberUniqueName="[Entidades].[Sigla].[All]" allUniqueName="[Entidades].[Sigla].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="7"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Entidades].[Tipo Entidad]" caption="Tipo Entidad" attribute="1" defaultMemberUniqueName="[Entidades].[Tipo Entidad].[All]" allUniqueName="[Entidades].[Tipo Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Estrato].[Cod Estrato]" caption="Cod Estrato" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Estrato].[Cod Estrato].[All]" allUniqueName="[Estrato].[Cod Estrato].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Estrato].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Estrato].[Descripcion].[All]" allUniqueName="[Estrato].[Descripcion].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Moneda Cambio].[Cod Moneda]" caption="Cod Moneda" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Moneda Cambio].[Cod Moneda].[All]" allUniqueName="[Moneda Cambio].[Cod Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Moneda Cambio].[Moneda]" caption="Moneda" attribute="1" defaultMemberUniqueName="[Moneda Cambio].[Moneda].[All]" allUniqueName="[Moneda Cambio].[Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Monto Menor].[Cod Monto Menor]" caption="Cod Monto Menor" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Monto Menor].[Cod Monto Menor].[All]" allUniqueName="[Monto Menor].[Cod Monto Menor].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Monto Menor].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Monto Menor].[Descripcion].[All]" allUniqueName="[Monto Menor].[Descripcion].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="5"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Subsistema].[Cod Subsistema]" caption="Cod Subsistema" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Subsistema].[Cod Subsistema].[All]" allUniqueName="[Subsistema].[Cod Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Subsistema].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Subsistema].[Nombre].[All]" allUniqueName="[Subsistema].[Nombre].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Subsistema].[Sigla Subsistema]" caption="Sigla Subsistema" attribute="1" defaultMemberUniqueName="[Subsistema].[Sigla Subsistema].[All]" allUniqueName="[Subsistema].[Sigla Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha]" caption="Cod Fecha" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Fecha]" caption="Fecha" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="6"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes]" caption="Ultimo Dia Mes" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transaccion].[Cod Transaccion]" caption="Cod Transaccion" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Transaccion].[Cod Transaccion].[All]" allUniqueName="[Transaccion].[Cod Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transaccion].[Transaccion]" caption="Transaccion" attribute="1" defaultMemberUniqueName="[Transaccion].[Transaccion].[All]" allUniqueName="[Transaccion].[Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Monto Usd]" caption="Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Usd]" caption="Tipo Cambio Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="8"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Mm Usd]" caption="Tipo Cambio Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Numero Operaciones]" caption="Numero Operaciones" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="10">
-    <dimension name="Actividad Economica" uniqueName="[Actividad Economica]" caption="Actividad Economica"/>
-    <dimension name="Concepto" uniqueName="[Concepto]" caption="Concepto"/>
-    <dimension name="Entidades" uniqueName="[Entidades]" caption="Entidades"/>
-    <dimension name="Estrato" uniqueName="[Estrato]" caption="Estrato"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Moneda Cambio" uniqueName="[Moneda Cambio]" caption="Moneda Cambio"/>
-    <dimension name="Monto Menor" uniqueName="[Monto Menor]" caption="Monto Menor"/>
-    <dimension name="Subsistema" uniqueName="[Subsistema]" caption="Subsistema"/>
-    <dimension name="Tipo Cambio Fecha Dia" uniqueName="[Tipo Cambio Fecha Dia]" caption="Tipo Cambio Fecha Dia"/>
-    <dimension name="Transaccion" uniqueName="[Transaccion]" caption="Transaccion"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Operaciones Cambiarias" caption="Fact Operaciones Cambiarias"/>
-  </measureGroups>
-  <maps count="9">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-    <map measureGroup="0" dimension="8"/>
-    <map measureGroup="0" dimension="9"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46272.637776620373" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{9ECE6D2C-0019-46A8-93F5-B57014A573FD}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="9">
-    <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
-      <sharedItems count="2">
-        <s v="[Transaccion].[Transaccion].&amp;[Compra]" c="Compra"/>
-        <s v="[Transaccion].[Transaccion].&amp;[Venta]" c="Venta"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda]" caption="Cod Moneda" numFmtId="0" hierarchy="12" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda].[Moneda]" caption="Moneda" propertyName="Moneda" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Monto Menor].[Descripcion].[Descripcion]" caption="Descripcion" numFmtId="0" hierarchy="15" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
-      <sharedItems count="96">
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-04T00:00:00]" c="2026-06-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-05T00:00:00]" c="2026-06-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-06T00:00:00]" c="2026-06-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-07T00:00:00]" c="2026-06-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-08T00:00:00]" c="2026-06-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-09T00:00:00]" c="2026-06-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-10T00:00:00]" c="2026-06-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-11T00:00:00]" c="2026-06-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-12T00:00:00]" c="2026-06-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-13T00:00:00]" c="2026-06-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-14T00:00:00]" c="2026-06-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-15T00:00:00]" c="2026-06-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-16T00:00:00]" c="2026-06-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-17T00:00:00]" c="2026-06-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-18T00:00:00]" c="2026-06-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-19T00:00:00]" c="2026-06-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-20T00:00:00]" c="2026-06-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-21T00:00:00]" c="2026-06-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-22T00:00:00]" c="2026-06-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-23T00:00:00]" c="2026-06-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-24T00:00:00]" c="2026-06-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-25T00:00:00]" c="2026-06-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-26T00:00:00]" c="2026-06-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-27T00:00:00]" c="2026-06-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-28T00:00:00]" c="2026-06-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-29T00:00:00]" c="2026-06-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-30T00:00:00]" c="2026-06-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-01T00:00:00]" c="2026-07-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-02T00:00:00]" c="2026-07-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-03T00:00:00]" c="2026-07-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-04T00:00:00]" c="2026-07-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-05T00:00:00]" c="2026-07-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-06T00:00:00]" c="2026-07-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-07T00:00:00]" c="2026-07-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-08T00:00:00]" c="2026-07-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-09T00:00:00]" c="2026-07-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-10T00:00:00]" c="2026-07-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-11T00:00:00]" c="2026-07-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-12T00:00:00]" c="2026-07-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-13T00:00:00]" c="2026-07-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-14T00:00:00]" c="2026-07-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-15T00:00:00]" c="2026-07-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-16T00:00:00]" c="2026-07-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-17T00:00:00]" c="2026-07-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-18T00:00:00]" c="2026-07-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-19T00:00:00]" c="2026-07-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-20T00:00:00]" c="2026-07-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-21T00:00:00]" c="2026-07-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-22T00:00:00]" c="2026-07-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-23T00:00:00]" c="2026-07-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-24T00:00:00]" c="2026-07-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-25T00:00:00]" c="2026-07-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-26T00:00:00]" c="2026-07-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-27T00:00:00]" c="2026-07-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-28T00:00:00]" c="2026-07-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-29T00:00:00]" c="2026-07-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-30T00:00:00]" c="2026-07-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-31T00:00:00]" c="2026-07-31"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-01T00:00:00]" c="2026-08-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-02T00:00:00]" c="2026-08-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-03T00:00:00]" c="2026-08-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-04T00:00:00]" c="2026-08-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-05T00:00:00]" c="2026-08-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-06T00:00:00]" c="2026-08-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-07T00:00:00]" c="2026-08-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-08T00:00:00]" c="2026-08-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-09T00:00:00]" c="2026-08-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-10T00:00:00]" c="2026-08-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-11T00:00:00]" c="2026-08-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-12T00:00:00]" c="2026-08-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-13T00:00:00]" c="2026-08-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-14T00:00:00]" c="2026-08-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-15T00:00:00]" c="2026-08-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-16T00:00:00]" c="2026-08-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-17T00:00:00]" c="2026-08-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-18T00:00:00]" c="2026-08-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-19T00:00:00]" c="2026-08-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-20T00:00:00]" c="2026-08-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-21T00:00:00]" c="2026-08-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-22T00:00:00]" c="2026-08-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-23T00:00:00]" c="2026-08-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-24T00:00:00]" c="2026-08-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-25T00:00:00]" c="2026-08-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-26T00:00:00]" c="2026-08-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-27T00:00:00]" c="2026-08-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-28T00:00:00]" c="2026-08-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-29T00:00:00]" c="2026-08-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-30T00:00:00]" c="2026-08-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-31T00:00:00]" c="2026-08-31"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-01T00:00:00]" c="2026-09-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-02T00:00:00]" c="2026-09-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-03T00:00:00]" c="2026-09-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-04T00:00:00]" c="2026-09-04"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
-      <sharedItems count="14">
-        <s v="[Entidades].[Sigla].&amp;[BCR]" c="BCR"/>
-        <s v="[Entidades].[Sigla].&amp;[BEC]" c="BEC"/>
-        <s v="[Entidades].[Sigla].&amp;[BFO]" c="BFO"/>
-        <s v="[Entidades].[Sigla].&amp;[BGA]" c="BGA"/>
-        <s v="[Entidades].[Sigla].&amp;[BIE]" c="BIE"/>
-        <s v="[Entidades].[Sigla].&amp;[BIS]" c="BIS"/>
-        <s v="[Entidades].[Sigla].&amp;[BME]" c="BME"/>
-        <s v="[Entidades].[Sigla].&amp;[BNA]" c="BNA"/>
-        <s v="[Entidades].[Sigla].&amp;[BNB]" c="BNB"/>
-        <s v="[Entidades].[Sigla].&amp;[BPR]" c="BPR"/>
-        <s v="[Entidades].[Sigla].&amp;[BSO]" c="BSO"/>
-        <s v="[Entidades].[Sigla].&amp;[BUN]" c="BUN"/>
-        <s v="[Entidades].[Sigla].&amp;[PCO]" c="PCO"/>
-        <s v="[Entidades].[Sigla].&amp;[PEF]" c="PEF"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Numero Operaciones]" caption="Numero Operaciones" numFmtId="0" hierarchy="28" level="32767"/>
-  </cacheFields>
-  <cacheHierarchies count="29">
-    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Categoria]" caption="Cod Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Categoria].[All]" allUniqueName="[Actividad Economica].[Cod Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Sector Actividad]" caption="Cod Sector Actividad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" allUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion].[All]" allUniqueName="[Actividad Economica].[Descripcion].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion Categoria]" caption="Descripcion Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" allUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Concepto].[Cod Concepto]" caption="Cod Concepto" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Concepto].[Cod Concepto].[All]" allUniqueName="[Concepto].[Cod Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Concepto].[Concepto]" caption="Concepto" attribute="1" defaultMemberUniqueName="[Concepto].[Concepto].[All]" allUniqueName="[Concepto].[Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Entidades].[Cod Entidad]" caption="Cod Entidad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Entidades].[Cod Entidad].[All]" allUniqueName="[Entidades].[Cod Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Entidades].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Entidades].[Nombre].[All]" allUniqueName="[Entidades].[Nombre].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Entidades].[Sigla]" caption="Sigla" attribute="1" defaultMemberUniqueName="[Entidades].[Sigla].[All]" allUniqueName="[Entidades].[Sigla].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="7"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Entidades].[Tipo Entidad]" caption="Tipo Entidad" attribute="1" defaultMemberUniqueName="[Entidades].[Tipo Entidad].[All]" allUniqueName="[Entidades].[Tipo Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Estrato].[Cod Estrato]" caption="Cod Estrato" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Estrato].[Cod Estrato].[All]" allUniqueName="[Estrato].[Cod Estrato].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Estrato].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Estrato].[Descripcion].[All]" allUniqueName="[Estrato].[Descripcion].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Moneda Cambio].[Cod Moneda]" caption="Cod Moneda" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Moneda Cambio].[Cod Moneda].[All]" allUniqueName="[Moneda Cambio].[Cod Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Moneda Cambio].[Moneda]" caption="Moneda" attribute="1" defaultMemberUniqueName="[Moneda Cambio].[Moneda].[All]" allUniqueName="[Moneda Cambio].[Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Monto Menor].[Cod Monto Menor]" caption="Cod Monto Menor" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Monto Menor].[Cod Monto Menor].[All]" allUniqueName="[Monto Menor].[Cod Monto Menor].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Monto Menor].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Monto Menor].[Descripcion].[All]" allUniqueName="[Monto Menor].[Descripcion].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="5"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Subsistema].[Cod Subsistema]" caption="Cod Subsistema" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Subsistema].[Cod Subsistema].[All]" allUniqueName="[Subsistema].[Cod Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Subsistema].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Subsistema].[Nombre].[All]" allUniqueName="[Subsistema].[Nombre].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Subsistema].[Sigla Subsistema]" caption="Sigla Subsistema" attribute="1" defaultMemberUniqueName="[Subsistema].[Sigla Subsistema].[All]" allUniqueName="[Subsistema].[Sigla Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha]" caption="Cod Fecha" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Fecha]" caption="Fecha" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="6"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes]" caption="Ultimo Dia Mes" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transaccion].[Cod Transaccion]" caption="Cod Transaccion" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Transaccion].[Cod Transaccion].[All]" allUniqueName="[Transaccion].[Cod Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transaccion].[Transaccion]" caption="Transaccion" attribute="1" defaultMemberUniqueName="[Transaccion].[Transaccion].[All]" allUniqueName="[Transaccion].[Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Monto Usd]" caption="Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Usd]" caption="Tipo Cambio Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Mm Usd]" caption="Tipo Cambio Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Numero Operaciones]" caption="Numero Operaciones" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="8"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="10">
-    <dimension name="Actividad Economica" uniqueName="[Actividad Economica]" caption="Actividad Economica"/>
-    <dimension name="Concepto" uniqueName="[Concepto]" caption="Concepto"/>
-    <dimension name="Entidades" uniqueName="[Entidades]" caption="Entidades"/>
-    <dimension name="Estrato" uniqueName="[Estrato]" caption="Estrato"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Moneda Cambio" uniqueName="[Moneda Cambio]" caption="Moneda Cambio"/>
-    <dimension name="Monto Menor" uniqueName="[Monto Menor]" caption="Monto Menor"/>
-    <dimension name="Subsistema" uniqueName="[Subsistema]" caption="Subsistema"/>
-    <dimension name="Tipo Cambio Fecha Dia" uniqueName="[Tipo Cambio Fecha Dia]" caption="Tipo Cambio Fecha Dia"/>
-    <dimension name="Transaccion" uniqueName="[Transaccion]" caption="Transaccion"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Operaciones Cambiarias" caption="Fact Operaciones Cambiarias"/>
-  </measureGroups>
-  <maps count="9">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-    <map measureGroup="0" dimension="8"/>
-    <map measureGroup="0" dimension="9"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C1A180-7D44-4F02-A61C-919F70C27D4D}" name="TablaDinámica1" cacheId="8" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
-  <location ref="A7:Q200" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="5" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C1A180-7D44-4F02-A61C-919F70C27D4D}" name="TablaDinámica1" cacheId="11" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+  <location ref="A7:Q208" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="5" colPageCount="1"/>
   <pivotFields count="10">
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
@@ -1309,7 +1333,7 @@
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="96">
+      <items count="100">
         <item s="1" x="0"/>
         <item s="1" x="1"/>
         <item s="1" x="2"/>
@@ -1406,6 +1430,10 @@
         <item s="1" x="93"/>
         <item s="1" x="94"/>
         <item s="1" x="95"/>
+        <item s="1" x="96"/>
+        <item s="1" x="97"/>
+        <item s="1" x="98"/>
+        <item s="1" x="99"/>
       </items>
     </pivotField>
     <pivotField axis="axisCol" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -1433,7 +1461,7 @@
     <field x="6"/>
     <field x="-2"/>
   </rowFields>
-  <rowItems count="192">
+  <rowItems count="200">
     <i>
       <x/>
       <x/>
@@ -2101,6 +2129,34 @@
     </i>
     <i>
       <x v="95"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="96"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="97"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="98"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="99"/>
       <x/>
     </i>
     <i r="1" i="1">
@@ -2235,8 +2291,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{971AADEF-3DB3-4761-B43F-E1EDE0CC9CC9}" name="TablaDinámica2" cacheId="11" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
-  <location ref="A7:AE105" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{971AADEF-3DB3-4761-B43F-E1EDE0CC9CC9}" name="TablaDinámica2" cacheId="8" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
+  <location ref="A7:AE109" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
       <items count="1">
@@ -2267,7 +2323,7 @@
       </items>
     </pivotField>
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="97">
+      <items count="101">
         <item s="1" x="0"/>
         <item s="1" x="1"/>
         <item s="1" x="2"/>
@@ -2364,6 +2420,10 @@
         <item s="1" x="93"/>
         <item s="1" x="94"/>
         <item s="1" x="95"/>
+        <item s="1" x="96"/>
+        <item s="1" x="97"/>
+        <item s="1" x="98"/>
+        <item s="1" x="99"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2391,7 +2451,7 @@
   <rowFields count="1">
     <field x="6"/>
   </rowFields>
-  <rowItems count="96">
+  <rowItems count="100">
     <i>
       <x/>
     </i>
@@ -2679,6 +2739,18 @@
     </i>
     <i>
       <x v="95"/>
+    </i>
+    <i>
+      <x v="96"/>
+    </i>
+    <i>
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="98"/>
+    </i>
+    <i>
+      <x v="99"/>
     </i>
   </rowItems>
   <colFields count="2">
@@ -2851,8 +2923,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80A53070-3740-4285-A7AE-6612867028BD}" name="TablaDinámica3" cacheId="14" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
-  <location ref="A7:AE105" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80A53070-3740-4285-A7AE-6612867028BD}" name="TablaDinámica3" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
+  <location ref="A7:AE109" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
       <items count="1">
@@ -2883,7 +2955,7 @@
       </items>
     </pivotField>
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="97">
+      <items count="101">
         <item s="1" x="0"/>
         <item s="1" x="1"/>
         <item s="1" x="2"/>
@@ -2980,6 +3052,10 @@
         <item s="1" x="93"/>
         <item s="1" x="94"/>
         <item s="1" x="95"/>
+        <item s="1" x="96"/>
+        <item s="1" x="97"/>
+        <item s="1" x="98"/>
+        <item s="1" x="99"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3007,7 +3083,7 @@
   <rowFields count="1">
     <field x="6"/>
   </rowFields>
-  <rowItems count="96">
+  <rowItems count="100">
     <i>
       <x/>
     </i>
@@ -3295,6 +3371,18 @@
     </i>
     <i>
       <x v="95"/>
+    </i>
+    <i>
+      <x v="96"/>
+    </i>
+    <i>
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="98"/>
+    </i>
+    <i>
+      <x v="99"/>
     </i>
   </rowItems>
   <colFields count="2">
@@ -3763,7 +3851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3F3DA76-2715-4C5C-9BC9-0D27B1FEBC80}">
-  <dimension ref="A1:Q200"/>
+  <dimension ref="A1:Q208"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
@@ -3929,7 +4017,7 @@
         <v>4.8909899999999997E-5</v>
       </c>
       <c r="Q9" s="2">
-        <v>21.5672456446</v>
+        <v>21.567245644600003</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3979,7 +4067,7 @@
         <v>3.3601170000000001E-4</v>
       </c>
       <c r="Q10" s="2">
-        <v>205.34297774300001</v>
+        <v>205.34297774299998</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -4032,7 +4120,7 @@
         <v>7.7719900000000001E-5</v>
       </c>
       <c r="Q11" s="2">
-        <v>35.103000314600003</v>
+        <v>35.10300031460001</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -4082,7 +4170,7 @@
         <v>5.3393639999999997E-4</v>
       </c>
       <c r="Q12" s="2">
-        <v>345.14507551060024</v>
+        <v>345.14507551060007</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -4135,7 +4223,7 @@
         <v>0.63050245989999998</v>
       </c>
       <c r="Q13" s="2">
-        <v>60.553322572399985</v>
+        <v>60.55332257240002</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -4228,7 +4316,7 @@
       </c>
       <c r="P15" s="2"/>
       <c r="Q15" s="2">
-        <v>1.5532462377999998</v>
+        <v>1.5532462377999996</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -4268,7 +4356,7 @@
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" s="2">
-        <v>14.984158568499991</v>
+        <v>14.984158568499996</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -4367,7 +4455,7 @@
         <v>1.7999399999999999E-5</v>
       </c>
       <c r="Q18" s="2">
-        <v>13.326049031899998</v>
+        <v>13.3260490319</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -4418,7 +4506,7 @@
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="Q19" s="2">
-        <v>1.9862418265000001</v>
+        <v>1.9862418264999999</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -4466,7 +4554,7 @@
         <v>3.435E-4</v>
       </c>
       <c r="Q20" s="2">
-        <v>18.961540054400018</v>
+        <v>18.961540054400004</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -4511,7 +4599,7 @@
       </c>
       <c r="P21" s="2"/>
       <c r="Q21" s="2">
-        <v>0.88122897820000001</v>
+        <v>0.8812289781999999</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -4604,7 +4692,7 @@
       </c>
       <c r="P23" s="2"/>
       <c r="Q23" s="2">
-        <v>58.391455503199985</v>
+        <v>58.391455503200014</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -4652,7 +4740,7 @@
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" s="2">
-        <v>509.76168361770016</v>
+        <v>509.7616836177001</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -4705,7 +4793,7 @@
         <v>0.60389552000000002</v>
       </c>
       <c r="Q25" s="2">
-        <v>28.731094414600015</v>
+        <v>28.731094414600001</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -4808,7 +4896,7 @@
         <v>1E-4</v>
       </c>
       <c r="Q27" s="2">
-        <v>53.941607935200025</v>
+        <v>53.941607935199997</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -4858,7 +4946,7 @@
         <v>6.87E-4</v>
       </c>
       <c r="Q28" s="2">
-        <v>525.09952656499991</v>
+        <v>525.09952656500013</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -4957,7 +5045,7 @@
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" s="2">
-        <v>321.43208792000001</v>
+        <v>321.43208792000013</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -5060,7 +5148,7 @@
         <v>1.74497999E-2</v>
       </c>
       <c r="Q32" s="2">
-        <v>251.12728738170009</v>
+        <v>251.12728738169997</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -5159,7 +5247,7 @@
         <v>2.8647900000000001E-5</v>
       </c>
       <c r="Q34" s="2">
-        <v>12.907625567999998</v>
+        <v>12.907625568</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -5301,7 +5389,7 @@
       </c>
       <c r="P37" s="2"/>
       <c r="Q37" s="2">
-        <v>18.153757315100002</v>
+        <v>18.153757315099998</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -5349,7 +5437,7 @@
       </c>
       <c r="P38" s="2"/>
       <c r="Q38" s="2">
-        <v>174.68947670530005</v>
+        <v>174.68947670530002</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -5402,7 +5490,7 @@
         <v>4.061399E-4</v>
       </c>
       <c r="Q39" s="2">
-        <v>44.695607214999981</v>
+        <v>44.695607215000003</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -5452,7 +5540,7 @@
         <v>2.7901816999999999E-3</v>
       </c>
       <c r="Q40" s="2">
-        <v>421.2092592021001</v>
+        <v>421.20925920210004</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -5503,7 +5591,7 @@
       </c>
       <c r="P41" s="2"/>
       <c r="Q41" s="2">
-        <v>38.354607105699976</v>
+        <v>38.354607105699984</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -5551,7 +5639,7 @@
       </c>
       <c r="P42" s="2"/>
       <c r="Q42" s="2">
-        <v>319.21009970329993</v>
+        <v>319.21009970330005</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -5604,7 +5692,7 @@
         <v>8.8116398999999995E-3</v>
       </c>
       <c r="Q43" s="2">
-        <v>29.494175395399996</v>
+        <v>29.494175395400006</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -5654,7 +5742,7 @@
         <v>6.05359668E-2</v>
       </c>
       <c r="Q44" s="2">
-        <v>283.01353403289988</v>
+        <v>283.0135340329</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -5757,7 +5845,7 @@
         <v>3.9006916715999997</v>
       </c>
       <c r="Q46" s="2">
-        <v>230.73195290530003</v>
+        <v>230.73195290529998</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -5806,7 +5894,7 @@
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" s="2">
-        <v>1.2410332981000001</v>
+        <v>1.2410332980999998</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -5852,7 +5940,7 @@
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" s="2">
-        <v>11.892514915399998</v>
+        <v>11.8925149154</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -5899,7 +5987,7 @@
       </c>
       <c r="P49" s="2"/>
       <c r="Q49" s="2">
-        <v>0.55276641819999983</v>
+        <v>0.55276641820000005</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -5943,7 +6031,7 @@
       </c>
       <c r="P50" s="2"/>
       <c r="Q50" s="2">
-        <v>5.3278248419000018</v>
+        <v>5.3278248419000009</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -5988,7 +6076,7 @@
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
       <c r="Q51" s="2">
-        <v>1.1387092589000001</v>
+        <v>1.1387092589000005</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -6030,7 +6118,7 @@
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
       <c r="Q52" s="2">
-        <v>10.769906805</v>
+        <v>10.769906804999998</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -6083,7 +6171,7 @@
         <v>2.5613299000000001E-3</v>
       </c>
       <c r="Q53" s="2">
-        <v>27.491150044400008</v>
+        <v>27.491150044399994</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -6133,7 +6221,7 @@
         <v>1.7596337100000001E-2</v>
       </c>
       <c r="Q54" s="2">
-        <v>262.29732198530013</v>
+        <v>262.29732198529996</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -6184,7 +6272,7 @@
         <v>3.0000000000000001E-6</v>
       </c>
       <c r="Q55" s="2">
-        <v>33.00764548570001</v>
+        <v>33.007645485700003</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -6283,7 +6371,7 @@
       </c>
       <c r="P57" s="2"/>
       <c r="Q57" s="2">
-        <v>42.187689166599995</v>
+        <v>42.187689166599988</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -6331,7 +6419,7 @@
       </c>
       <c r="P58" s="2"/>
       <c r="Q58" s="2">
-        <v>383.95653259740004</v>
+        <v>383.9565325974001</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -6384,7 +6472,7 @@
         <v>0.20559009</v>
       </c>
       <c r="Q59" s="2">
-        <v>42.239260764399987</v>
+        <v>42.239260764400008</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -6434,7 +6522,7 @@
         <v>1.9984039182</v>
       </c>
       <c r="Q60" s="2">
-        <v>380.25675713750007</v>
+        <v>380.25675713749996</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -6483,7 +6571,7 @@
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" s="2">
-        <v>1.6613404775999994</v>
+        <v>1.6613404776</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -6576,7 +6664,7 @@
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" s="2">
-        <v>0.82157908860000028</v>
+        <v>0.82157908860000006</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -6620,7 +6708,7 @@
       </c>
       <c r="P64" s="2"/>
       <c r="Q64" s="2">
-        <v>7.9359810379000004</v>
+        <v>7.9359810378999986</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -6723,7 +6811,7 @@
         <v>7.1028999000000001E-3</v>
       </c>
       <c r="Q66" s="2">
-        <v>239.42954212260005</v>
+        <v>239.42954212259997</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -6776,7 +6864,7 @@
         <v>7.0195000000000001E-4</v>
       </c>
       <c r="Q67" s="2">
-        <v>22.669151425899994</v>
+        <v>22.669151425900001</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -6826,7 +6914,7 @@
         <v>6.851032E-3</v>
       </c>
       <c r="Q68" s="2">
-        <v>221.07408722849996</v>
+        <v>221.07408722849999</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -6879,7 +6967,7 @@
         <v>3.62E-3</v>
       </c>
       <c r="Q69" s="2">
-        <v>42.303139865899986</v>
+        <v>42.303139865899993</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -6929,7 +7017,7 @@
         <v>3.3883199900000001E-2</v>
       </c>
       <c r="Q70" s="2">
-        <v>414.06713073930024</v>
+        <v>414.06713073930007</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -6982,7 +7070,7 @@
         <v>2.64E-3</v>
       </c>
       <c r="Q71" s="2">
-        <v>39.411361705699996</v>
+        <v>39.411361705700003</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -7032,7 +7120,7 @@
         <v>2.4763199999999999E-2</v>
       </c>
       <c r="Q72" s="2">
-        <v>386.55230779300018</v>
+        <v>386.55230779300007</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -7135,7 +7223,7 @@
         <v>0.1777983679</v>
       </c>
       <c r="Q74" s="2">
-        <v>380.97756969830021</v>
+        <v>380.97756969829987</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -7230,7 +7318,7 @@
       </c>
       <c r="P76" s="2"/>
       <c r="Q76" s="2">
-        <v>22.613311864800007</v>
+        <v>22.613311864800004</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -7277,7 +7365,7 @@
       </c>
       <c r="P77" s="2"/>
       <c r="Q77" s="2">
-        <v>0.98375599860000007</v>
+        <v>0.98375599859999996</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -7374,7 +7462,7 @@
         <v>4.7989909999999997E-2</v>
       </c>
       <c r="Q79" s="2">
-        <v>23.009471535899991</v>
+        <v>23.009471535899994</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -7424,7 +7512,7 @@
         <v>0.45254485119999999</v>
       </c>
       <c r="Q80" s="2">
-        <v>227.97688503139995</v>
+        <v>227.97688503140006</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -7477,7 +7565,7 @@
         <v>3.6366598999999999E-3</v>
       </c>
       <c r="Q81" s="2">
-        <v>36.053332876000006</v>
+        <v>36.053332875999999</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -7527,7 +7615,7 @@
         <v>3.4511903400000002E-2</v>
       </c>
       <c r="Q82" s="2">
-        <v>359.39086074320011</v>
+        <v>359.39086074319999</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -7580,7 +7668,7 @@
         <v>4.2200000000000001E-4</v>
       </c>
       <c r="Q83" s="2">
-        <v>43.206665516000008</v>
+        <v>43.206665515999994</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -7630,7 +7718,7 @@
         <v>4.0343200000000001E-3</v>
       </c>
       <c r="Q84" s="2">
-        <v>435.7148039665999</v>
+        <v>435.71480396660002</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -7683,7 +7771,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="Q85" s="2">
-        <v>29.770121457200009</v>
+        <v>29.770121457199998</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -7786,7 +7874,7 @@
         <v>1.1195E-4</v>
       </c>
       <c r="Q87" s="2">
-        <v>36.904584836699982</v>
+        <v>36.904584836699996</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -7836,7 +7924,7 @@
         <v>1.1015879999999999E-3</v>
       </c>
       <c r="Q88" s="2">
-        <v>383.74220176289998</v>
+        <v>383.74220176290004</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -7875,7 +7963,7 @@
         <v>3.0000000000000001E-5</v>
       </c>
       <c r="Q89" s="2">
-        <v>0.13119219909999999</v>
+        <v>0.13119219910000002</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -7911,7 +7999,7 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="Q90" s="2">
-        <v>1.3338902673999997</v>
+        <v>1.3338902673999999</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -7954,7 +8042,7 @@
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
       <c r="Q91" s="2">
-        <v>0.96091219819999985</v>
+        <v>0.96091219819999996</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -7994,7 +8082,7 @@
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
       <c r="Q92" s="2">
-        <v>9.775757801200001</v>
+        <v>9.7757578011999975</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -8047,7 +8135,7 @@
         <v>9.9359900000000004E-5</v>
       </c>
       <c r="Q93" s="2">
-        <v>14.821066284999995</v>
+        <v>14.821066285000002</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -8097,7 +8185,7 @@
         <v>9.9360000000000008E-4</v>
       </c>
       <c r="Q94" s="2">
-        <v>155.79719550710004</v>
+        <v>155.79719550709999</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -8150,7 +8238,7 @@
         <v>1.14638E-3</v>
       </c>
       <c r="Q95" s="2">
-        <v>42.988672885699991</v>
+        <v>42.988672885699998</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -8200,7 +8288,7 @@
         <v>1.1578438E-2</v>
       </c>
       <c r="Q96" s="2">
-        <v>459.8868432111999</v>
+        <v>459.88684321120007</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -8253,7 +8341,7 @@
         <v>1.4E-3</v>
       </c>
       <c r="Q97" s="2">
-        <v>53.436640636199989</v>
+        <v>53.436640636199996</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -8303,7 +8391,7 @@
         <v>1.4420000000000001E-2</v>
       </c>
       <c r="Q98" s="2">
-        <v>576.52342017029957</v>
+        <v>576.52342017030003</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -8356,7 +8444,7 @@
         <v>2.0012599999999999E-3</v>
       </c>
       <c r="Q99" s="2">
-        <v>19.244176295700015</v>
+        <v>19.244176295699997</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -8406,7 +8494,7 @@
         <v>2.0613040999999999E-2</v>
       </c>
       <c r="Q100" s="2">
-        <v>208.50425585899995</v>
+        <v>208.50425585900001</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -8459,7 +8547,7 @@
         <v>0.58557759980000001</v>
       </c>
       <c r="Q101" s="2">
-        <v>50.29385592470004</v>
+        <v>50.293855924699997</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -8509,7 +8597,7 @@
         <v>6.5166647280000003</v>
       </c>
       <c r="Q102" s="2">
-        <v>545.62124587439973</v>
+        <v>545.62124587439996</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -8608,7 +8696,7 @@
         <v>5.5541749999999995E-4</v>
       </c>
       <c r="Q104" s="2">
-        <v>77.444570936500014</v>
+        <v>77.444570936500028</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -8653,7 +8741,7 @@
       </c>
       <c r="P105" s="2"/>
       <c r="Q105" s="2">
-        <v>0.71176124909999983</v>
+        <v>0.71176124910000005</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -8695,7 +8783,7 @@
       </c>
       <c r="P106" s="2"/>
       <c r="Q106" s="2">
-        <v>7.6548801010999989</v>
+        <v>7.6548801010999998</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -8742,7 +8830,7 @@
         <v>6.0499999999999998E-3</v>
       </c>
       <c r="Q107" s="2">
-        <v>7.9554635272000009</v>
+        <v>7.9554635272000001</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -8786,7 +8874,7 @@
         <v>6.3222500000000001E-2</v>
       </c>
       <c r="Q108" s="2">
-        <v>86.57011372759996</v>
+        <v>86.570113727599988</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -8839,7 +8927,7 @@
         <v>0.2001868299</v>
       </c>
       <c r="Q109" s="2">
-        <v>24.822844845000017</v>
+        <v>24.822844844999995</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -8889,7 +8977,7 @@
         <v>2.1819097150000002</v>
       </c>
       <c r="Q110" s="2">
-        <v>273.15247697060016</v>
+        <v>273.15247697059999</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -8942,7 +9030,7 @@
         <v>1.6199999999999999E-3</v>
       </c>
       <c r="Q111" s="2">
-        <v>48.460941324400032</v>
+        <v>48.460941324399997</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -8992,7 +9080,7 @@
         <v>1.7172E-2</v>
       </c>
       <c r="Q112" s="2">
-        <v>539.43420332559981</v>
+        <v>539.43420332560004</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -9045,7 +9133,7 @@
         <v>4.6999999999999999E-4</v>
       </c>
       <c r="Q113" s="2">
-        <v>34.242672326100006</v>
+        <v>34.242672326099999</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
@@ -9148,7 +9236,7 @@
         <v>2.9804199000000001E-3</v>
       </c>
       <c r="Q115" s="2">
-        <v>38.397533714800005</v>
+        <v>38.397533714799998</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
@@ -9198,7 +9286,7 @@
         <v>3.2218339999999998E-2</v>
       </c>
       <c r="Q116" s="2">
-        <v>436.41635125920016</v>
+        <v>436.41635125920004</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
@@ -9249,7 +9337,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="Q117" s="2">
-        <v>1.4652720772000003</v>
+        <v>1.4652720772000001</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
@@ -9342,7 +9430,7 @@
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
       <c r="Q119" s="2">
-        <v>0.66358295849999993</v>
+        <v>0.66358295850000004</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
@@ -9384,7 +9472,7 @@
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
       <c r="Q120" s="2">
-        <v>7.4964557059000017</v>
+        <v>7.4964557059000008</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
@@ -9437,7 +9525,7 @@
         <v>3.5E-4</v>
       </c>
       <c r="Q121" s="2">
-        <v>21.140378636200005</v>
+        <v>21.140378636200001</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
@@ -9487,7 +9575,7 @@
         <v>3.8395E-3</v>
       </c>
       <c r="Q122" s="2">
-        <v>243.87857766580001</v>
+        <v>243.87857766580004</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
@@ -9540,7 +9628,7 @@
         <v>0.24246634990000002</v>
       </c>
       <c r="Q123" s="2">
-        <v>38.85347620629998</v>
+        <v>38.853476206300002</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
@@ -9590,7 +9678,7 @@
         <v>2.7619960863000004</v>
       </c>
       <c r="Q124" s="2">
-        <v>458.36739388019993</v>
+        <v>458.36739388019998</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
@@ -9643,7 +9731,7 @@
         <v>0.10233</v>
       </c>
       <c r="Q125" s="2">
-        <v>41.659336916599983</v>
+        <v>41.659336916599997</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
@@ -9693,7 +9781,7 @@
         <v>1.1665620000000001</v>
       </c>
       <c r="Q126" s="2">
-        <v>495.16521903429998</v>
+        <v>495.16521903430009</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
@@ -9746,7 +9834,7 @@
         <v>6.6E-4</v>
       </c>
       <c r="Q127" s="2">
-        <v>38.72584713639997</v>
+        <v>38.725847136400006</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
@@ -9796,7 +9884,7 @@
         <v>7.5833999000000001E-3</v>
       </c>
       <c r="Q128" s="2">
-        <v>470.58975796489983</v>
+        <v>470.5897579649</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
@@ -9849,7 +9937,7 @@
         <v>0.2202893299</v>
       </c>
       <c r="Q129" s="2">
-        <v>41.205993046099998</v>
+        <v>41.205993046099991</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
@@ -9950,7 +10038,7 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="Q131" s="2">
-        <v>7.8872121062999998</v>
+        <v>7.8872121062999989</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
@@ -9998,7 +10086,7 @@
         <v>4.692E-3</v>
       </c>
       <c r="Q132" s="2">
-        <v>94.772128771399963</v>
+        <v>94.772128771400006</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
@@ -10045,7 +10133,7 @@
       </c>
       <c r="P133" s="2"/>
       <c r="Q133" s="2">
-        <v>2.7384933491000001</v>
+        <v>2.7384933490999996</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
@@ -10089,7 +10177,7 @@
       </c>
       <c r="P134" s="2"/>
       <c r="Q134" s="2">
-        <v>33.069613391800011</v>
+        <v>33.06961339179999</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
@@ -10142,7 +10230,7 @@
         <v>2.8660000000000001E-2</v>
       </c>
       <c r="Q135" s="2">
-        <v>42.141154895199989</v>
+        <v>42.141154895200003</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
@@ -10192,7 +10280,7 @@
         <v>0.33618179990000002</v>
       </c>
       <c r="Q136" s="2">
-        <v>508.94268885359998</v>
+        <v>508.94268885359992</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
@@ -10245,7 +10333,7 @@
         <v>1.55534599E-2</v>
       </c>
       <c r="Q137" s="2">
-        <v>172.67081554429993</v>
+        <v>172.67081554429996</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
@@ -10348,7 +10436,7 @@
         <v>2.7139999999999998E-3</v>
       </c>
       <c r="Q139" s="2">
-        <v>72.426139224000039</v>
+        <v>72.426139224000011</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
@@ -10398,7 +10486,7 @@
         <v>3.1536679999999997E-2</v>
       </c>
       <c r="Q140" s="2">
-        <v>858.43880251740063</v>
+        <v>858.43880251740006</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
@@ -10441,7 +10529,7 @@
       </c>
       <c r="P141" s="2"/>
       <c r="Q141" s="2">
-        <v>3.7671756279000013</v>
+        <v>3.7671756279000004</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
@@ -10481,7 +10569,7 @@
       </c>
       <c r="P142" s="2"/>
       <c r="Q142" s="2">
-        <v>44.263169150500012</v>
+        <v>44.263169150499998</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
@@ -10528,7 +10616,7 @@
       </c>
       <c r="P143" s="2"/>
       <c r="Q143" s="2">
-        <v>2.6189162486999993</v>
+        <v>2.6189162486999997</v>
       </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
@@ -10572,7 +10660,7 @@
       </c>
       <c r="P144" s="2"/>
       <c r="Q144" s="2">
-        <v>30.759959545099999</v>
+        <v>30.759959545100003</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
@@ -10621,7 +10709,7 @@
       </c>
       <c r="P145" s="2"/>
       <c r="Q145" s="2">
-        <v>4.615882136599998</v>
+        <v>4.6158821366000007</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
@@ -10667,7 +10755,7 @@
       </c>
       <c r="P146" s="2"/>
       <c r="Q146" s="2">
-        <v>53.069700444900015</v>
+        <v>53.069700444899993</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
@@ -10758,7 +10846,7 @@
       </c>
       <c r="P148" s="2"/>
       <c r="Q148" s="2">
-        <v>17.680777803100003</v>
+        <v>17.6807778031</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
@@ -10811,7 +10899,7 @@
         <v>3.4163099000000001E-3</v>
       </c>
       <c r="Q149" s="2">
-        <v>84.71584690409999</v>
+        <v>84.715846904100005</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
@@ -10861,7 +10949,7 @@
         <v>3.9150912599999997E-2</v>
       </c>
       <c r="Q150" s="2">
-        <v>996.33793799979992</v>
+        <v>996.33793799980015</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
@@ -10914,7 +11002,7 @@
         <v>2.6670989999999999E-4</v>
       </c>
       <c r="Q151" s="2">
-        <v>124.50584123380006</v>
+        <v>124.5058412338</v>
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
@@ -10964,7 +11052,7 @@
         <v>3.0324926000000001E-3</v>
       </c>
       <c r="Q152" s="2">
-        <v>1459.2645159273006</v>
+        <v>1459.2645159273002</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
@@ -11015,7 +11103,7 @@
       </c>
       <c r="P153" s="2"/>
       <c r="Q153" s="2">
-        <v>57.943519933800019</v>
+        <v>57.943519933799998</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
@@ -11116,7 +11204,7 @@
         <v>1.5E-3</v>
       </c>
       <c r="Q155" s="2">
-        <v>50.559258843800002</v>
+        <v>50.559258843799995</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
@@ -11166,7 +11254,7 @@
         <v>1.6889999999999999E-2</v>
       </c>
       <c r="Q156" s="2">
-        <v>585.05717044270011</v>
+        <v>585.05717044269988</v>
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
@@ -11219,7 +11307,7 @@
         <v>0.30000092</v>
       </c>
       <c r="Q157" s="2">
-        <v>45.359499795300025</v>
+        <v>45.359499795299996</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
@@ -11318,7 +11406,7 @@
       </c>
       <c r="P159" s="2"/>
       <c r="Q159" s="2">
-        <v>1.9756634962999999</v>
+        <v>1.9756634963000002</v>
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
@@ -11364,7 +11452,7 @@
       </c>
       <c r="P160" s="2"/>
       <c r="Q160" s="2">
-        <v>22.554419617000004</v>
+        <v>22.554419616999997</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
@@ -11611,7 +11699,7 @@
         <v>2.5314999999999999E-3</v>
       </c>
       <c r="Q165" s="2">
-        <v>78.473257923399984</v>
+        <v>78.473257923400013</v>
       </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
@@ -11661,7 +11749,7 @@
         <v>2.8226224899999999E-2</v>
       </c>
       <c r="Q166" s="2">
-        <v>903.28385346280004</v>
+        <v>903.28385346279993</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
@@ -11760,7 +11848,7 @@
       </c>
       <c r="P168" s="2"/>
       <c r="Q168" s="2">
-        <v>492.28184646949978</v>
+        <v>492.2818464694999</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
@@ -11813,7 +11901,7 @@
         <v>0.45366299999999998</v>
       </c>
       <c r="Q169" s="2">
-        <v>45.275909323000029</v>
+        <v>45.275909322999993</v>
       </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
@@ -11863,7 +11951,7 @@
         <v>5.2299645000000003</v>
       </c>
       <c r="Q170" s="2">
-        <v>521.30610014689989</v>
+        <v>521.30610014690012</v>
       </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
@@ -11916,7 +12004,7 @@
         <v>6.3003149999999994E-2</v>
       </c>
       <c r="Q171" s="2">
-        <v>23.722516743900012</v>
+        <v>23.722516743900005</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
@@ -12017,7 +12105,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="Q173" s="2">
-        <v>1.5360112463999995</v>
+        <v>1.5360112464</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
@@ -12110,7 +12198,7 @@
       </c>
       <c r="P175" s="2"/>
       <c r="Q175" s="2">
-        <v>0.43987789849999986</v>
+        <v>0.43987789850000003</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
@@ -12152,7 +12240,7 @@
       </c>
       <c r="P176" s="2"/>
       <c r="Q176" s="2">
-        <v>5.035837421400001</v>
+        <v>5.0358374214000001</v>
       </c>
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
@@ -12203,7 +12291,7 @@
       </c>
       <c r="P177" s="2"/>
       <c r="Q177" s="2">
-        <v>28.077546925799993</v>
+        <v>28.077546925800004</v>
       </c>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.25">
@@ -12251,7 +12339,7 @@
       </c>
       <c r="P178" s="2"/>
       <c r="Q178" s="2">
-        <v>323.97181274579992</v>
+        <v>323.97181274579998</v>
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
@@ -12354,7 +12442,7 @@
         <v>5.8700063497999997</v>
       </c>
       <c r="Q180" s="2">
-        <v>697.03608261170041</v>
+        <v>697.03608261170007</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
@@ -12407,7 +12495,7 @@
         <v>3.3699999999999999E-6</v>
       </c>
       <c r="Q181" s="2">
-        <v>48.709359664500035</v>
+        <v>48.70935966450002</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
@@ -12510,7 +12598,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q183" s="2">
-        <v>32.793952332400011</v>
+        <v>32.793952332399989</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
@@ -12560,7 +12648,7 @@
         <v>1.1310000000000001E-2</v>
       </c>
       <c r="Q184" s="2">
-        <v>387.28705706190021</v>
+        <v>387.28705706189999</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.25">
@@ -12613,7 +12701,7 @@
         <v>8.8698999999999996E-6</v>
       </c>
       <c r="Q185" s="2">
-        <v>31.22188522370001</v>
+        <v>31.221885223699996</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
@@ -12663,7 +12751,7 @@
         <v>1.013841E-4</v>
       </c>
       <c r="Q186" s="2">
-        <v>372.41950910119994</v>
+        <v>372.41950910119999</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
@@ -12714,7 +12802,7 @@
         <v>7.0999999999999998E-7</v>
       </c>
       <c r="Q187" s="2">
-        <v>2.0072255561999999</v>
+        <v>2.0072255562000003</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
@@ -12762,7 +12850,7 @@
         <v>8.1790999999999993E-6</v>
       </c>
       <c r="Q188" s="2">
-        <v>23.661472491600001</v>
+        <v>23.661472491600012</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
@@ -12853,7 +12941,7 @@
       <c r="O190" s="2"/>
       <c r="P190" s="2"/>
       <c r="Q190" s="2">
-        <v>11.290654995600001</v>
+        <v>11.290654995599999</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
@@ -12906,7 +12994,7 @@
         <v>1.432E-5</v>
       </c>
       <c r="Q191" s="2">
-        <v>19.570135656399994</v>
+        <v>19.570135656399998</v>
       </c>
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.25">
@@ -12967,22 +13055,22 @@
         <v>94</v>
       </c>
       <c r="C193" s="2">
-        <v>10.541265099400004</v>
+        <v>10.541265099399999</v>
       </c>
       <c r="D193" s="2">
-        <v>1.5404671898000002</v>
+        <v>1.5404671898</v>
       </c>
       <c r="E193" s="2">
         <v>0.30973334990000001</v>
       </c>
       <c r="F193" s="2">
-        <v>10.676857608500001</v>
+        <v>10.676857608499999</v>
       </c>
       <c r="G193" s="2">
         <v>1.52429345</v>
       </c>
       <c r="H193" s="2">
-        <v>7.0495516189999998</v>
+        <v>7.0495516189999989</v>
       </c>
       <c r="I193" s="2">
         <v>8.1942503297999991</v>
@@ -12991,10 +13079,10 @@
         <v>2.5951819899999999E-2</v>
       </c>
       <c r="K193" s="2">
-        <v>6.4725927186999996</v>
+        <v>6.4725927187000005</v>
       </c>
       <c r="L193" s="2">
-        <v>2.04306699E-2</v>
+        <v>2.0430669899999997E-2</v>
       </c>
       <c r="M193" s="2">
         <v>2.0410046297999997</v>
@@ -13009,7 +13097,7 @@
         <v>0.15001043999999999</v>
       </c>
       <c r="Q193" s="2">
-        <v>49.356058984300013</v>
+        <v>49.356058984300006</v>
       </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
@@ -13017,37 +13105,37 @@
         <v>95</v>
       </c>
       <c r="C194" s="2">
-        <v>130.04404527919999</v>
+        <v>130.04404527920002</v>
       </c>
       <c r="D194" s="2">
-        <v>18.855870707199998</v>
+        <v>18.855870707200001</v>
       </c>
       <c r="E194" s="2">
         <v>3.7445659802</v>
       </c>
       <c r="F194" s="2">
-        <v>129.79106454269998</v>
+        <v>129.79106454269996</v>
       </c>
       <c r="G194" s="2">
-        <v>18.888172073900002</v>
+        <v>18.888172073899998</v>
       </c>
       <c r="H194" s="2">
-        <v>86.585119868299998</v>
+        <v>86.585119868300012</v>
       </c>
       <c r="I194" s="2">
-        <v>100.95028395929998</v>
+        <v>100.95028395929999</v>
       </c>
       <c r="J194" s="2">
         <v>0.31063251219999999</v>
       </c>
       <c r="K194" s="2">
-        <v>78.904366968699961</v>
+        <v>78.904366968699989</v>
       </c>
       <c r="L194" s="2">
-        <v>0.24149051929999998</v>
+        <v>0.24149051930000001</v>
       </c>
       <c r="M194" s="2">
-        <v>25.2136062686</v>
+        <v>25.213606268599996</v>
       </c>
       <c r="N194" s="2">
         <v>10.081866637300001</v>
@@ -13059,7 +13147,7 @@
         <v>1.7431223568000001</v>
       </c>
       <c r="Q194" s="2">
-        <v>605.37609793799959</v>
+        <v>605.37609793799993</v>
       </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
@@ -13070,31 +13158,31 @@
         <v>94</v>
       </c>
       <c r="C195" s="2">
-        <v>2.2410354895000002</v>
+        <v>2.2410354895000006</v>
       </c>
       <c r="D195" s="2">
-        <v>4.3218774097999999</v>
+        <v>4.321877409799999</v>
       </c>
       <c r="E195" s="2">
         <v>1.7164667598000001</v>
       </c>
       <c r="F195" s="2">
-        <v>6.1768947683999995</v>
+        <v>6.1768947684000004</v>
       </c>
       <c r="G195" s="2">
         <v>3.5403004299000003</v>
       </c>
       <c r="H195" s="2">
-        <v>28.744438628799998</v>
+        <v>28.744438628800001</v>
       </c>
       <c r="I195" s="2">
-        <v>3.9797154597</v>
+        <v>3.9797154597000004</v>
       </c>
       <c r="J195" s="2">
         <v>6.0730200000000002E-3</v>
       </c>
       <c r="K195" s="2">
-        <v>2.0242601280999994</v>
+        <v>2.0242601281000008</v>
       </c>
       <c r="L195" s="2">
         <v>2.0808800000000002E-3</v>
@@ -13112,7 +13200,7 @@
         <v>0.50007542999999999</v>
       </c>
       <c r="Q195" s="2">
-        <v>59.084914313599953</v>
+        <v>59.084914313600017</v>
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
@@ -13120,22 +13208,22 @@
         <v>95</v>
       </c>
       <c r="C196" s="2">
-        <v>27.552192623</v>
+        <v>27.552192622999996</v>
       </c>
       <c r="D196" s="2">
-        <v>53.64341789480001</v>
+        <v>53.643417894800002</v>
       </c>
       <c r="E196" s="2">
         <v>21.520790948299997</v>
       </c>
       <c r="F196" s="2">
-        <v>75.8714071733</v>
+        <v>75.871407173300014</v>
       </c>
       <c r="G196" s="2">
         <v>44.058783275700002</v>
       </c>
       <c r="H196" s="2">
-        <v>352.61151364479991</v>
+        <v>352.61151364479997</v>
       </c>
       <c r="I196" s="2">
         <v>49.208738769100002</v>
@@ -13144,13 +13232,13 @@
         <v>7.2633319099999996E-2</v>
       </c>
       <c r="K196" s="2">
-        <v>24.790075877300005</v>
+        <v>24.790075877300001</v>
       </c>
       <c r="L196" s="2">
         <v>2.4887324799999999E-2</v>
       </c>
       <c r="M196" s="2">
-        <v>69.0339198649</v>
+        <v>69.033919864900028</v>
       </c>
       <c r="N196" s="2">
         <v>2.9952346882000001</v>
@@ -13162,7 +13250,7 @@
         <v>6.2758945997</v>
       </c>
       <c r="Q196" s="2">
-        <v>728.01918897790051</v>
+        <v>728.01918897789994</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
@@ -13173,10 +13261,10 @@
         <v>94</v>
       </c>
       <c r="C197" s="2">
-        <v>4.2272902993999999</v>
+        <v>4.227290299399999</v>
       </c>
       <c r="D197" s="2">
-        <v>0.55025838990000009</v>
+        <v>0.55025838989999998</v>
       </c>
       <c r="E197" s="2">
         <v>0.16759871990000003</v>
@@ -13188,22 +13276,22 @@
         <v>1.32292995</v>
       </c>
       <c r="H197" s="2">
-        <v>9.6362721189000009</v>
+        <v>9.6362721188999991</v>
       </c>
       <c r="I197" s="2">
-        <v>2.5468940287999997</v>
+        <v>2.5468940288000002</v>
       </c>
       <c r="J197" s="2">
         <v>4.6518099900000005E-2</v>
       </c>
       <c r="K197" s="2">
-        <v>4.2512866591000016</v>
+        <v>4.2512866591000007</v>
       </c>
       <c r="L197" s="2">
-        <v>1.1868579900000002E-2</v>
+        <v>1.1868579899999999E-2</v>
       </c>
       <c r="M197" s="2">
-        <v>3.0043624296000004</v>
+        <v>3.0043624296</v>
       </c>
       <c r="N197" s="2">
         <v>4.4385997999999999E-3</v>
@@ -13215,7 +13303,7 @@
         <v>2.1098999999999999E-6</v>
       </c>
       <c r="Q197" s="2">
-        <v>35.332630863600009</v>
+        <v>35.332630863600002</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
@@ -13223,7 +13311,7 @@
         <v>95</v>
       </c>
       <c r="C198" s="2">
-        <v>52.374203587800004</v>
+        <v>52.374203587799997</v>
       </c>
       <c r="D198" s="2">
         <v>6.8732329237000007</v>
@@ -13232,22 +13320,22 @@
         <v>2.0419253160999999</v>
       </c>
       <c r="F198" s="2">
-        <v>118.95602852179999</v>
+        <v>118.95602852180001</v>
       </c>
       <c r="G198" s="2">
         <v>16.6178044615</v>
       </c>
       <c r="H198" s="2">
-        <v>119.79280048700002</v>
+        <v>119.79280048699999</v>
       </c>
       <c r="I198" s="2">
-        <v>31.8961255157</v>
+        <v>31.896125515700003</v>
       </c>
       <c r="J198" s="2">
         <v>0.5664975619</v>
       </c>
       <c r="K198" s="2">
-        <v>52.611228614500021</v>
+        <v>52.611228614500028</v>
       </c>
       <c r="L198" s="2">
         <v>0.1426603313</v>
@@ -13265,7 +13353,7 @@
         <v>2.51511E-5</v>
       </c>
       <c r="Q198" s="2">
-        <v>439.70693911139989</v>
+        <v>439.7069391114</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
@@ -13276,47 +13364,47 @@
         <v>94</v>
       </c>
       <c r="C199" s="2">
-        <v>4.4597062794000006</v>
+        <v>4.5686707090000001</v>
       </c>
       <c r="D199" s="2">
-        <v>4.0573789997</v>
+        <v>4.0573789996999992</v>
       </c>
       <c r="E199" s="2">
-        <v>0.81976880980000011</v>
+        <v>0.8197688098</v>
       </c>
       <c r="F199" s="2">
-        <v>20.567034208900001</v>
+        <v>21.622486007899997</v>
       </c>
       <c r="G199" s="2">
-        <v>1.5533594199999998</v>
+        <v>1.5932660199999999</v>
       </c>
       <c r="H199" s="2">
-        <v>9.5162221688999988</v>
+        <v>9.5712881088999993</v>
       </c>
       <c r="I199" s="2">
-        <v>10.4608374094</v>
+        <v>10.460837409400003</v>
       </c>
       <c r="J199" s="2">
-        <v>6.1089930000000001E-2</v>
+        <v>0.2543552</v>
       </c>
       <c r="K199" s="2">
-        <v>4.5200512785999978</v>
+        <v>5.8530080087000007</v>
       </c>
       <c r="L199" s="2">
         <v>1.9358249899999999E-2</v>
       </c>
       <c r="M199" s="2">
-        <v>0.81857284990000001</v>
+        <v>0.81909734990000005</v>
       </c>
       <c r="N199" s="2">
-        <v>3.3370069800000006E-2</v>
+        <v>3.4659929899999997E-2</v>
       </c>
       <c r="O199" s="2">
         <v>5.0299999999999997E-3</v>
       </c>
       <c r="P199" s="2"/>
       <c r="Q199" s="2">
-        <v>56.891779674300039</v>
+        <v>59.679204803100006</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
@@ -13324,7 +13412,7 @@
         <v>95</v>
       </c>
       <c r="C200" s="2">
-        <v>56.031755281400002</v>
+        <v>57.365538394000005</v>
       </c>
       <c r="D200" s="2">
         <v>51.081473910599996</v>
@@ -13333,38 +13421,430 @@
         <v>10.3597431935</v>
       </c>
       <c r="F200" s="2">
-        <v>259.5013504657</v>
+        <v>272.68226681180005</v>
       </c>
       <c r="G200" s="2">
-        <v>19.599818266500002</v>
+        <v>20.103040236399998</v>
       </c>
       <c r="H200" s="2">
-        <v>119.20292485709999</v>
+        <v>119.87848262189998</v>
       </c>
       <c r="I200" s="2">
-        <v>131.71087901529998</v>
+        <v>131.71087901530004</v>
       </c>
       <c r="J200" s="2">
-        <v>0.75647264950000015</v>
+        <v>3.1123956798999997</v>
       </c>
       <c r="K200" s="2">
-        <v>56.256868182100014</v>
+        <v>72.852179470499991</v>
       </c>
       <c r="L200" s="2">
         <v>0.23520273749999998</v>
       </c>
       <c r="M200" s="2">
-        <v>10.316046264000001</v>
+        <v>10.322535413900001</v>
       </c>
       <c r="N200" s="2">
-        <v>0.38573263459999996</v>
+        <v>0.39927616469999999</v>
       </c>
       <c r="O200" s="2">
         <v>6.0611499999999999E-2</v>
       </c>
       <c r="P200" s="2"/>
       <c r="Q200" s="2">
-        <v>715.49887895779955</v>
+        <v>750.16362515000026</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>129</v>
+      </c>
+      <c r="B201" t="s">
+        <v>94</v>
+      </c>
+      <c r="C201" s="2">
+        <v>0.22402117990000001</v>
+      </c>
+      <c r="D201" s="2">
+        <v>1.93566498E-2</v>
+      </c>
+      <c r="E201" s="2">
+        <v>1.0349999999999999E-4</v>
+      </c>
+      <c r="F201" s="2">
+        <v>2.3471744689</v>
+      </c>
+      <c r="G201" s="2">
+        <v>0.60749774999999995</v>
+      </c>
+      <c r="H201" s="2">
+        <v>9.3156009100000006E-2</v>
+      </c>
+      <c r="I201" s="2">
+        <v>5.0729019899999998E-2</v>
+      </c>
+      <c r="J201" s="2"/>
+      <c r="K201" s="2">
+        <v>1.1298302283999999</v>
+      </c>
+      <c r="L201" s="2">
+        <v>3.04916E-3</v>
+      </c>
+      <c r="M201" s="2">
+        <v>5.7993298E-3</v>
+      </c>
+      <c r="N201" s="2">
+        <v>9.9220596999999994E-3</v>
+      </c>
+      <c r="O201" s="2">
+        <v>2.5593699E-3</v>
+      </c>
+      <c r="P201" s="2">
+        <v>1.95E-6</v>
+      </c>
+      <c r="Q201" s="2">
+        <v>4.4932006753999998</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B202" t="s">
+        <v>95</v>
+      </c>
+      <c r="C202" s="2">
+        <v>2.8167657693000003</v>
+      </c>
+      <c r="D202" s="2">
+        <v>0.23825112999999998</v>
+      </c>
+      <c r="E202" s="2">
+        <v>1.30203E-3</v>
+      </c>
+      <c r="F202" s="2">
+        <v>29.300189705000005</v>
+      </c>
+      <c r="G202" s="2">
+        <v>7.6423216949000006</v>
+      </c>
+      <c r="H202" s="2">
+        <v>1.1348633928999998</v>
+      </c>
+      <c r="I202" s="2">
+        <v>0.61448656160000004</v>
+      </c>
+      <c r="J202" s="2"/>
+      <c r="K202" s="2">
+        <v>14.213264292099993</v>
+      </c>
+      <c r="L202" s="2">
+        <v>3.7443684800000002E-2</v>
+      </c>
+      <c r="M202" s="2">
+        <v>7.1505738900000004E-2</v>
+      </c>
+      <c r="N202" s="2">
+        <v>0.11211927790000001</v>
+      </c>
+      <c r="O202" s="2">
+        <v>3.1173126600000003E-2</v>
+      </c>
+      <c r="P202" s="2">
+        <v>2.3751E-5</v>
+      </c>
+      <c r="Q202" s="2">
+        <v>56.213710155000001</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>130</v>
+      </c>
+      <c r="B203" t="s">
+        <v>94</v>
+      </c>
+      <c r="C203" s="2">
+        <v>8.6954779900000001E-2</v>
+      </c>
+      <c r="D203" s="2">
+        <v>1.0398990000000001E-4</v>
+      </c>
+      <c r="E203" s="2">
+        <v>1.0794999999999999E-4</v>
+      </c>
+      <c r="F203" s="2">
+        <v>1.3016072693999998</v>
+      </c>
+      <c r="G203" s="2">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="H203" s="2">
+        <v>2.7448189499999998E-2</v>
+      </c>
+      <c r="I203" s="2">
+        <v>1.0082429800000001E-2</v>
+      </c>
+      <c r="J203" s="2"/>
+      <c r="K203" s="2">
+        <v>0.1493028096</v>
+      </c>
+      <c r="L203" s="2"/>
+      <c r="M203" s="2">
+        <v>1.155699E-4</v>
+      </c>
+      <c r="N203" s="2">
+        <v>1.7848797999999999E-3</v>
+      </c>
+      <c r="O203" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="P203" s="2"/>
+      <c r="Q203" s="2">
+        <v>1.5785478677999998</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B204" t="s">
+        <v>95</v>
+      </c>
+      <c r="C204" s="2">
+        <v>1.0958091272999999</v>
+      </c>
+      <c r="D204" s="2">
+        <v>1.2686780000000001E-3</v>
+      </c>
+      <c r="E204" s="2">
+        <v>1.3580109999999999E-3</v>
+      </c>
+      <c r="F204" s="2">
+        <v>16.3411713926</v>
+      </c>
+      <c r="G204" s="2">
+        <v>5.0319990000000005E-4</v>
+      </c>
+      <c r="H204" s="2">
+        <v>0.33729674100000001</v>
+      </c>
+      <c r="I204" s="2">
+        <v>0.1217957544</v>
+      </c>
+      <c r="J204" s="2"/>
+      <c r="K204" s="2">
+        <v>1.8782293491000002</v>
+      </c>
+      <c r="L204" s="2"/>
+      <c r="M204" s="2">
+        <v>1.4249781E-3</v>
+      </c>
+      <c r="N204" s="2">
+        <v>2.0169143899999999E-2</v>
+      </c>
+      <c r="O204" s="2">
+        <v>1.218E-2</v>
+      </c>
+      <c r="P204" s="2"/>
+      <c r="Q204" s="2">
+        <v>19.811206375299999</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>131</v>
+      </c>
+      <c r="B205" t="s">
+        <v>94</v>
+      </c>
+      <c r="C205" s="2">
+        <v>2.5096564793000002</v>
+      </c>
+      <c r="D205" s="2">
+        <v>0.38593560000000005</v>
+      </c>
+      <c r="E205" s="2">
+        <v>7.6094269899999997E-2</v>
+      </c>
+      <c r="F205" s="2">
+        <v>4.6978368786000004</v>
+      </c>
+      <c r="G205" s="2">
+        <v>0.89445370989999995</v>
+      </c>
+      <c r="H205" s="2">
+        <v>2.0722231493000001</v>
+      </c>
+      <c r="I205" s="2">
+        <v>4.3039844189000007</v>
+      </c>
+      <c r="J205" s="2">
+        <v>2.6595699E-3</v>
+      </c>
+      <c r="K205" s="2">
+        <v>4.7299834682000004</v>
+      </c>
+      <c r="L205" s="2">
+        <v>1.55873299E-2</v>
+      </c>
+      <c r="M205" s="2">
+        <v>0.4002653598</v>
+      </c>
+      <c r="N205" s="2">
+        <v>4.7858800000000002E-3</v>
+      </c>
+      <c r="O205" s="2">
+        <v>3.3824799999999998E-3</v>
+      </c>
+      <c r="P205" s="2">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="Q205" s="2">
+        <v>20.096849593700004</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B206" t="s">
+        <v>95</v>
+      </c>
+      <c r="C206" s="2">
+        <v>31.7940330092</v>
+      </c>
+      <c r="D206" s="2">
+        <v>4.8484143200000007</v>
+      </c>
+      <c r="E206" s="2">
+        <v>0.95982038030000005</v>
+      </c>
+      <c r="F206" s="2">
+        <v>58.732927618199994</v>
+      </c>
+      <c r="G206" s="2">
+        <v>11.256426151500001</v>
+      </c>
+      <c r="H206" s="2">
+        <v>26.077108946800003</v>
+      </c>
+      <c r="I206" s="2">
+        <v>54.582125338899999</v>
+      </c>
+      <c r="J206" s="2">
+        <v>3.2659519499999998E-2</v>
+      </c>
+      <c r="K206" s="2">
+        <v>59.396223827299991</v>
+      </c>
+      <c r="L206" s="2">
+        <v>0.1914124123</v>
+      </c>
+      <c r="M206" s="2">
+        <v>5.0085236483000006</v>
+      </c>
+      <c r="N206" s="2">
+        <v>5.4080443800000003E-2</v>
+      </c>
+      <c r="O206" s="2">
+        <v>4.1198606400000004E-2</v>
+      </c>
+      <c r="P206" s="2">
+        <v>1.218E-5</v>
+      </c>
+      <c r="Q206" s="2">
+        <v>252.97496640249994</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>132</v>
+      </c>
+      <c r="B207" t="s">
+        <v>94</v>
+      </c>
+      <c r="C207" s="2">
+        <v>2.8633718292999992</v>
+      </c>
+      <c r="D207" s="2">
+        <v>0.67271874990000002</v>
+      </c>
+      <c r="E207" s="2">
+        <v>0.56355119989999991</v>
+      </c>
+      <c r="F207" s="2">
+        <v>12.2575770487</v>
+      </c>
+      <c r="G207" s="2">
+        <v>1.44202221</v>
+      </c>
+      <c r="H207" s="2">
+        <v>13.599364889000002</v>
+      </c>
+      <c r="I207" s="2">
+        <v>5.8482524195000014</v>
+      </c>
+      <c r="J207" s="2">
+        <v>8.294195E-2</v>
+      </c>
+      <c r="K207" s="2">
+        <v>5.5395596579000008</v>
+      </c>
+      <c r="L207" s="2">
+        <v>2.0981879900000003E-2</v>
+      </c>
+      <c r="M207" s="2">
+        <v>3.2933772699000001</v>
+      </c>
+      <c r="N207" s="2">
+        <v>4.6434377898000001</v>
+      </c>
+      <c r="O207" s="2">
+        <v>7.5082019999999999E-2</v>
+      </c>
+      <c r="P207" s="2"/>
+      <c r="Q207" s="2">
+        <v>50.902238913799991</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B208" t="s">
+        <v>95</v>
+      </c>
+      <c r="C208" s="2">
+        <v>36.121187653700005</v>
+      </c>
+      <c r="D208" s="2">
+        <v>8.4399284267999999</v>
+      </c>
+      <c r="E208" s="2">
+        <v>7.0457036629999994</v>
+      </c>
+      <c r="F208" s="2">
+        <v>155.37985363440001</v>
+      </c>
+      <c r="G208" s="2">
+        <v>18.178178570699998</v>
+      </c>
+      <c r="H208" s="2">
+        <v>171.52395385080001</v>
+      </c>
+      <c r="I208" s="2">
+        <v>73.470754567499981</v>
+      </c>
+      <c r="J208" s="2">
+        <v>1.0330359849999999</v>
+      </c>
+      <c r="K208" s="2">
+        <v>69.593592681899963</v>
+      </c>
+      <c r="L208" s="2">
+        <v>0.25807712399999999</v>
+      </c>
+      <c r="M208" s="2">
+        <v>41.795572938100001</v>
+      </c>
+      <c r="N208" s="2">
+        <v>59.15849231659999</v>
+      </c>
+      <c r="O208" s="2">
+        <v>0.9446406437999999</v>
+      </c>
+      <c r="P208" s="2"/>
+      <c r="Q208" s="2">
+        <v>642.94297205629982</v>
       </c>
     </row>
   </sheetData>
@@ -13374,7 +13854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D2E8B6-8413-4B5C-882C-FCAE21C7E121}">
-  <dimension ref="A2:AE105"/>
+  <dimension ref="A2:AE109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -21771,22 +22251,22 @@
         <v>125</v>
       </c>
       <c r="B102" s="2">
-        <v>10.541265099400004</v>
+        <v>10.541265099399999</v>
       </c>
       <c r="C102" s="2">
-        <v>1.5404671898000002</v>
+        <v>1.5404671898</v>
       </c>
       <c r="D102" s="2">
         <v>0.30973334990000001</v>
       </c>
       <c r="E102" s="2">
-        <v>10.676857608500001</v>
+        <v>10.676857608499999</v>
       </c>
       <c r="F102" s="2">
         <v>1.52429345</v>
       </c>
       <c r="G102" s="2">
-        <v>7.0495516189999998</v>
+        <v>7.0495516189999989</v>
       </c>
       <c r="H102" s="2">
         <v>8.1942503297999991</v>
@@ -21795,10 +22275,10 @@
         <v>2.5951819899999999E-2</v>
       </c>
       <c r="J102" s="2">
-        <v>6.4725927186999996</v>
+        <v>6.4725927187000005</v>
       </c>
       <c r="K102" s="2">
-        <v>2.04306699E-2</v>
+        <v>2.0430669899999997E-2</v>
       </c>
       <c r="L102" s="2">
         <v>2.0410046297999997</v>
@@ -21819,16 +22299,16 @@
         <v>1.8323795698000001</v>
       </c>
       <c r="R102" s="2">
-        <v>0.57434707969999999</v>
+        <v>0.57434707969999987</v>
       </c>
       <c r="S102" s="2">
-        <v>0.10458753999999999</v>
+        <v>0.10458754000000001</v>
       </c>
       <c r="T102" s="2">
-        <v>6.8793667698000007</v>
+        <v>6.8793667697999998</v>
       </c>
       <c r="U102" s="2">
-        <v>0.79308789960000003</v>
+        <v>0.79308789959999992</v>
       </c>
       <c r="V102" s="2">
         <v>7.645875329599999</v>
@@ -21840,7 +22320,7 @@
         <v>3.5879199899999999E-2</v>
       </c>
       <c r="Y102" s="2">
-        <v>3.7261149620999992</v>
+        <v>3.7261149621000005</v>
       </c>
       <c r="Z102" s="2">
         <v>3.1035999999999998E-4</v>
@@ -21864,31 +22344,31 @@
         <v>126</v>
       </c>
       <c r="B103" s="2">
-        <v>2.2410354895000002</v>
+        <v>2.2410354895000006</v>
       </c>
       <c r="C103" s="2">
-        <v>4.3218774097999999</v>
+        <v>4.321877409799999</v>
       </c>
       <c r="D103" s="2">
         <v>1.7164667598000001</v>
       </c>
       <c r="E103" s="2">
-        <v>6.1768947683999995</v>
+        <v>6.1768947684000004</v>
       </c>
       <c r="F103" s="2">
         <v>3.5403004299000003</v>
       </c>
       <c r="G103" s="2">
-        <v>28.744438628799998</v>
+        <v>28.744438628800001</v>
       </c>
       <c r="H103" s="2">
-        <v>3.9797154597</v>
+        <v>3.9797154597000004</v>
       </c>
       <c r="I103" s="2">
         <v>6.0730200000000002E-3</v>
       </c>
       <c r="J103" s="2">
-        <v>2.0242601280999994</v>
+        <v>2.0242601281000008</v>
       </c>
       <c r="K103" s="2">
         <v>2.0808800000000002E-3</v>
@@ -21906,10 +22386,10 @@
         <v>0.50007542999999999</v>
       </c>
       <c r="P103" s="2">
-        <v>59.084914313600009</v>
+        <v>59.084914313600017</v>
       </c>
       <c r="Q103" s="2">
-        <v>6.0954479098999998</v>
+        <v>6.095447909899999</v>
       </c>
       <c r="R103" s="2">
         <v>0.96028374969999997</v>
@@ -21918,13 +22398,13 @@
         <v>0.1339586499</v>
       </c>
       <c r="T103" s="2">
-        <v>3.6203973294000003</v>
+        <v>3.6203973293999998</v>
       </c>
       <c r="U103" s="2">
-        <v>1.5519809892999998</v>
+        <v>1.5519809893000001</v>
       </c>
       <c r="V103" s="2">
-        <v>6.7983298395999991</v>
+        <v>6.7983298396000009</v>
       </c>
       <c r="W103" s="2">
         <v>4.2708199695999998</v>
@@ -21933,13 +22413,13 @@
         <v>3.6656629900000001E-2</v>
       </c>
       <c r="Y103" s="2">
-        <v>1.6357991537000001</v>
+        <v>1.6357991537000007</v>
       </c>
       <c r="Z103" s="2">
         <v>5.0851990000000001E-4</v>
       </c>
       <c r="AA103" s="2">
-        <v>2.5387599197999999</v>
+        <v>2.5387599198000004</v>
       </c>
       <c r="AB103" s="2">
         <v>0.26477757959999998</v>
@@ -21957,10 +22437,10 @@
         <v>127</v>
       </c>
       <c r="B104" s="2">
-        <v>4.2272902993999999</v>
+        <v>4.227290299399999</v>
       </c>
       <c r="C104" s="2">
-        <v>0.55025838990000009</v>
+        <v>0.55025838989999998</v>
       </c>
       <c r="D104" s="2">
         <v>0.16759871990000003</v>
@@ -21972,22 +22452,22 @@
         <v>1.32292995</v>
       </c>
       <c r="G104" s="2">
-        <v>9.6362721189000009</v>
+        <v>9.6362721188999991</v>
       </c>
       <c r="H104" s="2">
-        <v>2.5468940287999997</v>
+        <v>2.5468940288000002</v>
       </c>
       <c r="I104" s="2">
         <v>4.6518099900000005E-2</v>
       </c>
       <c r="J104" s="2">
-        <v>4.2512866591000016</v>
+        <v>4.2512866591000007</v>
       </c>
       <c r="K104" s="2">
-        <v>1.1868579900000002E-2</v>
+        <v>1.1868579899999999E-2</v>
       </c>
       <c r="L104" s="2">
-        <v>3.0043624296000004</v>
+        <v>3.0043624296</v>
       </c>
       <c r="M104" s="2">
         <v>4.4385997999999999E-3</v>
@@ -21999,7 +22479,7 @@
         <v>2.1098999999999999E-6</v>
       </c>
       <c r="P104" s="2">
-        <v>35.332630863600009</v>
+        <v>35.332630863600002</v>
       </c>
       <c r="Q104" s="2">
         <v>1.6615208799000001</v>
@@ -22011,28 +22491,28 @@
         <v>8.6651270000000002E-2</v>
       </c>
       <c r="T104" s="2">
-        <v>6.9704481293000002</v>
+        <v>6.9704481292999994</v>
       </c>
       <c r="U104" s="2">
-        <v>0.71459177969999998</v>
+        <v>0.7145917797000001</v>
       </c>
       <c r="V104" s="2">
-        <v>25.576800959300002</v>
+        <v>25.576800959300005</v>
       </c>
       <c r="W104" s="2">
-        <v>3.7193456194000003</v>
+        <v>3.7193456193999999</v>
       </c>
       <c r="X104" s="2">
-        <v>0.15393631989999998</v>
+        <v>0.15393631990000001</v>
       </c>
       <c r="Y104" s="2">
-        <v>3.4482846744000022</v>
+        <v>3.4482846744000026</v>
       </c>
       <c r="Z104" s="2">
         <v>5.2634999999999999E-3</v>
       </c>
       <c r="AA104" s="2">
-        <v>0.83277477980000003</v>
+        <v>0.83277477980000014</v>
       </c>
       <c r="AB104" s="2">
         <v>1.3298494292</v>
@@ -22042,7 +22522,7 @@
       </c>
       <c r="AD104" s="2"/>
       <c r="AE104" s="2">
-        <v>45.016536000500004</v>
+        <v>45.016536000500011</v>
       </c>
     </row>
     <row r="105" spans="1:31" x14ac:dyDescent="0.25">
@@ -22050,50 +22530,50 @@
         <v>128</v>
       </c>
       <c r="B105" s="2">
-        <v>4.4597062794000006</v>
+        <v>4.5686707090000001</v>
       </c>
       <c r="C105" s="2">
-        <v>4.0573789997</v>
+        <v>4.0573789996999992</v>
       </c>
       <c r="D105" s="2">
-        <v>0.81976880980000011</v>
+        <v>0.8197688098</v>
       </c>
       <c r="E105" s="2">
-        <v>20.567034208900001</v>
+        <v>21.622486007899997</v>
       </c>
       <c r="F105" s="2">
-        <v>1.5533594199999998</v>
+        <v>1.5932660199999999</v>
       </c>
       <c r="G105" s="2">
-        <v>9.5162221688999988</v>
+        <v>9.5712881088999993</v>
       </c>
       <c r="H105" s="2">
-        <v>10.4608374094</v>
+        <v>10.460837409400003</v>
       </c>
       <c r="I105" s="2">
-        <v>6.1089930000000001E-2</v>
+        <v>0.2543552</v>
       </c>
       <c r="J105" s="2">
-        <v>4.5200512785999978</v>
+        <v>5.8530080087000007</v>
       </c>
       <c r="K105" s="2">
         <v>1.9358249899999999E-2</v>
       </c>
       <c r="L105" s="2">
-        <v>0.81857284990000001</v>
+        <v>0.81909734990000005</v>
       </c>
       <c r="M105" s="2">
-        <v>3.3370069800000006E-2</v>
+        <v>3.4659929899999997E-2</v>
       </c>
       <c r="N105" s="2">
         <v>5.0299999999999997E-3</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2">
-        <v>56.891779674300004</v>
+        <v>59.679204803100006</v>
       </c>
       <c r="Q105" s="2">
-        <v>4.1478138599000003</v>
+        <v>4.3526002199000011</v>
       </c>
       <c r="R105" s="2">
         <v>1.0581553996999997</v>
@@ -22102,31 +22582,31 @@
         <v>0.1133477499</v>
       </c>
       <c r="T105" s="2">
-        <v>3.5194389600000008E-2</v>
+        <v>9.636341799300002</v>
       </c>
       <c r="U105" s="2">
-        <v>0.95045191969999976</v>
+        <v>1.8013652097999999</v>
       </c>
       <c r="V105" s="2">
-        <v>5.8086812494000011</v>
+        <v>10.649425239400001</v>
       </c>
       <c r="W105" s="2">
-        <v>1.6218086895999997</v>
+        <v>1.6218086896000001</v>
       </c>
       <c r="X105" s="2">
         <v>3.5955500000000001E-2</v>
       </c>
       <c r="Y105" s="2">
-        <v>0.45053385420000014</v>
+        <v>0.94669448290000013</v>
       </c>
       <c r="Z105" s="2">
         <v>4.9492999999999998E-4</v>
       </c>
       <c r="AA105" s="2">
-        <v>0.38966642960000003</v>
+        <v>0.39541672949999995</v>
       </c>
       <c r="AB105" s="2">
-        <v>0.12762251930000001</v>
+        <v>0.1252695395</v>
       </c>
       <c r="AC105" s="2">
         <v>3.4358400000000003E-3</v>
@@ -22135,7 +22615,365 @@
         <v>9.5616989999999997E-4</v>
       </c>
       <c r="AE105" s="2">
-        <v>14.744118500800003</v>
+        <v>30.741267499400003</v>
+      </c>
+    </row>
+    <row r="106" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>129</v>
+      </c>
+      <c r="B106" s="2">
+        <v>0.22402117990000001</v>
+      </c>
+      <c r="C106" s="2">
+        <v>1.93566498E-2</v>
+      </c>
+      <c r="D106" s="2">
+        <v>1.0349999999999999E-4</v>
+      </c>
+      <c r="E106" s="2">
+        <v>2.3471744689</v>
+      </c>
+      <c r="F106" s="2">
+        <v>0.60749774999999995</v>
+      </c>
+      <c r="G106" s="2">
+        <v>9.3156009100000006E-2</v>
+      </c>
+      <c r="H106" s="2">
+        <v>5.0729019899999998E-2</v>
+      </c>
+      <c r="I106" s="2"/>
+      <c r="J106" s="2">
+        <v>1.1298302283999999</v>
+      </c>
+      <c r="K106" s="2">
+        <v>3.04916E-3</v>
+      </c>
+      <c r="L106" s="2">
+        <v>5.7993298E-3</v>
+      </c>
+      <c r="M106" s="2">
+        <v>9.9220596999999994E-3</v>
+      </c>
+      <c r="N106" s="2">
+        <v>2.5593699E-3</v>
+      </c>
+      <c r="O106" s="2">
+        <v>1.95E-6</v>
+      </c>
+      <c r="P106" s="2">
+        <v>4.4932006753999998</v>
+      </c>
+      <c r="Q106" s="2">
+        <v>4.7702698E-3</v>
+      </c>
+      <c r="R106" s="2">
+        <v>2.5567209800000001E-2</v>
+      </c>
+      <c r="S106" s="2">
+        <v>5.5704989999999998E-4</v>
+      </c>
+      <c r="T106" s="2">
+        <v>6.1574249800000001E-2</v>
+      </c>
+      <c r="U106" s="2">
+        <v>5.2050699000000004E-3</v>
+      </c>
+      <c r="V106" s="2">
+        <v>2.4553830000000002E-2</v>
+      </c>
+      <c r="W106" s="2">
+        <v>7.5353409799999993E-2</v>
+      </c>
+      <c r="X106" s="2"/>
+      <c r="Y106" s="2">
+        <v>7.198933400000003E-2</v>
+      </c>
+      <c r="Z106" s="2">
+        <v>3.5058989999999998E-4</v>
+      </c>
+      <c r="AA106" s="2">
+        <v>5.6758600000000005E-3</v>
+      </c>
+      <c r="AB106" s="2">
+        <v>7.7215197999999999E-3</v>
+      </c>
+      <c r="AC106" s="2">
+        <v>7.3400989999999997E-4</v>
+      </c>
+      <c r="AD106" s="2">
+        <v>4.7319000000000001E-4</v>
+      </c>
+      <c r="AE106" s="2">
+        <v>0.28452559260000004</v>
+      </c>
+    </row>
+    <row r="107" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>130</v>
+      </c>
+      <c r="B107" s="2">
+        <v>8.6954779900000001E-2</v>
+      </c>
+      <c r="C107" s="2">
+        <v>1.0398990000000001E-4</v>
+      </c>
+      <c r="D107" s="2">
+        <v>1.0794999999999999E-4</v>
+      </c>
+      <c r="E107" s="2">
+        <v>1.3016072693999998</v>
+      </c>
+      <c r="F107" s="2">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="G107" s="2">
+        <v>2.7448189499999998E-2</v>
+      </c>
+      <c r="H107" s="2">
+        <v>1.0082429800000001E-2</v>
+      </c>
+      <c r="I107" s="2"/>
+      <c r="J107" s="2">
+        <v>0.1493028096</v>
+      </c>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2">
+        <v>1.155699E-4</v>
+      </c>
+      <c r="M107" s="2">
+        <v>1.7848797999999999E-3</v>
+      </c>
+      <c r="N107" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" s="2">
+        <v>1.5785478677999998</v>
+      </c>
+      <c r="Q107" s="2">
+        <v>7.3599999999999998E-6</v>
+      </c>
+      <c r="R107" s="2">
+        <v>2.40224198E-2</v>
+      </c>
+      <c r="S107" s="2"/>
+      <c r="T107" s="2">
+        <v>4.10506697E-2</v>
+      </c>
+      <c r="U107" s="2">
+        <v>5.1719499999999998E-3</v>
+      </c>
+      <c r="V107" s="2">
+        <v>2.390745E-2</v>
+      </c>
+      <c r="W107" s="2">
+        <v>7.0882520000000004E-2</v>
+      </c>
+      <c r="X107" s="2"/>
+      <c r="Y107" s="2">
+        <v>6.7336923600000057E-2</v>
+      </c>
+      <c r="Z107" s="2"/>
+      <c r="AA107" s="2">
+        <v>5.8966298999999995E-3</v>
+      </c>
+      <c r="AB107" s="2">
+        <v>2.7714698000000002E-3</v>
+      </c>
+      <c r="AC107" s="2"/>
+      <c r="AD107" s="2"/>
+      <c r="AE107" s="2">
+        <v>0.24104739280000007</v>
+      </c>
+    </row>
+    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>131</v>
+      </c>
+      <c r="B108" s="2">
+        <v>2.5096564793000002</v>
+      </c>
+      <c r="C108" s="2">
+        <v>0.38593560000000005</v>
+      </c>
+      <c r="D108" s="2">
+        <v>7.6094269899999997E-2</v>
+      </c>
+      <c r="E108" s="2">
+        <v>4.6978368786000004</v>
+      </c>
+      <c r="F108" s="2">
+        <v>0.89445370989999995</v>
+      </c>
+      <c r="G108" s="2">
+        <v>2.0722231493000001</v>
+      </c>
+      <c r="H108" s="2">
+        <v>4.3039844189000007</v>
+      </c>
+      <c r="I108" s="2">
+        <v>2.6595699E-3</v>
+      </c>
+      <c r="J108" s="2">
+        <v>4.7299834682000004</v>
+      </c>
+      <c r="K108" s="2">
+        <v>1.55873299E-2</v>
+      </c>
+      <c r="L108" s="2">
+        <v>0.4002653598</v>
+      </c>
+      <c r="M108" s="2">
+        <v>4.7858800000000002E-3</v>
+      </c>
+      <c r="N108" s="2">
+        <v>3.3824799999999998E-3</v>
+      </c>
+      <c r="O108" s="2">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="P108" s="2">
+        <v>20.096849593700004</v>
+      </c>
+      <c r="Q108" s="2">
+        <v>1.4394571098</v>
+      </c>
+      <c r="R108" s="2">
+        <v>0.31051675980000004</v>
+      </c>
+      <c r="S108" s="2">
+        <v>0.14568527990000002</v>
+      </c>
+      <c r="T108" s="2">
+        <v>6.8436526397000002</v>
+      </c>
+      <c r="U108" s="2">
+        <v>1.0969614694999998</v>
+      </c>
+      <c r="V108" s="2">
+        <v>3.8720962799000005</v>
+      </c>
+      <c r="W108" s="2">
+        <v>0.99706682870000007</v>
+      </c>
+      <c r="X108" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="Y108" s="2">
+        <v>0.70961261419999977</v>
+      </c>
+      <c r="Z108" s="2">
+        <v>1.426E-3</v>
+      </c>
+      <c r="AA108" s="2">
+        <v>1.2349703097999998</v>
+      </c>
+      <c r="AB108" s="2">
+        <v>6.4870549900000005E-2</v>
+      </c>
+      <c r="AC108" s="2">
+        <v>2.2431E-4</v>
+      </c>
+      <c r="AD108" s="2">
+        <v>1.9715999999999999E-4</v>
+      </c>
+      <c r="AE108" s="2">
+        <v>16.716837311200003</v>
+      </c>
+    </row>
+    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>132</v>
+      </c>
+      <c r="B109" s="2">
+        <v>2.8633718292999992</v>
+      </c>
+      <c r="C109" s="2">
+        <v>0.67271874990000002</v>
+      </c>
+      <c r="D109" s="2">
+        <v>0.56355119989999991</v>
+      </c>
+      <c r="E109" s="2">
+        <v>12.2575770487</v>
+      </c>
+      <c r="F109" s="2">
+        <v>1.44202221</v>
+      </c>
+      <c r="G109" s="2">
+        <v>13.599364889000002</v>
+      </c>
+      <c r="H109" s="2">
+        <v>5.8482524195000014</v>
+      </c>
+      <c r="I109" s="2">
+        <v>8.294195E-2</v>
+      </c>
+      <c r="J109" s="2">
+        <v>5.5395596579000008</v>
+      </c>
+      <c r="K109" s="2">
+        <v>2.0981879900000003E-2</v>
+      </c>
+      <c r="L109" s="2">
+        <v>3.2933772699000001</v>
+      </c>
+      <c r="M109" s="2">
+        <v>4.6434377898000001</v>
+      </c>
+      <c r="N109" s="2">
+        <v>7.5082019999999999E-2</v>
+      </c>
+      <c r="O109" s="2"/>
+      <c r="P109" s="2">
+        <v>50.902238913799991</v>
+      </c>
+      <c r="Q109" s="2">
+        <v>2.9099903197999999</v>
+      </c>
+      <c r="R109" s="2">
+        <v>1.2650178096000002</v>
+      </c>
+      <c r="S109" s="2">
+        <v>0.10653899990000001</v>
+      </c>
+      <c r="T109" s="2">
+        <v>9.9160820092000002</v>
+      </c>
+      <c r="U109" s="2">
+        <v>5.1299130896000005</v>
+      </c>
+      <c r="V109" s="2">
+        <v>17.7356039296</v>
+      </c>
+      <c r="W109" s="2">
+        <v>15.824149879600002</v>
+      </c>
+      <c r="X109" s="2">
+        <v>1.0145E-2</v>
+      </c>
+      <c r="Y109" s="2">
+        <v>1.8697059138000012</v>
+      </c>
+      <c r="Z109" s="2">
+        <v>1.7019E-4</v>
+      </c>
+      <c r="AA109" s="2">
+        <v>0.98909154979999991</v>
+      </c>
+      <c r="AB109" s="2">
+        <v>7.3265275295999999</v>
+      </c>
+      <c r="AC109" s="2">
+        <v>2.2160998999999999E-3</v>
+      </c>
+      <c r="AD109" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AE109" s="2">
+        <v>63.585152320400006</v>
       </c>
     </row>
   </sheetData>
@@ -22145,7 +22983,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B8D9CE-6C58-4665-83B8-0D13D9F92D59}">
-  <dimension ref="A2:AE105"/>
+  <dimension ref="A2:AE109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -30822,7 +31660,7 @@
         <v>128</v>
       </c>
       <c r="B105" s="2">
-        <v>522</v>
+        <v>1882</v>
       </c>
       <c r="C105" s="2">
         <v>60</v>
@@ -30831,41 +31669,41 @@
         <v>12</v>
       </c>
       <c r="E105" s="2">
-        <v>281</v>
+        <v>401</v>
       </c>
       <c r="F105" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G105" s="2">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="H105" s="2">
         <v>359</v>
       </c>
       <c r="I105" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J105" s="2">
-        <v>467</v>
+        <v>581</v>
       </c>
       <c r="K105" s="2">
         <v>17</v>
       </c>
       <c r="L105" s="2">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M105" s="2">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="N105" s="2">
         <v>2</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2">
-        <v>1974</v>
+        <v>3631</v>
       </c>
       <c r="Q105" s="2">
-        <v>50</v>
+        <v>4276</v>
       </c>
       <c r="R105" s="2">
         <v>3535</v>
@@ -30874,13 +31712,13 @@
         <v>13</v>
       </c>
       <c r="T105" s="2">
-        <v>1357</v>
+        <v>4184</v>
       </c>
       <c r="U105" s="2">
-        <v>445</v>
+        <v>752</v>
       </c>
       <c r="V105" s="2">
-        <v>2229</v>
+        <v>3336</v>
       </c>
       <c r="W105" s="2">
         <v>4053</v>
@@ -30889,16 +31727,16 @@
         <v>5</v>
       </c>
       <c r="Y105" s="2">
-        <v>7005</v>
+        <v>11284</v>
       </c>
       <c r="Z105" s="2">
         <v>7</v>
       </c>
       <c r="AA105" s="2">
-        <v>652</v>
+        <v>990</v>
       </c>
       <c r="AB105" s="2">
-        <v>5419</v>
+        <v>5590</v>
       </c>
       <c r="AC105" s="2">
         <v>7</v>
@@ -30907,7 +31745,365 @@
         <v>2</v>
       </c>
       <c r="AE105" s="2">
-        <v>24779</v>
+        <v>38034</v>
+      </c>
+    </row>
+    <row r="106" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>129</v>
+      </c>
+      <c r="B106" s="2">
+        <v>1710</v>
+      </c>
+      <c r="C106" s="2">
+        <v>24</v>
+      </c>
+      <c r="D106" s="2">
+        <v>3</v>
+      </c>
+      <c r="E106" s="2">
+        <v>169</v>
+      </c>
+      <c r="F106" s="2">
+        <v>26</v>
+      </c>
+      <c r="G106" s="2">
+        <v>36</v>
+      </c>
+      <c r="H106" s="2">
+        <v>60</v>
+      </c>
+      <c r="I106" s="2"/>
+      <c r="J106" s="2">
+        <v>439</v>
+      </c>
+      <c r="K106" s="2">
+        <v>11</v>
+      </c>
+      <c r="L106" s="2">
+        <v>20</v>
+      </c>
+      <c r="M106" s="2">
+        <v>32</v>
+      </c>
+      <c r="N106" s="2">
+        <v>4</v>
+      </c>
+      <c r="O106" s="2">
+        <v>1</v>
+      </c>
+      <c r="P106" s="2">
+        <v>2535</v>
+      </c>
+      <c r="Q106" s="2">
+        <v>31</v>
+      </c>
+      <c r="R106" s="2">
+        <v>3567</v>
+      </c>
+      <c r="S106" s="2">
+        <v>1</v>
+      </c>
+      <c r="T106" s="2">
+        <v>4139</v>
+      </c>
+      <c r="U106" s="2">
+        <v>749</v>
+      </c>
+      <c r="V106" s="2">
+        <v>2229</v>
+      </c>
+      <c r="W106" s="2">
+        <v>6161</v>
+      </c>
+      <c r="X106" s="2"/>
+      <c r="Y106" s="2">
+        <v>10360</v>
+      </c>
+      <c r="Z106" s="2">
+        <v>5</v>
+      </c>
+      <c r="AA106" s="2">
+        <v>510</v>
+      </c>
+      <c r="AB106" s="2">
+        <v>563</v>
+      </c>
+      <c r="AC106" s="2">
+        <v>5</v>
+      </c>
+      <c r="AD106" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE106" s="2">
+        <v>28321</v>
+      </c>
+    </row>
+    <row r="107" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>130</v>
+      </c>
+      <c r="B107" s="2">
+        <v>1036</v>
+      </c>
+      <c r="C107" s="2">
+        <v>3</v>
+      </c>
+      <c r="D107" s="2">
+        <v>2</v>
+      </c>
+      <c r="E107" s="2">
+        <v>91</v>
+      </c>
+      <c r="F107" s="2">
+        <v>2</v>
+      </c>
+      <c r="G107" s="2">
+        <v>22</v>
+      </c>
+      <c r="H107" s="2">
+        <v>97</v>
+      </c>
+      <c r="I107" s="2"/>
+      <c r="J107" s="2">
+        <v>175</v>
+      </c>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2">
+        <v>4</v>
+      </c>
+      <c r="M107" s="2">
+        <v>26</v>
+      </c>
+      <c r="N107" s="2">
+        <v>1</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" s="2">
+        <v>1459</v>
+      </c>
+      <c r="Q107" s="2">
+        <v>5</v>
+      </c>
+      <c r="R107" s="2">
+        <v>3599</v>
+      </c>
+      <c r="S107" s="2"/>
+      <c r="T107" s="2">
+        <v>4115</v>
+      </c>
+      <c r="U107" s="2">
+        <v>808</v>
+      </c>
+      <c r="V107" s="2">
+        <v>2264</v>
+      </c>
+      <c r="W107" s="2">
+        <v>6127</v>
+      </c>
+      <c r="X107" s="2"/>
+      <c r="Y107" s="2">
+        <v>10465</v>
+      </c>
+      <c r="Z107" s="2"/>
+      <c r="AA107" s="2">
+        <v>582</v>
+      </c>
+      <c r="AB107" s="2">
+        <v>529</v>
+      </c>
+      <c r="AC107" s="2"/>
+      <c r="AD107" s="2"/>
+      <c r="AE107" s="2">
+        <v>28494</v>
+      </c>
+    </row>
+    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>131</v>
+      </c>
+      <c r="B108" s="2">
+        <v>1034</v>
+      </c>
+      <c r="C108" s="2">
+        <v>48</v>
+      </c>
+      <c r="D108" s="2">
+        <v>11</v>
+      </c>
+      <c r="E108" s="2">
+        <v>237</v>
+      </c>
+      <c r="F108" s="2">
+        <v>42</v>
+      </c>
+      <c r="G108" s="2">
+        <v>95</v>
+      </c>
+      <c r="H108" s="2">
+        <v>215</v>
+      </c>
+      <c r="I108" s="2">
+        <v>22</v>
+      </c>
+      <c r="J108" s="2">
+        <v>602</v>
+      </c>
+      <c r="K108" s="2">
+        <v>24</v>
+      </c>
+      <c r="L108" s="2">
+        <v>49</v>
+      </c>
+      <c r="M108" s="2">
+        <v>59</v>
+      </c>
+      <c r="N108" s="2">
+        <v>7</v>
+      </c>
+      <c r="O108" s="2">
+        <v>1</v>
+      </c>
+      <c r="P108" s="2">
+        <v>2446</v>
+      </c>
+      <c r="Q108" s="2">
+        <v>3883</v>
+      </c>
+      <c r="R108" s="2">
+        <v>3565</v>
+      </c>
+      <c r="S108" s="2">
+        <v>13</v>
+      </c>
+      <c r="T108" s="2">
+        <v>4360</v>
+      </c>
+      <c r="U108" s="2">
+        <v>733</v>
+      </c>
+      <c r="V108" s="2">
+        <v>2490</v>
+      </c>
+      <c r="W108" s="2">
+        <v>4025</v>
+      </c>
+      <c r="X108" s="2">
+        <v>7</v>
+      </c>
+      <c r="Y108" s="2">
+        <v>10212</v>
+      </c>
+      <c r="Z108" s="2">
+        <v>6</v>
+      </c>
+      <c r="AA108" s="2">
+        <v>585</v>
+      </c>
+      <c r="AB108" s="2">
+        <v>5575</v>
+      </c>
+      <c r="AC108" s="2">
+        <v>6</v>
+      </c>
+      <c r="AD108" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE108" s="2">
+        <v>35461</v>
+      </c>
+    </row>
+    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>132</v>
+      </c>
+      <c r="B109" s="2">
+        <v>1131</v>
+      </c>
+      <c r="C109" s="2">
+        <v>53</v>
+      </c>
+      <c r="D109" s="2">
+        <v>18</v>
+      </c>
+      <c r="E109" s="2">
+        <v>278</v>
+      </c>
+      <c r="F109" s="2">
+        <v>35</v>
+      </c>
+      <c r="G109" s="2">
+        <v>129</v>
+      </c>
+      <c r="H109" s="2">
+        <v>287</v>
+      </c>
+      <c r="I109" s="2">
+        <v>16</v>
+      </c>
+      <c r="J109" s="2">
+        <v>530</v>
+      </c>
+      <c r="K109" s="2">
+        <v>30</v>
+      </c>
+      <c r="L109" s="2">
+        <v>46</v>
+      </c>
+      <c r="M109" s="2">
+        <v>61</v>
+      </c>
+      <c r="N109" s="2">
+        <v>6</v>
+      </c>
+      <c r="O109" s="2"/>
+      <c r="P109" s="2">
+        <v>2620</v>
+      </c>
+      <c r="Q109" s="2">
+        <v>3865</v>
+      </c>
+      <c r="R109" s="2">
+        <v>3463</v>
+      </c>
+      <c r="S109" s="2">
+        <v>11</v>
+      </c>
+      <c r="T109" s="2">
+        <v>4290</v>
+      </c>
+      <c r="U109" s="2">
+        <v>767</v>
+      </c>
+      <c r="V109" s="2">
+        <v>2406</v>
+      </c>
+      <c r="W109" s="2">
+        <v>6082</v>
+      </c>
+      <c r="X109" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y109" s="2">
+        <v>10465</v>
+      </c>
+      <c r="Z109" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA109" s="2">
+        <v>650</v>
+      </c>
+      <c r="AB109" s="2">
+        <v>5943</v>
+      </c>
+      <c r="AC109" s="2">
+        <v>6</v>
+      </c>
+      <c r="AD109" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE109" s="2">
+        <v>37958</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base_Op_Cam.xlsx
+++ b/data/Base_Op_Cam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mefp\Sergio Garnica\Documents\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162716B3-6300-4C5F-86B1-E29D369F2641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69D7CCF-1C8D-4BB1-9A34-484BA89BFE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D18D9BAD-78DE-4368-BCF3-29E6374A660B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{D18D9BAD-78DE-4368-BCF3-29E6374A660B}"/>
   </bookViews>
   <sheets>
     <sheet name="TC" sheetId="1" r:id="rId1"/>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="140">
   <si>
     <t>Nombre</t>
   </si>
@@ -503,6 +503,27 @@
   <si>
     <t>2026-09-08</t>
   </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
 </sst>
 </file>
 
@@ -559,17 +580,14 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46275.696096412037" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{9ECE6D2C-0019-46A8-93F5-B57014A573FD}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46282.51002627315" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{04D15196-6A10-4FCA-A07B-7666B41B44BD}">
   <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="9">
+  <cacheFields count="10">
     <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
     </cacheField>
     <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
-      <sharedItems count="2">
-        <s v="[Transaccion].[Transaccion].&amp;[Compra]" c="Compra"/>
-        <s v="[Transaccion].[Transaccion].&amp;[Venta]" c="Venta"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
     </cacheField>
     <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
@@ -584,7 +602,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
     </cacheField>
     <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
-      <sharedItems count="100">
+      <sharedItems count="107">
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
@@ -685,511 +703,13 @@
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-06T00:00:00]" c="2026-09-06"/>
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-07T00:00:00]" c="2026-09-07"/>
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-08T00:00:00]" c="2026-09-08"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
-      <sharedItems count="14">
-        <s v="[Entidades].[Sigla].&amp;[BCR]" c="BCR"/>
-        <s v="[Entidades].[Sigla].&amp;[BEC]" c="BEC"/>
-        <s v="[Entidades].[Sigla].&amp;[BFO]" c="BFO"/>
-        <s v="[Entidades].[Sigla].&amp;[BGA]" c="BGA"/>
-        <s v="[Entidades].[Sigla].&amp;[BIE]" c="BIE"/>
-        <s v="[Entidades].[Sigla].&amp;[BIS]" c="BIS"/>
-        <s v="[Entidades].[Sigla].&amp;[BME]" c="BME"/>
-        <s v="[Entidades].[Sigla].&amp;[BNA]" c="BNA"/>
-        <s v="[Entidades].[Sigla].&amp;[BNB]" c="BNB"/>
-        <s v="[Entidades].[Sigla].&amp;[BPR]" c="BPR"/>
-        <s v="[Entidades].[Sigla].&amp;[BSO]" c="BSO"/>
-        <s v="[Entidades].[Sigla].&amp;[BUN]" c="BUN"/>
-        <s v="[Entidades].[Sigla].&amp;[PCO]" c="PCO"/>
-        <s v="[Entidades].[Sigla].&amp;[PEF]" c="PEF"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Numero Operaciones]" caption="Numero Operaciones" numFmtId="0" hierarchy="28" level="32767"/>
-  </cacheFields>
-  <cacheHierarchies count="29">
-    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Categoria]" caption="Cod Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Categoria].[All]" allUniqueName="[Actividad Economica].[Cod Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Sector Actividad]" caption="Cod Sector Actividad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" allUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion].[All]" allUniqueName="[Actividad Economica].[Descripcion].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion Categoria]" caption="Descripcion Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" allUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Concepto].[Cod Concepto]" caption="Cod Concepto" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Concepto].[Cod Concepto].[All]" allUniqueName="[Concepto].[Cod Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Concepto].[Concepto]" caption="Concepto" attribute="1" defaultMemberUniqueName="[Concepto].[Concepto].[All]" allUniqueName="[Concepto].[Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Entidades].[Cod Entidad]" caption="Cod Entidad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Entidades].[Cod Entidad].[All]" allUniqueName="[Entidades].[Cod Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Entidades].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Entidades].[Nombre].[All]" allUniqueName="[Entidades].[Nombre].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Entidades].[Sigla]" caption="Sigla" attribute="1" defaultMemberUniqueName="[Entidades].[Sigla].[All]" allUniqueName="[Entidades].[Sigla].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="7"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Entidades].[Tipo Entidad]" caption="Tipo Entidad" attribute="1" defaultMemberUniqueName="[Entidades].[Tipo Entidad].[All]" allUniqueName="[Entidades].[Tipo Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Estrato].[Cod Estrato]" caption="Cod Estrato" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Estrato].[Cod Estrato].[All]" allUniqueName="[Estrato].[Cod Estrato].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Estrato].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Estrato].[Descripcion].[All]" allUniqueName="[Estrato].[Descripcion].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Moneda Cambio].[Cod Moneda]" caption="Cod Moneda" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Moneda Cambio].[Cod Moneda].[All]" allUniqueName="[Moneda Cambio].[Cod Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Moneda Cambio].[Moneda]" caption="Moneda" attribute="1" defaultMemberUniqueName="[Moneda Cambio].[Moneda].[All]" allUniqueName="[Moneda Cambio].[Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Monto Menor].[Cod Monto Menor]" caption="Cod Monto Menor" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Monto Menor].[Cod Monto Menor].[All]" allUniqueName="[Monto Menor].[Cod Monto Menor].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Monto Menor].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Monto Menor].[Descripcion].[All]" allUniqueName="[Monto Menor].[Descripcion].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="5"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Subsistema].[Cod Subsistema]" caption="Cod Subsistema" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Subsistema].[Cod Subsistema].[All]" allUniqueName="[Subsistema].[Cod Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Subsistema].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Subsistema].[Nombre].[All]" allUniqueName="[Subsistema].[Nombre].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Subsistema].[Sigla Subsistema]" caption="Sigla Subsistema" attribute="1" defaultMemberUniqueName="[Subsistema].[Sigla Subsistema].[All]" allUniqueName="[Subsistema].[Sigla Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha]" caption="Cod Fecha" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Fecha]" caption="Fecha" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="6"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes]" caption="Ultimo Dia Mes" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transaccion].[Cod Transaccion]" caption="Cod Transaccion" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Transaccion].[Cod Transaccion].[All]" allUniqueName="[Transaccion].[Cod Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transaccion].[Transaccion]" caption="Transaccion" attribute="1" defaultMemberUniqueName="[Transaccion].[Transaccion].[All]" allUniqueName="[Transaccion].[Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Monto Usd]" caption="Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Usd]" caption="Tipo Cambio Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Mm Usd]" caption="Tipo Cambio Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Numero Operaciones]" caption="Numero Operaciones" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="8"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="10">
-    <dimension name="Actividad Economica" uniqueName="[Actividad Economica]" caption="Actividad Economica"/>
-    <dimension name="Concepto" uniqueName="[Concepto]" caption="Concepto"/>
-    <dimension name="Entidades" uniqueName="[Entidades]" caption="Entidades"/>
-    <dimension name="Estrato" uniqueName="[Estrato]" caption="Estrato"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Moneda Cambio" uniqueName="[Moneda Cambio]" caption="Moneda Cambio"/>
-    <dimension name="Monto Menor" uniqueName="[Monto Menor]" caption="Monto Menor"/>
-    <dimension name="Subsistema" uniqueName="[Subsistema]" caption="Subsistema"/>
-    <dimension name="Tipo Cambio Fecha Dia" uniqueName="[Tipo Cambio Fecha Dia]" caption="Tipo Cambio Fecha Dia"/>
-    <dimension name="Transaccion" uniqueName="[Transaccion]" caption="Transaccion"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Operaciones Cambiarias" caption="Fact Operaciones Cambiarias"/>
-  </measureGroups>
-  <maps count="9">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-    <map measureGroup="0" dimension="8"/>
-    <map measureGroup="0" dimension="9"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46275.696365046293" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{F7995ADC-F0B3-4CE9-B66F-D51574EF46B6}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="9">
-    <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
-      <sharedItems count="2">
-        <s v="[Transaccion].[Transaccion].&amp;[Compra]" c="Compra"/>
-        <s v="[Transaccion].[Transaccion].&amp;[Venta]" c="Venta"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda]" caption="Cod Moneda" numFmtId="0" hierarchy="12" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda].[Moneda]" caption="Moneda" propertyName="Moneda" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Monto Menor].[Descripcion].[Descripcion]" caption="Descripcion" numFmtId="0" hierarchy="15" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
-      <sharedItems count="100">
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-04T00:00:00]" c="2026-06-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-05T00:00:00]" c="2026-06-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-06T00:00:00]" c="2026-06-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-07T00:00:00]" c="2026-06-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-08T00:00:00]" c="2026-06-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-09T00:00:00]" c="2026-06-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-10T00:00:00]" c="2026-06-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-11T00:00:00]" c="2026-06-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-12T00:00:00]" c="2026-06-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-13T00:00:00]" c="2026-06-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-14T00:00:00]" c="2026-06-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-15T00:00:00]" c="2026-06-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-16T00:00:00]" c="2026-06-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-17T00:00:00]" c="2026-06-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-18T00:00:00]" c="2026-06-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-19T00:00:00]" c="2026-06-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-20T00:00:00]" c="2026-06-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-21T00:00:00]" c="2026-06-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-22T00:00:00]" c="2026-06-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-23T00:00:00]" c="2026-06-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-24T00:00:00]" c="2026-06-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-25T00:00:00]" c="2026-06-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-26T00:00:00]" c="2026-06-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-27T00:00:00]" c="2026-06-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-28T00:00:00]" c="2026-06-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-29T00:00:00]" c="2026-06-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-30T00:00:00]" c="2026-06-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-01T00:00:00]" c="2026-07-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-02T00:00:00]" c="2026-07-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-03T00:00:00]" c="2026-07-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-04T00:00:00]" c="2026-07-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-05T00:00:00]" c="2026-07-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-06T00:00:00]" c="2026-07-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-07T00:00:00]" c="2026-07-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-08T00:00:00]" c="2026-07-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-09T00:00:00]" c="2026-07-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-10T00:00:00]" c="2026-07-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-11T00:00:00]" c="2026-07-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-12T00:00:00]" c="2026-07-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-13T00:00:00]" c="2026-07-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-14T00:00:00]" c="2026-07-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-15T00:00:00]" c="2026-07-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-16T00:00:00]" c="2026-07-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-17T00:00:00]" c="2026-07-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-18T00:00:00]" c="2026-07-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-19T00:00:00]" c="2026-07-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-20T00:00:00]" c="2026-07-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-21T00:00:00]" c="2026-07-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-22T00:00:00]" c="2026-07-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-23T00:00:00]" c="2026-07-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-24T00:00:00]" c="2026-07-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-25T00:00:00]" c="2026-07-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-26T00:00:00]" c="2026-07-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-27T00:00:00]" c="2026-07-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-28T00:00:00]" c="2026-07-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-29T00:00:00]" c="2026-07-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-30T00:00:00]" c="2026-07-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-31T00:00:00]" c="2026-07-31"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-01T00:00:00]" c="2026-08-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-02T00:00:00]" c="2026-08-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-03T00:00:00]" c="2026-08-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-04T00:00:00]" c="2026-08-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-05T00:00:00]" c="2026-08-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-06T00:00:00]" c="2026-08-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-07T00:00:00]" c="2026-08-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-08T00:00:00]" c="2026-08-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-09T00:00:00]" c="2026-08-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-10T00:00:00]" c="2026-08-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-11T00:00:00]" c="2026-08-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-12T00:00:00]" c="2026-08-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-13T00:00:00]" c="2026-08-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-14T00:00:00]" c="2026-08-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-15T00:00:00]" c="2026-08-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-16T00:00:00]" c="2026-08-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-17T00:00:00]" c="2026-08-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-18T00:00:00]" c="2026-08-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-19T00:00:00]" c="2026-08-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-20T00:00:00]" c="2026-08-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-21T00:00:00]" c="2026-08-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-22T00:00:00]" c="2026-08-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-23T00:00:00]" c="2026-08-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-24T00:00:00]" c="2026-08-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-25T00:00:00]" c="2026-08-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-26T00:00:00]" c="2026-08-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-27T00:00:00]" c="2026-08-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-28T00:00:00]" c="2026-08-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-29T00:00:00]" c="2026-08-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-30T00:00:00]" c="2026-08-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-31T00:00:00]" c="2026-08-31"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-01T00:00:00]" c="2026-09-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-02T00:00:00]" c="2026-09-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-03T00:00:00]" c="2026-09-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-04T00:00:00]" c="2026-09-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-05T00:00:00]" c="2026-09-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-06T00:00:00]" c="2026-09-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-07T00:00:00]" c="2026-09-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-08T00:00:00]" c="2026-09-08"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
-      <sharedItems count="14">
-        <s v="[Entidades].[Sigla].&amp;[BCR]" c="BCR"/>
-        <s v="[Entidades].[Sigla].&amp;[BEC]" c="BEC"/>
-        <s v="[Entidades].[Sigla].&amp;[BFO]" c="BFO"/>
-        <s v="[Entidades].[Sigla].&amp;[BGA]" c="BGA"/>
-        <s v="[Entidades].[Sigla].&amp;[BIE]" c="BIE"/>
-        <s v="[Entidades].[Sigla].&amp;[BIS]" c="BIS"/>
-        <s v="[Entidades].[Sigla].&amp;[BME]" c="BME"/>
-        <s v="[Entidades].[Sigla].&amp;[BNA]" c="BNA"/>
-        <s v="[Entidades].[Sigla].&amp;[BNB]" c="BNB"/>
-        <s v="[Entidades].[Sigla].&amp;[BPR]" c="BPR"/>
-        <s v="[Entidades].[Sigla].&amp;[BSO]" c="BSO"/>
-        <s v="[Entidades].[Sigla].&amp;[BUN]" c="BUN"/>
-        <s v="[Entidades].[Sigla].&amp;[PCO]" c="PCO"/>
-        <s v="[Entidades].[Sigla].&amp;[PEF]" c="PEF"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" numFmtId="0" hierarchy="26" level="32767"/>
-  </cacheFields>
-  <cacheHierarchies count="29">
-    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Categoria]" caption="Cod Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Categoria].[All]" allUniqueName="[Actividad Economica].[Cod Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Sector Actividad]" caption="Cod Sector Actividad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" allUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion].[All]" allUniqueName="[Actividad Economica].[Descripcion].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion Categoria]" caption="Descripcion Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" allUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Concepto].[Cod Concepto]" caption="Cod Concepto" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Concepto].[Cod Concepto].[All]" allUniqueName="[Concepto].[Cod Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Concepto].[Concepto]" caption="Concepto" attribute="1" defaultMemberUniqueName="[Concepto].[Concepto].[All]" allUniqueName="[Concepto].[Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Entidades].[Cod Entidad]" caption="Cod Entidad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Entidades].[Cod Entidad].[All]" allUniqueName="[Entidades].[Cod Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Entidades].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Entidades].[Nombre].[All]" allUniqueName="[Entidades].[Nombre].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Entidades].[Sigla]" caption="Sigla" attribute="1" defaultMemberUniqueName="[Entidades].[Sigla].[All]" allUniqueName="[Entidades].[Sigla].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="7"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Entidades].[Tipo Entidad]" caption="Tipo Entidad" attribute="1" defaultMemberUniqueName="[Entidades].[Tipo Entidad].[All]" allUniqueName="[Entidades].[Tipo Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Estrato].[Cod Estrato]" caption="Cod Estrato" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Estrato].[Cod Estrato].[All]" allUniqueName="[Estrato].[Cod Estrato].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Estrato].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Estrato].[Descripcion].[All]" allUniqueName="[Estrato].[Descripcion].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Moneda Cambio].[Cod Moneda]" caption="Cod Moneda" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Moneda Cambio].[Cod Moneda].[All]" allUniqueName="[Moneda Cambio].[Cod Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Moneda Cambio].[Moneda]" caption="Moneda" attribute="1" defaultMemberUniqueName="[Moneda Cambio].[Moneda].[All]" allUniqueName="[Moneda Cambio].[Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Monto Menor].[Cod Monto Menor]" caption="Cod Monto Menor" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Monto Menor].[Cod Monto Menor].[All]" allUniqueName="[Monto Menor].[Cod Monto Menor].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Monto Menor].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Monto Menor].[Descripcion].[All]" allUniqueName="[Monto Menor].[Descripcion].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="5"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Subsistema].[Cod Subsistema]" caption="Cod Subsistema" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Subsistema].[Cod Subsistema].[All]" allUniqueName="[Subsistema].[Cod Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Subsistema].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Subsistema].[Nombre].[All]" allUniqueName="[Subsistema].[Nombre].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Subsistema].[Sigla Subsistema]" caption="Sigla Subsistema" attribute="1" defaultMemberUniqueName="[Subsistema].[Sigla Subsistema].[All]" allUniqueName="[Subsistema].[Sigla Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha]" caption="Cod Fecha" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Fecha]" caption="Fecha" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="6"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes]" caption="Ultimo Dia Mes" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transaccion].[Cod Transaccion]" caption="Cod Transaccion" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Transaccion].[Cod Transaccion].[All]" allUniqueName="[Transaccion].[Cod Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transaccion].[Transaccion]" caption="Transaccion" attribute="1" defaultMemberUniqueName="[Transaccion].[Transaccion].[All]" allUniqueName="[Transaccion].[Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Monto Usd]" caption="Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Usd]" caption="Tipo Cambio Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="8"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Mm Usd]" caption="Tipo Cambio Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Numero Operaciones]" caption="Numero Operaciones" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="10">
-    <dimension name="Actividad Economica" uniqueName="[Actividad Economica]" caption="Actividad Economica"/>
-    <dimension name="Concepto" uniqueName="[Concepto]" caption="Concepto"/>
-    <dimension name="Entidades" uniqueName="[Entidades]" caption="Entidades"/>
-    <dimension name="Estrato" uniqueName="[Estrato]" caption="Estrato"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Moneda Cambio" uniqueName="[Moneda Cambio]" caption="Moneda Cambio"/>
-    <dimension name="Monto Menor" uniqueName="[Monto Menor]" caption="Monto Menor"/>
-    <dimension name="Subsistema" uniqueName="[Subsistema]" caption="Subsistema"/>
-    <dimension name="Tipo Cambio Fecha Dia" uniqueName="[Tipo Cambio Fecha Dia]" caption="Tipo Cambio Fecha Dia"/>
-    <dimension name="Transaccion" uniqueName="[Transaccion]" caption="Transaccion"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Operaciones Cambiarias" caption="Fact Operaciones Cambiarias"/>
-  </measureGroups>
-  <maps count="9">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-    <map measureGroup="0" dimension="8"/>
-    <map measureGroup="0" dimension="9"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46275.696549768516" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{04D15196-6A10-4FCA-A07B-7666B41B44BD}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="10">
-    <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda]" caption="Cod Moneda" numFmtId="0" hierarchy="12" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda].[Moneda]" caption="Moneda" propertyName="Moneda" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Monto Menor].[Descripcion].[Descripcion]" caption="Descripcion" numFmtId="0" hierarchy="15" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
-      <sharedItems count="100">
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-04T00:00:00]" c="2026-06-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-05T00:00:00]" c="2026-06-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-06T00:00:00]" c="2026-06-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-07T00:00:00]" c="2026-06-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-08T00:00:00]" c="2026-06-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-09T00:00:00]" c="2026-06-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-10T00:00:00]" c="2026-06-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-11T00:00:00]" c="2026-06-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-12T00:00:00]" c="2026-06-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-13T00:00:00]" c="2026-06-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-14T00:00:00]" c="2026-06-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-15T00:00:00]" c="2026-06-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-16T00:00:00]" c="2026-06-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-17T00:00:00]" c="2026-06-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-18T00:00:00]" c="2026-06-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-19T00:00:00]" c="2026-06-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-20T00:00:00]" c="2026-06-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-21T00:00:00]" c="2026-06-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-22T00:00:00]" c="2026-06-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-23T00:00:00]" c="2026-06-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-24T00:00:00]" c="2026-06-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-25T00:00:00]" c="2026-06-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-26T00:00:00]" c="2026-06-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-27T00:00:00]" c="2026-06-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-28T00:00:00]" c="2026-06-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-29T00:00:00]" c="2026-06-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-30T00:00:00]" c="2026-06-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-01T00:00:00]" c="2026-07-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-02T00:00:00]" c="2026-07-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-03T00:00:00]" c="2026-07-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-04T00:00:00]" c="2026-07-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-05T00:00:00]" c="2026-07-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-06T00:00:00]" c="2026-07-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-07T00:00:00]" c="2026-07-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-08T00:00:00]" c="2026-07-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-09T00:00:00]" c="2026-07-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-10T00:00:00]" c="2026-07-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-11T00:00:00]" c="2026-07-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-12T00:00:00]" c="2026-07-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-13T00:00:00]" c="2026-07-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-14T00:00:00]" c="2026-07-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-15T00:00:00]" c="2026-07-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-16T00:00:00]" c="2026-07-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-17T00:00:00]" c="2026-07-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-18T00:00:00]" c="2026-07-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-19T00:00:00]" c="2026-07-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-20T00:00:00]" c="2026-07-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-21T00:00:00]" c="2026-07-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-22T00:00:00]" c="2026-07-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-23T00:00:00]" c="2026-07-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-24T00:00:00]" c="2026-07-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-25T00:00:00]" c="2026-07-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-26T00:00:00]" c="2026-07-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-27T00:00:00]" c="2026-07-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-28T00:00:00]" c="2026-07-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-29T00:00:00]" c="2026-07-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-30T00:00:00]" c="2026-07-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-31T00:00:00]" c="2026-07-31"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-01T00:00:00]" c="2026-08-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-02T00:00:00]" c="2026-08-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-03T00:00:00]" c="2026-08-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-04T00:00:00]" c="2026-08-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-05T00:00:00]" c="2026-08-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-06T00:00:00]" c="2026-08-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-07T00:00:00]" c="2026-08-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-08T00:00:00]" c="2026-08-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-09T00:00:00]" c="2026-08-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-10T00:00:00]" c="2026-08-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-11T00:00:00]" c="2026-08-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-12T00:00:00]" c="2026-08-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-13T00:00:00]" c="2026-08-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-14T00:00:00]" c="2026-08-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-15T00:00:00]" c="2026-08-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-16T00:00:00]" c="2026-08-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-17T00:00:00]" c="2026-08-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-18T00:00:00]" c="2026-08-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-19T00:00:00]" c="2026-08-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-20T00:00:00]" c="2026-08-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-21T00:00:00]" c="2026-08-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-22T00:00:00]" c="2026-08-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-23T00:00:00]" c="2026-08-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-24T00:00:00]" c="2026-08-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-25T00:00:00]" c="2026-08-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-26T00:00:00]" c="2026-08-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-27T00:00:00]" c="2026-08-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-28T00:00:00]" c="2026-08-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-29T00:00:00]" c="2026-08-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-30T00:00:00]" c="2026-08-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-31T00:00:00]" c="2026-08-31"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-01T00:00:00]" c="2026-09-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-02T00:00:00]" c="2026-09-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-03T00:00:00]" c="2026-09-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-04T00:00:00]" c="2026-09-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-05T00:00:00]" c="2026-09-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-06T00:00:00]" c="2026-09-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-07T00:00:00]" c="2026-09-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-08T00:00:00]" c="2026-09-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-09T00:00:00]" c="2026-09-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-10T00:00:00]" c="2026-09-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-11T00:00:00]" c="2026-09-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-12T00:00:00]" c="2026-09-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-13T00:00:00]" c="2026-09-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-14T00:00:00]" c="2026-09-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-15T00:00:00]" c="2026-09-15"/>
       </sharedItems>
     </cacheField>
     <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
@@ -1322,9 +842,531 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46282.510346990741" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{F7995ADC-F0B3-4CE9-B66F-D51574EF46B6}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="9">
+    <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
+      <sharedItems count="2">
+        <s v="[Transaccion].[Transaccion].&amp;[Compra]" c="Compra"/>
+        <s v="[Transaccion].[Transaccion].&amp;[Venta]" c="Venta"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda]" caption="Cod Moneda" numFmtId="0" hierarchy="12" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda].[Moneda]" caption="Moneda" propertyName="Moneda" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Monto Menor].[Descripcion].[Descripcion]" caption="Descripcion" numFmtId="0" hierarchy="15" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
+      <sharedItems count="107">
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-04T00:00:00]" c="2026-06-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-05T00:00:00]" c="2026-06-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-06T00:00:00]" c="2026-06-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-07T00:00:00]" c="2026-06-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-08T00:00:00]" c="2026-06-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-09T00:00:00]" c="2026-06-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-10T00:00:00]" c="2026-06-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-11T00:00:00]" c="2026-06-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-12T00:00:00]" c="2026-06-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-13T00:00:00]" c="2026-06-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-14T00:00:00]" c="2026-06-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-15T00:00:00]" c="2026-06-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-16T00:00:00]" c="2026-06-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-17T00:00:00]" c="2026-06-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-18T00:00:00]" c="2026-06-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-19T00:00:00]" c="2026-06-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-20T00:00:00]" c="2026-06-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-21T00:00:00]" c="2026-06-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-22T00:00:00]" c="2026-06-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-23T00:00:00]" c="2026-06-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-24T00:00:00]" c="2026-06-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-25T00:00:00]" c="2026-06-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-26T00:00:00]" c="2026-06-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-27T00:00:00]" c="2026-06-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-28T00:00:00]" c="2026-06-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-29T00:00:00]" c="2026-06-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-30T00:00:00]" c="2026-06-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-01T00:00:00]" c="2026-07-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-02T00:00:00]" c="2026-07-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-03T00:00:00]" c="2026-07-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-04T00:00:00]" c="2026-07-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-05T00:00:00]" c="2026-07-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-06T00:00:00]" c="2026-07-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-07T00:00:00]" c="2026-07-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-08T00:00:00]" c="2026-07-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-09T00:00:00]" c="2026-07-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-10T00:00:00]" c="2026-07-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-11T00:00:00]" c="2026-07-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-12T00:00:00]" c="2026-07-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-13T00:00:00]" c="2026-07-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-14T00:00:00]" c="2026-07-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-15T00:00:00]" c="2026-07-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-16T00:00:00]" c="2026-07-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-17T00:00:00]" c="2026-07-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-18T00:00:00]" c="2026-07-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-19T00:00:00]" c="2026-07-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-20T00:00:00]" c="2026-07-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-21T00:00:00]" c="2026-07-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-22T00:00:00]" c="2026-07-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-23T00:00:00]" c="2026-07-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-24T00:00:00]" c="2026-07-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-25T00:00:00]" c="2026-07-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-26T00:00:00]" c="2026-07-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-27T00:00:00]" c="2026-07-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-28T00:00:00]" c="2026-07-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-29T00:00:00]" c="2026-07-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-30T00:00:00]" c="2026-07-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-31T00:00:00]" c="2026-07-31"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-01T00:00:00]" c="2026-08-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-02T00:00:00]" c="2026-08-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-03T00:00:00]" c="2026-08-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-04T00:00:00]" c="2026-08-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-05T00:00:00]" c="2026-08-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-06T00:00:00]" c="2026-08-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-07T00:00:00]" c="2026-08-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-08T00:00:00]" c="2026-08-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-09T00:00:00]" c="2026-08-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-10T00:00:00]" c="2026-08-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-11T00:00:00]" c="2026-08-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-12T00:00:00]" c="2026-08-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-13T00:00:00]" c="2026-08-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-14T00:00:00]" c="2026-08-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-15T00:00:00]" c="2026-08-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-16T00:00:00]" c="2026-08-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-17T00:00:00]" c="2026-08-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-18T00:00:00]" c="2026-08-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-19T00:00:00]" c="2026-08-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-20T00:00:00]" c="2026-08-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-21T00:00:00]" c="2026-08-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-22T00:00:00]" c="2026-08-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-23T00:00:00]" c="2026-08-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-24T00:00:00]" c="2026-08-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-25T00:00:00]" c="2026-08-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-26T00:00:00]" c="2026-08-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-27T00:00:00]" c="2026-08-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-28T00:00:00]" c="2026-08-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-29T00:00:00]" c="2026-08-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-30T00:00:00]" c="2026-08-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-31T00:00:00]" c="2026-08-31"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-01T00:00:00]" c="2026-09-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-02T00:00:00]" c="2026-09-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-03T00:00:00]" c="2026-09-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-04T00:00:00]" c="2026-09-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-05T00:00:00]" c="2026-09-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-06T00:00:00]" c="2026-09-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-07T00:00:00]" c="2026-09-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-08T00:00:00]" c="2026-09-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-09T00:00:00]" c="2026-09-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-10T00:00:00]" c="2026-09-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-11T00:00:00]" c="2026-09-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-12T00:00:00]" c="2026-09-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-13T00:00:00]" c="2026-09-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-14T00:00:00]" c="2026-09-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-15T00:00:00]" c="2026-09-15"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
+      <sharedItems count="14">
+        <s v="[Entidades].[Sigla].&amp;[BCR]" c="BCR"/>
+        <s v="[Entidades].[Sigla].&amp;[BEC]" c="BEC"/>
+        <s v="[Entidades].[Sigla].&amp;[BFO]" c="BFO"/>
+        <s v="[Entidades].[Sigla].&amp;[BGA]" c="BGA"/>
+        <s v="[Entidades].[Sigla].&amp;[BIE]" c="BIE"/>
+        <s v="[Entidades].[Sigla].&amp;[BIS]" c="BIS"/>
+        <s v="[Entidades].[Sigla].&amp;[BME]" c="BME"/>
+        <s v="[Entidades].[Sigla].&amp;[BNA]" c="BNA"/>
+        <s v="[Entidades].[Sigla].&amp;[BNB]" c="BNB"/>
+        <s v="[Entidades].[Sigla].&amp;[BPR]" c="BPR"/>
+        <s v="[Entidades].[Sigla].&amp;[BSO]" c="BSO"/>
+        <s v="[Entidades].[Sigla].&amp;[BUN]" c="BUN"/>
+        <s v="[Entidades].[Sigla].&amp;[PCO]" c="PCO"/>
+        <s v="[Entidades].[Sigla].&amp;[PEF]" c="PEF"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" numFmtId="0" hierarchy="26" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="29">
+    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Categoria]" caption="Cod Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Categoria].[All]" allUniqueName="[Actividad Economica].[Cod Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Sector Actividad]" caption="Cod Sector Actividad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" allUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion].[All]" allUniqueName="[Actividad Economica].[Descripcion].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion Categoria]" caption="Descripcion Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" allUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Concepto].[Cod Concepto]" caption="Cod Concepto" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Concepto].[Cod Concepto].[All]" allUniqueName="[Concepto].[Cod Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Concepto].[Concepto]" caption="Concepto" attribute="1" defaultMemberUniqueName="[Concepto].[Concepto].[All]" allUniqueName="[Concepto].[Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Entidades].[Cod Entidad]" caption="Cod Entidad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Entidades].[Cod Entidad].[All]" allUniqueName="[Entidades].[Cod Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Entidades].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Entidades].[Nombre].[All]" allUniqueName="[Entidades].[Nombre].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Entidades].[Sigla]" caption="Sigla" attribute="1" defaultMemberUniqueName="[Entidades].[Sigla].[All]" allUniqueName="[Entidades].[Sigla].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="7"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Entidades].[Tipo Entidad]" caption="Tipo Entidad" attribute="1" defaultMemberUniqueName="[Entidades].[Tipo Entidad].[All]" allUniqueName="[Entidades].[Tipo Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Estrato].[Cod Estrato]" caption="Cod Estrato" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Estrato].[Cod Estrato].[All]" allUniqueName="[Estrato].[Cod Estrato].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Estrato].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Estrato].[Descripcion].[All]" allUniqueName="[Estrato].[Descripcion].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Moneda Cambio].[Cod Moneda]" caption="Cod Moneda" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Moneda Cambio].[Cod Moneda].[All]" allUniqueName="[Moneda Cambio].[Cod Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Moneda Cambio].[Moneda]" caption="Moneda" attribute="1" defaultMemberUniqueName="[Moneda Cambio].[Moneda].[All]" allUniqueName="[Moneda Cambio].[Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Monto Menor].[Cod Monto Menor]" caption="Cod Monto Menor" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Monto Menor].[Cod Monto Menor].[All]" allUniqueName="[Monto Menor].[Cod Monto Menor].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Monto Menor].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Monto Menor].[Descripcion].[All]" allUniqueName="[Monto Menor].[Descripcion].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="5"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Subsistema].[Cod Subsistema]" caption="Cod Subsistema" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Subsistema].[Cod Subsistema].[All]" allUniqueName="[Subsistema].[Cod Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Subsistema].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Subsistema].[Nombre].[All]" allUniqueName="[Subsistema].[Nombre].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Subsistema].[Sigla Subsistema]" caption="Sigla Subsistema" attribute="1" defaultMemberUniqueName="[Subsistema].[Sigla Subsistema].[All]" allUniqueName="[Subsistema].[Sigla Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha]" caption="Cod Fecha" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Fecha]" caption="Fecha" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="6"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes]" caption="Ultimo Dia Mes" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transaccion].[Cod Transaccion]" caption="Cod Transaccion" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Transaccion].[Cod Transaccion].[All]" allUniqueName="[Transaccion].[Cod Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transaccion].[Transaccion]" caption="Transaccion" attribute="1" defaultMemberUniqueName="[Transaccion].[Transaccion].[All]" allUniqueName="[Transaccion].[Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Monto Usd]" caption="Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Usd]" caption="Tipo Cambio Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="8"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Mm Usd]" caption="Tipo Cambio Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Numero Operaciones]" caption="Numero Operaciones" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="10">
+    <dimension name="Actividad Economica" uniqueName="[Actividad Economica]" caption="Actividad Economica"/>
+    <dimension name="Concepto" uniqueName="[Concepto]" caption="Concepto"/>
+    <dimension name="Entidades" uniqueName="[Entidades]" caption="Entidades"/>
+    <dimension name="Estrato" uniqueName="[Estrato]" caption="Estrato"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Moneda Cambio" uniqueName="[Moneda Cambio]" caption="Moneda Cambio"/>
+    <dimension name="Monto Menor" uniqueName="[Monto Menor]" caption="Monto Menor"/>
+    <dimension name="Subsistema" uniqueName="[Subsistema]" caption="Subsistema"/>
+    <dimension name="Tipo Cambio Fecha Dia" uniqueName="[Tipo Cambio Fecha Dia]" caption="Tipo Cambio Fecha Dia"/>
+    <dimension name="Transaccion" uniqueName="[Transaccion]" caption="Transaccion"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Operaciones Cambiarias" caption="Fact Operaciones Cambiarias"/>
+  </measureGroups>
+  <maps count="9">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+    <map measureGroup="0" dimension="8"/>
+    <map measureGroup="0" dimension="9"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46282.510572569445" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{9ECE6D2C-0019-46A8-93F5-B57014A573FD}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="9">
+    <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
+      <sharedItems count="2">
+        <s v="[Transaccion].[Transaccion].&amp;[Compra]" c="Compra"/>
+        <s v="[Transaccion].[Transaccion].&amp;[Venta]" c="Venta"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda]" caption="Cod Moneda" numFmtId="0" hierarchy="12" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda].[Moneda]" caption="Moneda" propertyName="Moneda" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Monto Menor].[Descripcion].[Descripcion]" caption="Descripcion" numFmtId="0" hierarchy="15" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
+      <sharedItems count="107">
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-04T00:00:00]" c="2026-06-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-05T00:00:00]" c="2026-06-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-06T00:00:00]" c="2026-06-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-07T00:00:00]" c="2026-06-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-08T00:00:00]" c="2026-06-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-09T00:00:00]" c="2026-06-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-10T00:00:00]" c="2026-06-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-11T00:00:00]" c="2026-06-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-12T00:00:00]" c="2026-06-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-13T00:00:00]" c="2026-06-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-14T00:00:00]" c="2026-06-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-15T00:00:00]" c="2026-06-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-16T00:00:00]" c="2026-06-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-17T00:00:00]" c="2026-06-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-18T00:00:00]" c="2026-06-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-19T00:00:00]" c="2026-06-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-20T00:00:00]" c="2026-06-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-21T00:00:00]" c="2026-06-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-22T00:00:00]" c="2026-06-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-23T00:00:00]" c="2026-06-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-24T00:00:00]" c="2026-06-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-25T00:00:00]" c="2026-06-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-26T00:00:00]" c="2026-06-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-27T00:00:00]" c="2026-06-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-28T00:00:00]" c="2026-06-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-29T00:00:00]" c="2026-06-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-30T00:00:00]" c="2026-06-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-01T00:00:00]" c="2026-07-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-02T00:00:00]" c="2026-07-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-03T00:00:00]" c="2026-07-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-04T00:00:00]" c="2026-07-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-05T00:00:00]" c="2026-07-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-06T00:00:00]" c="2026-07-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-07T00:00:00]" c="2026-07-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-08T00:00:00]" c="2026-07-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-09T00:00:00]" c="2026-07-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-10T00:00:00]" c="2026-07-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-11T00:00:00]" c="2026-07-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-12T00:00:00]" c="2026-07-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-13T00:00:00]" c="2026-07-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-14T00:00:00]" c="2026-07-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-15T00:00:00]" c="2026-07-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-16T00:00:00]" c="2026-07-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-17T00:00:00]" c="2026-07-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-18T00:00:00]" c="2026-07-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-19T00:00:00]" c="2026-07-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-20T00:00:00]" c="2026-07-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-21T00:00:00]" c="2026-07-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-22T00:00:00]" c="2026-07-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-23T00:00:00]" c="2026-07-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-24T00:00:00]" c="2026-07-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-25T00:00:00]" c="2026-07-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-26T00:00:00]" c="2026-07-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-27T00:00:00]" c="2026-07-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-28T00:00:00]" c="2026-07-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-29T00:00:00]" c="2026-07-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-30T00:00:00]" c="2026-07-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-31T00:00:00]" c="2026-07-31"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-01T00:00:00]" c="2026-08-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-02T00:00:00]" c="2026-08-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-03T00:00:00]" c="2026-08-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-04T00:00:00]" c="2026-08-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-05T00:00:00]" c="2026-08-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-06T00:00:00]" c="2026-08-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-07T00:00:00]" c="2026-08-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-08T00:00:00]" c="2026-08-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-09T00:00:00]" c="2026-08-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-10T00:00:00]" c="2026-08-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-11T00:00:00]" c="2026-08-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-12T00:00:00]" c="2026-08-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-13T00:00:00]" c="2026-08-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-14T00:00:00]" c="2026-08-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-15T00:00:00]" c="2026-08-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-16T00:00:00]" c="2026-08-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-17T00:00:00]" c="2026-08-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-18T00:00:00]" c="2026-08-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-19T00:00:00]" c="2026-08-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-20T00:00:00]" c="2026-08-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-21T00:00:00]" c="2026-08-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-22T00:00:00]" c="2026-08-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-23T00:00:00]" c="2026-08-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-24T00:00:00]" c="2026-08-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-25T00:00:00]" c="2026-08-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-26T00:00:00]" c="2026-08-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-27T00:00:00]" c="2026-08-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-28T00:00:00]" c="2026-08-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-29T00:00:00]" c="2026-08-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-30T00:00:00]" c="2026-08-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-31T00:00:00]" c="2026-08-31"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-01T00:00:00]" c="2026-09-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-02T00:00:00]" c="2026-09-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-03T00:00:00]" c="2026-09-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-04T00:00:00]" c="2026-09-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-05T00:00:00]" c="2026-09-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-06T00:00:00]" c="2026-09-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-07T00:00:00]" c="2026-09-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-08T00:00:00]" c="2026-09-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-09T00:00:00]" c="2026-09-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-10T00:00:00]" c="2026-09-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-11T00:00:00]" c="2026-09-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-12T00:00:00]" c="2026-09-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-13T00:00:00]" c="2026-09-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-14T00:00:00]" c="2026-09-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-15T00:00:00]" c="2026-09-15"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
+      <sharedItems count="14">
+        <s v="[Entidades].[Sigla].&amp;[BCR]" c="BCR"/>
+        <s v="[Entidades].[Sigla].&amp;[BEC]" c="BEC"/>
+        <s v="[Entidades].[Sigla].&amp;[BFO]" c="BFO"/>
+        <s v="[Entidades].[Sigla].&amp;[BGA]" c="BGA"/>
+        <s v="[Entidades].[Sigla].&amp;[BIE]" c="BIE"/>
+        <s v="[Entidades].[Sigla].&amp;[BIS]" c="BIS"/>
+        <s v="[Entidades].[Sigla].&amp;[BME]" c="BME"/>
+        <s v="[Entidades].[Sigla].&amp;[BNA]" c="BNA"/>
+        <s v="[Entidades].[Sigla].&amp;[BNB]" c="BNB"/>
+        <s v="[Entidades].[Sigla].&amp;[BPR]" c="BPR"/>
+        <s v="[Entidades].[Sigla].&amp;[BSO]" c="BSO"/>
+        <s v="[Entidades].[Sigla].&amp;[BUN]" c="BUN"/>
+        <s v="[Entidades].[Sigla].&amp;[PCO]" c="PCO"/>
+        <s v="[Entidades].[Sigla].&amp;[PEF]" c="PEF"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Numero Operaciones]" caption="Numero Operaciones" numFmtId="0" hierarchy="28" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="29">
+    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Categoria]" caption="Cod Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Categoria].[All]" allUniqueName="[Actividad Economica].[Cod Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Sector Actividad]" caption="Cod Sector Actividad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" allUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion].[All]" allUniqueName="[Actividad Economica].[Descripcion].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion Categoria]" caption="Descripcion Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" allUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Concepto].[Cod Concepto]" caption="Cod Concepto" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Concepto].[Cod Concepto].[All]" allUniqueName="[Concepto].[Cod Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Concepto].[Concepto]" caption="Concepto" attribute="1" defaultMemberUniqueName="[Concepto].[Concepto].[All]" allUniqueName="[Concepto].[Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Entidades].[Cod Entidad]" caption="Cod Entidad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Entidades].[Cod Entidad].[All]" allUniqueName="[Entidades].[Cod Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Entidades].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Entidades].[Nombre].[All]" allUniqueName="[Entidades].[Nombre].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Entidades].[Sigla]" caption="Sigla" attribute="1" defaultMemberUniqueName="[Entidades].[Sigla].[All]" allUniqueName="[Entidades].[Sigla].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="7"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Entidades].[Tipo Entidad]" caption="Tipo Entidad" attribute="1" defaultMemberUniqueName="[Entidades].[Tipo Entidad].[All]" allUniqueName="[Entidades].[Tipo Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Estrato].[Cod Estrato]" caption="Cod Estrato" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Estrato].[Cod Estrato].[All]" allUniqueName="[Estrato].[Cod Estrato].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Estrato].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Estrato].[Descripcion].[All]" allUniqueName="[Estrato].[Descripcion].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Moneda Cambio].[Cod Moneda]" caption="Cod Moneda" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Moneda Cambio].[Cod Moneda].[All]" allUniqueName="[Moneda Cambio].[Cod Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Moneda Cambio].[Moneda]" caption="Moneda" attribute="1" defaultMemberUniqueName="[Moneda Cambio].[Moneda].[All]" allUniqueName="[Moneda Cambio].[Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Monto Menor].[Cod Monto Menor]" caption="Cod Monto Menor" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Monto Menor].[Cod Monto Menor].[All]" allUniqueName="[Monto Menor].[Cod Monto Menor].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Monto Menor].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Monto Menor].[Descripcion].[All]" allUniqueName="[Monto Menor].[Descripcion].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="5"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Subsistema].[Cod Subsistema]" caption="Cod Subsistema" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Subsistema].[Cod Subsistema].[All]" allUniqueName="[Subsistema].[Cod Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Subsistema].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Subsistema].[Nombre].[All]" allUniqueName="[Subsistema].[Nombre].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Subsistema].[Sigla Subsistema]" caption="Sigla Subsistema" attribute="1" defaultMemberUniqueName="[Subsistema].[Sigla Subsistema].[All]" allUniqueName="[Subsistema].[Sigla Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha]" caption="Cod Fecha" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Fecha]" caption="Fecha" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="6"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes]" caption="Ultimo Dia Mes" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transaccion].[Cod Transaccion]" caption="Cod Transaccion" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Transaccion].[Cod Transaccion].[All]" allUniqueName="[Transaccion].[Cod Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transaccion].[Transaccion]" caption="Transaccion" attribute="1" defaultMemberUniqueName="[Transaccion].[Transaccion].[All]" allUniqueName="[Transaccion].[Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Monto Usd]" caption="Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Usd]" caption="Tipo Cambio Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Mm Usd]" caption="Tipo Cambio Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Numero Operaciones]" caption="Numero Operaciones" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="8"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="10">
+    <dimension name="Actividad Economica" uniqueName="[Actividad Economica]" caption="Actividad Economica"/>
+    <dimension name="Concepto" uniqueName="[Concepto]" caption="Concepto"/>
+    <dimension name="Entidades" uniqueName="[Entidades]" caption="Entidades"/>
+    <dimension name="Estrato" uniqueName="[Estrato]" caption="Estrato"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Moneda Cambio" uniqueName="[Moneda Cambio]" caption="Moneda Cambio"/>
+    <dimension name="Monto Menor" uniqueName="[Monto Menor]" caption="Monto Menor"/>
+    <dimension name="Subsistema" uniqueName="[Subsistema]" caption="Subsistema"/>
+    <dimension name="Tipo Cambio Fecha Dia" uniqueName="[Tipo Cambio Fecha Dia]" caption="Tipo Cambio Fecha Dia"/>
+    <dimension name="Transaccion" uniqueName="[Transaccion]" caption="Transaccion"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Operaciones Cambiarias" caption="Fact Operaciones Cambiarias"/>
+  </measureGroups>
+  <maps count="9">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+    <map measureGroup="0" dimension="8"/>
+    <map measureGroup="0" dimension="9"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C1A180-7D44-4F02-A61C-919F70C27D4D}" name="TablaDinámica1" cacheId="11" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
-  <location ref="A7:Q208" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="5" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C1A180-7D44-4F02-A61C-919F70C27D4D}" name="TablaDinámica1" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+  <location ref="A7:Q222" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="5" colPageCount="1"/>
   <pivotFields count="10">
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
@@ -1333,7 +1375,7 @@
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="100">
+      <items count="107">
         <item s="1" x="0"/>
         <item s="1" x="1"/>
         <item s="1" x="2"/>
@@ -1434,6 +1476,13 @@
         <item s="1" x="97"/>
         <item s="1" x="98"/>
         <item s="1" x="99"/>
+        <item s="1" x="100"/>
+        <item s="1" x="101"/>
+        <item s="1" x="102"/>
+        <item s="1" x="103"/>
+        <item s="1" x="104"/>
+        <item s="1" x="105"/>
+        <item s="1" x="106"/>
       </items>
     </pivotField>
     <pivotField axis="axisCol" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -1461,7 +1510,7 @@
     <field x="6"/>
     <field x="-2"/>
   </rowFields>
-  <rowItems count="200">
+  <rowItems count="214">
     <i>
       <x/>
       <x/>
@@ -2157,6 +2206,55 @@
     </i>
     <i>
       <x v="99"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="100"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="101"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="102"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="103"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="104"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="105"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="106"/>
       <x/>
     </i>
     <i r="1" i="1">
@@ -2257,7 +2355,118 @@
     </pivotHierarchy>
     <pivotHierarchy/>
     <pivotHierarchy/>
-    <pivotHierarchy/>
+    <pivotHierarchy>
+      <members count="108" level="1">
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name=""/>
+        <member name="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-16T00:00:00]"/>
+      </members>
+    </pivotHierarchy>
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy multipleItemSelectionAllowed="1">
@@ -2292,7 +2501,7 @@
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{971AADEF-3DB3-4761-B43F-E1EDE0CC9CC9}" name="TablaDinámica2" cacheId="8" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
-  <location ref="A7:AE109" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
+  <location ref="A7:AE116" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
       <items count="1">
@@ -2323,7 +2532,7 @@
       </items>
     </pivotField>
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="101">
+      <items count="108">
         <item s="1" x="0"/>
         <item s="1" x="1"/>
         <item s="1" x="2"/>
@@ -2424,6 +2633,13 @@
         <item s="1" x="97"/>
         <item s="1" x="98"/>
         <item s="1" x="99"/>
+        <item s="1" x="100"/>
+        <item s="1" x="101"/>
+        <item s="1" x="102"/>
+        <item s="1" x="103"/>
+        <item s="1" x="104"/>
+        <item s="1" x="105"/>
+        <item s="1" x="106"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2451,7 +2667,7 @@
   <rowFields count="1">
     <field x="6"/>
   </rowFields>
-  <rowItems count="100">
+  <rowItems count="107">
     <i>
       <x/>
     </i>
@@ -2751,6 +2967,27 @@
     </i>
     <i>
       <x v="99"/>
+    </i>
+    <i>
+      <x v="100"/>
+    </i>
+    <i>
+      <x v="101"/>
+    </i>
+    <i>
+      <x v="102"/>
+    </i>
+    <i>
+      <x v="103"/>
+    </i>
+    <i>
+      <x v="104"/>
+    </i>
+    <i>
+      <x v="105"/>
+    </i>
+    <i>
+      <x v="106"/>
     </i>
   </rowItems>
   <colFields count="2">
@@ -2923,8 +3160,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80A53070-3740-4285-A7AE-6612867028BD}" name="TablaDinámica3" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
-  <location ref="A7:AE109" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80A53070-3740-4285-A7AE-6612867028BD}" name="TablaDinámica3" cacheId="11" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
+  <location ref="A7:AE116" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
       <items count="1">
@@ -2955,7 +3192,7 @@
       </items>
     </pivotField>
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="101">
+      <items count="108">
         <item s="1" x="0"/>
         <item s="1" x="1"/>
         <item s="1" x="2"/>
@@ -3056,6 +3293,13 @@
         <item s="1" x="97"/>
         <item s="1" x="98"/>
         <item s="1" x="99"/>
+        <item s="1" x="100"/>
+        <item s="1" x="101"/>
+        <item s="1" x="102"/>
+        <item s="1" x="103"/>
+        <item s="1" x="104"/>
+        <item s="1" x="105"/>
+        <item s="1" x="106"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3083,7 +3327,7 @@
   <rowFields count="1">
     <field x="6"/>
   </rowFields>
-  <rowItems count="100">
+  <rowItems count="107">
     <i>
       <x/>
     </i>
@@ -3383,6 +3627,27 @@
     </i>
     <i>
       <x v="99"/>
+    </i>
+    <i>
+      <x v="100"/>
+    </i>
+    <i>
+      <x v="101"/>
+    </i>
+    <i>
+      <x v="102"/>
+    </i>
+    <i>
+      <x v="103"/>
+    </i>
+    <i>
+      <x v="104"/>
+    </i>
+    <i>
+      <x v="105"/>
+    </i>
+    <i>
+      <x v="106"/>
     </i>
   </rowItems>
   <colFields count="2">
@@ -3851,7 +4116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3F3DA76-2715-4C5C-9BC9-0D27B1FEBC80}">
-  <dimension ref="A1:Q208"/>
+  <dimension ref="A1:Q222"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
@@ -5795,7 +6060,7 @@
         <v>0.40010068000000004</v>
       </c>
       <c r="Q45" s="2">
-        <v>25.032258476300001</v>
+        <v>25.032258476300004</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -13055,10 +13320,10 @@
         <v>94</v>
       </c>
       <c r="C193" s="2">
-        <v>10.541265099399999</v>
+        <v>10.5412650994</v>
       </c>
       <c r="D193" s="2">
-        <v>1.5404671898</v>
+        <v>1.5404671898000002</v>
       </c>
       <c r="E193" s="2">
         <v>0.30973334990000001</v>
@@ -13070,25 +13335,25 @@
         <v>1.52429345</v>
       </c>
       <c r="H193" s="2">
-        <v>7.0495516189999989</v>
+        <v>7.049551618999998</v>
       </c>
       <c r="I193" s="2">
-        <v>8.1942503297999991</v>
+        <v>8.1942503297999973</v>
       </c>
       <c r="J193" s="2">
         <v>2.5951819899999999E-2</v>
       </c>
       <c r="K193" s="2">
-        <v>6.4725927187000005</v>
+        <v>6.4725927186999996</v>
       </c>
       <c r="L193" s="2">
         <v>2.0430669899999997E-2</v>
       </c>
       <c r="M193" s="2">
-        <v>2.0410046297999997</v>
+        <v>2.0410046298000002</v>
       </c>
       <c r="N193" s="2">
-        <v>0.80778228969999999</v>
+        <v>0.80778228969999988</v>
       </c>
       <c r="O193" s="2">
         <v>1.8677698999999999E-3</v>
@@ -13097,7 +13362,7 @@
         <v>0.15001043999999999</v>
       </c>
       <c r="Q193" s="2">
-        <v>49.356058984300006</v>
+        <v>49.356058984300013</v>
       </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
@@ -13105,7 +13370,7 @@
         <v>95</v>
       </c>
       <c r="C194" s="2">
-        <v>130.04404527920002</v>
+        <v>130.04404527919999</v>
       </c>
       <c r="D194" s="2">
         <v>18.855870707200001</v>
@@ -13114,7 +13379,7 @@
         <v>3.7445659802</v>
       </c>
       <c r="F194" s="2">
-        <v>129.79106454269996</v>
+        <v>129.79106454269998</v>
       </c>
       <c r="G194" s="2">
         <v>18.888172073899998</v>
@@ -13129,13 +13394,13 @@
         <v>0.31063251219999999</v>
       </c>
       <c r="K194" s="2">
-        <v>78.904366968699989</v>
+        <v>78.904366968700018</v>
       </c>
       <c r="L194" s="2">
-        <v>0.24149051930000001</v>
+        <v>0.24149051929999998</v>
       </c>
       <c r="M194" s="2">
-        <v>25.213606268599996</v>
+        <v>25.213606268600003</v>
       </c>
       <c r="N194" s="2">
         <v>10.081866637300001</v>
@@ -13147,7 +13412,7 @@
         <v>1.7431223568000001</v>
       </c>
       <c r="Q194" s="2">
-        <v>605.37609793799993</v>
+        <v>605.37609793800004</v>
       </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
@@ -13158,19 +13423,19 @@
         <v>94</v>
       </c>
       <c r="C195" s="2">
-        <v>2.2410354895000006</v>
+        <v>2.2410354895000002</v>
       </c>
       <c r="D195" s="2">
         <v>4.321877409799999</v>
       </c>
       <c r="E195" s="2">
-        <v>1.7164667598000001</v>
+        <v>1.7164667597999999</v>
       </c>
       <c r="F195" s="2">
         <v>6.1768947684000004</v>
       </c>
       <c r="G195" s="2">
-        <v>3.5403004299000003</v>
+        <v>3.5403004298999998</v>
       </c>
       <c r="H195" s="2">
         <v>28.744438628800001</v>
@@ -13182,13 +13447,13 @@
         <v>6.0730200000000002E-3</v>
       </c>
       <c r="K195" s="2">
-        <v>2.0242601281000008</v>
+        <v>2.0242601280999994</v>
       </c>
       <c r="L195" s="2">
         <v>2.0808800000000002E-3</v>
       </c>
       <c r="M195" s="2">
-        <v>5.5570111197000003</v>
+        <v>5.5570111197000012</v>
       </c>
       <c r="N195" s="2">
         <v>0.24435603989999999</v>
@@ -13200,7 +13465,7 @@
         <v>0.50007542999999999</v>
       </c>
       <c r="Q195" s="2">
-        <v>59.084914313600017</v>
+        <v>59.084914313600009</v>
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
@@ -13208,7 +13473,7 @@
         <v>95</v>
       </c>
       <c r="C196" s="2">
-        <v>27.552192622999996</v>
+        <v>27.552192623</v>
       </c>
       <c r="D196" s="2">
         <v>53.643417894800002</v>
@@ -13220,13 +13485,13 @@
         <v>75.871407173300014</v>
       </c>
       <c r="G196" s="2">
-        <v>44.058783275700002</v>
+        <v>44.058783275700009</v>
       </c>
       <c r="H196" s="2">
         <v>352.61151364479997</v>
       </c>
       <c r="I196" s="2">
-        <v>49.208738769100002</v>
+        <v>49.208738769099995</v>
       </c>
       <c r="J196" s="2">
         <v>7.2633319099999996E-2</v>
@@ -13238,7 +13503,7 @@
         <v>2.4887324799999999E-2</v>
       </c>
       <c r="M196" s="2">
-        <v>69.033919864900028</v>
+        <v>69.0339198649</v>
       </c>
       <c r="N196" s="2">
         <v>2.9952346882000001</v>
@@ -13261,19 +13526,19 @@
         <v>94</v>
       </c>
       <c r="C197" s="2">
-        <v>4.227290299399999</v>
+        <v>4.2272902993999999</v>
       </c>
       <c r="D197" s="2">
-        <v>0.55025838989999998</v>
+        <v>0.55025838990000009</v>
       </c>
       <c r="E197" s="2">
-        <v>0.16759871990000003</v>
+        <v>0.1675987199</v>
       </c>
       <c r="F197" s="2">
-        <v>9.5613452585000012</v>
+        <v>9.5613452584999994</v>
       </c>
       <c r="G197" s="2">
-        <v>1.32292995</v>
+        <v>1.3229299500000002</v>
       </c>
       <c r="H197" s="2">
         <v>9.6362721188999991</v>
@@ -13288,10 +13553,10 @@
         <v>4.2512866591000007</v>
       </c>
       <c r="L197" s="2">
-        <v>1.1868579899999999E-2</v>
+        <v>1.1868579900000001E-2</v>
       </c>
       <c r="M197" s="2">
-        <v>3.0043624296</v>
+        <v>3.0043624296000004</v>
       </c>
       <c r="N197" s="2">
         <v>4.4385997999999999E-3</v>
@@ -13317,10 +13582,10 @@
         <v>6.8732329237000007</v>
       </c>
       <c r="E198" s="2">
-        <v>2.0419253160999999</v>
+        <v>2.0419253161000004</v>
       </c>
       <c r="F198" s="2">
-        <v>118.95602852180001</v>
+        <v>118.95602852179999</v>
       </c>
       <c r="G198" s="2">
         <v>16.6178044615</v>
@@ -13335,13 +13600,13 @@
         <v>0.5664975619</v>
       </c>
       <c r="K198" s="2">
-        <v>52.611228614500028</v>
+        <v>52.611228614500021</v>
       </c>
       <c r="L198" s="2">
         <v>0.1426603313</v>
       </c>
       <c r="M198" s="2">
-        <v>37.769139148799994</v>
+        <v>37.769139148799987</v>
       </c>
       <c r="N198" s="2">
         <v>4.66052998E-2</v>
@@ -13353,7 +13618,7 @@
         <v>2.51511E-5</v>
       </c>
       <c r="Q198" s="2">
-        <v>439.7069391114</v>
+        <v>439.70693911139989</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
@@ -13367,44 +13632,44 @@
         <v>4.5686707090000001</v>
       </c>
       <c r="D199" s="2">
-        <v>4.0573789996999992</v>
+        <v>4.0573789997</v>
       </c>
       <c r="E199" s="2">
         <v>0.8197688098</v>
       </c>
       <c r="F199" s="2">
-        <v>21.622486007899997</v>
+        <v>21.622486007900001</v>
       </c>
       <c r="G199" s="2">
-        <v>1.5932660199999999</v>
+        <v>1.5932660199999997</v>
       </c>
       <c r="H199" s="2">
         <v>9.5712881088999993</v>
       </c>
       <c r="I199" s="2">
-        <v>10.460837409400003</v>
+        <v>11.750750289799997</v>
       </c>
       <c r="J199" s="2">
         <v>0.2543552</v>
       </c>
       <c r="K199" s="2">
-        <v>5.8530080087000007</v>
+        <v>5.8530080087000016</v>
       </c>
       <c r="L199" s="2">
         <v>1.9358249899999999E-2</v>
       </c>
       <c r="M199" s="2">
-        <v>0.81909734990000005</v>
+        <v>0.81909734989999994</v>
       </c>
       <c r="N199" s="2">
-        <v>3.4659929899999997E-2</v>
+        <v>3.4659929900000004E-2</v>
       </c>
       <c r="O199" s="2">
         <v>5.0299999999999997E-3</v>
       </c>
       <c r="P199" s="2"/>
       <c r="Q199" s="2">
-        <v>59.679204803100006</v>
+        <v>60.969117683500002</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
@@ -13415,22 +13680,22 @@
         <v>57.365538394000005</v>
       </c>
       <c r="D200" s="2">
-        <v>51.081473910599996</v>
+        <v>51.081473910600003</v>
       </c>
       <c r="E200" s="2">
         <v>10.3597431935</v>
       </c>
       <c r="F200" s="2">
-        <v>272.68226681180005</v>
+        <v>272.68226681179999</v>
       </c>
       <c r="G200" s="2">
         <v>20.103040236399998</v>
       </c>
       <c r="H200" s="2">
-        <v>119.87848262189998</v>
+        <v>119.87848262189999</v>
       </c>
       <c r="I200" s="2">
-        <v>131.71087901530004</v>
+        <v>147.77237513130001</v>
       </c>
       <c r="J200" s="2">
         <v>3.1123956798999997</v>
@@ -13442,7 +13707,7 @@
         <v>0.23520273749999998</v>
       </c>
       <c r="M200" s="2">
-        <v>10.322535413900001</v>
+        <v>10.322535413899999</v>
       </c>
       <c r="N200" s="2">
         <v>0.39927616469999999</v>
@@ -13452,7 +13717,7 @@
       </c>
       <c r="P200" s="2"/>
       <c r="Q200" s="2">
-        <v>750.16362515000026</v>
+        <v>766.2251212660002</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
@@ -13485,7 +13750,7 @@
       </c>
       <c r="J201" s="2"/>
       <c r="K201" s="2">
-        <v>1.1298302283999999</v>
+        <v>1.1298302284000001</v>
       </c>
       <c r="L201" s="2">
         <v>3.04916E-3</v>
@@ -13494,7 +13759,7 @@
         <v>5.7993298E-3</v>
       </c>
       <c r="N201" s="2">
-        <v>9.9220596999999994E-3</v>
+        <v>9.9220597000000011E-3</v>
       </c>
       <c r="O201" s="2">
         <v>2.5593699E-3</v>
@@ -13503,7 +13768,7 @@
         <v>1.95E-6</v>
       </c>
       <c r="Q201" s="2">
-        <v>4.4932006753999998</v>
+        <v>4.4932006754000007</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
@@ -13511,7 +13776,7 @@
         <v>95</v>
       </c>
       <c r="C202" s="2">
-        <v>2.8167657693000003</v>
+        <v>2.8167657692999999</v>
       </c>
       <c r="D202" s="2">
         <v>0.23825112999999998</v>
@@ -13523,7 +13788,7 @@
         <v>29.300189705000005</v>
       </c>
       <c r="G202" s="2">
-        <v>7.6423216949000006</v>
+        <v>7.6423216948999997</v>
       </c>
       <c r="H202" s="2">
         <v>1.1348633928999998</v>
@@ -13533,7 +13798,7 @@
       </c>
       <c r="J202" s="2"/>
       <c r="K202" s="2">
-        <v>14.213264292099993</v>
+        <v>14.213264292099998</v>
       </c>
       <c r="L202" s="2">
         <v>3.7443684800000002E-2</v>
@@ -13542,7 +13807,7 @@
         <v>7.1505738900000004E-2</v>
       </c>
       <c r="N202" s="2">
-        <v>0.11211927790000001</v>
+        <v>0.11211927789999999</v>
       </c>
       <c r="O202" s="2">
         <v>3.1173126600000003E-2</v>
@@ -13551,7 +13816,7 @@
         <v>2.3751E-5</v>
       </c>
       <c r="Q202" s="2">
-        <v>56.213710155000001</v>
+        <v>56.213710155000015</v>
       </c>
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.25">
@@ -13584,7 +13849,7 @@
       </c>
       <c r="J203" s="2"/>
       <c r="K203" s="2">
-        <v>0.1493028096</v>
+        <v>0.14930280960000006</v>
       </c>
       <c r="L203" s="2"/>
       <c r="M203" s="2">
@@ -13621,7 +13886,7 @@
         <v>5.0319990000000005E-4</v>
       </c>
       <c r="H204" s="2">
-        <v>0.33729674100000001</v>
+        <v>0.33729674099999996</v>
       </c>
       <c r="I204" s="2">
         <v>0.1217957544</v>
@@ -13653,22 +13918,22 @@
         <v>94</v>
       </c>
       <c r="C205" s="2">
-        <v>2.5096564793000002</v>
+        <v>2.5096564792999998</v>
       </c>
       <c r="D205" s="2">
-        <v>0.38593560000000005</v>
+        <v>0.38593559999999999</v>
       </c>
       <c r="E205" s="2">
-        <v>7.6094269899999997E-2</v>
+        <v>7.6094269899999983E-2</v>
       </c>
       <c r="F205" s="2">
-        <v>4.6978368786000004</v>
+        <v>4.6978368785999995</v>
       </c>
       <c r="G205" s="2">
         <v>0.89445370989999995</v>
       </c>
       <c r="H205" s="2">
-        <v>2.0722231493000001</v>
+        <v>2.0722231492999996</v>
       </c>
       <c r="I205" s="2">
         <v>4.3039844189000007</v>
@@ -13677,7 +13942,7 @@
         <v>2.6595699E-3</v>
       </c>
       <c r="K205" s="2">
-        <v>4.7299834682000004</v>
+        <v>4.7299834682000022</v>
       </c>
       <c r="L205" s="2">
         <v>1.55873299E-2</v>
@@ -13695,7 +13960,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="Q205" s="2">
-        <v>20.096849593700004</v>
+        <v>20.0968495937</v>
       </c>
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
@@ -13712,7 +13977,7 @@
         <v>0.95982038030000005</v>
       </c>
       <c r="F206" s="2">
-        <v>58.732927618199994</v>
+        <v>58.732927618200009</v>
       </c>
       <c r="G206" s="2">
         <v>11.256426151500001</v>
@@ -13721,13 +13986,13 @@
         <v>26.077108946800003</v>
       </c>
       <c r="I206" s="2">
-        <v>54.582125338899999</v>
+        <v>54.582125338899985</v>
       </c>
       <c r="J206" s="2">
         <v>3.2659519499999998E-2</v>
       </c>
       <c r="K206" s="2">
-        <v>59.396223827299991</v>
+        <v>59.396223827299977</v>
       </c>
       <c r="L206" s="2">
         <v>0.1914124123</v>
@@ -13745,7 +14010,7 @@
         <v>1.218E-5</v>
       </c>
       <c r="Q206" s="2">
-        <v>252.97496640249994</v>
+        <v>252.97496640249997</v>
       </c>
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
@@ -13756,7 +14021,7 @@
         <v>94</v>
       </c>
       <c r="C207" s="2">
-        <v>2.8633718292999992</v>
+        <v>2.8633718292999997</v>
       </c>
       <c r="D207" s="2">
         <v>0.67271874990000002</v>
@@ -13768,22 +14033,22 @@
         <v>12.2575770487</v>
       </c>
       <c r="G207" s="2">
-        <v>1.44202221</v>
+        <v>1.4420222100000002</v>
       </c>
       <c r="H207" s="2">
-        <v>13.599364889000002</v>
+        <v>13.599364889</v>
       </c>
       <c r="I207" s="2">
-        <v>5.8482524195000014</v>
+        <v>5.8482524195000005</v>
       </c>
       <c r="J207" s="2">
         <v>8.294195E-2</v>
       </c>
       <c r="K207" s="2">
-        <v>5.5395596579000008</v>
+        <v>5.5395596578999999</v>
       </c>
       <c r="L207" s="2">
-        <v>2.0981879900000003E-2</v>
+        <v>2.09818799E-2</v>
       </c>
       <c r="M207" s="2">
         <v>3.2933772699000001</v>
@@ -13796,7 +14061,7 @@
       </c>
       <c r="P207" s="2"/>
       <c r="Q207" s="2">
-        <v>50.902238913799991</v>
+        <v>50.902238913799998</v>
       </c>
     </row>
     <row r="208" spans="1:17" x14ac:dyDescent="0.25">
@@ -13804,7 +14069,7 @@
         <v>95</v>
       </c>
       <c r="C208" s="2">
-        <v>36.121187653700005</v>
+        <v>36.121187653699991</v>
       </c>
       <c r="D208" s="2">
         <v>8.4399284267999999</v>
@@ -13813,7 +14078,7 @@
         <v>7.0457036629999994</v>
       </c>
       <c r="F208" s="2">
-        <v>155.37985363440001</v>
+        <v>155.37985363440006</v>
       </c>
       <c r="G208" s="2">
         <v>18.178178570699998</v>
@@ -13822,13 +14087,13 @@
         <v>171.52395385080001</v>
       </c>
       <c r="I208" s="2">
-        <v>73.470754567499981</v>
+        <v>73.470754567500009</v>
       </c>
       <c r="J208" s="2">
         <v>1.0330359849999999</v>
       </c>
       <c r="K208" s="2">
-        <v>69.593592681899963</v>
+        <v>69.593592681900006</v>
       </c>
       <c r="L208" s="2">
         <v>0.25807712399999999</v>
@@ -13837,14 +14102,699 @@
         <v>41.795572938100001</v>
       </c>
       <c r="N208" s="2">
-        <v>59.15849231659999</v>
+        <v>59.158492316600004</v>
       </c>
       <c r="O208" s="2">
         <v>0.9446406437999999</v>
       </c>
       <c r="P208" s="2"/>
       <c r="Q208" s="2">
-        <v>642.94297205629982</v>
+        <v>642.94297205630005</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>133</v>
+      </c>
+      <c r="B209" t="s">
+        <v>94</v>
+      </c>
+      <c r="C209" s="2">
+        <v>5.8705452693</v>
+      </c>
+      <c r="D209" s="2">
+        <v>1.2450495999000002</v>
+      </c>
+      <c r="E209" s="2">
+        <v>2.3746740098999997</v>
+      </c>
+      <c r="F209" s="2">
+        <v>18.101094888000006</v>
+      </c>
+      <c r="G209" s="2">
+        <v>2.7011731796</v>
+      </c>
+      <c r="H209" s="2">
+        <v>28.055478878599995</v>
+      </c>
+      <c r="I209" s="2">
+        <v>10.904366849800001</v>
+      </c>
+      <c r="J209" s="2">
+        <v>5.6418119900000001E-2</v>
+      </c>
+      <c r="K209" s="2">
+        <v>4.988294688299999</v>
+      </c>
+      <c r="L209" s="2">
+        <v>8.8044989900000009E-2</v>
+      </c>
+      <c r="M209" s="2">
+        <v>3.8952739898999997</v>
+      </c>
+      <c r="N209" s="2">
+        <v>10.2664836099</v>
+      </c>
+      <c r="O209" s="2">
+        <v>1.64502799E-2</v>
+      </c>
+      <c r="P209" s="2">
+        <v>0.28201194989999995</v>
+      </c>
+      <c r="Q209" s="2">
+        <v>88.845360302799989</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B210" t="s">
+        <v>95</v>
+      </c>
+      <c r="C210" s="2">
+        <v>72.274457498000004</v>
+      </c>
+      <c r="D210" s="2">
+        <v>15.448586199900001</v>
+      </c>
+      <c r="E210" s="2">
+        <v>29.850276077499998</v>
+      </c>
+      <c r="F210" s="2">
+        <v>225.21602601589996</v>
+      </c>
+      <c r="G210" s="2">
+        <v>34.104328908799999</v>
+      </c>
+      <c r="H210" s="2">
+        <v>347.52194972910002</v>
+      </c>
+      <c r="I210" s="2">
+        <v>134.6418090521</v>
+      </c>
+      <c r="J210" s="2">
+        <v>0.69619958430000006</v>
+      </c>
+      <c r="K210" s="2">
+        <v>62.467125090900005</v>
+      </c>
+      <c r="L210" s="2">
+        <v>1.0864751765999998</v>
+      </c>
+      <c r="M210" s="2">
+        <v>47.680418272200001</v>
+      </c>
+      <c r="N210" s="2">
+        <v>130.74705869299999</v>
+      </c>
+      <c r="O210" s="2">
+        <v>0.20135142720000002</v>
+      </c>
+      <c r="P210" s="2">
+        <v>3.5561662680000001</v>
+      </c>
+      <c r="Q210" s="2">
+        <v>1105.4922279935001</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>134</v>
+      </c>
+      <c r="B211" t="s">
+        <v>94</v>
+      </c>
+      <c r="C211" s="2">
+        <v>1.1333617697</v>
+      </c>
+      <c r="D211" s="2">
+        <v>0.89631024999999998</v>
+      </c>
+      <c r="E211" s="2">
+        <v>0.31111789000000001</v>
+      </c>
+      <c r="F211" s="2">
+        <v>7.4121021276999999</v>
+      </c>
+      <c r="G211" s="2">
+        <v>5.0692466798</v>
+      </c>
+      <c r="H211" s="2">
+        <v>10.0619224887</v>
+      </c>
+      <c r="I211" s="2">
+        <v>11.731190969499998</v>
+      </c>
+      <c r="J211" s="2">
+        <v>5.5333E-2</v>
+      </c>
+      <c r="K211" s="2">
+        <v>1.0005415778000002</v>
+      </c>
+      <c r="L211" s="2">
+        <v>9.4723209799999999E-2</v>
+      </c>
+      <c r="M211" s="2">
+        <v>1.7938587298000002</v>
+      </c>
+      <c r="N211" s="2">
+        <v>8.9329959799999997E-2</v>
+      </c>
+      <c r="O211" s="2">
+        <v>2.7275399999999997E-3</v>
+      </c>
+      <c r="P211" s="2">
+        <v>7.4599000000000004E-6</v>
+      </c>
+      <c r="Q211" s="2">
+        <v>39.65177365249999</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B212" t="s">
+        <v>95</v>
+      </c>
+      <c r="C212" s="2">
+        <v>13.6310908795</v>
+      </c>
+      <c r="D212" s="2">
+        <v>10.561406073699999</v>
+      </c>
+      <c r="E212" s="2">
+        <v>3.7955883187000001</v>
+      </c>
+      <c r="F212" s="2">
+        <v>86.469692310100001</v>
+      </c>
+      <c r="G212" s="2">
+        <v>60.8022771256</v>
+      </c>
+      <c r="H212" s="2">
+        <v>119.386124266</v>
+      </c>
+      <c r="I212" s="2">
+        <v>142.66625150230007</v>
+      </c>
+      <c r="J212" s="2">
+        <v>0.6706659599</v>
+      </c>
+      <c r="K212" s="2">
+        <v>11.594436751100003</v>
+      </c>
+      <c r="L212" s="2">
+        <v>1.1480453051000001</v>
+      </c>
+      <c r="M212" s="2">
+        <v>21.403405677899997</v>
+      </c>
+      <c r="N212" s="2">
+        <v>1.0248225479999999</v>
+      </c>
+      <c r="O212" s="2">
+        <v>3.2785030700000002E-2</v>
+      </c>
+      <c r="P212" s="2">
+        <v>8.9669199999999999E-5</v>
+      </c>
+      <c r="Q212" s="2">
+        <v>473.1866814178</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>135</v>
+      </c>
+      <c r="B213" t="s">
+        <v>94</v>
+      </c>
+      <c r="C213" s="2">
+        <v>1.0217140897000001</v>
+      </c>
+      <c r="D213" s="2">
+        <v>6.5043974797999997</v>
+      </c>
+      <c r="E213" s="2">
+        <v>0.52745240999999998</v>
+      </c>
+      <c r="F213" s="2">
+        <v>3.6945644886000002</v>
+      </c>
+      <c r="G213" s="2">
+        <v>4.1965709899999995E-2</v>
+      </c>
+      <c r="H213" s="2">
+        <v>11.790913559099996</v>
+      </c>
+      <c r="I213" s="2">
+        <v>1.1048527398000003</v>
+      </c>
+      <c r="J213" s="2">
+        <v>5.4248020000000001E-2</v>
+      </c>
+      <c r="K213" s="2">
+        <v>1.8321259883999996</v>
+      </c>
+      <c r="L213" s="2">
+        <v>0.22342341979999999</v>
+      </c>
+      <c r="M213" s="2">
+        <v>1.2727332994999998</v>
+      </c>
+      <c r="N213" s="2">
+        <v>6.660663E-2</v>
+      </c>
+      <c r="O213" s="2">
+        <v>2.4951700000000001E-3</v>
+      </c>
+      <c r="P213" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="Q213" s="2">
+        <v>28.3874930046</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B214" t="s">
+        <v>95</v>
+      </c>
+      <c r="C214" s="2">
+        <v>11.5998478912</v>
+      </c>
+      <c r="D214" s="2">
+        <v>71.848372279800003</v>
+      </c>
+      <c r="E214" s="2">
+        <v>6.1731471858999996</v>
+      </c>
+      <c r="F214" s="2">
+        <v>43.45898273209999</v>
+      </c>
+      <c r="G214" s="2">
+        <v>0.4842842933</v>
+      </c>
+      <c r="H214" s="2">
+        <v>136.23821512999999</v>
+      </c>
+      <c r="I214" s="2">
+        <v>12.5856473644</v>
+      </c>
+      <c r="J214" s="2">
+        <v>0.63067734879999993</v>
+      </c>
+      <c r="K214" s="2">
+        <v>20.817421339499983</v>
+      </c>
+      <c r="L214" s="2">
+        <v>2.6229909507000002</v>
+      </c>
+      <c r="M214" s="2">
+        <v>14.817833654300001</v>
+      </c>
+      <c r="N214" s="2">
+        <v>0.75265491880000002</v>
+      </c>
+      <c r="O214" s="2">
+        <v>2.9043778699999998E-2</v>
+      </c>
+      <c r="P214" s="2">
+        <v>2.9249999999999998</v>
+      </c>
+      <c r="Q214" s="2">
+        <v>324.98411886749994</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>136</v>
+      </c>
+      <c r="B215" t="s">
+        <v>94</v>
+      </c>
+      <c r="C215" s="2">
+        <v>6.8038109700000002E-2</v>
+      </c>
+      <c r="D215" s="2">
+        <v>2.2292698000000001E-3</v>
+      </c>
+      <c r="E215" s="2">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="F215" s="2">
+        <v>1.6522773781999998</v>
+      </c>
+      <c r="G215" s="2">
+        <v>8.60199E-5</v>
+      </c>
+      <c r="H215" s="2">
+        <v>0.1031850797</v>
+      </c>
+      <c r="I215" s="2">
+        <v>2.2065109999999999E-2</v>
+      </c>
+      <c r="J215" s="2"/>
+      <c r="K215" s="2">
+        <v>3.05195181E-2</v>
+      </c>
+      <c r="L215" s="2">
+        <v>6.6482999000000006E-3</v>
+      </c>
+      <c r="M215" s="2">
+        <v>5.6577097999999998E-3</v>
+      </c>
+      <c r="N215" s="2">
+        <v>6.2666798999999997E-3</v>
+      </c>
+      <c r="O215" s="2">
+        <v>1.7346899999999999E-3</v>
+      </c>
+      <c r="P215" s="2"/>
+      <c r="Q215" s="2">
+        <v>1.9003078649999994</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B216" t="s">
+        <v>95</v>
+      </c>
+      <c r="C216" s="2">
+        <v>0.73586636490000001</v>
+      </c>
+      <c r="D216" s="2">
+        <v>2.40761159E-2</v>
+      </c>
+      <c r="E216" s="2">
+        <v>1.8447999999999999E-2</v>
+      </c>
+      <c r="F216" s="2">
+        <v>18.979718179700001</v>
+      </c>
+      <c r="G216" s="2">
+        <v>9.4880059999999996E-4</v>
+      </c>
+      <c r="H216" s="2">
+        <v>1.2298153265999998</v>
+      </c>
+      <c r="I216" s="2">
+        <v>0.22131305330000001</v>
+      </c>
+      <c r="J216" s="2"/>
+      <c r="K216" s="2">
+        <v>0.31076304760000001</v>
+      </c>
+      <c r="L216" s="2">
+        <v>7.4660409000000011E-2</v>
+      </c>
+      <c r="M216" s="2">
+        <v>6.0367765599999998E-2</v>
+      </c>
+      <c r="N216" s="2">
+        <v>7.0813483999999996E-2</v>
+      </c>
+      <c r="O216" s="2">
+        <v>1.9307099599999999E-2</v>
+      </c>
+      <c r="P216" s="2"/>
+      <c r="Q216" s="2">
+        <v>21.746097646799999</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>137</v>
+      </c>
+      <c r="B217" t="s">
+        <v>94</v>
+      </c>
+      <c r="C217" s="2">
+        <v>2.6353729899999997E-2</v>
+      </c>
+      <c r="D217" s="2">
+        <v>3.9180000000000001E-5</v>
+      </c>
+      <c r="E217" s="2"/>
+      <c r="F217" s="2">
+        <v>0.75265275980000002</v>
+      </c>
+      <c r="G217" s="2">
+        <v>3.0423000000000001E-4</v>
+      </c>
+      <c r="H217" s="2">
+        <v>3.07552699E-2</v>
+      </c>
+      <c r="I217" s="2">
+        <v>8.0274799000000004E-3</v>
+      </c>
+      <c r="J217" s="2"/>
+      <c r="K217" s="2">
+        <v>1.0460969399999999E-2</v>
+      </c>
+      <c r="L217" s="2"/>
+      <c r="M217" s="2"/>
+      <c r="N217" s="2">
+        <v>4.4545698000000005E-3</v>
+      </c>
+      <c r="O217" s="2"/>
+      <c r="P217" s="2"/>
+      <c r="Q217" s="2">
+        <v>0.83304818869999997</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B218" t="s">
+        <v>95</v>
+      </c>
+      <c r="C218" s="2">
+        <v>0.28709530999999999</v>
+      </c>
+      <c r="D218" s="2">
+        <v>4.2314400000000003E-4</v>
+      </c>
+      <c r="E218" s="2"/>
+      <c r="F218" s="2">
+        <v>8.6118397088000016</v>
+      </c>
+      <c r="G218" s="2">
+        <v>3.3556569000000001E-3</v>
+      </c>
+      <c r="H218" s="2">
+        <v>0.3388441136</v>
+      </c>
+      <c r="I218" s="2">
+        <v>8.0515624199999997E-2</v>
+      </c>
+      <c r="J218" s="2"/>
+      <c r="K218" s="2">
+        <v>0.10715152690000002</v>
+      </c>
+      <c r="L218" s="2"/>
+      <c r="M218" s="2"/>
+      <c r="N218" s="2">
+        <v>5.03366409E-2</v>
+      </c>
+      <c r="O218" s="2"/>
+      <c r="P218" s="2"/>
+      <c r="Q218" s="2">
+        <v>9.4795617253000017</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>138</v>
+      </c>
+      <c r="B219" t="s">
+        <v>94</v>
+      </c>
+      <c r="C219" s="2">
+        <v>4.1718715696999995</v>
+      </c>
+      <c r="D219" s="2">
+        <v>4.9330698000000003E-3</v>
+      </c>
+      <c r="E219" s="2">
+        <v>0.18359998979999997</v>
+      </c>
+      <c r="F219" s="2">
+        <v>1.9030036384000004</v>
+      </c>
+      <c r="G219" s="2">
+        <v>1.4166719899999999E-2</v>
+      </c>
+      <c r="H219" s="2">
+        <v>7.3240962696</v>
+      </c>
+      <c r="I219" s="2">
+        <v>0.28268344979999999</v>
+      </c>
+      <c r="J219" s="2">
+        <v>4.8653498999999996E-3</v>
+      </c>
+      <c r="K219" s="2">
+        <v>0.94212681830000011</v>
+      </c>
+      <c r="L219" s="2">
+        <v>2.1589099E-3</v>
+      </c>
+      <c r="M219" s="2">
+        <v>0.95493683979999999</v>
+      </c>
+      <c r="N219" s="2">
+        <v>2.3483739899999998E-2</v>
+      </c>
+      <c r="O219" s="2">
+        <v>1.1590000000000001E-3</v>
+      </c>
+      <c r="P219" s="2"/>
+      <c r="Q219" s="2">
+        <v>15.813085364799999</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B220" t="s">
+        <v>95</v>
+      </c>
+      <c r="C220" s="2">
+        <v>45.854369898500003</v>
+      </c>
+      <c r="D220" s="2">
+        <v>5.3277155899999998E-2</v>
+      </c>
+      <c r="E220" s="2">
+        <v>2.0133382286000003</v>
+      </c>
+      <c r="F220" s="2">
+        <v>21.619368151600003</v>
+      </c>
+      <c r="G220" s="2">
+        <v>0.15625892159999999</v>
+      </c>
+      <c r="H220" s="2">
+        <v>79.934291185799992</v>
+      </c>
+      <c r="I220" s="2">
+        <v>3.0587373033</v>
+      </c>
+      <c r="J220" s="2">
+        <v>5.3178275499999997E-2</v>
+      </c>
+      <c r="K220" s="2">
+        <v>10.4866338854</v>
+      </c>
+      <c r="L220" s="2">
+        <v>2.42445591E-2</v>
+      </c>
+      <c r="M220" s="2">
+        <v>10.3483380446</v>
+      </c>
+      <c r="N220" s="2">
+        <v>0.26536626190000001</v>
+      </c>
+      <c r="O220" s="2">
+        <v>1.289967E-2</v>
+      </c>
+      <c r="P220" s="2"/>
+      <c r="Q220" s="2">
+        <v>173.88030154179998</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>139</v>
+      </c>
+      <c r="B221" t="s">
+        <v>94</v>
+      </c>
+      <c r="C221" s="2">
+        <v>4.4089374596000006</v>
+      </c>
+      <c r="D221" s="2">
+        <v>1.1544905099999998</v>
+      </c>
+      <c r="E221" s="2">
+        <v>0.21959732979999999</v>
+      </c>
+      <c r="F221" s="2">
+        <v>2.8340743380000002</v>
+      </c>
+      <c r="G221" s="2">
+        <v>4.4409935799999998</v>
+      </c>
+      <c r="H221" s="2">
+        <v>17.608619569399998</v>
+      </c>
+      <c r="I221" s="2">
+        <v>2.1314959997000003</v>
+      </c>
+      <c r="J221" s="2">
+        <v>1.115909E-2</v>
+      </c>
+      <c r="K221" s="2">
+        <v>1.2647888485000003</v>
+      </c>
+      <c r="L221" s="2">
+        <v>1.4593398999999999E-3</v>
+      </c>
+      <c r="M221" s="2">
+        <v>6.1242180397000014</v>
+      </c>
+      <c r="N221" s="2">
+        <v>0.53442169949999996</v>
+      </c>
+      <c r="O221" s="2">
+        <v>4.8697999999999998E-4</v>
+      </c>
+      <c r="P221" s="2">
+        <v>0.15600999999999998</v>
+      </c>
+      <c r="Q221" s="2">
+        <v>40.890752784100002</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B222" t="s">
+        <v>95</v>
+      </c>
+      <c r="C222" s="2">
+        <v>45.502503856200001</v>
+      </c>
+      <c r="D222" s="2">
+        <v>12.254873099900001</v>
+      </c>
+      <c r="E222" s="2">
+        <v>2.3130319035000002</v>
+      </c>
+      <c r="F222" s="2">
+        <v>29.817458589399997</v>
+      </c>
+      <c r="G222" s="2">
+        <v>46.524805398200002</v>
+      </c>
+      <c r="H222" s="2">
+        <v>173.37130044540001</v>
+      </c>
+      <c r="I222" s="2">
+        <v>21.590170588799996</v>
+      </c>
+      <c r="J222" s="2">
+        <v>0.116062945</v>
+      </c>
+      <c r="K222" s="2">
+        <v>13.189703121400001</v>
+      </c>
+      <c r="L222" s="2">
+        <v>1.56003446E-2</v>
+      </c>
+      <c r="M222" s="2">
+        <v>64.876122410999969</v>
+      </c>
+      <c r="N222" s="2">
+        <v>5.6821343599</v>
+      </c>
+      <c r="O222" s="2">
+        <v>5.1571181000000001E-3</v>
+      </c>
+      <c r="P222" s="2">
+        <v>1.6341459</v>
+      </c>
+      <c r="Q222" s="2">
+        <v>416.89307008139997</v>
       </c>
     </row>
   </sheetData>
@@ -13854,7 +14804,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D2E8B6-8413-4B5C-882C-FCAE21C7E121}">
-  <dimension ref="A2:AE109"/>
+  <dimension ref="A2:AE116"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -22251,10 +23201,10 @@
         <v>125</v>
       </c>
       <c r="B102" s="2">
-        <v>10.541265099399999</v>
+        <v>10.5412650994</v>
       </c>
       <c r="C102" s="2">
-        <v>1.5404671898</v>
+        <v>1.5404671898000002</v>
       </c>
       <c r="D102" s="2">
         <v>0.30973334990000001</v>
@@ -22266,25 +23216,25 @@
         <v>1.52429345</v>
       </c>
       <c r="G102" s="2">
-        <v>7.0495516189999989</v>
+        <v>7.049551618999998</v>
       </c>
       <c r="H102" s="2">
-        <v>8.1942503297999991</v>
+        <v>8.1942503297999973</v>
       </c>
       <c r="I102" s="2">
         <v>2.5951819899999999E-2</v>
       </c>
       <c r="J102" s="2">
-        <v>6.4725927187000005</v>
+        <v>6.4725927186999996</v>
       </c>
       <c r="K102" s="2">
         <v>2.0430669899999997E-2</v>
       </c>
       <c r="L102" s="2">
-        <v>2.0410046297999997</v>
+        <v>2.0410046298000002</v>
       </c>
       <c r="M102" s="2">
-        <v>0.80778228969999999</v>
+        <v>0.80778228969999988</v>
       </c>
       <c r="N102" s="2">
         <v>1.8677698999999999E-3</v>
@@ -22293,13 +23243,13 @@
         <v>0.15001043999999999</v>
       </c>
       <c r="P102" s="2">
-        <v>49.356058984300006</v>
+        <v>49.356058984300013</v>
       </c>
       <c r="Q102" s="2">
-        <v>1.8323795698000001</v>
+        <v>1.8323795698000003</v>
       </c>
       <c r="R102" s="2">
-        <v>0.57434707969999987</v>
+        <v>0.57434707969999999</v>
       </c>
       <c r="S102" s="2">
         <v>0.10458754000000001</v>
@@ -22308,19 +23258,19 @@
         <v>6.8793667697999998</v>
       </c>
       <c r="U102" s="2">
-        <v>0.79308789959999992</v>
+        <v>0.79308789959999981</v>
       </c>
       <c r="V102" s="2">
-        <v>7.645875329599999</v>
+        <v>7.6458753295999999</v>
       </c>
       <c r="W102" s="2">
-        <v>6.1348258998</v>
+        <v>6.1348258998000009</v>
       </c>
       <c r="X102" s="2">
         <v>3.5879199899999999E-2</v>
       </c>
       <c r="Y102" s="2">
-        <v>3.7261149621000005</v>
+        <v>3.7261149620999983</v>
       </c>
       <c r="Z102" s="2">
         <v>3.1035999999999998E-4</v>
@@ -22336,7 +23286,7 @@
       </c>
       <c r="AD102" s="2"/>
       <c r="AE102" s="2">
-        <v>28.126867349799998</v>
+        <v>28.126867349800001</v>
       </c>
     </row>
     <row r="103" spans="1:31" x14ac:dyDescent="0.25">
@@ -22344,19 +23294,19 @@
         <v>126</v>
       </c>
       <c r="B103" s="2">
-        <v>2.2410354895000006</v>
+        <v>2.2410354895000002</v>
       </c>
       <c r="C103" s="2">
         <v>4.321877409799999</v>
       </c>
       <c r="D103" s="2">
-        <v>1.7164667598000001</v>
+        <v>1.7164667597999999</v>
       </c>
       <c r="E103" s="2">
         <v>6.1768947684000004</v>
       </c>
       <c r="F103" s="2">
-        <v>3.5403004299000003</v>
+        <v>3.5403004298999998</v>
       </c>
       <c r="G103" s="2">
         <v>28.744438628800001</v>
@@ -22368,13 +23318,13 @@
         <v>6.0730200000000002E-3</v>
       </c>
       <c r="J103" s="2">
-        <v>2.0242601281000008</v>
+        <v>2.0242601280999994</v>
       </c>
       <c r="K103" s="2">
         <v>2.0808800000000002E-3</v>
       </c>
       <c r="L103" s="2">
-        <v>5.5570111197000003</v>
+        <v>5.5570111197000012</v>
       </c>
       <c r="M103" s="2">
         <v>0.24435603989999999</v>
@@ -22386,10 +23336,10 @@
         <v>0.50007542999999999</v>
       </c>
       <c r="P103" s="2">
-        <v>59.084914313600017</v>
+        <v>59.084914313600009</v>
       </c>
       <c r="Q103" s="2">
-        <v>6.095447909899999</v>
+        <v>6.0954479098999998</v>
       </c>
       <c r="R103" s="2">
         <v>0.96028374969999997</v>
@@ -22398,10 +23348,10 @@
         <v>0.1339586499</v>
       </c>
       <c r="T103" s="2">
-        <v>3.6203973293999998</v>
+        <v>3.6203973293999994</v>
       </c>
       <c r="U103" s="2">
-        <v>1.5519809893000001</v>
+        <v>1.5519809893000003</v>
       </c>
       <c r="V103" s="2">
         <v>6.7983298396000009</v>
@@ -22413,16 +23363,16 @@
         <v>3.6656629900000001E-2</v>
       </c>
       <c r="Y103" s="2">
-        <v>1.6357991537000007</v>
+        <v>1.6357991537000003</v>
       </c>
       <c r="Z103" s="2">
         <v>5.0851990000000001E-4</v>
       </c>
       <c r="AA103" s="2">
-        <v>2.5387599198000004</v>
+        <v>2.5387599197999999</v>
       </c>
       <c r="AB103" s="2">
-        <v>0.26477757959999998</v>
+        <v>0.26477757960000003</v>
       </c>
       <c r="AC103" s="2">
         <v>1.9672749899999998E-2</v>
@@ -22437,19 +23387,19 @@
         <v>127</v>
       </c>
       <c r="B104" s="2">
-        <v>4.227290299399999</v>
+        <v>4.2272902993999999</v>
       </c>
       <c r="C104" s="2">
-        <v>0.55025838989999998</v>
+        <v>0.55025838990000009</v>
       </c>
       <c r="D104" s="2">
-        <v>0.16759871990000003</v>
+        <v>0.1675987199</v>
       </c>
       <c r="E104" s="2">
-        <v>9.5613452585000012</v>
+        <v>9.5613452584999994</v>
       </c>
       <c r="F104" s="2">
-        <v>1.32292995</v>
+        <v>1.3229299500000002</v>
       </c>
       <c r="G104" s="2">
         <v>9.6362721188999991</v>
@@ -22464,10 +23414,10 @@
         <v>4.2512866591000007</v>
       </c>
       <c r="K104" s="2">
-        <v>1.1868579899999999E-2</v>
+        <v>1.1868579900000001E-2</v>
       </c>
       <c r="L104" s="2">
-        <v>3.0043624296</v>
+        <v>3.0043624296000004</v>
       </c>
       <c r="M104" s="2">
         <v>4.4385997999999999E-3</v>
@@ -22497,22 +23447,22 @@
         <v>0.7145917797000001</v>
       </c>
       <c r="V104" s="2">
-        <v>25.576800959300005</v>
+        <v>25.576800959300002</v>
       </c>
       <c r="W104" s="2">
-        <v>3.7193456193999999</v>
+        <v>3.7193456194000003</v>
       </c>
       <c r="X104" s="2">
         <v>0.15393631990000001</v>
       </c>
       <c r="Y104" s="2">
-        <v>3.4482846744000026</v>
+        <v>3.448284674400004</v>
       </c>
       <c r="Z104" s="2">
         <v>5.2634999999999999E-3</v>
       </c>
       <c r="AA104" s="2">
-        <v>0.83277477980000014</v>
+        <v>0.83277477980000003</v>
       </c>
       <c r="AB104" s="2">
         <v>1.3298494292</v>
@@ -22522,7 +23472,7 @@
       </c>
       <c r="AD104" s="2"/>
       <c r="AE104" s="2">
-        <v>45.016536000500011</v>
+        <v>45.016536000499997</v>
       </c>
     </row>
     <row r="105" spans="1:31" x14ac:dyDescent="0.25">
@@ -22533,50 +23483,50 @@
         <v>4.5686707090000001</v>
       </c>
       <c r="C105" s="2">
-        <v>4.0573789996999992</v>
+        <v>4.0573789997</v>
       </c>
       <c r="D105" s="2">
         <v>0.8197688098</v>
       </c>
       <c r="E105" s="2">
-        <v>21.622486007899997</v>
+        <v>21.622486007900001</v>
       </c>
       <c r="F105" s="2">
-        <v>1.5932660199999999</v>
+        <v>1.5932660199999997</v>
       </c>
       <c r="G105" s="2">
         <v>9.5712881088999993</v>
       </c>
       <c r="H105" s="2">
-        <v>10.460837409400003</v>
+        <v>11.750750289799997</v>
       </c>
       <c r="I105" s="2">
         <v>0.2543552</v>
       </c>
       <c r="J105" s="2">
-        <v>5.8530080087000007</v>
+        <v>5.8530080087000016</v>
       </c>
       <c r="K105" s="2">
         <v>1.9358249899999999E-2</v>
       </c>
       <c r="L105" s="2">
-        <v>0.81909734990000005</v>
+        <v>0.81909734989999994</v>
       </c>
       <c r="M105" s="2">
-        <v>3.4659929899999997E-2</v>
+        <v>3.4659929900000004E-2</v>
       </c>
       <c r="N105" s="2">
         <v>5.0299999999999997E-3</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2">
-        <v>59.679204803100006</v>
+        <v>60.969117683500002</v>
       </c>
       <c r="Q105" s="2">
-        <v>4.3526002199000011</v>
+        <v>4.3526002198999993</v>
       </c>
       <c r="R105" s="2">
-        <v>1.0581553996999997</v>
+        <v>1.0581553996999999</v>
       </c>
       <c r="S105" s="2">
         <v>0.1133477499</v>
@@ -22585,25 +23535,25 @@
         <v>9.636341799300002</v>
       </c>
       <c r="U105" s="2">
-        <v>1.8013652097999999</v>
+        <v>1.8013652098000001</v>
       </c>
       <c r="V105" s="2">
         <v>10.649425239400001</v>
       </c>
       <c r="W105" s="2">
-        <v>1.6218086896000001</v>
+        <v>1.2856835993</v>
       </c>
       <c r="X105" s="2">
         <v>3.5955500000000001E-2</v>
       </c>
       <c r="Y105" s="2">
-        <v>0.94669448290000013</v>
+        <v>0.9466944828999998</v>
       </c>
       <c r="Z105" s="2">
         <v>4.9492999999999998E-4</v>
       </c>
       <c r="AA105" s="2">
-        <v>0.39541672949999995</v>
+        <v>0.39541672950000001</v>
       </c>
       <c r="AB105" s="2">
         <v>0.1252695395</v>
@@ -22615,7 +23565,7 @@
         <v>9.5616989999999997E-4</v>
       </c>
       <c r="AE105" s="2">
-        <v>30.741267499400003</v>
+        <v>30.405142409100002</v>
       </c>
     </row>
     <row r="106" spans="1:31" x14ac:dyDescent="0.25">
@@ -22645,7 +23595,7 @@
       </c>
       <c r="I106" s="2"/>
       <c r="J106" s="2">
-        <v>1.1298302283999999</v>
+        <v>1.1298302284000001</v>
       </c>
       <c r="K106" s="2">
         <v>3.04916E-3</v>
@@ -22654,7 +23604,7 @@
         <v>5.7993298E-3</v>
       </c>
       <c r="M106" s="2">
-        <v>9.9220596999999994E-3</v>
+        <v>9.9220597000000011E-3</v>
       </c>
       <c r="N106" s="2">
         <v>2.5593699E-3</v>
@@ -22663,7 +23613,7 @@
         <v>1.95E-6</v>
       </c>
       <c r="P106" s="2">
-        <v>4.4932006753999998</v>
+        <v>4.4932006754000007</v>
       </c>
       <c r="Q106" s="2">
         <v>4.7702698E-3</v>
@@ -22706,7 +23656,7 @@
         <v>4.7319000000000001E-4</v>
       </c>
       <c r="AE106" s="2">
-        <v>0.28452559260000004</v>
+        <v>0.28452559259999999</v>
       </c>
     </row>
     <row r="107" spans="1:31" x14ac:dyDescent="0.25">
@@ -22736,7 +23686,7 @@
       </c>
       <c r="I107" s="2"/>
       <c r="J107" s="2">
-        <v>0.1493028096</v>
+        <v>0.14930280960000006</v>
       </c>
       <c r="K107" s="2"/>
       <c r="L107" s="2">
@@ -22756,7 +23706,7 @@
         <v>7.3599999999999998E-6</v>
       </c>
       <c r="R107" s="2">
-        <v>2.40224198E-2</v>
+        <v>2.4022419799999997E-2</v>
       </c>
       <c r="S107" s="2"/>
       <c r="T107" s="2">
@@ -22773,19 +23723,19 @@
       </c>
       <c r="X107" s="2"/>
       <c r="Y107" s="2">
-        <v>6.7336923600000057E-2</v>
+        <v>6.7336923600000015E-2</v>
       </c>
       <c r="Z107" s="2"/>
       <c r="AA107" s="2">
         <v>5.8966298999999995E-3</v>
       </c>
       <c r="AB107" s="2">
-        <v>2.7714698000000002E-3</v>
+        <v>2.7714697999999998E-3</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" s="2"/>
       <c r="AE107" s="2">
-        <v>0.24104739280000007</v>
+        <v>0.24104739280000004</v>
       </c>
     </row>
     <row r="108" spans="1:31" x14ac:dyDescent="0.25">
@@ -22793,22 +23743,22 @@
         <v>131</v>
       </c>
       <c r="B108" s="2">
-        <v>2.5096564793000002</v>
+        <v>2.5096564792999998</v>
       </c>
       <c r="C108" s="2">
-        <v>0.38593560000000005</v>
+        <v>0.38593559999999999</v>
       </c>
       <c r="D108" s="2">
-        <v>7.6094269899999997E-2</v>
+        <v>7.6094269899999983E-2</v>
       </c>
       <c r="E108" s="2">
-        <v>4.6978368786000004</v>
+        <v>4.6978368785999995</v>
       </c>
       <c r="F108" s="2">
         <v>0.89445370989999995</v>
       </c>
       <c r="G108" s="2">
-        <v>2.0722231493000001</v>
+        <v>2.0722231492999996</v>
       </c>
       <c r="H108" s="2">
         <v>4.3039844189000007</v>
@@ -22817,7 +23767,7 @@
         <v>2.6595699E-3</v>
       </c>
       <c r="J108" s="2">
-        <v>4.7299834682000004</v>
+        <v>4.7299834682000022</v>
       </c>
       <c r="K108" s="2">
         <v>1.55873299E-2</v>
@@ -22835,13 +23785,13 @@
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="P108" s="2">
-        <v>20.096849593700004</v>
+        <v>20.0968495937</v>
       </c>
       <c r="Q108" s="2">
-        <v>1.4394571098</v>
+        <v>1.4394571097999997</v>
       </c>
       <c r="R108" s="2">
-        <v>0.31051675980000004</v>
+        <v>0.31051675979999999</v>
       </c>
       <c r="S108" s="2">
         <v>0.14568527990000002</v>
@@ -22850,10 +23800,10 @@
         <v>6.8436526397000002</v>
       </c>
       <c r="U108" s="2">
-        <v>1.0969614694999998</v>
+        <v>1.0969614695000001</v>
       </c>
       <c r="V108" s="2">
-        <v>3.8720962799000005</v>
+        <v>3.8720962798999996</v>
       </c>
       <c r="W108" s="2">
         <v>0.99706682870000007</v>
@@ -22862,13 +23812,13 @@
         <v>1E-4</v>
       </c>
       <c r="Y108" s="2">
-        <v>0.70961261419999977</v>
+        <v>0.70961261419999966</v>
       </c>
       <c r="Z108" s="2">
         <v>1.426E-3</v>
       </c>
       <c r="AA108" s="2">
-        <v>1.2349703097999998</v>
+        <v>1.2349703098</v>
       </c>
       <c r="AB108" s="2">
         <v>6.4870549900000005E-2</v>
@@ -22880,7 +23830,7 @@
         <v>1.9715999999999999E-4</v>
       </c>
       <c r="AE108" s="2">
-        <v>16.716837311200003</v>
+        <v>16.716837311199995</v>
       </c>
     </row>
     <row r="109" spans="1:31" x14ac:dyDescent="0.25">
@@ -22888,7 +23838,7 @@
         <v>132</v>
       </c>
       <c r="B109" s="2">
-        <v>2.8633718292999992</v>
+        <v>2.8633718292999997</v>
       </c>
       <c r="C109" s="2">
         <v>0.67271874990000002</v>
@@ -22900,22 +23850,22 @@
         <v>12.2575770487</v>
       </c>
       <c r="F109" s="2">
-        <v>1.44202221</v>
+        <v>1.4420222100000002</v>
       </c>
       <c r="G109" s="2">
-        <v>13.599364889000002</v>
+        <v>13.599364889</v>
       </c>
       <c r="H109" s="2">
-        <v>5.8482524195000014</v>
+        <v>5.8482524195000005</v>
       </c>
       <c r="I109" s="2">
         <v>8.294195E-2</v>
       </c>
       <c r="J109" s="2">
-        <v>5.5395596579000008</v>
+        <v>5.5395596578999999</v>
       </c>
       <c r="K109" s="2">
-        <v>2.0981879900000003E-2</v>
+        <v>2.09818799E-2</v>
       </c>
       <c r="L109" s="2">
         <v>3.2933772699000001</v>
@@ -22928,16 +23878,16 @@
       </c>
       <c r="O109" s="2"/>
       <c r="P109" s="2">
-        <v>50.902238913799991</v>
+        <v>50.902238913799998</v>
       </c>
       <c r="Q109" s="2">
         <v>2.9099903197999999</v>
       </c>
       <c r="R109" s="2">
-        <v>1.2650178096000002</v>
+        <v>1.2650178096</v>
       </c>
       <c r="S109" s="2">
-        <v>0.10653899990000001</v>
+        <v>0.1065389999</v>
       </c>
       <c r="T109" s="2">
         <v>9.9160820092000002</v>
@@ -22949,19 +23899,19 @@
         <v>17.7356039296</v>
       </c>
       <c r="W109" s="2">
-        <v>15.824149879600002</v>
+        <v>15.8241498796</v>
       </c>
       <c r="X109" s="2">
         <v>1.0145E-2</v>
       </c>
       <c r="Y109" s="2">
-        <v>1.8697059138000012</v>
+        <v>1.8697059138000007</v>
       </c>
       <c r="Z109" s="2">
         <v>1.7019E-4</v>
       </c>
       <c r="AA109" s="2">
-        <v>0.98909154979999991</v>
+        <v>0.98909154980000014</v>
       </c>
       <c r="AB109" s="2">
         <v>7.3265275295999999</v>
@@ -22973,7 +23923,634 @@
         <v>0.5</v>
       </c>
       <c r="AE109" s="2">
-        <v>63.585152320400006</v>
+        <v>63.585152320399999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>133</v>
+      </c>
+      <c r="B110" s="2">
+        <v>5.8705452693</v>
+      </c>
+      <c r="C110" s="2">
+        <v>1.2450495999000002</v>
+      </c>
+      <c r="D110" s="2">
+        <v>2.3746740098999997</v>
+      </c>
+      <c r="E110" s="2">
+        <v>18.101094888000006</v>
+      </c>
+      <c r="F110" s="2">
+        <v>2.7011731796</v>
+      </c>
+      <c r="G110" s="2">
+        <v>28.055478878599995</v>
+      </c>
+      <c r="H110" s="2">
+        <v>10.904366849800001</v>
+      </c>
+      <c r="I110" s="2">
+        <v>5.6418119900000001E-2</v>
+      </c>
+      <c r="J110" s="2">
+        <v>4.988294688299999</v>
+      </c>
+      <c r="K110" s="2">
+        <v>8.8044989900000009E-2</v>
+      </c>
+      <c r="L110" s="2">
+        <v>3.8952739898999997</v>
+      </c>
+      <c r="M110" s="2">
+        <v>10.2664836099</v>
+      </c>
+      <c r="N110" s="2">
+        <v>1.64502799E-2</v>
+      </c>
+      <c r="O110" s="2">
+        <v>0.28201194989999995</v>
+      </c>
+      <c r="P110" s="2">
+        <v>88.845360302799989</v>
+      </c>
+      <c r="Q110" s="2">
+        <v>1.2830309696</v>
+      </c>
+      <c r="R110" s="2">
+        <v>3.1578427090000001</v>
+      </c>
+      <c r="S110" s="2">
+        <v>8.2800989800000002E-2</v>
+      </c>
+      <c r="T110" s="2">
+        <v>0.37280868950000001</v>
+      </c>
+      <c r="U110" s="2">
+        <v>7.8622929699999997E-2</v>
+      </c>
+      <c r="V110" s="2">
+        <v>12.991646919200001</v>
+      </c>
+      <c r="W110" s="2">
+        <v>4.4442158596000008</v>
+      </c>
+      <c r="X110" s="2">
+        <v>0.20809047999999999</v>
+      </c>
+      <c r="Y110" s="2">
+        <v>2.5034657940000011</v>
+      </c>
+      <c r="Z110" s="2">
+        <v>3.030299E-4</v>
+      </c>
+      <c r="AA110" s="2">
+        <v>0.37291251980000001</v>
+      </c>
+      <c r="AB110" s="2">
+        <v>5.2992661893999999</v>
+      </c>
+      <c r="AC110" s="2">
+        <v>1.7443099000000002E-3</v>
+      </c>
+      <c r="AD110" s="2"/>
+      <c r="AE110" s="2">
+        <v>30.796751389400001</v>
+      </c>
+    </row>
+    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>134</v>
+      </c>
+      <c r="B111" s="2">
+        <v>1.1333617697</v>
+      </c>
+      <c r="C111" s="2">
+        <v>0.89631024999999998</v>
+      </c>
+      <c r="D111" s="2">
+        <v>0.31111789000000001</v>
+      </c>
+      <c r="E111" s="2">
+        <v>7.4121021276999999</v>
+      </c>
+      <c r="F111" s="2">
+        <v>5.0692466798</v>
+      </c>
+      <c r="G111" s="2">
+        <v>10.0619224887</v>
+      </c>
+      <c r="H111" s="2">
+        <v>11.731190969499998</v>
+      </c>
+      <c r="I111" s="2">
+        <v>5.5333E-2</v>
+      </c>
+      <c r="J111" s="2">
+        <v>1.0005415778000002</v>
+      </c>
+      <c r="K111" s="2">
+        <v>9.4723209799999999E-2</v>
+      </c>
+      <c r="L111" s="2">
+        <v>1.7938587298000002</v>
+      </c>
+      <c r="M111" s="2">
+        <v>8.9329959799999997E-2</v>
+      </c>
+      <c r="N111" s="2">
+        <v>2.7275399999999997E-3</v>
+      </c>
+      <c r="O111" s="2">
+        <v>7.4599000000000004E-6</v>
+      </c>
+      <c r="P111" s="2">
+        <v>39.65177365249999</v>
+      </c>
+      <c r="Q111" s="2">
+        <v>3.5045785396000002</v>
+      </c>
+      <c r="R111" s="2">
+        <v>1.0006790296000003</v>
+      </c>
+      <c r="S111" s="2">
+        <v>0.1787738797</v>
+      </c>
+      <c r="T111" s="2">
+        <v>2.5606531391999994</v>
+      </c>
+      <c r="U111" s="2">
+        <v>1.0874557998000001</v>
+      </c>
+      <c r="V111" s="2">
+        <v>11.886549478599999</v>
+      </c>
+      <c r="W111" s="2">
+        <v>4.2417172294999999</v>
+      </c>
+      <c r="X111" s="2">
+        <v>6.7949999999999998E-3</v>
+      </c>
+      <c r="Y111" s="2">
+        <v>2.1491516443000016</v>
+      </c>
+      <c r="Z111" s="2">
+        <v>5.4343999999999996E-4</v>
+      </c>
+      <c r="AA111" s="2">
+        <v>0.65736201990000009</v>
+      </c>
+      <c r="AB111" s="2">
+        <v>0.2060131798</v>
+      </c>
+      <c r="AC111" s="2">
+        <v>2.5252299999999998E-3</v>
+      </c>
+      <c r="AD111" s="2">
+        <v>1.3847899999999999E-3</v>
+      </c>
+      <c r="AE111" s="2">
+        <v>27.484182400000002</v>
+      </c>
+    </row>
+    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>135</v>
+      </c>
+      <c r="B112" s="2">
+        <v>1.0217140897000001</v>
+      </c>
+      <c r="C112" s="2">
+        <v>6.5043974797999997</v>
+      </c>
+      <c r="D112" s="2">
+        <v>0.52745240999999998</v>
+      </c>
+      <c r="E112" s="2">
+        <v>3.6945644886000002</v>
+      </c>
+      <c r="F112" s="2">
+        <v>4.1965709899999995E-2</v>
+      </c>
+      <c r="G112" s="2">
+        <v>11.790913559099996</v>
+      </c>
+      <c r="H112" s="2">
+        <v>1.1048527398000003</v>
+      </c>
+      <c r="I112" s="2">
+        <v>5.4248020000000001E-2</v>
+      </c>
+      <c r="J112" s="2">
+        <v>1.8321259883999996</v>
+      </c>
+      <c r="K112" s="2">
+        <v>0.22342341979999999</v>
+      </c>
+      <c r="L112" s="2">
+        <v>1.2727332994999998</v>
+      </c>
+      <c r="M112" s="2">
+        <v>6.660663E-2</v>
+      </c>
+      <c r="N112" s="2">
+        <v>2.4951700000000001E-3</v>
+      </c>
+      <c r="O112" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="P112" s="2">
+        <v>28.3874930046</v>
+      </c>
+      <c r="Q112" s="2">
+        <v>4.5575444996999996</v>
+      </c>
+      <c r="R112" s="2">
+        <v>2.6546592692999997</v>
+      </c>
+      <c r="S112" s="2">
+        <v>4.2404459800000002E-2</v>
+      </c>
+      <c r="T112" s="2">
+        <v>3.7475695992000002</v>
+      </c>
+      <c r="U112" s="2">
+        <v>0.96941356979999993</v>
+      </c>
+      <c r="V112" s="2">
+        <v>13.683405768500002</v>
+      </c>
+      <c r="W112" s="2">
+        <v>10.998298199399999</v>
+      </c>
+      <c r="X112" s="2">
+        <v>3.2468069999999995E-2</v>
+      </c>
+      <c r="Y112" s="2">
+        <v>1.2645985633000005</v>
+      </c>
+      <c r="Z112" s="2">
+        <v>1.3406499000000001E-3</v>
+      </c>
+      <c r="AA112" s="2">
+        <v>0.46019248979999999</v>
+      </c>
+      <c r="AB112" s="2">
+        <v>0.11799761959999999</v>
+      </c>
+      <c r="AC112" s="2">
+        <v>0.26443068990000002</v>
+      </c>
+      <c r="AD112" s="2"/>
+      <c r="AE112" s="2">
+        <v>38.794323448200004</v>
+      </c>
+    </row>
+    <row r="113" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>136</v>
+      </c>
+      <c r="B113" s="2">
+        <v>6.8038109700000002E-2</v>
+      </c>
+      <c r="C113" s="2">
+        <v>2.2292698000000001E-3</v>
+      </c>
+      <c r="D113" s="2">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="E113" s="2">
+        <v>1.6522773781999998</v>
+      </c>
+      <c r="F113" s="2">
+        <v>8.60199E-5</v>
+      </c>
+      <c r="G113" s="2">
+        <v>0.1031850797</v>
+      </c>
+      <c r="H113" s="2">
+        <v>2.2065109999999999E-2</v>
+      </c>
+      <c r="I113" s="2"/>
+      <c r="J113" s="2">
+        <v>3.05195181E-2</v>
+      </c>
+      <c r="K113" s="2">
+        <v>6.6482999000000006E-3</v>
+      </c>
+      <c r="L113" s="2">
+        <v>5.6577097999999998E-3</v>
+      </c>
+      <c r="M113" s="2">
+        <v>6.2666798999999997E-3</v>
+      </c>
+      <c r="N113" s="2">
+        <v>1.7346899999999999E-3</v>
+      </c>
+      <c r="O113" s="2"/>
+      <c r="P113" s="2">
+        <v>1.9003078649999994</v>
+      </c>
+      <c r="Q113" s="2">
+        <v>8.4460200000000003E-3</v>
+      </c>
+      <c r="R113" s="2">
+        <v>2.79652598E-2</v>
+      </c>
+      <c r="S113" s="2"/>
+      <c r="T113" s="2">
+        <v>6.0807919799999999E-2</v>
+      </c>
+      <c r="U113" s="2">
+        <v>5.2773797999999999E-3</v>
+      </c>
+      <c r="V113" s="2">
+        <v>2.4426099600000001E-2</v>
+      </c>
+      <c r="W113" s="2">
+        <v>7.8297139499999988E-2</v>
+      </c>
+      <c r="X113" s="2"/>
+      <c r="Y113" s="2">
+        <v>0.18072428600000018</v>
+      </c>
+      <c r="Z113" s="2">
+        <v>1.1853000000000001E-4</v>
+      </c>
+      <c r="AA113" s="2">
+        <v>7.3607899999999999E-3</v>
+      </c>
+      <c r="AB113" s="2">
+        <v>1.2347349700000001E-2</v>
+      </c>
+      <c r="AC113" s="2">
+        <v>2.2301799E-3</v>
+      </c>
+      <c r="AD113" s="2"/>
+      <c r="AE113" s="2">
+        <v>0.4080009541000002</v>
+      </c>
+    </row>
+    <row r="114" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>137</v>
+      </c>
+      <c r="B114" s="2">
+        <v>2.6353729899999997E-2</v>
+      </c>
+      <c r="C114" s="2">
+        <v>3.9180000000000001E-5</v>
+      </c>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2">
+        <v>0.75265275980000002</v>
+      </c>
+      <c r="F114" s="2">
+        <v>3.0423000000000001E-4</v>
+      </c>
+      <c r="G114" s="2">
+        <v>3.07552699E-2</v>
+      </c>
+      <c r="H114" s="2">
+        <v>8.0274799000000004E-3</v>
+      </c>
+      <c r="I114" s="2"/>
+      <c r="J114" s="2">
+        <v>1.0460969399999999E-2</v>
+      </c>
+      <c r="K114" s="2"/>
+      <c r="L114" s="2"/>
+      <c r="M114" s="2">
+        <v>4.4545698000000005E-3</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
+      <c r="P114" s="2">
+        <v>0.83304818869999997</v>
+      </c>
+      <c r="Q114" s="2">
+        <v>1.140699E-4</v>
+      </c>
+      <c r="R114" s="2">
+        <v>2.5212109699999999E-2</v>
+      </c>
+      <c r="S114" s="2"/>
+      <c r="T114" s="2">
+        <v>4.7083699999999999E-2</v>
+      </c>
+      <c r="U114" s="2">
+        <v>4.2154399000000004E-3</v>
+      </c>
+      <c r="V114" s="2">
+        <v>2.5805599799999999E-2</v>
+      </c>
+      <c r="W114" s="2">
+        <v>7.9909689899999997E-2</v>
+      </c>
+      <c r="X114" s="2"/>
+      <c r="Y114" s="2">
+        <v>8.9083614799999974E-2</v>
+      </c>
+      <c r="Z114" s="2"/>
+      <c r="AA114" s="2">
+        <v>7.2890400000000001E-3</v>
+      </c>
+      <c r="AB114" s="2">
+        <v>1.52754E-3</v>
+      </c>
+      <c r="AC114" s="2"/>
+      <c r="AD114" s="2"/>
+      <c r="AE114" s="2">
+        <v>0.28024080399999995</v>
+      </c>
+    </row>
+    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>138</v>
+      </c>
+      <c r="B115" s="2">
+        <v>4.1718715696999995</v>
+      </c>
+      <c r="C115" s="2">
+        <v>4.9330698000000003E-3</v>
+      </c>
+      <c r="D115" s="2">
+        <v>0.18359998979999997</v>
+      </c>
+      <c r="E115" s="2">
+        <v>1.9030036384000004</v>
+      </c>
+      <c r="F115" s="2">
+        <v>1.4166719899999999E-2</v>
+      </c>
+      <c r="G115" s="2">
+        <v>7.3240962696</v>
+      </c>
+      <c r="H115" s="2">
+        <v>0.28268344979999999</v>
+      </c>
+      <c r="I115" s="2">
+        <v>4.8653498999999996E-3</v>
+      </c>
+      <c r="J115" s="2">
+        <v>0.94212681830000011</v>
+      </c>
+      <c r="K115" s="2">
+        <v>2.1589099E-3</v>
+      </c>
+      <c r="L115" s="2">
+        <v>0.95493683979999999</v>
+      </c>
+      <c r="M115" s="2">
+        <v>2.3483739899999998E-2</v>
+      </c>
+      <c r="N115" s="2">
+        <v>1.1590000000000001E-3</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" s="2">
+        <v>15.813085364799999</v>
+      </c>
+      <c r="Q115" s="2">
+        <v>3.5419900194999991</v>
+      </c>
+      <c r="R115" s="2">
+        <v>3.6475143194000008</v>
+      </c>
+      <c r="S115" s="2">
+        <v>0.19353318990000001</v>
+      </c>
+      <c r="T115" s="2">
+        <v>1.9581311591000001</v>
+      </c>
+      <c r="U115" s="2">
+        <v>5.8971540394000002</v>
+      </c>
+      <c r="V115" s="2">
+        <v>9.1594764796000021</v>
+      </c>
+      <c r="W115" s="2">
+        <v>4.3546414897999997</v>
+      </c>
+      <c r="X115" s="2">
+        <v>4.5000000000000003E-5</v>
+      </c>
+      <c r="Y115" s="2">
+        <v>1.9936713545000004</v>
+      </c>
+      <c r="Z115" s="2">
+        <v>4.8655999999999998E-4</v>
+      </c>
+      <c r="AA115" s="2">
+        <v>2.2227973695000003</v>
+      </c>
+      <c r="AB115" s="2">
+        <v>4.0621299699999995E-2</v>
+      </c>
+      <c r="AC115" s="2">
+        <v>1.3020789999999999E-2</v>
+      </c>
+      <c r="AD115" s="2">
+        <v>0.30016596000000001</v>
+      </c>
+      <c r="AE115" s="2">
+        <v>33.3232490304</v>
+      </c>
+    </row>
+    <row r="116" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>139</v>
+      </c>
+      <c r="B116" s="2">
+        <v>4.4089374596000006</v>
+      </c>
+      <c r="C116" s="2">
+        <v>1.1544905099999998</v>
+      </c>
+      <c r="D116" s="2">
+        <v>0.21959732979999999</v>
+      </c>
+      <c r="E116" s="2">
+        <v>2.8340743380000002</v>
+      </c>
+      <c r="F116" s="2">
+        <v>4.4409935799999998</v>
+      </c>
+      <c r="G116" s="2">
+        <v>17.608619569399998</v>
+      </c>
+      <c r="H116" s="2">
+        <v>2.1314959997000003</v>
+      </c>
+      <c r="I116" s="2">
+        <v>1.115909E-2</v>
+      </c>
+      <c r="J116" s="2">
+        <v>1.2647888485000003</v>
+      </c>
+      <c r="K116" s="2">
+        <v>1.4593398999999999E-3</v>
+      </c>
+      <c r="L116" s="2">
+        <v>6.1242180397000014</v>
+      </c>
+      <c r="M116" s="2">
+        <v>0.53442169949999996</v>
+      </c>
+      <c r="N116" s="2">
+        <v>4.8697999999999998E-4</v>
+      </c>
+      <c r="O116" s="2">
+        <v>0.15600999999999998</v>
+      </c>
+      <c r="P116" s="2">
+        <v>40.890752784100002</v>
+      </c>
+      <c r="Q116" s="2">
+        <v>4.4633243696999996</v>
+      </c>
+      <c r="R116" s="2">
+        <v>4.0268172795000003</v>
+      </c>
+      <c r="S116" s="2">
+        <v>0.37622475960000001</v>
+      </c>
+      <c r="T116" s="2">
+        <v>3.5421008388999997</v>
+      </c>
+      <c r="U116" s="2">
+        <v>2.5056096797999996</v>
+      </c>
+      <c r="V116" s="2">
+        <v>23.694637568500003</v>
+      </c>
+      <c r="W116" s="2">
+        <v>4.3206386792999991</v>
+      </c>
+      <c r="X116" s="2">
+        <v>9.0015000000000008E-3</v>
+      </c>
+      <c r="Y116" s="2">
+        <v>9.5305304044000039</v>
+      </c>
+      <c r="Z116" s="2">
+        <v>1.46470399E-2</v>
+      </c>
+      <c r="AA116" s="2">
+        <v>5.6982490896000009</v>
+      </c>
+      <c r="AB116" s="2">
+        <v>0.21192324959999997</v>
+      </c>
+      <c r="AC116" s="2">
+        <v>4.8664799999999994E-3</v>
+      </c>
+      <c r="AD116" s="2">
+        <v>0.13086400970000001</v>
+      </c>
+      <c r="AE116" s="2">
+        <v>58.529434948499997</v>
       </c>
     </row>
   </sheetData>
@@ -22983,7 +24560,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B8D9CE-6C58-4665-83B8-0D13D9F92D59}">
-  <dimension ref="A2:AE109"/>
+  <dimension ref="A2:AE116"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -31678,7 +33255,7 @@
         <v>139</v>
       </c>
       <c r="H105" s="2">
-        <v>359</v>
+        <v>445</v>
       </c>
       <c r="I105" s="2">
         <v>25</v>
@@ -31700,7 +33277,7 @@
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2">
-        <v>3631</v>
+        <v>3717</v>
       </c>
       <c r="Q105" s="2">
         <v>4276</v>
@@ -31721,7 +33298,7 @@
         <v>3336</v>
       </c>
       <c r="W105" s="2">
-        <v>4053</v>
+        <v>6234</v>
       </c>
       <c r="X105" s="2">
         <v>5</v>
@@ -31745,7 +33322,7 @@
         <v>2</v>
       </c>
       <c r="AE105" s="2">
-        <v>38034</v>
+        <v>40215</v>
       </c>
     </row>
     <row r="106" spans="1:31" x14ac:dyDescent="0.25">
@@ -32106,6 +33683,633 @@
         <v>37958</v>
       </c>
     </row>
+    <row r="110" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>133</v>
+      </c>
+      <c r="B110" s="2">
+        <v>1101</v>
+      </c>
+      <c r="C110" s="2">
+        <v>42</v>
+      </c>
+      <c r="D110" s="2">
+        <v>28</v>
+      </c>
+      <c r="E110" s="2">
+        <v>273</v>
+      </c>
+      <c r="F110" s="2">
+        <v>33</v>
+      </c>
+      <c r="G110" s="2">
+        <v>171</v>
+      </c>
+      <c r="H110" s="2">
+        <v>329</v>
+      </c>
+      <c r="I110" s="2">
+        <v>12</v>
+      </c>
+      <c r="J110" s="2">
+        <v>522</v>
+      </c>
+      <c r="K110" s="2">
+        <v>32</v>
+      </c>
+      <c r="L110" s="2">
+        <v>61</v>
+      </c>
+      <c r="M110" s="2">
+        <v>63</v>
+      </c>
+      <c r="N110" s="2">
+        <v>11</v>
+      </c>
+      <c r="O110" s="2">
+        <v>2</v>
+      </c>
+      <c r="P110" s="2">
+        <v>2680</v>
+      </c>
+      <c r="Q110" s="2">
+        <v>3922</v>
+      </c>
+      <c r="R110" s="2">
+        <v>3591</v>
+      </c>
+      <c r="S110" s="2">
+        <v>3</v>
+      </c>
+      <c r="T110" s="2">
+        <v>4202</v>
+      </c>
+      <c r="U110" s="2">
+        <v>731</v>
+      </c>
+      <c r="V110" s="2">
+        <v>2489</v>
+      </c>
+      <c r="W110" s="2">
+        <v>6065</v>
+      </c>
+      <c r="X110" s="2">
+        <v>7</v>
+      </c>
+      <c r="Y110" s="2">
+        <v>10053</v>
+      </c>
+      <c r="Z110" s="2">
+        <v>5</v>
+      </c>
+      <c r="AA110" s="2">
+        <v>562</v>
+      </c>
+      <c r="AB110" s="2">
+        <v>15857</v>
+      </c>
+      <c r="AC110" s="2">
+        <v>10</v>
+      </c>
+      <c r="AD110" s="2"/>
+      <c r="AE110" s="2">
+        <v>47497</v>
+      </c>
+    </row>
+    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>134</v>
+      </c>
+      <c r="B111" s="2">
+        <v>1021</v>
+      </c>
+      <c r="C111" s="2">
+        <v>95</v>
+      </c>
+      <c r="D111" s="2">
+        <v>13</v>
+      </c>
+      <c r="E111" s="2">
+        <v>302</v>
+      </c>
+      <c r="F111" s="2">
+        <v>28</v>
+      </c>
+      <c r="G111" s="2">
+        <v>344</v>
+      </c>
+      <c r="H111" s="2">
+        <v>481</v>
+      </c>
+      <c r="I111" s="2">
+        <v>16</v>
+      </c>
+      <c r="J111" s="2">
+        <v>395</v>
+      </c>
+      <c r="K111" s="2">
+        <v>58</v>
+      </c>
+      <c r="L111" s="2">
+        <v>59</v>
+      </c>
+      <c r="M111" s="2">
+        <v>66</v>
+      </c>
+      <c r="N111" s="2">
+        <v>13</v>
+      </c>
+      <c r="O111" s="2">
+        <v>2</v>
+      </c>
+      <c r="P111" s="2">
+        <v>2893</v>
+      </c>
+      <c r="Q111" s="2">
+        <v>3839</v>
+      </c>
+      <c r="R111" s="2">
+        <v>3466</v>
+      </c>
+      <c r="S111" s="2">
+        <v>8</v>
+      </c>
+      <c r="T111" s="2">
+        <v>4164</v>
+      </c>
+      <c r="U111" s="2">
+        <v>785</v>
+      </c>
+      <c r="V111" s="2">
+        <v>2510</v>
+      </c>
+      <c r="W111" s="2">
+        <v>5793</v>
+      </c>
+      <c r="X111" s="2">
+        <v>7</v>
+      </c>
+      <c r="Y111" s="2">
+        <v>10270</v>
+      </c>
+      <c r="Z111" s="2">
+        <v>7</v>
+      </c>
+      <c r="AA111" s="2">
+        <v>600</v>
+      </c>
+      <c r="AB111" s="2">
+        <v>5512</v>
+      </c>
+      <c r="AC111" s="2">
+        <v>11</v>
+      </c>
+      <c r="AD111" s="2">
+        <v>5</v>
+      </c>
+      <c r="AE111" s="2">
+        <v>36977</v>
+      </c>
+    </row>
+    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>135</v>
+      </c>
+      <c r="B112" s="2">
+        <v>1115</v>
+      </c>
+      <c r="C112" s="2">
+        <v>41</v>
+      </c>
+      <c r="D112" s="2">
+        <v>9</v>
+      </c>
+      <c r="E112" s="2">
+        <v>264</v>
+      </c>
+      <c r="F112" s="2">
+        <v>16</v>
+      </c>
+      <c r="G112" s="2">
+        <v>276</v>
+      </c>
+      <c r="H112" s="2">
+        <v>275</v>
+      </c>
+      <c r="I112" s="2">
+        <v>15</v>
+      </c>
+      <c r="J112" s="2">
+        <v>385</v>
+      </c>
+      <c r="K112" s="2">
+        <v>59</v>
+      </c>
+      <c r="L112" s="2">
+        <v>45</v>
+      </c>
+      <c r="M112" s="2">
+        <v>66</v>
+      </c>
+      <c r="N112" s="2">
+        <v>6</v>
+      </c>
+      <c r="O112" s="2">
+        <v>1</v>
+      </c>
+      <c r="P112" s="2">
+        <v>2573</v>
+      </c>
+      <c r="Q112" s="2">
+        <v>3927</v>
+      </c>
+      <c r="R112" s="2">
+        <v>3461</v>
+      </c>
+      <c r="S112" s="2">
+        <v>8</v>
+      </c>
+      <c r="T112" s="2">
+        <v>4260</v>
+      </c>
+      <c r="U112" s="2">
+        <v>758</v>
+      </c>
+      <c r="V112" s="2">
+        <v>2380</v>
+      </c>
+      <c r="W112" s="2">
+        <v>6044</v>
+      </c>
+      <c r="X112" s="2">
+        <v>6</v>
+      </c>
+      <c r="Y112" s="2">
+        <v>10723</v>
+      </c>
+      <c r="Z112" s="2">
+        <v>6</v>
+      </c>
+      <c r="AA112" s="2">
+        <v>666</v>
+      </c>
+      <c r="AB112" s="2">
+        <v>5516</v>
+      </c>
+      <c r="AC112" s="2">
+        <v>7</v>
+      </c>
+      <c r="AD112" s="2"/>
+      <c r="AE112" s="2">
+        <v>37762</v>
+      </c>
+    </row>
+    <row r="113" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>136</v>
+      </c>
+      <c r="B113" s="2">
+        <v>836</v>
+      </c>
+      <c r="C113" s="2">
+        <v>17</v>
+      </c>
+      <c r="D113" s="2">
+        <v>1</v>
+      </c>
+      <c r="E113" s="2">
+        <v>157</v>
+      </c>
+      <c r="F113" s="2">
+        <v>11</v>
+      </c>
+      <c r="G113" s="2">
+        <v>281</v>
+      </c>
+      <c r="H113" s="2">
+        <v>142</v>
+      </c>
+      <c r="I113" s="2"/>
+      <c r="J113" s="2">
+        <v>214</v>
+      </c>
+      <c r="K113" s="2">
+        <v>14</v>
+      </c>
+      <c r="L113" s="2">
+        <v>13</v>
+      </c>
+      <c r="M113" s="2">
+        <v>38</v>
+      </c>
+      <c r="N113" s="2">
+        <v>4</v>
+      </c>
+      <c r="O113" s="2"/>
+      <c r="P113" s="2">
+        <v>1728</v>
+      </c>
+      <c r="Q113" s="2">
+        <v>22</v>
+      </c>
+      <c r="R113" s="2">
+        <v>3640</v>
+      </c>
+      <c r="S113" s="2"/>
+      <c r="T113" s="2">
+        <v>4253</v>
+      </c>
+      <c r="U113" s="2">
+        <v>808</v>
+      </c>
+      <c r="V113" s="2">
+        <v>2276</v>
+      </c>
+      <c r="W113" s="2">
+        <v>6028</v>
+      </c>
+      <c r="X113" s="2"/>
+      <c r="Y113" s="2">
+        <v>10281</v>
+      </c>
+      <c r="Z113" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA113" s="2">
+        <v>713</v>
+      </c>
+      <c r="AB113" s="2">
+        <v>420</v>
+      </c>
+      <c r="AC113" s="2">
+        <v>4</v>
+      </c>
+      <c r="AD113" s="2"/>
+      <c r="AE113" s="2">
+        <v>28447</v>
+      </c>
+    </row>
+    <row r="114" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>137</v>
+      </c>
+      <c r="B114" s="2">
+        <v>699</v>
+      </c>
+      <c r="C114" s="2">
+        <v>2</v>
+      </c>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2">
+        <v>140</v>
+      </c>
+      <c r="F114" s="2">
+        <v>9</v>
+      </c>
+      <c r="G114" s="2">
+        <v>122</v>
+      </c>
+      <c r="H114" s="2">
+        <v>115</v>
+      </c>
+      <c r="I114" s="2"/>
+      <c r="J114" s="2">
+        <v>130</v>
+      </c>
+      <c r="K114" s="2"/>
+      <c r="L114" s="2"/>
+      <c r="M114" s="2">
+        <v>30</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
+      <c r="P114" s="2">
+        <v>1247</v>
+      </c>
+      <c r="Q114" s="2">
+        <v>12</v>
+      </c>
+      <c r="R114" s="2">
+        <v>3415</v>
+      </c>
+      <c r="S114" s="2"/>
+      <c r="T114" s="2">
+        <v>4125</v>
+      </c>
+      <c r="U114" s="2">
+        <v>647</v>
+      </c>
+      <c r="V114" s="2">
+        <v>2235</v>
+      </c>
+      <c r="W114" s="2">
+        <v>5822</v>
+      </c>
+      <c r="X114" s="2"/>
+      <c r="Y114" s="2">
+        <v>9463</v>
+      </c>
+      <c r="Z114" s="2"/>
+      <c r="AA114" s="2">
+        <v>604</v>
+      </c>
+      <c r="AB114" s="2">
+        <v>386</v>
+      </c>
+      <c r="AC114" s="2"/>
+      <c r="AD114" s="2"/>
+      <c r="AE114" s="2">
+        <v>26709</v>
+      </c>
+    </row>
+    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>138</v>
+      </c>
+      <c r="B115" s="2">
+        <v>855</v>
+      </c>
+      <c r="C115" s="2">
+        <v>26</v>
+      </c>
+      <c r="D115" s="2">
+        <v>12</v>
+      </c>
+      <c r="E115" s="2">
+        <v>2134</v>
+      </c>
+      <c r="F115" s="2">
+        <v>14</v>
+      </c>
+      <c r="G115" s="2">
+        <v>175</v>
+      </c>
+      <c r="H115" s="2">
+        <v>208</v>
+      </c>
+      <c r="I115" s="2">
+        <v>11</v>
+      </c>
+      <c r="J115" s="2">
+        <v>287</v>
+      </c>
+      <c r="K115" s="2">
+        <v>21</v>
+      </c>
+      <c r="L115" s="2">
+        <v>45</v>
+      </c>
+      <c r="M115" s="2">
+        <v>69</v>
+      </c>
+      <c r="N115" s="2">
+        <v>3</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" s="2">
+        <v>3860</v>
+      </c>
+      <c r="Q115" s="2">
+        <v>4002</v>
+      </c>
+      <c r="R115" s="2">
+        <v>3510</v>
+      </c>
+      <c r="S115" s="2">
+        <v>14</v>
+      </c>
+      <c r="T115" s="2">
+        <v>4411</v>
+      </c>
+      <c r="U115" s="2">
+        <v>890</v>
+      </c>
+      <c r="V115" s="2">
+        <v>2577</v>
+      </c>
+      <c r="W115" s="2">
+        <v>5941</v>
+      </c>
+      <c r="X115" s="2">
+        <v>7</v>
+      </c>
+      <c r="Y115" s="2">
+        <v>9686</v>
+      </c>
+      <c r="Z115" s="2">
+        <v>9</v>
+      </c>
+      <c r="AA115" s="2">
+        <v>687</v>
+      </c>
+      <c r="AB115" s="2">
+        <v>5184</v>
+      </c>
+      <c r="AC115" s="2">
+        <v>7</v>
+      </c>
+      <c r="AD115" s="2">
+        <v>2</v>
+      </c>
+      <c r="AE115" s="2">
+        <v>36927</v>
+      </c>
+    </row>
+    <row r="116" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>139</v>
+      </c>
+      <c r="B116" s="2">
+        <v>1414</v>
+      </c>
+      <c r="C116" s="2">
+        <v>37</v>
+      </c>
+      <c r="D116" s="2">
+        <v>13</v>
+      </c>
+      <c r="E116" s="2">
+        <v>234</v>
+      </c>
+      <c r="F116" s="2">
+        <v>23</v>
+      </c>
+      <c r="G116" s="2">
+        <v>266</v>
+      </c>
+      <c r="H116" s="2">
+        <v>217</v>
+      </c>
+      <c r="I116" s="2">
+        <v>13</v>
+      </c>
+      <c r="J116" s="2">
+        <v>352</v>
+      </c>
+      <c r="K116" s="2">
+        <v>10</v>
+      </c>
+      <c r="L116" s="2">
+        <v>41</v>
+      </c>
+      <c r="M116" s="2">
+        <v>72</v>
+      </c>
+      <c r="N116" s="2">
+        <v>5</v>
+      </c>
+      <c r="O116" s="2">
+        <v>4</v>
+      </c>
+      <c r="P116" s="2">
+        <v>2701</v>
+      </c>
+      <c r="Q116" s="2">
+        <v>3994</v>
+      </c>
+      <c r="R116" s="2">
+        <v>3585</v>
+      </c>
+      <c r="S116" s="2">
+        <v>20</v>
+      </c>
+      <c r="T116" s="2">
+        <v>3873</v>
+      </c>
+      <c r="U116" s="2">
+        <v>440</v>
+      </c>
+      <c r="V116" s="2">
+        <v>2670</v>
+      </c>
+      <c r="W116" s="2">
+        <v>5885</v>
+      </c>
+      <c r="X116" s="2">
+        <v>6</v>
+      </c>
+      <c r="Y116" s="2">
+        <v>9758</v>
+      </c>
+      <c r="Z116" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA116" s="2">
+        <v>736</v>
+      </c>
+      <c r="AB116" s="2">
+        <v>5169</v>
+      </c>
+      <c r="AC116" s="2">
+        <v>8</v>
+      </c>
+      <c r="AD116" s="2">
+        <v>7</v>
+      </c>
+      <c r="AE116" s="2">
+        <v>36170</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Base_Op_Cam.xlsx
+++ b/data/Base_Op_Cam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mefp\Sergio Garnica\Documents\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69D7CCF-1C8D-4BB1-9A34-484BA89BFE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6625E895-8304-4C51-981A-08AABB402B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{D18D9BAD-78DE-4368-BCF3-29E6374A660B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D18D9BAD-78DE-4368-BCF3-29E6374A660B}"/>
   </bookViews>
   <sheets>
     <sheet name="TC" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,9 @@
   </sheets>
   <calcPr calcId="191029" concurrentCalc="0" concurrentManualCount="4"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId4"/>
-    <pivotCache cacheId="8" r:id="rId5"/>
-    <pivotCache cacheId="11" r:id="rId6"/>
+    <pivotCache cacheId="13" r:id="rId4"/>
+    <pivotCache cacheId="16" r:id="rId5"/>
+    <pivotCache cacheId="19" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="146">
   <si>
     <t>Nombre</t>
   </si>
@@ -524,6 +524,24 @@
   <si>
     <t>2026-09-15</t>
   </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
 </sst>
 </file>
 
@@ -580,14 +598,17 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46282.51002627315" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{04D15196-6A10-4FCA-A07B-7666B41B44BD}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46288.631337384257" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{9ECE6D2C-0019-46A8-93F5-B57014A573FD}">
   <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="10">
+  <cacheFields count="9">
     <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
     </cacheField>
     <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+      <sharedItems count="2">
+        <s v="[Transaccion].[Transaccion].&amp;[Compra]" c="Compra"/>
+        <s v="[Transaccion].[Transaccion].&amp;[Venta]" c="Venta"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
@@ -602,7 +623,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
     </cacheField>
     <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
-      <sharedItems count="107">
+      <sharedItems count="113">
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
@@ -710,6 +731,543 @@
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-13T00:00:00]" c="2026-09-13"/>
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-14T00:00:00]" c="2026-09-14"/>
         <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-15T00:00:00]" c="2026-09-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-16T00:00:00]" c="2026-09-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-17T00:00:00]" c="2026-09-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-18T00:00:00]" c="2026-09-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-19T00:00:00]" c="2026-09-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-20T00:00:00]" c="2026-09-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-21T00:00:00]" c="2026-09-21"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
+      <sharedItems count="14">
+        <s v="[Entidades].[Sigla].&amp;[BCR]" c="BCR"/>
+        <s v="[Entidades].[Sigla].&amp;[BEC]" c="BEC"/>
+        <s v="[Entidades].[Sigla].&amp;[BFO]" c="BFO"/>
+        <s v="[Entidades].[Sigla].&amp;[BGA]" c="BGA"/>
+        <s v="[Entidades].[Sigla].&amp;[BIE]" c="BIE"/>
+        <s v="[Entidades].[Sigla].&amp;[BIS]" c="BIS"/>
+        <s v="[Entidades].[Sigla].&amp;[BME]" c="BME"/>
+        <s v="[Entidades].[Sigla].&amp;[BNA]" c="BNA"/>
+        <s v="[Entidades].[Sigla].&amp;[BNB]" c="BNB"/>
+        <s v="[Entidades].[Sigla].&amp;[BPR]" c="BPR"/>
+        <s v="[Entidades].[Sigla].&amp;[BSO]" c="BSO"/>
+        <s v="[Entidades].[Sigla].&amp;[BUN]" c="BUN"/>
+        <s v="[Entidades].[Sigla].&amp;[PCO]" c="PCO"/>
+        <s v="[Entidades].[Sigla].&amp;[PEF]" c="PEF"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Numero Operaciones]" caption="Numero Operaciones" numFmtId="0" hierarchy="28" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="29">
+    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Categoria]" caption="Cod Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Categoria].[All]" allUniqueName="[Actividad Economica].[Cod Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Sector Actividad]" caption="Cod Sector Actividad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" allUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion].[All]" allUniqueName="[Actividad Economica].[Descripcion].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion Categoria]" caption="Descripcion Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" allUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Concepto].[Cod Concepto]" caption="Cod Concepto" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Concepto].[Cod Concepto].[All]" allUniqueName="[Concepto].[Cod Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Concepto].[Concepto]" caption="Concepto" attribute="1" defaultMemberUniqueName="[Concepto].[Concepto].[All]" allUniqueName="[Concepto].[Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Entidades].[Cod Entidad]" caption="Cod Entidad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Entidades].[Cod Entidad].[All]" allUniqueName="[Entidades].[Cod Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Entidades].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Entidades].[Nombre].[All]" allUniqueName="[Entidades].[Nombre].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Entidades].[Sigla]" caption="Sigla" attribute="1" defaultMemberUniqueName="[Entidades].[Sigla].[All]" allUniqueName="[Entidades].[Sigla].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="7"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Entidades].[Tipo Entidad]" caption="Tipo Entidad" attribute="1" defaultMemberUniqueName="[Entidades].[Tipo Entidad].[All]" allUniqueName="[Entidades].[Tipo Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Estrato].[Cod Estrato]" caption="Cod Estrato" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Estrato].[Cod Estrato].[All]" allUniqueName="[Estrato].[Cod Estrato].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Estrato].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Estrato].[Descripcion].[All]" allUniqueName="[Estrato].[Descripcion].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Moneda Cambio].[Cod Moneda]" caption="Cod Moneda" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Moneda Cambio].[Cod Moneda].[All]" allUniqueName="[Moneda Cambio].[Cod Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Moneda Cambio].[Moneda]" caption="Moneda" attribute="1" defaultMemberUniqueName="[Moneda Cambio].[Moneda].[All]" allUniqueName="[Moneda Cambio].[Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Monto Menor].[Cod Monto Menor]" caption="Cod Monto Menor" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Monto Menor].[Cod Monto Menor].[All]" allUniqueName="[Monto Menor].[Cod Monto Menor].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Monto Menor].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Monto Menor].[Descripcion].[All]" allUniqueName="[Monto Menor].[Descripcion].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="5"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Subsistema].[Cod Subsistema]" caption="Cod Subsistema" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Subsistema].[Cod Subsistema].[All]" allUniqueName="[Subsistema].[Cod Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Subsistema].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Subsistema].[Nombre].[All]" allUniqueName="[Subsistema].[Nombre].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Subsistema].[Sigla Subsistema]" caption="Sigla Subsistema" attribute="1" defaultMemberUniqueName="[Subsistema].[Sigla Subsistema].[All]" allUniqueName="[Subsistema].[Sigla Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha]" caption="Cod Fecha" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Fecha]" caption="Fecha" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="6"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes]" caption="Ultimo Dia Mes" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transaccion].[Cod Transaccion]" caption="Cod Transaccion" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Transaccion].[Cod Transaccion].[All]" allUniqueName="[Transaccion].[Cod Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transaccion].[Transaccion]" caption="Transaccion" attribute="1" defaultMemberUniqueName="[Transaccion].[Transaccion].[All]" allUniqueName="[Transaccion].[Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Monto Usd]" caption="Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Usd]" caption="Tipo Cambio Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Mm Usd]" caption="Tipo Cambio Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Numero Operaciones]" caption="Numero Operaciones" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="8"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="10">
+    <dimension name="Actividad Economica" uniqueName="[Actividad Economica]" caption="Actividad Economica"/>
+    <dimension name="Concepto" uniqueName="[Concepto]" caption="Concepto"/>
+    <dimension name="Entidades" uniqueName="[Entidades]" caption="Entidades"/>
+    <dimension name="Estrato" uniqueName="[Estrato]" caption="Estrato"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Moneda Cambio" uniqueName="[Moneda Cambio]" caption="Moneda Cambio"/>
+    <dimension name="Monto Menor" uniqueName="[Monto Menor]" caption="Monto Menor"/>
+    <dimension name="Subsistema" uniqueName="[Subsistema]" caption="Subsistema"/>
+    <dimension name="Tipo Cambio Fecha Dia" uniqueName="[Tipo Cambio Fecha Dia]" caption="Tipo Cambio Fecha Dia"/>
+    <dimension name="Transaccion" uniqueName="[Transaccion]" caption="Transaccion"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Operaciones Cambiarias" caption="Fact Operaciones Cambiarias"/>
+  </measureGroups>
+  <maps count="9">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+    <map measureGroup="0" dimension="8"/>
+    <map measureGroup="0" dimension="9"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46288.631558912035" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{F7995ADC-F0B3-4CE9-B66F-D51574EF46B6}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="9">
+    <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
+      <sharedItems count="2">
+        <s v="[Transaccion].[Transaccion].&amp;[Compra]" c="Compra"/>
+        <s v="[Transaccion].[Transaccion].&amp;[Venta]" c="Venta"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda]" caption="Cod Moneda" numFmtId="0" hierarchy="12" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda].[Moneda]" caption="Moneda" propertyName="Moneda" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Monto Menor].[Descripcion].[Descripcion]" caption="Descripcion" numFmtId="0" hierarchy="15" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
+      <sharedItems count="113">
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-04T00:00:00]" c="2026-06-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-05T00:00:00]" c="2026-06-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-06T00:00:00]" c="2026-06-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-07T00:00:00]" c="2026-06-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-08T00:00:00]" c="2026-06-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-09T00:00:00]" c="2026-06-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-10T00:00:00]" c="2026-06-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-11T00:00:00]" c="2026-06-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-12T00:00:00]" c="2026-06-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-13T00:00:00]" c="2026-06-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-14T00:00:00]" c="2026-06-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-15T00:00:00]" c="2026-06-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-16T00:00:00]" c="2026-06-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-17T00:00:00]" c="2026-06-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-18T00:00:00]" c="2026-06-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-19T00:00:00]" c="2026-06-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-20T00:00:00]" c="2026-06-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-21T00:00:00]" c="2026-06-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-22T00:00:00]" c="2026-06-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-23T00:00:00]" c="2026-06-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-24T00:00:00]" c="2026-06-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-25T00:00:00]" c="2026-06-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-26T00:00:00]" c="2026-06-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-27T00:00:00]" c="2026-06-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-28T00:00:00]" c="2026-06-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-29T00:00:00]" c="2026-06-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-30T00:00:00]" c="2026-06-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-01T00:00:00]" c="2026-07-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-02T00:00:00]" c="2026-07-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-03T00:00:00]" c="2026-07-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-04T00:00:00]" c="2026-07-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-05T00:00:00]" c="2026-07-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-06T00:00:00]" c="2026-07-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-07T00:00:00]" c="2026-07-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-08T00:00:00]" c="2026-07-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-09T00:00:00]" c="2026-07-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-10T00:00:00]" c="2026-07-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-11T00:00:00]" c="2026-07-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-12T00:00:00]" c="2026-07-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-13T00:00:00]" c="2026-07-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-14T00:00:00]" c="2026-07-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-15T00:00:00]" c="2026-07-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-16T00:00:00]" c="2026-07-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-17T00:00:00]" c="2026-07-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-18T00:00:00]" c="2026-07-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-19T00:00:00]" c="2026-07-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-20T00:00:00]" c="2026-07-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-21T00:00:00]" c="2026-07-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-22T00:00:00]" c="2026-07-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-23T00:00:00]" c="2026-07-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-24T00:00:00]" c="2026-07-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-25T00:00:00]" c="2026-07-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-26T00:00:00]" c="2026-07-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-27T00:00:00]" c="2026-07-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-28T00:00:00]" c="2026-07-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-29T00:00:00]" c="2026-07-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-30T00:00:00]" c="2026-07-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-31T00:00:00]" c="2026-07-31"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-01T00:00:00]" c="2026-08-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-02T00:00:00]" c="2026-08-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-03T00:00:00]" c="2026-08-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-04T00:00:00]" c="2026-08-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-05T00:00:00]" c="2026-08-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-06T00:00:00]" c="2026-08-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-07T00:00:00]" c="2026-08-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-08T00:00:00]" c="2026-08-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-09T00:00:00]" c="2026-08-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-10T00:00:00]" c="2026-08-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-11T00:00:00]" c="2026-08-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-12T00:00:00]" c="2026-08-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-13T00:00:00]" c="2026-08-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-14T00:00:00]" c="2026-08-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-15T00:00:00]" c="2026-08-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-16T00:00:00]" c="2026-08-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-17T00:00:00]" c="2026-08-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-18T00:00:00]" c="2026-08-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-19T00:00:00]" c="2026-08-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-20T00:00:00]" c="2026-08-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-21T00:00:00]" c="2026-08-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-22T00:00:00]" c="2026-08-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-23T00:00:00]" c="2026-08-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-24T00:00:00]" c="2026-08-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-25T00:00:00]" c="2026-08-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-26T00:00:00]" c="2026-08-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-27T00:00:00]" c="2026-08-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-28T00:00:00]" c="2026-08-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-29T00:00:00]" c="2026-08-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-30T00:00:00]" c="2026-08-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-31T00:00:00]" c="2026-08-31"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-01T00:00:00]" c="2026-09-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-02T00:00:00]" c="2026-09-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-03T00:00:00]" c="2026-09-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-04T00:00:00]" c="2026-09-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-05T00:00:00]" c="2026-09-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-06T00:00:00]" c="2026-09-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-07T00:00:00]" c="2026-09-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-08T00:00:00]" c="2026-09-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-09T00:00:00]" c="2026-09-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-10T00:00:00]" c="2026-09-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-11T00:00:00]" c="2026-09-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-12T00:00:00]" c="2026-09-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-13T00:00:00]" c="2026-09-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-14T00:00:00]" c="2026-09-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-15T00:00:00]" c="2026-09-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-16T00:00:00]" c="2026-09-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-17T00:00:00]" c="2026-09-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-18T00:00:00]" c="2026-09-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-19T00:00:00]" c="2026-09-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-20T00:00:00]" c="2026-09-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-21T00:00:00]" c="2026-09-21"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
+      <sharedItems count="14">
+        <s v="[Entidades].[Sigla].&amp;[BCR]" c="BCR"/>
+        <s v="[Entidades].[Sigla].&amp;[BEC]" c="BEC"/>
+        <s v="[Entidades].[Sigla].&amp;[BFO]" c="BFO"/>
+        <s v="[Entidades].[Sigla].&amp;[BGA]" c="BGA"/>
+        <s v="[Entidades].[Sigla].&amp;[BIE]" c="BIE"/>
+        <s v="[Entidades].[Sigla].&amp;[BIS]" c="BIS"/>
+        <s v="[Entidades].[Sigla].&amp;[BME]" c="BME"/>
+        <s v="[Entidades].[Sigla].&amp;[BNA]" c="BNA"/>
+        <s v="[Entidades].[Sigla].&amp;[BNB]" c="BNB"/>
+        <s v="[Entidades].[Sigla].&amp;[BPR]" c="BPR"/>
+        <s v="[Entidades].[Sigla].&amp;[BSO]" c="BSO"/>
+        <s v="[Entidades].[Sigla].&amp;[BUN]" c="BUN"/>
+        <s v="[Entidades].[Sigla].&amp;[PCO]" c="PCO"/>
+        <s v="[Entidades].[Sigla].&amp;[PEF]" c="PEF"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" numFmtId="0" hierarchy="26" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="29">
+    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Categoria]" caption="Cod Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Categoria].[All]" allUniqueName="[Actividad Economica].[Cod Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Sector Actividad]" caption="Cod Sector Actividad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" allUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion].[All]" allUniqueName="[Actividad Economica].[Descripcion].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion Categoria]" caption="Descripcion Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" allUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Concepto].[Cod Concepto]" caption="Cod Concepto" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Concepto].[Cod Concepto].[All]" allUniqueName="[Concepto].[Cod Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Concepto].[Concepto]" caption="Concepto" attribute="1" defaultMemberUniqueName="[Concepto].[Concepto].[All]" allUniqueName="[Concepto].[Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Entidades].[Cod Entidad]" caption="Cod Entidad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Entidades].[Cod Entidad].[All]" allUniqueName="[Entidades].[Cod Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Entidades].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Entidades].[Nombre].[All]" allUniqueName="[Entidades].[Nombre].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Entidades].[Sigla]" caption="Sigla" attribute="1" defaultMemberUniqueName="[Entidades].[Sigla].[All]" allUniqueName="[Entidades].[Sigla].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="7"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Entidades].[Tipo Entidad]" caption="Tipo Entidad" attribute="1" defaultMemberUniqueName="[Entidades].[Tipo Entidad].[All]" allUniqueName="[Entidades].[Tipo Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Estrato].[Cod Estrato]" caption="Cod Estrato" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Estrato].[Cod Estrato].[All]" allUniqueName="[Estrato].[Cod Estrato].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Estrato].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Estrato].[Descripcion].[All]" allUniqueName="[Estrato].[Descripcion].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Moneda Cambio].[Cod Moneda]" caption="Cod Moneda" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Moneda Cambio].[Cod Moneda].[All]" allUniqueName="[Moneda Cambio].[Cod Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Moneda Cambio].[Moneda]" caption="Moneda" attribute="1" defaultMemberUniqueName="[Moneda Cambio].[Moneda].[All]" allUniqueName="[Moneda Cambio].[Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Monto Menor].[Cod Monto Menor]" caption="Cod Monto Menor" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Monto Menor].[Cod Monto Menor].[All]" allUniqueName="[Monto Menor].[Cod Monto Menor].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Monto Menor].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Monto Menor].[Descripcion].[All]" allUniqueName="[Monto Menor].[Descripcion].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="5"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Subsistema].[Cod Subsistema]" caption="Cod Subsistema" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Subsistema].[Cod Subsistema].[All]" allUniqueName="[Subsistema].[Cod Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Subsistema].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Subsistema].[Nombre].[All]" allUniqueName="[Subsistema].[Nombre].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Subsistema].[Sigla Subsistema]" caption="Sigla Subsistema" attribute="1" defaultMemberUniqueName="[Subsistema].[Sigla Subsistema].[All]" allUniqueName="[Subsistema].[Sigla Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha]" caption="Cod Fecha" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Fecha]" caption="Fecha" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="6"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes]" caption="Ultimo Dia Mes" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transaccion].[Cod Transaccion]" caption="Cod Transaccion" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Transaccion].[Cod Transaccion].[All]" allUniqueName="[Transaccion].[Cod Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transaccion].[Transaccion]" caption="Transaccion" attribute="1" defaultMemberUniqueName="[Transaccion].[Transaccion].[All]" allUniqueName="[Transaccion].[Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Monto Usd]" caption="Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Usd]" caption="Tipo Cambio Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="8"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Mm Usd]" caption="Tipo Cambio Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Numero Operaciones]" caption="Numero Operaciones" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="10">
+    <dimension name="Actividad Economica" uniqueName="[Actividad Economica]" caption="Actividad Economica"/>
+    <dimension name="Concepto" uniqueName="[Concepto]" caption="Concepto"/>
+    <dimension name="Entidades" uniqueName="[Entidades]" caption="Entidades"/>
+    <dimension name="Estrato" uniqueName="[Estrato]" caption="Estrato"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Moneda Cambio" uniqueName="[Moneda Cambio]" caption="Moneda Cambio"/>
+    <dimension name="Monto Menor" uniqueName="[Monto Menor]" caption="Monto Menor"/>
+    <dimension name="Subsistema" uniqueName="[Subsistema]" caption="Subsistema"/>
+    <dimension name="Tipo Cambio Fecha Dia" uniqueName="[Tipo Cambio Fecha Dia]" caption="Tipo Cambio Fecha Dia"/>
+    <dimension name="Transaccion" uniqueName="[Transaccion]" caption="Transaccion"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Operaciones Cambiarias" caption="Fact Operaciones Cambiarias"/>
+  </measureGroups>
+  <maps count="9">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+    <map measureGroup="0" dimension="8"/>
+    <map measureGroup="0" dimension="9"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46288.631754745373" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{04D15196-6A10-4FCA-A07B-7666B41B44BD}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="10">
+    <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda]" caption="Cod Moneda" numFmtId="0" hierarchy="12" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda].[Moneda]" caption="Moneda" propertyName="Moneda" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Monto Menor].[Descripcion].[Descripcion]" caption="Descripcion" numFmtId="0" hierarchy="15" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
+      <sharedItems count="113">
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-04T00:00:00]" c="2026-06-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-05T00:00:00]" c="2026-06-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-06T00:00:00]" c="2026-06-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-07T00:00:00]" c="2026-06-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-08T00:00:00]" c="2026-06-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-09T00:00:00]" c="2026-06-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-10T00:00:00]" c="2026-06-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-11T00:00:00]" c="2026-06-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-12T00:00:00]" c="2026-06-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-13T00:00:00]" c="2026-06-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-14T00:00:00]" c="2026-06-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-15T00:00:00]" c="2026-06-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-16T00:00:00]" c="2026-06-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-17T00:00:00]" c="2026-06-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-18T00:00:00]" c="2026-06-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-19T00:00:00]" c="2026-06-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-20T00:00:00]" c="2026-06-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-21T00:00:00]" c="2026-06-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-22T00:00:00]" c="2026-06-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-23T00:00:00]" c="2026-06-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-24T00:00:00]" c="2026-06-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-25T00:00:00]" c="2026-06-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-26T00:00:00]" c="2026-06-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-27T00:00:00]" c="2026-06-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-28T00:00:00]" c="2026-06-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-29T00:00:00]" c="2026-06-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-30T00:00:00]" c="2026-06-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-01T00:00:00]" c="2026-07-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-02T00:00:00]" c="2026-07-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-03T00:00:00]" c="2026-07-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-04T00:00:00]" c="2026-07-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-05T00:00:00]" c="2026-07-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-06T00:00:00]" c="2026-07-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-07T00:00:00]" c="2026-07-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-08T00:00:00]" c="2026-07-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-09T00:00:00]" c="2026-07-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-10T00:00:00]" c="2026-07-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-11T00:00:00]" c="2026-07-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-12T00:00:00]" c="2026-07-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-13T00:00:00]" c="2026-07-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-14T00:00:00]" c="2026-07-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-15T00:00:00]" c="2026-07-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-16T00:00:00]" c="2026-07-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-17T00:00:00]" c="2026-07-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-18T00:00:00]" c="2026-07-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-19T00:00:00]" c="2026-07-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-20T00:00:00]" c="2026-07-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-21T00:00:00]" c="2026-07-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-22T00:00:00]" c="2026-07-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-23T00:00:00]" c="2026-07-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-24T00:00:00]" c="2026-07-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-25T00:00:00]" c="2026-07-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-26T00:00:00]" c="2026-07-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-27T00:00:00]" c="2026-07-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-28T00:00:00]" c="2026-07-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-29T00:00:00]" c="2026-07-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-30T00:00:00]" c="2026-07-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-31T00:00:00]" c="2026-07-31"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-01T00:00:00]" c="2026-08-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-02T00:00:00]" c="2026-08-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-03T00:00:00]" c="2026-08-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-04T00:00:00]" c="2026-08-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-05T00:00:00]" c="2026-08-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-06T00:00:00]" c="2026-08-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-07T00:00:00]" c="2026-08-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-08T00:00:00]" c="2026-08-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-09T00:00:00]" c="2026-08-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-10T00:00:00]" c="2026-08-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-11T00:00:00]" c="2026-08-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-12T00:00:00]" c="2026-08-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-13T00:00:00]" c="2026-08-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-14T00:00:00]" c="2026-08-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-15T00:00:00]" c="2026-08-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-16T00:00:00]" c="2026-08-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-17T00:00:00]" c="2026-08-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-18T00:00:00]" c="2026-08-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-19T00:00:00]" c="2026-08-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-20T00:00:00]" c="2026-08-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-21T00:00:00]" c="2026-08-21"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-22T00:00:00]" c="2026-08-22"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-23T00:00:00]" c="2026-08-23"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-24T00:00:00]" c="2026-08-24"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-25T00:00:00]" c="2026-08-25"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-26T00:00:00]" c="2026-08-26"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-27T00:00:00]" c="2026-08-27"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-28T00:00:00]" c="2026-08-28"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-29T00:00:00]" c="2026-08-29"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-30T00:00:00]" c="2026-08-30"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-31T00:00:00]" c="2026-08-31"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-01T00:00:00]" c="2026-09-01"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-02T00:00:00]" c="2026-09-02"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-03T00:00:00]" c="2026-09-03"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-04T00:00:00]" c="2026-09-04"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-05T00:00:00]" c="2026-09-05"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-06T00:00:00]" c="2026-09-06"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-07T00:00:00]" c="2026-09-07"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-08T00:00:00]" c="2026-09-08"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-09T00:00:00]" c="2026-09-09"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-10T00:00:00]" c="2026-09-10"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-11T00:00:00]" c="2026-09-11"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-12T00:00:00]" c="2026-09-12"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-13T00:00:00]" c="2026-09-13"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-14T00:00:00]" c="2026-09-14"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-15T00:00:00]" c="2026-09-15"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-16T00:00:00]" c="2026-09-16"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-17T00:00:00]" c="2026-09-17"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-18T00:00:00]" c="2026-09-18"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-19T00:00:00]" c="2026-09-19"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-20T00:00:00]" c="2026-09-20"/>
+        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-21T00:00:00]" c="2026-09-21"/>
       </sharedItems>
     </cacheField>
     <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
@@ -842,531 +1400,9 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46282.510346990741" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{F7995ADC-F0B3-4CE9-B66F-D51574EF46B6}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="9">
-    <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
-      <sharedItems count="2">
-        <s v="[Transaccion].[Transaccion].&amp;[Compra]" c="Compra"/>
-        <s v="[Transaccion].[Transaccion].&amp;[Venta]" c="Venta"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda]" caption="Cod Moneda" numFmtId="0" hierarchy="12" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda].[Moneda]" caption="Moneda" propertyName="Moneda" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Monto Menor].[Descripcion].[Descripcion]" caption="Descripcion" numFmtId="0" hierarchy="15" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
-      <sharedItems count="107">
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-04T00:00:00]" c="2026-06-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-05T00:00:00]" c="2026-06-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-06T00:00:00]" c="2026-06-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-07T00:00:00]" c="2026-06-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-08T00:00:00]" c="2026-06-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-09T00:00:00]" c="2026-06-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-10T00:00:00]" c="2026-06-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-11T00:00:00]" c="2026-06-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-12T00:00:00]" c="2026-06-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-13T00:00:00]" c="2026-06-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-14T00:00:00]" c="2026-06-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-15T00:00:00]" c="2026-06-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-16T00:00:00]" c="2026-06-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-17T00:00:00]" c="2026-06-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-18T00:00:00]" c="2026-06-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-19T00:00:00]" c="2026-06-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-20T00:00:00]" c="2026-06-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-21T00:00:00]" c="2026-06-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-22T00:00:00]" c="2026-06-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-23T00:00:00]" c="2026-06-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-24T00:00:00]" c="2026-06-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-25T00:00:00]" c="2026-06-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-26T00:00:00]" c="2026-06-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-27T00:00:00]" c="2026-06-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-28T00:00:00]" c="2026-06-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-29T00:00:00]" c="2026-06-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-30T00:00:00]" c="2026-06-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-01T00:00:00]" c="2026-07-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-02T00:00:00]" c="2026-07-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-03T00:00:00]" c="2026-07-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-04T00:00:00]" c="2026-07-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-05T00:00:00]" c="2026-07-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-06T00:00:00]" c="2026-07-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-07T00:00:00]" c="2026-07-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-08T00:00:00]" c="2026-07-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-09T00:00:00]" c="2026-07-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-10T00:00:00]" c="2026-07-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-11T00:00:00]" c="2026-07-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-12T00:00:00]" c="2026-07-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-13T00:00:00]" c="2026-07-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-14T00:00:00]" c="2026-07-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-15T00:00:00]" c="2026-07-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-16T00:00:00]" c="2026-07-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-17T00:00:00]" c="2026-07-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-18T00:00:00]" c="2026-07-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-19T00:00:00]" c="2026-07-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-20T00:00:00]" c="2026-07-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-21T00:00:00]" c="2026-07-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-22T00:00:00]" c="2026-07-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-23T00:00:00]" c="2026-07-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-24T00:00:00]" c="2026-07-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-25T00:00:00]" c="2026-07-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-26T00:00:00]" c="2026-07-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-27T00:00:00]" c="2026-07-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-28T00:00:00]" c="2026-07-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-29T00:00:00]" c="2026-07-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-30T00:00:00]" c="2026-07-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-31T00:00:00]" c="2026-07-31"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-01T00:00:00]" c="2026-08-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-02T00:00:00]" c="2026-08-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-03T00:00:00]" c="2026-08-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-04T00:00:00]" c="2026-08-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-05T00:00:00]" c="2026-08-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-06T00:00:00]" c="2026-08-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-07T00:00:00]" c="2026-08-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-08T00:00:00]" c="2026-08-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-09T00:00:00]" c="2026-08-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-10T00:00:00]" c="2026-08-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-11T00:00:00]" c="2026-08-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-12T00:00:00]" c="2026-08-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-13T00:00:00]" c="2026-08-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-14T00:00:00]" c="2026-08-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-15T00:00:00]" c="2026-08-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-16T00:00:00]" c="2026-08-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-17T00:00:00]" c="2026-08-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-18T00:00:00]" c="2026-08-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-19T00:00:00]" c="2026-08-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-20T00:00:00]" c="2026-08-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-21T00:00:00]" c="2026-08-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-22T00:00:00]" c="2026-08-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-23T00:00:00]" c="2026-08-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-24T00:00:00]" c="2026-08-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-25T00:00:00]" c="2026-08-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-26T00:00:00]" c="2026-08-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-27T00:00:00]" c="2026-08-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-28T00:00:00]" c="2026-08-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-29T00:00:00]" c="2026-08-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-30T00:00:00]" c="2026-08-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-31T00:00:00]" c="2026-08-31"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-01T00:00:00]" c="2026-09-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-02T00:00:00]" c="2026-09-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-03T00:00:00]" c="2026-09-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-04T00:00:00]" c="2026-09-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-05T00:00:00]" c="2026-09-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-06T00:00:00]" c="2026-09-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-07T00:00:00]" c="2026-09-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-08T00:00:00]" c="2026-09-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-09T00:00:00]" c="2026-09-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-10T00:00:00]" c="2026-09-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-11T00:00:00]" c="2026-09-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-12T00:00:00]" c="2026-09-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-13T00:00:00]" c="2026-09-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-14T00:00:00]" c="2026-09-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-15T00:00:00]" c="2026-09-15"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
-      <sharedItems count="14">
-        <s v="[Entidades].[Sigla].&amp;[BCR]" c="BCR"/>
-        <s v="[Entidades].[Sigla].&amp;[BEC]" c="BEC"/>
-        <s v="[Entidades].[Sigla].&amp;[BFO]" c="BFO"/>
-        <s v="[Entidades].[Sigla].&amp;[BGA]" c="BGA"/>
-        <s v="[Entidades].[Sigla].&amp;[BIE]" c="BIE"/>
-        <s v="[Entidades].[Sigla].&amp;[BIS]" c="BIS"/>
-        <s v="[Entidades].[Sigla].&amp;[BME]" c="BME"/>
-        <s v="[Entidades].[Sigla].&amp;[BNA]" c="BNA"/>
-        <s v="[Entidades].[Sigla].&amp;[BNB]" c="BNB"/>
-        <s v="[Entidades].[Sigla].&amp;[BPR]" c="BPR"/>
-        <s v="[Entidades].[Sigla].&amp;[BSO]" c="BSO"/>
-        <s v="[Entidades].[Sigla].&amp;[BUN]" c="BUN"/>
-        <s v="[Entidades].[Sigla].&amp;[PCO]" c="PCO"/>
-        <s v="[Entidades].[Sigla].&amp;[PEF]" c="PEF"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" numFmtId="0" hierarchy="26" level="32767"/>
-  </cacheFields>
-  <cacheHierarchies count="29">
-    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Categoria]" caption="Cod Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Categoria].[All]" allUniqueName="[Actividad Economica].[Cod Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Sector Actividad]" caption="Cod Sector Actividad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" allUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion].[All]" allUniqueName="[Actividad Economica].[Descripcion].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion Categoria]" caption="Descripcion Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" allUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Concepto].[Cod Concepto]" caption="Cod Concepto" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Concepto].[Cod Concepto].[All]" allUniqueName="[Concepto].[Cod Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Concepto].[Concepto]" caption="Concepto" attribute="1" defaultMemberUniqueName="[Concepto].[Concepto].[All]" allUniqueName="[Concepto].[Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Entidades].[Cod Entidad]" caption="Cod Entidad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Entidades].[Cod Entidad].[All]" allUniqueName="[Entidades].[Cod Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Entidades].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Entidades].[Nombre].[All]" allUniqueName="[Entidades].[Nombre].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Entidades].[Sigla]" caption="Sigla" attribute="1" defaultMemberUniqueName="[Entidades].[Sigla].[All]" allUniqueName="[Entidades].[Sigla].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="7"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Entidades].[Tipo Entidad]" caption="Tipo Entidad" attribute="1" defaultMemberUniqueName="[Entidades].[Tipo Entidad].[All]" allUniqueName="[Entidades].[Tipo Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Estrato].[Cod Estrato]" caption="Cod Estrato" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Estrato].[Cod Estrato].[All]" allUniqueName="[Estrato].[Cod Estrato].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Estrato].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Estrato].[Descripcion].[All]" allUniqueName="[Estrato].[Descripcion].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Moneda Cambio].[Cod Moneda]" caption="Cod Moneda" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Moneda Cambio].[Cod Moneda].[All]" allUniqueName="[Moneda Cambio].[Cod Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Moneda Cambio].[Moneda]" caption="Moneda" attribute="1" defaultMemberUniqueName="[Moneda Cambio].[Moneda].[All]" allUniqueName="[Moneda Cambio].[Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Monto Menor].[Cod Monto Menor]" caption="Cod Monto Menor" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Monto Menor].[Cod Monto Menor].[All]" allUniqueName="[Monto Menor].[Cod Monto Menor].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Monto Menor].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Monto Menor].[Descripcion].[All]" allUniqueName="[Monto Menor].[Descripcion].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="5"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Subsistema].[Cod Subsistema]" caption="Cod Subsistema" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Subsistema].[Cod Subsistema].[All]" allUniqueName="[Subsistema].[Cod Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Subsistema].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Subsistema].[Nombre].[All]" allUniqueName="[Subsistema].[Nombre].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Subsistema].[Sigla Subsistema]" caption="Sigla Subsistema" attribute="1" defaultMemberUniqueName="[Subsistema].[Sigla Subsistema].[All]" allUniqueName="[Subsistema].[Sigla Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha]" caption="Cod Fecha" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Fecha]" caption="Fecha" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="6"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes]" caption="Ultimo Dia Mes" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transaccion].[Cod Transaccion]" caption="Cod Transaccion" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Transaccion].[Cod Transaccion].[All]" allUniqueName="[Transaccion].[Cod Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transaccion].[Transaccion]" caption="Transaccion" attribute="1" defaultMemberUniqueName="[Transaccion].[Transaccion].[All]" allUniqueName="[Transaccion].[Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Monto Usd]" caption="Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Usd]" caption="Tipo Cambio Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="8"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Mm Usd]" caption="Tipo Cambio Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Numero Operaciones]" caption="Numero Operaciones" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="10">
-    <dimension name="Actividad Economica" uniqueName="[Actividad Economica]" caption="Actividad Economica"/>
-    <dimension name="Concepto" uniqueName="[Concepto]" caption="Concepto"/>
-    <dimension name="Entidades" uniqueName="[Entidades]" caption="Entidades"/>
-    <dimension name="Estrato" uniqueName="[Estrato]" caption="Estrato"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Moneda Cambio" uniqueName="[Moneda Cambio]" caption="Moneda Cambio"/>
-    <dimension name="Monto Menor" uniqueName="[Monto Menor]" caption="Monto Menor"/>
-    <dimension name="Subsistema" uniqueName="[Subsistema]" caption="Subsistema"/>
-    <dimension name="Tipo Cambio Fecha Dia" uniqueName="[Tipo Cambio Fecha Dia]" caption="Tipo Cambio Fecha Dia"/>
-    <dimension name="Transaccion" uniqueName="[Transaccion]" caption="Transaccion"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Operaciones Cambiarias" caption="Fact Operaciones Cambiarias"/>
-  </measureGroups>
-  <maps count="9">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-    <map measureGroup="0" dimension="8"/>
-    <map measureGroup="0" dimension="9"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Sergio Pablo Garnica Pantoja" refreshedDate="46282.510572569445" backgroundQuery="1" createdVersion="8" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{9ECE6D2C-0019-46A8-93F5-B57014A573FD}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="9">
-    <cacheField name="[Subsistema].[Nombre].[Nombre]" caption="Nombre" numFmtId="0" hierarchy="17" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Transaccion].[Transaccion].[Transaccion]" caption="Transaccion" numFmtId="0" hierarchy="23" level="1">
-      <sharedItems count="2">
-        <s v="[Transaccion].[Transaccion].&amp;[Compra]" c="Compra"/>
-        <s v="[Transaccion].[Transaccion].&amp;[Venta]" c="Venta"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Concepto].[Concepto].[Concepto]" caption="Concepto" numFmtId="0" hierarchy="5" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda]" caption="Cod Moneda" numFmtId="0" hierarchy="12" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Moneda Cambio].[Cod Moneda].[Cod Moneda].[Moneda]" caption="Moneda" propertyName="Moneda" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Monto Menor].[Descripcion].[Descripcion]" caption="Descripcion" numFmtId="0" hierarchy="15" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Tipo Cambio Fecha Dia].[Fecha].[Fecha]" caption="Fecha" numFmtId="0" hierarchy="20" level="1">
-      <sharedItems count="107">
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-01T00:00:00]" c="2026-06-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-02T00:00:00]" c="2026-06-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-03T00:00:00]" c="2026-06-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-04T00:00:00]" c="2026-06-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-05T00:00:00]" c="2026-06-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-06T00:00:00]" c="2026-06-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-07T00:00:00]" c="2026-06-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-08T00:00:00]" c="2026-06-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-09T00:00:00]" c="2026-06-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-10T00:00:00]" c="2026-06-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-11T00:00:00]" c="2026-06-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-12T00:00:00]" c="2026-06-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-13T00:00:00]" c="2026-06-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-14T00:00:00]" c="2026-06-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-15T00:00:00]" c="2026-06-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-16T00:00:00]" c="2026-06-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-17T00:00:00]" c="2026-06-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-18T00:00:00]" c="2026-06-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-19T00:00:00]" c="2026-06-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-20T00:00:00]" c="2026-06-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-21T00:00:00]" c="2026-06-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-22T00:00:00]" c="2026-06-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-23T00:00:00]" c="2026-06-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-24T00:00:00]" c="2026-06-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-25T00:00:00]" c="2026-06-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-26T00:00:00]" c="2026-06-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-27T00:00:00]" c="2026-06-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-28T00:00:00]" c="2026-06-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-29T00:00:00]" c="2026-06-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-06-30T00:00:00]" c="2026-06-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-01T00:00:00]" c="2026-07-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-02T00:00:00]" c="2026-07-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-03T00:00:00]" c="2026-07-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-04T00:00:00]" c="2026-07-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-05T00:00:00]" c="2026-07-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-06T00:00:00]" c="2026-07-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-07T00:00:00]" c="2026-07-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-08T00:00:00]" c="2026-07-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-09T00:00:00]" c="2026-07-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-10T00:00:00]" c="2026-07-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-11T00:00:00]" c="2026-07-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-12T00:00:00]" c="2026-07-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-13T00:00:00]" c="2026-07-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-14T00:00:00]" c="2026-07-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-15T00:00:00]" c="2026-07-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-16T00:00:00]" c="2026-07-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-17T00:00:00]" c="2026-07-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-18T00:00:00]" c="2026-07-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-19T00:00:00]" c="2026-07-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-20T00:00:00]" c="2026-07-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-21T00:00:00]" c="2026-07-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-22T00:00:00]" c="2026-07-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-23T00:00:00]" c="2026-07-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-24T00:00:00]" c="2026-07-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-25T00:00:00]" c="2026-07-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-26T00:00:00]" c="2026-07-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-27T00:00:00]" c="2026-07-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-28T00:00:00]" c="2026-07-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-29T00:00:00]" c="2026-07-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-30T00:00:00]" c="2026-07-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-07-31T00:00:00]" c="2026-07-31"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-01T00:00:00]" c="2026-08-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-02T00:00:00]" c="2026-08-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-03T00:00:00]" c="2026-08-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-04T00:00:00]" c="2026-08-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-05T00:00:00]" c="2026-08-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-06T00:00:00]" c="2026-08-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-07T00:00:00]" c="2026-08-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-08T00:00:00]" c="2026-08-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-09T00:00:00]" c="2026-08-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-10T00:00:00]" c="2026-08-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-11T00:00:00]" c="2026-08-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-12T00:00:00]" c="2026-08-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-13T00:00:00]" c="2026-08-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-14T00:00:00]" c="2026-08-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-15T00:00:00]" c="2026-08-15"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-16T00:00:00]" c="2026-08-16"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-17T00:00:00]" c="2026-08-17"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-18T00:00:00]" c="2026-08-18"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-19T00:00:00]" c="2026-08-19"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-20T00:00:00]" c="2026-08-20"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-21T00:00:00]" c="2026-08-21"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-22T00:00:00]" c="2026-08-22"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-23T00:00:00]" c="2026-08-23"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-24T00:00:00]" c="2026-08-24"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-25T00:00:00]" c="2026-08-25"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-26T00:00:00]" c="2026-08-26"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-27T00:00:00]" c="2026-08-27"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-28T00:00:00]" c="2026-08-28"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-29T00:00:00]" c="2026-08-29"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-30T00:00:00]" c="2026-08-30"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-08-31T00:00:00]" c="2026-08-31"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-01T00:00:00]" c="2026-09-01"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-02T00:00:00]" c="2026-09-02"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-03T00:00:00]" c="2026-09-03"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-04T00:00:00]" c="2026-09-04"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-05T00:00:00]" c="2026-09-05"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-06T00:00:00]" c="2026-09-06"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-07T00:00:00]" c="2026-09-07"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-08T00:00:00]" c="2026-09-08"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-09T00:00:00]" c="2026-09-09"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-10T00:00:00]" c="2026-09-10"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-11T00:00:00]" c="2026-09-11"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-12T00:00:00]" c="2026-09-12"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-13T00:00:00]" c="2026-09-13"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-14T00:00:00]" c="2026-09-14"/>
-        <s v="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-15T00:00:00]" c="2026-09-15"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Entidades].[Sigla].[Sigla]" caption="Sigla" numFmtId="0" hierarchy="8" level="1">
-      <sharedItems count="14">
-        <s v="[Entidades].[Sigla].&amp;[BCR]" c="BCR"/>
-        <s v="[Entidades].[Sigla].&amp;[BEC]" c="BEC"/>
-        <s v="[Entidades].[Sigla].&amp;[BFO]" c="BFO"/>
-        <s v="[Entidades].[Sigla].&amp;[BGA]" c="BGA"/>
-        <s v="[Entidades].[Sigla].&amp;[BIE]" c="BIE"/>
-        <s v="[Entidades].[Sigla].&amp;[BIS]" c="BIS"/>
-        <s v="[Entidades].[Sigla].&amp;[BME]" c="BME"/>
-        <s v="[Entidades].[Sigla].&amp;[BNA]" c="BNA"/>
-        <s v="[Entidades].[Sigla].&amp;[BNB]" c="BNB"/>
-        <s v="[Entidades].[Sigla].&amp;[BPR]" c="BPR"/>
-        <s v="[Entidades].[Sigla].&amp;[BSO]" c="BSO"/>
-        <s v="[Entidades].[Sigla].&amp;[BUN]" c="BUN"/>
-        <s v="[Entidades].[Sigla].&amp;[PCO]" c="PCO"/>
-        <s v="[Entidades].[Sigla].&amp;[PEF]" c="PEF"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Numero Operaciones]" caption="Numero Operaciones" numFmtId="0" hierarchy="28" level="32767"/>
-  </cacheFields>
-  <cacheHierarchies count="29">
-    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Categoria]" caption="Cod Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Categoria].[All]" allUniqueName="[Actividad Economica].[Cod Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Cod Sector Actividad]" caption="Cod Sector Actividad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" allUniqueName="[Actividad Economica].[Cod Sector Actividad].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion].[All]" allUniqueName="[Actividad Economica].[Descripcion].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Actividad Economica].[Descripcion Categoria]" caption="Descripcion Categoria" attribute="1" defaultMemberUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" allUniqueName="[Actividad Economica].[Descripcion Categoria].[All]" dimensionUniqueName="[Actividad Economica]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Concepto].[Cod Concepto]" caption="Cod Concepto" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Concepto].[Cod Concepto].[All]" allUniqueName="[Concepto].[Cod Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Concepto].[Concepto]" caption="Concepto" attribute="1" defaultMemberUniqueName="[Concepto].[Concepto].[All]" allUniqueName="[Concepto].[Concepto].[All]" dimensionUniqueName="[Concepto]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Entidades].[Cod Entidad]" caption="Cod Entidad" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Entidades].[Cod Entidad].[All]" allUniqueName="[Entidades].[Cod Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Entidades].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Entidades].[Nombre].[All]" allUniqueName="[Entidades].[Nombre].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Entidades].[Sigla]" caption="Sigla" attribute="1" defaultMemberUniqueName="[Entidades].[Sigla].[All]" allUniqueName="[Entidades].[Sigla].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="7"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Entidades].[Tipo Entidad]" caption="Tipo Entidad" attribute="1" defaultMemberUniqueName="[Entidades].[Tipo Entidad].[All]" allUniqueName="[Entidades].[Tipo Entidad].[All]" dimensionUniqueName="[Entidades]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Estrato].[Cod Estrato]" caption="Cod Estrato" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Estrato].[Cod Estrato].[All]" allUniqueName="[Estrato].[Cod Estrato].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Estrato].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Estrato].[Descripcion].[All]" allUniqueName="[Estrato].[Descripcion].[All]" dimensionUniqueName="[Estrato]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Moneda Cambio].[Cod Moneda]" caption="Cod Moneda" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Moneda Cambio].[Cod Moneda].[All]" allUniqueName="[Moneda Cambio].[Cod Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Moneda Cambio].[Moneda]" caption="Moneda" attribute="1" defaultMemberUniqueName="[Moneda Cambio].[Moneda].[All]" allUniqueName="[Moneda Cambio].[Moneda].[All]" dimensionUniqueName="[Moneda Cambio]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Monto Menor].[Cod Monto Menor]" caption="Cod Monto Menor" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Monto Menor].[Cod Monto Menor].[All]" allUniqueName="[Monto Menor].[Cod Monto Menor].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Monto Menor].[Descripcion]" caption="Descripcion" attribute="1" defaultMemberUniqueName="[Monto Menor].[Descripcion].[All]" allUniqueName="[Monto Menor].[Descripcion].[All]" dimensionUniqueName="[Monto Menor]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="5"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Subsistema].[Cod Subsistema]" caption="Cod Subsistema" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Subsistema].[Cod Subsistema].[All]" allUniqueName="[Subsistema].[Cod Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Subsistema].[Nombre]" caption="Nombre" attribute="1" defaultMemberUniqueName="[Subsistema].[Nombre].[All]" allUniqueName="[Subsistema].[Nombre].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Subsistema].[Sigla Subsistema]" caption="Sigla Subsistema" attribute="1" defaultMemberUniqueName="[Subsistema].[Sigla Subsistema].[All]" allUniqueName="[Subsistema].[Sigla Subsistema].[All]" dimensionUniqueName="[Subsistema]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha]" caption="Cod Fecha" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Cod Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Fecha]" caption="Fecha" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Fecha].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="6"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes]" caption="Ultimo Dia Mes" attribute="1" defaultMemberUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" allUniqueName="[Tipo Cambio Fecha Dia].[Ultimo Dia Mes].[All]" dimensionUniqueName="[Tipo Cambio Fecha Dia]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transaccion].[Cod Transaccion]" caption="Cod Transaccion" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Transaccion].[Cod Transaccion].[All]" allUniqueName="[Transaccion].[Cod Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transaccion].[Transaccion]" caption="Transaccion" attribute="1" defaultMemberUniqueName="[Transaccion].[Transaccion].[All]" allUniqueName="[Transaccion].[Transaccion].[All]" dimensionUniqueName="[Transaccion]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Monto Usd]" caption="Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Usd]" caption="Tipo Cambio Monto Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Monto Mm Usd]" caption="Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Tipo Cambio Monto Mm Usd]" caption="Tipo Cambio Monto Mm Usd" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Numero Operaciones]" caption="Numero Operaciones" measure="1" displayFolder="" measureGroup="Fact Operaciones Cambiarias" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="8"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="10">
-    <dimension name="Actividad Economica" uniqueName="[Actividad Economica]" caption="Actividad Economica"/>
-    <dimension name="Concepto" uniqueName="[Concepto]" caption="Concepto"/>
-    <dimension name="Entidades" uniqueName="[Entidades]" caption="Entidades"/>
-    <dimension name="Estrato" uniqueName="[Estrato]" caption="Estrato"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Moneda Cambio" uniqueName="[Moneda Cambio]" caption="Moneda Cambio"/>
-    <dimension name="Monto Menor" uniqueName="[Monto Menor]" caption="Monto Menor"/>
-    <dimension name="Subsistema" uniqueName="[Subsistema]" caption="Subsistema"/>
-    <dimension name="Tipo Cambio Fecha Dia" uniqueName="[Tipo Cambio Fecha Dia]" caption="Tipo Cambio Fecha Dia"/>
-    <dimension name="Transaccion" uniqueName="[Transaccion]" caption="Transaccion"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Operaciones Cambiarias" caption="Fact Operaciones Cambiarias"/>
-  </measureGroups>
-  <maps count="9">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-    <map measureGroup="0" dimension="8"/>
-    <map measureGroup="0" dimension="9"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C1A180-7D44-4F02-A61C-919F70C27D4D}" name="TablaDinámica1" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
-  <location ref="A7:Q222" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="5" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C1A180-7D44-4F02-A61C-919F70C27D4D}" name="TablaDinámica1" cacheId="19" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+  <location ref="A7:Q234" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="5" colPageCount="1"/>
   <pivotFields count="10">
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
@@ -1375,7 +1411,7 @@
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="107">
+      <items count="113">
         <item s="1" x="0"/>
         <item s="1" x="1"/>
         <item s="1" x="2"/>
@@ -1483,6 +1519,12 @@
         <item s="1" x="104"/>
         <item s="1" x="105"/>
         <item s="1" x="106"/>
+        <item s="1" x="107"/>
+        <item s="1" x="108"/>
+        <item s="1" x="109"/>
+        <item s="1" x="110"/>
+        <item s="1" x="111"/>
+        <item s="1" x="112"/>
       </items>
     </pivotField>
     <pivotField axis="axisCol" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -1510,7 +1552,7 @@
     <field x="6"/>
     <field x="-2"/>
   </rowFields>
-  <rowItems count="214">
+  <rowItems count="226">
     <i>
       <x/>
       <x/>
@@ -2255,6 +2297,48 @@
     </i>
     <i>
       <x v="106"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="107"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="108"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="109"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="110"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="111"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="112"/>
       <x/>
     </i>
     <i r="1" i="1">
@@ -2355,118 +2439,7 @@
     </pivotHierarchy>
     <pivotHierarchy/>
     <pivotHierarchy/>
-    <pivotHierarchy>
-      <members count="108" level="1">
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name=""/>
-        <member name="[Tipo Cambio Fecha Dia].[Fecha].&amp;[2026-09-16T00:00:00]"/>
-      </members>
-    </pivotHierarchy>
+    <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy multipleItemSelectionAllowed="1">
@@ -2500,8 +2473,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{971AADEF-3DB3-4761-B43F-E1EDE0CC9CC9}" name="TablaDinámica2" cacheId="8" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
-  <location ref="A7:AE116" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{971AADEF-3DB3-4761-B43F-E1EDE0CC9CC9}" name="TablaDinámica2" cacheId="16" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
+  <location ref="A7:AE122" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
       <items count="1">
@@ -2532,7 +2505,7 @@
       </items>
     </pivotField>
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="108">
+      <items count="114">
         <item s="1" x="0"/>
         <item s="1" x="1"/>
         <item s="1" x="2"/>
@@ -2640,6 +2613,12 @@
         <item s="1" x="104"/>
         <item s="1" x="105"/>
         <item s="1" x="106"/>
+        <item s="1" x="107"/>
+        <item s="1" x="108"/>
+        <item s="1" x="109"/>
+        <item s="1" x="110"/>
+        <item s="1" x="111"/>
+        <item s="1" x="112"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2667,7 +2646,7 @@
   <rowFields count="1">
     <field x="6"/>
   </rowFields>
-  <rowItems count="107">
+  <rowItems count="113">
     <i>
       <x/>
     </i>
@@ -2988,6 +2967,24 @@
     </i>
     <i>
       <x v="106"/>
+    </i>
+    <i>
+      <x v="107"/>
+    </i>
+    <i>
+      <x v="108"/>
+    </i>
+    <i>
+      <x v="109"/>
+    </i>
+    <i>
+      <x v="110"/>
+    </i>
+    <i>
+      <x v="111"/>
+    </i>
+    <i>
+      <x v="112"/>
     </i>
   </rowItems>
   <colFields count="2">
@@ -3160,8 +3157,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80A53070-3740-4285-A7AE-6612867028BD}" name="TablaDinámica3" cacheId="11" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
-  <location ref="A7:AE116" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80A53070-3740-4285-A7AE-6612867028BD}" name="TablaDinámica3" cacheId="13" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
+  <location ref="A7:AE122" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
       <items count="1">
@@ -3192,7 +3189,7 @@
       </items>
     </pivotField>
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="108">
+      <items count="114">
         <item s="1" x="0"/>
         <item s="1" x="1"/>
         <item s="1" x="2"/>
@@ -3300,6 +3297,12 @@
         <item s="1" x="104"/>
         <item s="1" x="105"/>
         <item s="1" x="106"/>
+        <item s="1" x="107"/>
+        <item s="1" x="108"/>
+        <item s="1" x="109"/>
+        <item s="1" x="110"/>
+        <item s="1" x="111"/>
+        <item s="1" x="112"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3327,7 +3330,7 @@
   <rowFields count="1">
     <field x="6"/>
   </rowFields>
-  <rowItems count="107">
+  <rowItems count="113">
     <i>
       <x/>
     </i>
@@ -3648,6 +3651,24 @@
     </i>
     <i>
       <x v="106"/>
+    </i>
+    <i>
+      <x v="107"/>
+    </i>
+    <i>
+      <x v="108"/>
+    </i>
+    <i>
+      <x v="109"/>
+    </i>
+    <i>
+      <x v="110"/>
+    </i>
+    <i>
+      <x v="111"/>
+    </i>
+    <i>
+      <x v="112"/>
     </i>
   </rowItems>
   <colFields count="2">
@@ -4116,7 +4137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3F3DA76-2715-4C5C-9BC9-0D27B1FEBC80}">
-  <dimension ref="A1:Q222"/>
+  <dimension ref="A1:Q234"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
@@ -6060,7 +6081,7 @@
         <v>0.40010068000000004</v>
       </c>
       <c r="Q45" s="2">
-        <v>25.032258476300004</v>
+        <v>25.032258476300001</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -13320,31 +13341,31 @@
         <v>94</v>
       </c>
       <c r="C193" s="2">
-        <v>10.5412650994</v>
+        <v>10.541265099400004</v>
       </c>
       <c r="D193" s="2">
-        <v>1.5404671898000002</v>
+        <v>1.5404671897999997</v>
       </c>
       <c r="E193" s="2">
         <v>0.30973334990000001</v>
       </c>
       <c r="F193" s="2">
-        <v>10.676857608499999</v>
+        <v>10.676857608500004</v>
       </c>
       <c r="G193" s="2">
         <v>1.52429345</v>
       </c>
       <c r="H193" s="2">
-        <v>7.049551618999998</v>
+        <v>7.0495516189999989</v>
       </c>
       <c r="I193" s="2">
-        <v>8.1942503297999973</v>
+        <v>8.1942503297999991</v>
       </c>
       <c r="J193" s="2">
         <v>2.5951819899999999E-2</v>
       </c>
       <c r="K193" s="2">
-        <v>6.4725927186999996</v>
+        <v>6.4725927187000005</v>
       </c>
       <c r="L193" s="2">
         <v>2.0430669899999997E-2</v>
@@ -13353,7 +13374,7 @@
         <v>2.0410046298000002</v>
       </c>
       <c r="N193" s="2">
-        <v>0.80778228969999988</v>
+        <v>0.80778228969999999</v>
       </c>
       <c r="O193" s="2">
         <v>1.8677698999999999E-3</v>
@@ -13362,7 +13383,7 @@
         <v>0.15001043999999999</v>
       </c>
       <c r="Q193" s="2">
-        <v>49.356058984300013</v>
+        <v>49.35605898430002</v>
       </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
@@ -13376,7 +13397,7 @@
         <v>18.855870707200001</v>
       </c>
       <c r="E194" s="2">
-        <v>3.7445659802</v>
+        <v>3.7445659802000004</v>
       </c>
       <c r="F194" s="2">
         <v>129.79106454269998</v>
@@ -13388,19 +13409,19 @@
         <v>86.585119868300012</v>
       </c>
       <c r="I194" s="2">
-        <v>100.95028395929999</v>
+        <v>100.95028395930001</v>
       </c>
       <c r="J194" s="2">
         <v>0.31063251219999999</v>
       </c>
       <c r="K194" s="2">
-        <v>78.904366968700018</v>
+        <v>78.904366968699989</v>
       </c>
       <c r="L194" s="2">
         <v>0.24149051929999998</v>
       </c>
       <c r="M194" s="2">
-        <v>25.213606268600003</v>
+        <v>25.2136062686</v>
       </c>
       <c r="N194" s="2">
         <v>10.081866637300001</v>
@@ -13412,7 +13433,7 @@
         <v>1.7431223568000001</v>
       </c>
       <c r="Q194" s="2">
-        <v>605.37609793800004</v>
+        <v>605.37609793799993</v>
       </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
@@ -13423,10 +13444,10 @@
         <v>94</v>
       </c>
       <c r="C195" s="2">
-        <v>2.2410354895000002</v>
+        <v>2.2410354894999993</v>
       </c>
       <c r="D195" s="2">
-        <v>4.321877409799999</v>
+        <v>4.3218774097999999</v>
       </c>
       <c r="E195" s="2">
         <v>1.7164667597999999</v>
@@ -13441,7 +13462,7 @@
         <v>28.744438628800001</v>
       </c>
       <c r="I195" s="2">
-        <v>3.9797154597000004</v>
+        <v>3.9797154597</v>
       </c>
       <c r="J195" s="2">
         <v>6.0730200000000002E-3</v>
@@ -13453,7 +13474,7 @@
         <v>2.0808800000000002E-3</v>
       </c>
       <c r="M195" s="2">
-        <v>5.5570111197000012</v>
+        <v>5.5570111197000003</v>
       </c>
       <c r="N195" s="2">
         <v>0.24435603989999999</v>
@@ -13473,13 +13494,13 @@
         <v>95</v>
       </c>
       <c r="C196" s="2">
-        <v>27.552192623</v>
+        <v>27.552192622999996</v>
       </c>
       <c r="D196" s="2">
         <v>53.643417894800002</v>
       </c>
       <c r="E196" s="2">
-        <v>21.520790948299997</v>
+        <v>21.5207909483</v>
       </c>
       <c r="F196" s="2">
         <v>75.871407173300014</v>
@@ -13503,7 +13524,7 @@
         <v>2.4887324799999999E-2</v>
       </c>
       <c r="M196" s="2">
-        <v>69.0339198649</v>
+        <v>69.033919864900014</v>
       </c>
       <c r="N196" s="2">
         <v>2.9952346882000001</v>
@@ -13526,7 +13547,7 @@
         <v>94</v>
       </c>
       <c r="C197" s="2">
-        <v>4.2272902993999999</v>
+        <v>4.227290299399999</v>
       </c>
       <c r="D197" s="2">
         <v>0.55025838990000009</v>
@@ -13538,25 +13559,25 @@
         <v>9.5613452584999994</v>
       </c>
       <c r="G197" s="2">
-        <v>1.3229299500000002</v>
+        <v>1.32292995</v>
       </c>
       <c r="H197" s="2">
-        <v>9.6362721188999991</v>
+        <v>9.6362721189000009</v>
       </c>
       <c r="I197" s="2">
-        <v>2.5468940288000002</v>
+        <v>2.5468940287999993</v>
       </c>
       <c r="J197" s="2">
-        <v>4.6518099900000005E-2</v>
+        <v>4.6518099899999998E-2</v>
       </c>
       <c r="K197" s="2">
-        <v>4.2512866591000007</v>
+        <v>4.251286659099998</v>
       </c>
       <c r="L197" s="2">
-        <v>1.1868579900000001E-2</v>
+        <v>1.1868579900000002E-2</v>
       </c>
       <c r="M197" s="2">
-        <v>3.0043624296000004</v>
+        <v>3.0043624296</v>
       </c>
       <c r="N197" s="2">
         <v>4.4385997999999999E-3</v>
@@ -13568,7 +13589,7 @@
         <v>2.1098999999999999E-6</v>
       </c>
       <c r="Q197" s="2">
-        <v>35.332630863600002</v>
+        <v>35.332630863599995</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
@@ -13576,13 +13597,13 @@
         <v>95</v>
       </c>
       <c r="C198" s="2">
-        <v>52.374203587799997</v>
+        <v>52.374203587800004</v>
       </c>
       <c r="D198" s="2">
         <v>6.8732329237000007</v>
       </c>
       <c r="E198" s="2">
-        <v>2.0419253161000004</v>
+        <v>2.0419253160999999</v>
       </c>
       <c r="F198" s="2">
         <v>118.95602852179999</v>
@@ -13594,19 +13615,19 @@
         <v>119.79280048699999</v>
       </c>
       <c r="I198" s="2">
-        <v>31.896125515700003</v>
+        <v>31.8961255157</v>
       </c>
       <c r="J198" s="2">
         <v>0.5664975619</v>
       </c>
       <c r="K198" s="2">
-        <v>52.611228614500021</v>
+        <v>52.611228614500028</v>
       </c>
       <c r="L198" s="2">
         <v>0.1426603313</v>
       </c>
       <c r="M198" s="2">
-        <v>37.769139148799987</v>
+        <v>37.769139148799994</v>
       </c>
       <c r="N198" s="2">
         <v>4.66052998E-2</v>
@@ -13618,7 +13639,7 @@
         <v>2.51511E-5</v>
       </c>
       <c r="Q198" s="2">
-        <v>439.70693911139989</v>
+        <v>439.7069391114</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
@@ -13632,34 +13653,34 @@
         <v>4.5686707090000001</v>
       </c>
       <c r="D199" s="2">
-        <v>4.0573789997</v>
+        <v>4.0573789996999992</v>
       </c>
       <c r="E199" s="2">
-        <v>0.8197688098</v>
+        <v>0.81976880980000011</v>
       </c>
       <c r="F199" s="2">
-        <v>21.622486007900001</v>
+        <v>21.622486007899997</v>
       </c>
       <c r="G199" s="2">
-        <v>1.5932660199999997</v>
+        <v>1.5932660200000002</v>
       </c>
       <c r="H199" s="2">
-        <v>9.5712881088999993</v>
+        <v>9.571288108900001</v>
       </c>
       <c r="I199" s="2">
-        <v>11.750750289799997</v>
+        <v>11.750750289799999</v>
       </c>
       <c r="J199" s="2">
         <v>0.2543552</v>
       </c>
       <c r="K199" s="2">
-        <v>5.8530080087000016</v>
+        <v>5.8530080086999998</v>
       </c>
       <c r="L199" s="2">
         <v>1.9358249899999999E-2</v>
       </c>
       <c r="M199" s="2">
-        <v>0.81909734989999994</v>
+        <v>0.81909734990000005</v>
       </c>
       <c r="N199" s="2">
         <v>3.4659929900000004E-2</v>
@@ -13669,7 +13690,7 @@
       </c>
       <c r="P199" s="2"/>
       <c r="Q199" s="2">
-        <v>60.969117683500002</v>
+        <v>60.969117683499995</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
@@ -13677,31 +13698,31 @@
         <v>95</v>
       </c>
       <c r="C200" s="2">
-        <v>57.365538394000005</v>
+        <v>57.365538393999998</v>
       </c>
       <c r="D200" s="2">
-        <v>51.081473910600003</v>
+        <v>51.081473910599996</v>
       </c>
       <c r="E200" s="2">
         <v>10.3597431935</v>
       </c>
       <c r="F200" s="2">
-        <v>272.68226681179999</v>
+        <v>272.68226681180005</v>
       </c>
       <c r="G200" s="2">
         <v>20.103040236399998</v>
       </c>
       <c r="H200" s="2">
-        <v>119.87848262189999</v>
+        <v>119.87848262189998</v>
       </c>
       <c r="I200" s="2">
-        <v>147.77237513130001</v>
+        <v>147.77237513129998</v>
       </c>
       <c r="J200" s="2">
         <v>3.1123956798999997</v>
       </c>
       <c r="K200" s="2">
-        <v>72.852179470499991</v>
+        <v>72.852179470499976</v>
       </c>
       <c r="L200" s="2">
         <v>0.23520273749999998</v>
@@ -13710,14 +13731,14 @@
         <v>10.322535413899999</v>
       </c>
       <c r="N200" s="2">
-        <v>0.39927616469999999</v>
+        <v>0.39927616470000005</v>
       </c>
       <c r="O200" s="2">
         <v>6.0611499999999999E-2</v>
       </c>
       <c r="P200" s="2"/>
       <c r="Q200" s="2">
-        <v>766.2251212660002</v>
+        <v>766.22512126599997</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
@@ -13743,10 +13764,10 @@
         <v>0.60749774999999995</v>
       </c>
       <c r="H201" s="2">
-        <v>9.3156009100000006E-2</v>
+        <v>9.3156009099999992E-2</v>
       </c>
       <c r="I201" s="2">
-        <v>5.0729019899999998E-2</v>
+        <v>5.0729019900000012E-2</v>
       </c>
       <c r="J201" s="2"/>
       <c r="K201" s="2">
@@ -13759,7 +13780,7 @@
         <v>5.7993298E-3</v>
       </c>
       <c r="N201" s="2">
-        <v>9.9220597000000011E-3</v>
+        <v>9.9220596999999994E-3</v>
       </c>
       <c r="O201" s="2">
         <v>2.5593699E-3</v>
@@ -13768,7 +13789,7 @@
         <v>1.95E-6</v>
       </c>
       <c r="Q201" s="2">
-        <v>4.4932006754000007</v>
+        <v>4.4932006753999998</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
@@ -13776,7 +13797,7 @@
         <v>95</v>
       </c>
       <c r="C202" s="2">
-        <v>2.8167657692999999</v>
+        <v>2.8167657693000003</v>
       </c>
       <c r="D202" s="2">
         <v>0.23825112999999998</v>
@@ -13785,20 +13806,20 @@
         <v>1.30203E-3</v>
       </c>
       <c r="F202" s="2">
-        <v>29.300189705000005</v>
+        <v>29.300189705000001</v>
       </c>
       <c r="G202" s="2">
-        <v>7.6423216948999997</v>
+        <v>7.6423216949000006</v>
       </c>
       <c r="H202" s="2">
-        <v>1.1348633928999998</v>
+        <v>1.1348633929</v>
       </c>
       <c r="I202" s="2">
         <v>0.61448656160000004</v>
       </c>
       <c r="J202" s="2"/>
       <c r="K202" s="2">
-        <v>14.213264292099998</v>
+        <v>14.213264292099996</v>
       </c>
       <c r="L202" s="2">
         <v>3.7443684800000002E-2</v>
@@ -13807,16 +13828,16 @@
         <v>7.1505738900000004E-2</v>
       </c>
       <c r="N202" s="2">
-        <v>0.11211927789999999</v>
+        <v>0.11211927790000001</v>
       </c>
       <c r="O202" s="2">
-        <v>3.1173126600000003E-2</v>
+        <v>3.11731266E-2</v>
       </c>
       <c r="P202" s="2">
         <v>2.3751E-5</v>
       </c>
       <c r="Q202" s="2">
-        <v>56.213710155000015</v>
+        <v>56.213710155000001</v>
       </c>
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.25">
@@ -13849,7 +13870,7 @@
       </c>
       <c r="J203" s="2"/>
       <c r="K203" s="2">
-        <v>0.14930280960000006</v>
+        <v>0.14930280960000003</v>
       </c>
       <c r="L203" s="2"/>
       <c r="M203" s="2">
@@ -13880,16 +13901,16 @@
         <v>1.3580109999999999E-3</v>
       </c>
       <c r="F204" s="2">
-        <v>16.3411713926</v>
+        <v>16.341171392600003</v>
       </c>
       <c r="G204" s="2">
         <v>5.0319990000000005E-4</v>
       </c>
       <c r="H204" s="2">
-        <v>0.33729674099999996</v>
+        <v>0.33729674100000001</v>
       </c>
       <c r="I204" s="2">
-        <v>0.1217957544</v>
+        <v>0.12179575440000001</v>
       </c>
       <c r="J204" s="2"/>
       <c r="K204" s="2">
@@ -13907,7 +13928,7 @@
       </c>
       <c r="P204" s="2"/>
       <c r="Q204" s="2">
-        <v>19.811206375299999</v>
+        <v>19.811206375300003</v>
       </c>
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
@@ -13918,25 +13939,25 @@
         <v>94</v>
       </c>
       <c r="C205" s="2">
-        <v>2.5096564792999998</v>
+        <v>2.5096564793000002</v>
       </c>
       <c r="D205" s="2">
         <v>0.38593559999999999</v>
       </c>
       <c r="E205" s="2">
-        <v>7.6094269899999983E-2</v>
+        <v>7.6094269899999997E-2</v>
       </c>
       <c r="F205" s="2">
-        <v>4.6978368785999995</v>
+        <v>4.6978368786000004</v>
       </c>
       <c r="G205" s="2">
-        <v>0.89445370989999995</v>
+        <v>0.89445370990000006</v>
       </c>
       <c r="H205" s="2">
-        <v>2.0722231492999996</v>
+        <v>2.0722231493000001</v>
       </c>
       <c r="I205" s="2">
-        <v>4.3039844189000007</v>
+        <v>4.3039844189000025</v>
       </c>
       <c r="J205" s="2">
         <v>2.6595699E-3</v>
@@ -13960,7 +13981,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="Q205" s="2">
-        <v>20.0968495937</v>
+        <v>20.096849593700004</v>
       </c>
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
@@ -13974,31 +13995,31 @@
         <v>4.8484143200000007</v>
       </c>
       <c r="E206" s="2">
-        <v>0.95982038030000005</v>
+        <v>0.95982038029999994</v>
       </c>
       <c r="F206" s="2">
-        <v>58.732927618200009</v>
+        <v>58.732927618199994</v>
       </c>
       <c r="G206" s="2">
         <v>11.256426151500001</v>
       </c>
       <c r="H206" s="2">
-        <v>26.077108946800003</v>
+        <v>26.077108946799999</v>
       </c>
       <c r="I206" s="2">
-        <v>54.582125338899985</v>
+        <v>54.582125338899992</v>
       </c>
       <c r="J206" s="2">
         <v>3.2659519499999998E-2</v>
       </c>
       <c r="K206" s="2">
-        <v>59.396223827299977</v>
+        <v>59.396223827299991</v>
       </c>
       <c r="L206" s="2">
         <v>0.1914124123</v>
       </c>
       <c r="M206" s="2">
-        <v>5.0085236483000006</v>
+        <v>5.0085236482999989</v>
       </c>
       <c r="N206" s="2">
         <v>5.4080443800000003E-2</v>
@@ -14010,7 +14031,7 @@
         <v>1.218E-5</v>
       </c>
       <c r="Q206" s="2">
-        <v>252.97496640249997</v>
+        <v>252.97496640249992</v>
       </c>
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
@@ -14027,28 +14048,28 @@
         <v>0.67271874990000002</v>
       </c>
       <c r="E207" s="2">
-        <v>0.56355119989999991</v>
+        <v>0.56355119990000002</v>
       </c>
       <c r="F207" s="2">
-        <v>12.2575770487</v>
+        <v>12.257577048699998</v>
       </c>
       <c r="G207" s="2">
-        <v>1.4420222100000002</v>
+        <v>1.44202221</v>
       </c>
       <c r="H207" s="2">
-        <v>13.599364889</v>
+        <v>13.599364889000002</v>
       </c>
       <c r="I207" s="2">
-        <v>5.8482524195000005</v>
+        <v>5.8482524194999996</v>
       </c>
       <c r="J207" s="2">
         <v>8.294195E-2</v>
       </c>
       <c r="K207" s="2">
-        <v>5.5395596578999999</v>
+        <v>5.539559657899999</v>
       </c>
       <c r="L207" s="2">
-        <v>2.09818799E-2</v>
+        <v>2.0981879900000003E-2</v>
       </c>
       <c r="M207" s="2">
         <v>3.2933772699000001</v>
@@ -14061,7 +14082,7 @@
       </c>
       <c r="P207" s="2"/>
       <c r="Q207" s="2">
-        <v>50.902238913799998</v>
+        <v>50.902238913799991</v>
       </c>
     </row>
     <row r="208" spans="1:17" x14ac:dyDescent="0.25">
@@ -14069,7 +14090,7 @@
         <v>95</v>
       </c>
       <c r="C208" s="2">
-        <v>36.121187653699991</v>
+        <v>36.121187653699998</v>
       </c>
       <c r="D208" s="2">
         <v>8.4399284267999999</v>
@@ -14078,7 +14099,7 @@
         <v>7.0457036629999994</v>
       </c>
       <c r="F208" s="2">
-        <v>155.37985363440006</v>
+        <v>155.37985363440004</v>
       </c>
       <c r="G208" s="2">
         <v>18.178178570699998</v>
@@ -14087,29 +14108,29 @@
         <v>171.52395385080001</v>
       </c>
       <c r="I208" s="2">
-        <v>73.470754567500009</v>
+        <v>73.470754567499995</v>
       </c>
       <c r="J208" s="2">
         <v>1.0330359849999999</v>
       </c>
       <c r="K208" s="2">
-        <v>69.593592681900006</v>
+        <v>69.59359268190002</v>
       </c>
       <c r="L208" s="2">
         <v>0.25807712399999999</v>
       </c>
       <c r="M208" s="2">
-        <v>41.795572938100001</v>
+        <v>41.795572938100008</v>
       </c>
       <c r="N208" s="2">
-        <v>59.158492316600004</v>
+        <v>59.158492316599997</v>
       </c>
       <c r="O208" s="2">
         <v>0.9446406437999999</v>
       </c>
       <c r="P208" s="2"/>
       <c r="Q208" s="2">
-        <v>642.94297205630005</v>
+        <v>642.94297205629994</v>
       </c>
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
@@ -14129,13 +14150,13 @@
         <v>2.3746740098999997</v>
       </c>
       <c r="F209" s="2">
-        <v>18.101094888000006</v>
+        <v>18.101094887999999</v>
       </c>
       <c r="G209" s="2">
-        <v>2.7011731796</v>
+        <v>2.7011731796000005</v>
       </c>
       <c r="H209" s="2">
-        <v>28.055478878599995</v>
+        <v>28.055478878599999</v>
       </c>
       <c r="I209" s="2">
         <v>10.904366849800001</v>
@@ -14144,7 +14165,7 @@
         <v>5.6418119900000001E-2</v>
       </c>
       <c r="K209" s="2">
-        <v>4.988294688299999</v>
+        <v>4.9882946882999999</v>
       </c>
       <c r="L209" s="2">
         <v>8.8044989900000009E-2</v>
@@ -14170,16 +14191,16 @@
         <v>95</v>
       </c>
       <c r="C210" s="2">
-        <v>72.274457498000004</v>
+        <v>72.274457498000018</v>
       </c>
       <c r="D210" s="2">
-        <v>15.448586199900001</v>
+        <v>15.448586199899999</v>
       </c>
       <c r="E210" s="2">
         <v>29.850276077499998</v>
       </c>
       <c r="F210" s="2">
-        <v>225.21602601589996</v>
+        <v>225.21602601589998</v>
       </c>
       <c r="G210" s="2">
         <v>34.104328908799999</v>
@@ -14188,22 +14209,22 @@
         <v>347.52194972910002</v>
       </c>
       <c r="I210" s="2">
-        <v>134.6418090521</v>
+        <v>134.64180905209997</v>
       </c>
       <c r="J210" s="2">
         <v>0.69619958430000006</v>
       </c>
       <c r="K210" s="2">
-        <v>62.467125090900005</v>
+        <v>62.467125090899998</v>
       </c>
       <c r="L210" s="2">
-        <v>1.0864751765999998</v>
+        <v>1.0864751766</v>
       </c>
       <c r="M210" s="2">
         <v>47.680418272200001</v>
       </c>
       <c r="N210" s="2">
-        <v>130.74705869299999</v>
+        <v>130.74705869300001</v>
       </c>
       <c r="O210" s="2">
         <v>0.20135142720000002</v>
@@ -14212,7 +14233,7 @@
         <v>3.5561662680000001</v>
       </c>
       <c r="Q210" s="2">
-        <v>1105.4922279935001</v>
+        <v>1105.4922279934999</v>
       </c>
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.25">
@@ -14223,7 +14244,7 @@
         <v>94</v>
       </c>
       <c r="C211" s="2">
-        <v>1.1333617697</v>
+        <v>1.1333617696999998</v>
       </c>
       <c r="D211" s="2">
         <v>0.89631024999999998</v>
@@ -14241,19 +14262,19 @@
         <v>10.0619224887</v>
       </c>
       <c r="I211" s="2">
-        <v>11.731190969499998</v>
+        <v>11.7311909695</v>
       </c>
       <c r="J211" s="2">
         <v>5.5333E-2</v>
       </c>
       <c r="K211" s="2">
-        <v>1.0005415778000002</v>
+        <v>1.0005415778</v>
       </c>
       <c r="L211" s="2">
-        <v>9.4723209799999999E-2</v>
+        <v>9.4723209800000013E-2</v>
       </c>
       <c r="M211" s="2">
-        <v>1.7938587298000002</v>
+        <v>1.7938587297999999</v>
       </c>
       <c r="N211" s="2">
         <v>8.9329959799999997E-2</v>
@@ -14265,7 +14286,7 @@
         <v>7.4599000000000004E-6</v>
       </c>
       <c r="Q211" s="2">
-        <v>39.65177365249999</v>
+        <v>39.651773652499998</v>
       </c>
     </row>
     <row r="212" spans="1:17" x14ac:dyDescent="0.25">
@@ -14291,19 +14312,19 @@
         <v>119.386124266</v>
       </c>
       <c r="I212" s="2">
-        <v>142.66625150230007</v>
+        <v>142.66625150229999</v>
       </c>
       <c r="J212" s="2">
-        <v>0.6706659599</v>
+        <v>0.67066595989999989</v>
       </c>
       <c r="K212" s="2">
-        <v>11.594436751100003</v>
+        <v>11.594436751100002</v>
       </c>
       <c r="L212" s="2">
         <v>1.1480453051000001</v>
       </c>
       <c r="M212" s="2">
-        <v>21.403405677899997</v>
+        <v>21.4034056779</v>
       </c>
       <c r="N212" s="2">
         <v>1.0248225479999999</v>
@@ -14329,25 +14350,25 @@
         <v>1.0217140897000001</v>
       </c>
       <c r="D213" s="2">
-        <v>6.5043974797999997</v>
+        <v>6.5043974798000006</v>
       </c>
       <c r="E213" s="2">
         <v>0.52745240999999998</v>
       </c>
       <c r="F213" s="2">
-        <v>3.6945644886000002</v>
+        <v>3.6945644885999998</v>
       </c>
       <c r="G213" s="2">
-        <v>4.1965709899999995E-2</v>
+        <v>4.1965709900000002E-2</v>
       </c>
       <c r="H213" s="2">
-        <v>11.790913559099996</v>
+        <v>11.7909135591</v>
       </c>
       <c r="I213" s="2">
-        <v>1.1048527398000003</v>
+        <v>1.1048527398000001</v>
       </c>
       <c r="J213" s="2">
-        <v>5.4248020000000001E-2</v>
+        <v>5.4248019999999994E-2</v>
       </c>
       <c r="K213" s="2">
         <v>1.8321259883999996</v>
@@ -14356,7 +14377,7 @@
         <v>0.22342341979999999</v>
       </c>
       <c r="M213" s="2">
-        <v>1.2727332994999998</v>
+        <v>1.2727332995</v>
       </c>
       <c r="N213" s="2">
         <v>6.660663E-2</v>
@@ -14376,7 +14397,7 @@
         <v>95</v>
       </c>
       <c r="C214" s="2">
-        <v>11.5998478912</v>
+        <v>11.599847891200001</v>
       </c>
       <c r="D214" s="2">
         <v>71.848372279800003</v>
@@ -14385,25 +14406,25 @@
         <v>6.1731471858999996</v>
       </c>
       <c r="F214" s="2">
-        <v>43.45898273209999</v>
+        <v>43.458982732100004</v>
       </c>
       <c r="G214" s="2">
-        <v>0.4842842933</v>
+        <v>0.48428429329999995</v>
       </c>
       <c r="H214" s="2">
-        <v>136.23821512999999</v>
+        <v>136.23821513000001</v>
       </c>
       <c r="I214" s="2">
-        <v>12.5856473644</v>
+        <v>12.585647364399998</v>
       </c>
       <c r="J214" s="2">
-        <v>0.63067734879999993</v>
+        <v>0.63067734880000004</v>
       </c>
       <c r="K214" s="2">
-        <v>20.817421339499983</v>
+        <v>20.817421339499994</v>
       </c>
       <c r="L214" s="2">
-        <v>2.6229909507000002</v>
+        <v>2.6229909507000007</v>
       </c>
       <c r="M214" s="2">
         <v>14.817833654300001</v>
@@ -14418,7 +14439,7 @@
         <v>2.9249999999999998</v>
       </c>
       <c r="Q214" s="2">
-        <v>324.98411886749994</v>
+        <v>324.9841188675</v>
       </c>
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.25">
@@ -14438,23 +14459,23 @@
         <v>1.6000000000000001E-3</v>
       </c>
       <c r="F215" s="2">
-        <v>1.6522773781999998</v>
+        <v>1.6522773782</v>
       </c>
       <c r="G215" s="2">
         <v>8.60199E-5</v>
       </c>
       <c r="H215" s="2">
-        <v>0.1031850797</v>
+        <v>0.10318507969999999</v>
       </c>
       <c r="I215" s="2">
         <v>2.2065109999999999E-2</v>
       </c>
       <c r="J215" s="2"/>
       <c r="K215" s="2">
-        <v>3.05195181E-2</v>
+        <v>3.0519518099999997E-2</v>
       </c>
       <c r="L215" s="2">
-        <v>6.6482999000000006E-3</v>
+        <v>6.6482998999999997E-3</v>
       </c>
       <c r="M215" s="2">
         <v>5.6577097999999998E-3</v>
@@ -14467,7 +14488,7 @@
       </c>
       <c r="P215" s="2"/>
       <c r="Q215" s="2">
-        <v>1.9003078649999994</v>
+        <v>1.9003078649999996</v>
       </c>
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.25">
@@ -14475,7 +14496,7 @@
         <v>95</v>
       </c>
       <c r="C216" s="2">
-        <v>0.73586636490000001</v>
+        <v>0.73586636490000013</v>
       </c>
       <c r="D216" s="2">
         <v>2.40761159E-2</v>
@@ -14490,7 +14511,7 @@
         <v>9.4880059999999996E-4</v>
       </c>
       <c r="H216" s="2">
-        <v>1.2298153265999998</v>
+        <v>1.2298153266</v>
       </c>
       <c r="I216" s="2">
         <v>0.22131305330000001</v>
@@ -14500,7 +14521,7 @@
         <v>0.31076304760000001</v>
       </c>
       <c r="L216" s="2">
-        <v>7.4660409000000011E-2</v>
+        <v>7.4660408999999997E-2</v>
       </c>
       <c r="M216" s="2">
         <v>6.0367765599999998E-2</v>
@@ -14544,7 +14565,7 @@
       </c>
       <c r="J217" s="2"/>
       <c r="K217" s="2">
-        <v>1.0460969399999999E-2</v>
+        <v>1.0460969400000002E-2</v>
       </c>
       <c r="L217" s="2"/>
       <c r="M217" s="2"/>
@@ -14569,7 +14590,7 @@
       </c>
       <c r="E218" s="2"/>
       <c r="F218" s="2">
-        <v>8.6118397088000016</v>
+        <v>8.6118397087999998</v>
       </c>
       <c r="G218" s="2">
         <v>3.3556569000000001E-3</v>
@@ -14582,7 +14603,7 @@
       </c>
       <c r="J218" s="2"/>
       <c r="K218" s="2">
-        <v>0.10715152690000002</v>
+        <v>0.1071515269</v>
       </c>
       <c r="L218" s="2"/>
       <c r="M218" s="2"/>
@@ -14603,7 +14624,7 @@
         <v>94</v>
       </c>
       <c r="C219" s="2">
-        <v>4.1718715696999995</v>
+        <v>4.1718715697000004</v>
       </c>
       <c r="D219" s="2">
         <v>4.9330698000000003E-3</v>
@@ -14612,13 +14633,13 @@
         <v>0.18359998979999997</v>
       </c>
       <c r="F219" s="2">
-        <v>1.9030036384000004</v>
+        <v>1.9030036384</v>
       </c>
       <c r="G219" s="2">
         <v>1.4166719899999999E-2</v>
       </c>
       <c r="H219" s="2">
-        <v>7.3240962696</v>
+        <v>7.3240962695999992</v>
       </c>
       <c r="I219" s="2">
         <v>0.28268344979999999</v>
@@ -14627,16 +14648,16 @@
         <v>4.8653498999999996E-3</v>
       </c>
       <c r="K219" s="2">
-        <v>0.94212681830000011</v>
+        <v>0.9421268183</v>
       </c>
       <c r="L219" s="2">
         <v>2.1589099E-3</v>
       </c>
       <c r="M219" s="2">
-        <v>0.95493683979999999</v>
+        <v>0.9549368398000001</v>
       </c>
       <c r="N219" s="2">
-        <v>2.3483739899999998E-2</v>
+        <v>2.3483739899999995E-2</v>
       </c>
       <c r="O219" s="2">
         <v>1.1590000000000001E-3</v>
@@ -14651,16 +14672,16 @@
         <v>95</v>
       </c>
       <c r="C220" s="2">
-        <v>45.854369898500003</v>
+        <v>45.854369898499996</v>
       </c>
       <c r="D220" s="2">
         <v>5.3277155899999998E-2</v>
       </c>
       <c r="E220" s="2">
-        <v>2.0133382286000003</v>
+        <v>2.0133382285999999</v>
       </c>
       <c r="F220" s="2">
-        <v>21.619368151600003</v>
+        <v>21.6193681516</v>
       </c>
       <c r="G220" s="2">
         <v>0.15625892159999999</v>
@@ -14681,7 +14702,7 @@
         <v>2.42445591E-2</v>
       </c>
       <c r="M220" s="2">
-        <v>10.3483380446</v>
+        <v>10.348338044599998</v>
       </c>
       <c r="N220" s="2">
         <v>0.26536626190000001</v>
@@ -14691,7 +14712,7 @@
       </c>
       <c r="P220" s="2"/>
       <c r="Q220" s="2">
-        <v>173.88030154179998</v>
+        <v>173.88030154179995</v>
       </c>
     </row>
     <row r="221" spans="1:17" x14ac:dyDescent="0.25">
@@ -14705,19 +14726,19 @@
         <v>4.4089374596000006</v>
       </c>
       <c r="D221" s="2">
-        <v>1.1544905099999998</v>
+        <v>1.15449051</v>
       </c>
       <c r="E221" s="2">
         <v>0.21959732979999999</v>
       </c>
       <c r="F221" s="2">
-        <v>2.8340743380000002</v>
+        <v>2.8340743380000006</v>
       </c>
       <c r="G221" s="2">
-        <v>4.4409935799999998</v>
+        <v>4.4409935800000007</v>
       </c>
       <c r="H221" s="2">
-        <v>17.608619569399998</v>
+        <v>17.608619569400002</v>
       </c>
       <c r="I221" s="2">
         <v>2.1314959997000003</v>
@@ -14726,16 +14747,16 @@
         <v>1.115909E-2</v>
       </c>
       <c r="K221" s="2">
-        <v>1.2647888485000003</v>
+        <v>1.2647888484999998</v>
       </c>
       <c r="L221" s="2">
         <v>1.4593398999999999E-3</v>
       </c>
       <c r="M221" s="2">
-        <v>6.1242180397000014</v>
+        <v>6.1242180396999997</v>
       </c>
       <c r="N221" s="2">
-        <v>0.53442169949999996</v>
+        <v>0.53442169950000007</v>
       </c>
       <c r="O221" s="2">
         <v>4.8697999999999998E-4</v>
@@ -14744,7 +14765,7 @@
         <v>0.15600999999999998</v>
       </c>
       <c r="Q221" s="2">
-        <v>40.890752784100002</v>
+        <v>40.890752784100009</v>
       </c>
     </row>
     <row r="222" spans="1:17" x14ac:dyDescent="0.25">
@@ -14752,10 +14773,10 @@
         <v>95</v>
       </c>
       <c r="C222" s="2">
-        <v>45.502503856200001</v>
+        <v>45.502503856199993</v>
       </c>
       <c r="D222" s="2">
-        <v>12.254873099900001</v>
+        <v>12.254873099899999</v>
       </c>
       <c r="E222" s="2">
         <v>2.3130319035000002</v>
@@ -14767,22 +14788,22 @@
         <v>46.524805398200002</v>
       </c>
       <c r="H222" s="2">
-        <v>173.37130044540001</v>
+        <v>173.37130044540004</v>
       </c>
       <c r="I222" s="2">
-        <v>21.590170588799996</v>
+        <v>21.590170588800003</v>
       </c>
       <c r="J222" s="2">
         <v>0.116062945</v>
       </c>
       <c r="K222" s="2">
-        <v>13.189703121400001</v>
+        <v>13.189703121399999</v>
       </c>
       <c r="L222" s="2">
         <v>1.56003446E-2</v>
       </c>
       <c r="M222" s="2">
-        <v>64.876122410999969</v>
+        <v>64.876122410999983</v>
       </c>
       <c r="N222" s="2">
         <v>5.6821343599</v>
@@ -14794,7 +14815,593 @@
         <v>1.6341459</v>
       </c>
       <c r="Q222" s="2">
-        <v>416.89307008139997</v>
+        <v>416.89307008140003</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>140</v>
+      </c>
+      <c r="B223" t="s">
+        <v>94</v>
+      </c>
+      <c r="C223" s="2">
+        <v>2.4249565095999999</v>
+      </c>
+      <c r="D223" s="2">
+        <v>2.2730884398000004</v>
+      </c>
+      <c r="E223" s="2">
+        <v>6.6615639800000001E-2</v>
+      </c>
+      <c r="F223" s="2">
+        <v>1.8550803674</v>
+      </c>
+      <c r="G223" s="2">
+        <v>0.77554355990000001</v>
+      </c>
+      <c r="H223" s="2">
+        <v>18.5775569993</v>
+      </c>
+      <c r="I223" s="2">
+        <v>2.2981995896999994</v>
+      </c>
+      <c r="J223" s="2">
+        <v>0.17071804999999998</v>
+      </c>
+      <c r="K223" s="2">
+        <v>4.2378244185000007</v>
+      </c>
+      <c r="L223" s="2">
+        <v>8.8948E-4</v>
+      </c>
+      <c r="M223" s="2">
+        <v>1.5976589097999998</v>
+      </c>
+      <c r="N223" s="2">
+        <v>0.13514408980000001</v>
+      </c>
+      <c r="O223" s="2">
+        <v>3.7877000000000001E-4</v>
+      </c>
+      <c r="P223" s="2">
+        <v>0.25136757990000003</v>
+      </c>
+      <c r="Q223" s="2">
+        <v>34.665022403499997</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B224" t="s">
+        <v>95</v>
+      </c>
+      <c r="C224" s="2">
+        <v>24.097924818300001</v>
+      </c>
+      <c r="D224" s="2">
+        <v>22.689838207900003</v>
+      </c>
+      <c r="E224" s="2">
+        <v>0.66675049880000004</v>
+      </c>
+      <c r="F224" s="2">
+        <v>18.545303333999996</v>
+      </c>
+      <c r="G224" s="2">
+        <v>7.2516603462999996</v>
+      </c>
+      <c r="H224" s="2">
+        <v>181.36642822970001</v>
+      </c>
+      <c r="I224" s="2">
+        <v>22.4070280784</v>
+      </c>
+      <c r="J224" s="2">
+        <v>1.6984237674</v>
+      </c>
+      <c r="K224" s="2">
+        <v>42.391137100299972</v>
+      </c>
+      <c r="L224" s="2">
+        <v>8.7613780000000002E-3</v>
+      </c>
+      <c r="M224" s="2">
+        <v>15.978481197799997</v>
+      </c>
+      <c r="N224" s="2">
+        <v>1.2365684233000001</v>
+      </c>
+      <c r="O224" s="2">
+        <v>3.7741424E-3</v>
+      </c>
+      <c r="P224" s="2">
+        <v>2.4858339050000002</v>
+      </c>
+      <c r="Q224" s="2">
+        <v>340.82791342759998</v>
+      </c>
+    </row>
+    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>141</v>
+      </c>
+      <c r="B225" t="s">
+        <v>94</v>
+      </c>
+      <c r="C225" s="2">
+        <v>3.1846716895999996</v>
+      </c>
+      <c r="D225" s="2">
+        <v>0.62872975990000002</v>
+      </c>
+      <c r="E225" s="2">
+        <v>2.5661769900000003E-2</v>
+      </c>
+      <c r="F225" s="2">
+        <v>1.7990672481000001</v>
+      </c>
+      <c r="G225" s="2">
+        <v>0.38508512989999999</v>
+      </c>
+      <c r="H225" s="2">
+        <v>8.2126466693999998</v>
+      </c>
+      <c r="I225" s="2">
+        <v>3.3679871098</v>
+      </c>
+      <c r="J225" s="2">
+        <v>1.7524459999999999E-2</v>
+      </c>
+      <c r="K225" s="2">
+        <v>3.0730268883000003</v>
+      </c>
+      <c r="L225" s="2">
+        <v>4.6474997999999997E-3</v>
+      </c>
+      <c r="M225" s="2">
+        <v>2.3753682897000004</v>
+      </c>
+      <c r="N225" s="2">
+        <v>1.33431399E-2</v>
+      </c>
+      <c r="O225" s="2">
+        <v>2.6613990000000002E-4</v>
+      </c>
+      <c r="P225" s="2">
+        <v>1.7819999999999999E-5</v>
+      </c>
+      <c r="Q225" s="2">
+        <v>23.0880436142</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B226" t="s">
+        <v>95</v>
+      </c>
+      <c r="C226" s="2">
+        <v>32.880384810000002</v>
+      </c>
+      <c r="D226" s="2">
+        <v>6.4564994248000005</v>
+      </c>
+      <c r="E226" s="2">
+        <v>0.25220011199999998</v>
+      </c>
+      <c r="F226" s="2">
+        <v>17.830204313700001</v>
+      </c>
+      <c r="G226" s="2">
+        <v>3.7452334208</v>
+      </c>
+      <c r="H226" s="2">
+        <v>81.645555451799993</v>
+      </c>
+      <c r="I226" s="2">
+        <v>33.827008876400001</v>
+      </c>
+      <c r="J226" s="2">
+        <v>0.1712958738</v>
+      </c>
+      <c r="K226" s="2">
+        <v>30.588842019599994</v>
+      </c>
+      <c r="L226" s="2">
+        <v>4.4290674899999993E-2</v>
+      </c>
+      <c r="M226" s="2">
+        <v>23.556705104900004</v>
+      </c>
+      <c r="N226" s="2">
+        <v>0.1200567261</v>
+      </c>
+      <c r="O226" s="2">
+        <v>2.5097002000000002E-3</v>
+      </c>
+      <c r="P226" s="2">
+        <v>1.6804250000000001E-4</v>
+      </c>
+      <c r="Q226" s="2">
+        <v>231.12095455149998</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>142</v>
+      </c>
+      <c r="B227" t="s">
+        <v>94</v>
+      </c>
+      <c r="C227" s="2">
+        <v>3.9797424395999998</v>
+      </c>
+      <c r="D227" s="2">
+        <v>3.0326020197000001</v>
+      </c>
+      <c r="E227" s="2">
+        <v>9.1755009700000015E-2</v>
+      </c>
+      <c r="F227" s="2">
+        <v>6.7601680280000007</v>
+      </c>
+      <c r="G227" s="2">
+        <v>0.87398166989999992</v>
+      </c>
+      <c r="H227" s="2">
+        <v>10.026497469499999</v>
+      </c>
+      <c r="I227" s="2">
+        <v>7.3240203799999977</v>
+      </c>
+      <c r="J227" s="2">
+        <v>5.56319E-3</v>
+      </c>
+      <c r="K227" s="2">
+        <v>2.4935459886000002</v>
+      </c>
+      <c r="L227" s="2">
+        <v>6.1733000000000003E-4</v>
+      </c>
+      <c r="M227" s="2">
+        <v>1.3239372598999999</v>
+      </c>
+      <c r="N227" s="2">
+        <v>8.7697019799999998E-2</v>
+      </c>
+      <c r="O227" s="2">
+        <v>1.04E-2</v>
+      </c>
+      <c r="P227" s="2">
+        <v>1.0499999999999999E-6</v>
+      </c>
+      <c r="Q227" s="2">
+        <v>36.010528854699984</v>
+      </c>
+    </row>
+    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B228" t="s">
+        <v>95</v>
+      </c>
+      <c r="C228" s="2">
+        <v>43.113060183500004</v>
+      </c>
+      <c r="D228" s="2">
+        <v>35.272189289899998</v>
+      </c>
+      <c r="E228" s="2">
+        <v>0.91699278519999994</v>
+      </c>
+      <c r="F228" s="2">
+        <v>70.626765027999994</v>
+      </c>
+      <c r="G228" s="2">
+        <v>8.7704586917</v>
+      </c>
+      <c r="H228" s="2">
+        <v>106.03334132839998</v>
+      </c>
+      <c r="I228" s="2">
+        <v>86.0617556407</v>
+      </c>
+      <c r="J228" s="2">
+        <v>5.2701979900000001E-2</v>
+      </c>
+      <c r="K228" s="2">
+        <v>25.704985495300001</v>
+      </c>
+      <c r="L228" s="2">
+        <v>5.9942742999999996E-3</v>
+      </c>
+      <c r="M228" s="2">
+        <v>13.332272374199999</v>
+      </c>
+      <c r="N228" s="2">
+        <v>0.79015015020000001</v>
+      </c>
+      <c r="O228" s="2">
+        <v>9.9944000000000005E-2</v>
+      </c>
+      <c r="P228" s="2">
+        <v>1.0090499999999999E-5</v>
+      </c>
+      <c r="Q228" s="2">
+        <v>390.78062131180008</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>143</v>
+      </c>
+      <c r="B229" t="s">
+        <v>94</v>
+      </c>
+      <c r="C229" s="2">
+        <v>0.1226959297</v>
+      </c>
+      <c r="D229" s="2">
+        <v>6.757E-4</v>
+      </c>
+      <c r="E229" s="2">
+        <v>9.0969899999999998E-5</v>
+      </c>
+      <c r="F229" s="2">
+        <v>0.96665056849999997</v>
+      </c>
+      <c r="G229" s="2">
+        <v>1.9619E-4</v>
+      </c>
+      <c r="H229" s="2">
+        <v>8.07463296E-2</v>
+      </c>
+      <c r="I229" s="2">
+        <v>1.2235129999999999E-2</v>
+      </c>
+      <c r="J229" s="2"/>
+      <c r="K229" s="2">
+        <v>0.14371123899999999</v>
+      </c>
+      <c r="L229" s="2">
+        <v>1.1174900000000001E-3</v>
+      </c>
+      <c r="M229" s="2">
+        <v>6.7643797999999995E-3</v>
+      </c>
+      <c r="N229" s="2">
+        <v>4.3060899000000007E-3</v>
+      </c>
+      <c r="O229" s="2">
+        <v>1.11019E-3</v>
+      </c>
+      <c r="P229" s="2"/>
+      <c r="Q229" s="2">
+        <v>1.3403002064</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B230" t="s">
+        <v>95</v>
+      </c>
+      <c r="C230" s="2">
+        <v>1.3856734368000001</v>
+      </c>
+      <c r="D230" s="2">
+        <v>7.0948499999999998E-3</v>
+      </c>
+      <c r="E230" s="2">
+        <v>1.0006699999999999E-3</v>
+      </c>
+      <c r="F230" s="2">
+        <v>10.5961760258</v>
+      </c>
+      <c r="G230" s="2">
+        <v>2.0599949000000002E-3</v>
+      </c>
+      <c r="H230" s="2">
+        <v>0.81637767309999998</v>
+      </c>
+      <c r="I230" s="2">
+        <v>0.1315276474</v>
+      </c>
+      <c r="J230" s="2"/>
+      <c r="K230" s="2">
+        <v>1.5949362213</v>
+      </c>
+      <c r="L230" s="2">
+        <v>1.1957143E-2</v>
+      </c>
+      <c r="M230" s="2">
+        <v>6.69673618E-2</v>
+      </c>
+      <c r="N230" s="2">
+        <v>4.3060899999999999E-2</v>
+      </c>
+      <c r="O230" s="2">
+        <v>1.1768013899999999E-2</v>
+      </c>
+      <c r="P230" s="2"/>
+      <c r="Q230" s="2">
+        <v>14.668599937999998</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>144</v>
+      </c>
+      <c r="B231" t="s">
+        <v>94</v>
+      </c>
+      <c r="C231" s="2">
+        <v>8.6563000000000005E-3</v>
+      </c>
+      <c r="D231" s="2">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="E231" s="2">
+        <v>3.1817999999999999E-4</v>
+      </c>
+      <c r="F231" s="2">
+        <v>0.50897346939999988</v>
+      </c>
+      <c r="G231" s="2">
+        <v>1.4238E-4</v>
+      </c>
+      <c r="H231" s="2">
+        <v>1.5935849700000001E-2</v>
+      </c>
+      <c r="I231" s="2">
+        <v>4.3849398000000003E-3</v>
+      </c>
+      <c r="J231" s="2"/>
+      <c r="K231" s="2">
+        <v>7.8782592999999991E-3</v>
+      </c>
+      <c r="L231" s="2"/>
+      <c r="M231" s="2"/>
+      <c r="N231" s="2">
+        <v>1.73317E-3</v>
+      </c>
+      <c r="O231" s="2"/>
+      <c r="P231" s="2"/>
+      <c r="Q231" s="2">
+        <v>0.5483225481999997</v>
+      </c>
+    </row>
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B232" t="s">
+        <v>95</v>
+      </c>
+      <c r="C232" s="2">
+        <v>9.6529820000000002E-2</v>
+      </c>
+      <c r="D232" s="2">
+        <v>3.15E-3</v>
+      </c>
+      <c r="E232" s="2">
+        <v>3.4999800000000002E-3</v>
+      </c>
+      <c r="F232" s="2">
+        <v>5.7099277832000004</v>
+      </c>
+      <c r="G232" s="2">
+        <v>1.4949900000000001E-3</v>
+      </c>
+      <c r="H232" s="2">
+        <v>0.16102565290000001</v>
+      </c>
+      <c r="I232" s="2">
+        <v>4.7138105E-2</v>
+      </c>
+      <c r="J232" s="2"/>
+      <c r="K232" s="2">
+        <v>8.7447993200000004E-2</v>
+      </c>
+      <c r="L232" s="2"/>
+      <c r="M232" s="2"/>
+      <c r="N232" s="2">
+        <v>1.7331699899999997E-2</v>
+      </c>
+      <c r="O232" s="2"/>
+      <c r="P232" s="2"/>
+      <c r="Q232" s="2">
+        <v>6.1275460241999999</v>
+      </c>
+    </row>
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>145</v>
+      </c>
+      <c r="B233" t="s">
+        <v>94</v>
+      </c>
+      <c r="C233" s="2">
+        <v>3.4565984594000003</v>
+      </c>
+      <c r="D233" s="2">
+        <v>4.0530007899000005</v>
+      </c>
+      <c r="E233" s="2">
+        <v>9.7755990000000001E-2</v>
+      </c>
+      <c r="F233" s="2">
+        <v>7.3356065579999994</v>
+      </c>
+      <c r="G233" s="2">
+        <v>1.7080680000000001E-2</v>
+      </c>
+      <c r="H233" s="2">
+        <v>1.8812888993999997</v>
+      </c>
+      <c r="I233" s="2">
+        <v>4.5670779396999999</v>
+      </c>
+      <c r="J233" s="2">
+        <v>6.4868609999999993E-2</v>
+      </c>
+      <c r="K233" s="2">
+        <v>1.6700030388</v>
+      </c>
+      <c r="L233" s="2">
+        <v>5.9423700000000006E-3</v>
+      </c>
+      <c r="M233" s="2">
+        <v>1.0992869800000001E-2</v>
+      </c>
+      <c r="N233" s="2">
+        <v>2.2451529800000002E-2</v>
+      </c>
+      <c r="O233" s="2">
+        <v>3.1314400000000001E-3</v>
+      </c>
+      <c r="P233" s="2"/>
+      <c r="Q233" s="2">
+        <v>23.185799174800003</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B234" t="s">
+        <v>95</v>
+      </c>
+      <c r="C234" s="2">
+        <v>41.702728597300009</v>
+      </c>
+      <c r="D234" s="2">
+        <v>49.901498429899995</v>
+      </c>
+      <c r="E234" s="2">
+        <v>1.1533225899000001</v>
+      </c>
+      <c r="F234" s="2">
+        <v>87.306846898499998</v>
+      </c>
+      <c r="G234" s="2">
+        <v>0.17934713999999999</v>
+      </c>
+      <c r="H234" s="2">
+        <v>22.087344547400001</v>
+      </c>
+      <c r="I234" s="2">
+        <v>52.845635322199996</v>
+      </c>
+      <c r="J234" s="2">
+        <v>0.74056040489999997</v>
+      </c>
+      <c r="K234" s="2">
+        <v>18.597860709700001</v>
+      </c>
+      <c r="L234" s="2">
+        <v>6.3583358899999998E-2</v>
+      </c>
+      <c r="M234" s="2">
+        <v>0.1089487729</v>
+      </c>
+      <c r="N234" s="2">
+        <v>0.2245152997</v>
+      </c>
+      <c r="O234" s="2">
+        <v>3.3193263899999999E-2</v>
+      </c>
+      <c r="P234" s="2"/>
+      <c r="Q234" s="2">
+        <v>274.94538533520006</v>
       </c>
     </row>
   </sheetData>
@@ -14804,7 +15411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D2E8B6-8413-4B5C-882C-FCAE21C7E121}">
-  <dimension ref="A2:AE116"/>
+  <dimension ref="A2:AE122"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -23201,31 +23808,31 @@
         <v>125</v>
       </c>
       <c r="B102" s="2">
-        <v>10.5412650994</v>
+        <v>10.541265099400004</v>
       </c>
       <c r="C102" s="2">
-        <v>1.5404671898000002</v>
+        <v>1.5404671897999997</v>
       </c>
       <c r="D102" s="2">
         <v>0.30973334990000001</v>
       </c>
       <c r="E102" s="2">
-        <v>10.676857608499999</v>
+        <v>10.676857608500004</v>
       </c>
       <c r="F102" s="2">
         <v>1.52429345</v>
       </c>
       <c r="G102" s="2">
-        <v>7.049551618999998</v>
+        <v>7.0495516189999989</v>
       </c>
       <c r="H102" s="2">
-        <v>8.1942503297999973</v>
+        <v>8.1942503297999991</v>
       </c>
       <c r="I102" s="2">
         <v>2.5951819899999999E-2</v>
       </c>
       <c r="J102" s="2">
-        <v>6.4725927186999996</v>
+        <v>6.4725927187000005</v>
       </c>
       <c r="K102" s="2">
         <v>2.0430669899999997E-2</v>
@@ -23234,7 +23841,7 @@
         <v>2.0410046298000002</v>
       </c>
       <c r="M102" s="2">
-        <v>0.80778228969999988</v>
+        <v>0.80778228969999999</v>
       </c>
       <c r="N102" s="2">
         <v>1.8677698999999999E-3</v>
@@ -23243,10 +23850,10 @@
         <v>0.15001043999999999</v>
       </c>
       <c r="P102" s="2">
-        <v>49.356058984300013</v>
+        <v>49.35605898430002</v>
       </c>
       <c r="Q102" s="2">
-        <v>1.8323795698000003</v>
+        <v>1.8323795698000001</v>
       </c>
       <c r="R102" s="2">
         <v>0.57434707969999999</v>
@@ -23258,25 +23865,25 @@
         <v>6.8793667697999998</v>
       </c>
       <c r="U102" s="2">
-        <v>0.79308789959999981</v>
+        <v>0.79308789959999992</v>
       </c>
       <c r="V102" s="2">
         <v>7.6458753295999999</v>
       </c>
       <c r="W102" s="2">
-        <v>6.1348258998000009</v>
+        <v>6.1348258998</v>
       </c>
       <c r="X102" s="2">
         <v>3.5879199899999999E-2</v>
       </c>
       <c r="Y102" s="2">
-        <v>3.7261149620999983</v>
+        <v>3.7261149621000005</v>
       </c>
       <c r="Z102" s="2">
         <v>3.1035999999999998E-4</v>
       </c>
       <c r="AA102" s="2">
-        <v>0.27105190979999999</v>
+        <v>0.27105190979999993</v>
       </c>
       <c r="AB102" s="2">
         <v>0.1273728697</v>
@@ -23286,7 +23893,7 @@
       </c>
       <c r="AD102" s="2"/>
       <c r="AE102" s="2">
-        <v>28.126867349800001</v>
+        <v>28.126867349799998</v>
       </c>
     </row>
     <row r="103" spans="1:31" x14ac:dyDescent="0.25">
@@ -23294,10 +23901,10 @@
         <v>126</v>
       </c>
       <c r="B103" s="2">
-        <v>2.2410354895000002</v>
+        <v>2.2410354894999993</v>
       </c>
       <c r="C103" s="2">
-        <v>4.321877409799999</v>
+        <v>4.3218774097999999</v>
       </c>
       <c r="D103" s="2">
         <v>1.7164667597999999</v>
@@ -23312,7 +23919,7 @@
         <v>28.744438628800001</v>
       </c>
       <c r="H103" s="2">
-        <v>3.9797154597000004</v>
+        <v>3.9797154597</v>
       </c>
       <c r="I103" s="2">
         <v>6.0730200000000002E-3</v>
@@ -23324,7 +23931,7 @@
         <v>2.0808800000000002E-3</v>
       </c>
       <c r="L103" s="2">
-        <v>5.5570111197000012</v>
+        <v>5.5570111197000003</v>
       </c>
       <c r="M103" s="2">
         <v>0.24435603989999999</v>
@@ -23351,10 +23958,10 @@
         <v>3.6203973293999994</v>
       </c>
       <c r="U103" s="2">
-        <v>1.5519809893000003</v>
+        <v>1.5519809893000001</v>
       </c>
       <c r="V103" s="2">
-        <v>6.7983298396000009</v>
+        <v>6.7983298396</v>
       </c>
       <c r="W103" s="2">
         <v>4.2708199695999998</v>
@@ -23363,7 +23970,7 @@
         <v>3.6656629900000001E-2</v>
       </c>
       <c r="Y103" s="2">
-        <v>1.6357991537000003</v>
+        <v>1.6357991537000005</v>
       </c>
       <c r="Z103" s="2">
         <v>5.0851990000000001E-4</v>
@@ -23379,7 +23986,7 @@
       </c>
       <c r="AD103" s="2"/>
       <c r="AE103" s="2">
-        <v>27.927392990199998</v>
+        <v>27.927392990200001</v>
       </c>
     </row>
     <row r="104" spans="1:31" x14ac:dyDescent="0.25">
@@ -23387,7 +23994,7 @@
         <v>127</v>
       </c>
       <c r="B104" s="2">
-        <v>4.2272902993999999</v>
+        <v>4.227290299399999</v>
       </c>
       <c r="C104" s="2">
         <v>0.55025838990000009</v>
@@ -23399,25 +24006,25 @@
         <v>9.5613452584999994</v>
       </c>
       <c r="F104" s="2">
-        <v>1.3229299500000002</v>
+        <v>1.32292995</v>
       </c>
       <c r="G104" s="2">
-        <v>9.6362721188999991</v>
+        <v>9.6362721189000009</v>
       </c>
       <c r="H104" s="2">
-        <v>2.5468940288000002</v>
+        <v>2.5468940287999993</v>
       </c>
       <c r="I104" s="2">
-        <v>4.6518099900000005E-2</v>
+        <v>4.6518099899999998E-2</v>
       </c>
       <c r="J104" s="2">
-        <v>4.2512866591000007</v>
+        <v>4.251286659099998</v>
       </c>
       <c r="K104" s="2">
-        <v>1.1868579900000001E-2</v>
+        <v>1.1868579900000002E-2</v>
       </c>
       <c r="L104" s="2">
-        <v>3.0043624296000004</v>
+        <v>3.0043624296</v>
       </c>
       <c r="M104" s="2">
         <v>4.4385997999999999E-3</v>
@@ -23429,34 +24036,34 @@
         <v>2.1098999999999999E-6</v>
       </c>
       <c r="P104" s="2">
-        <v>35.332630863600002</v>
+        <v>35.332630863599995</v>
       </c>
       <c r="Q104" s="2">
         <v>1.6615208799000001</v>
       </c>
       <c r="R104" s="2">
-        <v>0.51589150960000008</v>
+        <v>0.51589150959999996</v>
       </c>
       <c r="S104" s="2">
         <v>8.6651270000000002E-2</v>
       </c>
       <c r="T104" s="2">
-        <v>6.9704481292999994</v>
+        <v>6.9704481292999985</v>
       </c>
       <c r="U104" s="2">
-        <v>0.7145917797000001</v>
+        <v>0.71459177969999998</v>
       </c>
       <c r="V104" s="2">
         <v>25.576800959300002</v>
       </c>
       <c r="W104" s="2">
-        <v>3.7193456194000003</v>
+        <v>3.7193456193999994</v>
       </c>
       <c r="X104" s="2">
         <v>0.15393631990000001</v>
       </c>
       <c r="Y104" s="2">
-        <v>3.448284674400004</v>
+        <v>3.4482846744000013</v>
       </c>
       <c r="Z104" s="2">
         <v>5.2634999999999999E-3</v>
@@ -23465,7 +24072,7 @@
         <v>0.83277477980000003</v>
       </c>
       <c r="AB104" s="2">
-        <v>1.3298494292</v>
+        <v>1.3298494291999998</v>
       </c>
       <c r="AC104" s="2">
         <v>1.1771499999999999E-3</v>
@@ -23483,34 +24090,34 @@
         <v>4.5686707090000001</v>
       </c>
       <c r="C105" s="2">
-        <v>4.0573789997</v>
+        <v>4.0573789996999992</v>
       </c>
       <c r="D105" s="2">
-        <v>0.8197688098</v>
+        <v>0.81976880980000011</v>
       </c>
       <c r="E105" s="2">
-        <v>21.622486007900001</v>
+        <v>21.622486007899997</v>
       </c>
       <c r="F105" s="2">
-        <v>1.5932660199999997</v>
+        <v>1.5932660200000002</v>
       </c>
       <c r="G105" s="2">
-        <v>9.5712881088999993</v>
+        <v>9.571288108900001</v>
       </c>
       <c r="H105" s="2">
-        <v>11.750750289799997</v>
+        <v>11.750750289799999</v>
       </c>
       <c r="I105" s="2">
         <v>0.2543552</v>
       </c>
       <c r="J105" s="2">
-        <v>5.8530080087000016</v>
+        <v>5.8530080086999998</v>
       </c>
       <c r="K105" s="2">
         <v>1.9358249899999999E-2</v>
       </c>
       <c r="L105" s="2">
-        <v>0.81909734989999994</v>
+        <v>0.81909734990000005</v>
       </c>
       <c r="M105" s="2">
         <v>3.4659929900000004E-2</v>
@@ -23520,25 +24127,25 @@
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2">
-        <v>60.969117683500002</v>
+        <v>60.969117683499995</v>
       </c>
       <c r="Q105" s="2">
-        <v>4.3526002198999993</v>
+        <v>4.3526002199000011</v>
       </c>
       <c r="R105" s="2">
-        <v>1.0581553996999999</v>
+        <v>1.0581553996999997</v>
       </c>
       <c r="S105" s="2">
         <v>0.1133477499</v>
       </c>
       <c r="T105" s="2">
-        <v>9.636341799300002</v>
+        <v>9.6363417993000002</v>
       </c>
       <c r="U105" s="2">
         <v>1.8013652098000001</v>
       </c>
       <c r="V105" s="2">
-        <v>10.649425239400001</v>
+        <v>10.649425239399999</v>
       </c>
       <c r="W105" s="2">
         <v>1.2856835993</v>
@@ -23547,13 +24154,13 @@
         <v>3.5955500000000001E-2</v>
       </c>
       <c r="Y105" s="2">
-        <v>0.9466944828999998</v>
+        <v>0.94669448290000047</v>
       </c>
       <c r="Z105" s="2">
         <v>4.9492999999999998E-4</v>
       </c>
       <c r="AA105" s="2">
-        <v>0.39541672950000001</v>
+        <v>0.39541672949999995</v>
       </c>
       <c r="AB105" s="2">
         <v>0.1252695395</v>
@@ -23588,10 +24195,10 @@
         <v>0.60749774999999995</v>
       </c>
       <c r="G106" s="2">
-        <v>9.3156009100000006E-2</v>
+        <v>9.3156009099999992E-2</v>
       </c>
       <c r="H106" s="2">
-        <v>5.0729019899999998E-2</v>
+        <v>5.0729019900000012E-2</v>
       </c>
       <c r="I106" s="2"/>
       <c r="J106" s="2">
@@ -23604,7 +24211,7 @@
         <v>5.7993298E-3</v>
       </c>
       <c r="M106" s="2">
-        <v>9.9220597000000011E-3</v>
+        <v>9.9220596999999994E-3</v>
       </c>
       <c r="N106" s="2">
         <v>2.5593699E-3</v>
@@ -23613,13 +24220,13 @@
         <v>1.95E-6</v>
       </c>
       <c r="P106" s="2">
-        <v>4.4932006754000007</v>
+        <v>4.4932006753999998</v>
       </c>
       <c r="Q106" s="2">
         <v>4.7702698E-3</v>
       </c>
       <c r="R106" s="2">
-        <v>2.5567209800000001E-2</v>
+        <v>2.5567209799999997E-2</v>
       </c>
       <c r="S106" s="2">
         <v>5.5704989999999998E-4</v>
@@ -23638,7 +24245,7 @@
       </c>
       <c r="X106" s="2"/>
       <c r="Y106" s="2">
-        <v>7.198933400000003E-2</v>
+        <v>7.1989334000000044E-2</v>
       </c>
       <c r="Z106" s="2">
         <v>3.5058989999999998E-4</v>
@@ -23656,7 +24263,7 @@
         <v>4.7319000000000001E-4</v>
       </c>
       <c r="AE106" s="2">
-        <v>0.28452559259999999</v>
+        <v>0.28452559260000004</v>
       </c>
     </row>
     <row r="107" spans="1:31" x14ac:dyDescent="0.25">
@@ -23686,7 +24293,7 @@
       </c>
       <c r="I107" s="2"/>
       <c r="J107" s="2">
-        <v>0.14930280960000006</v>
+        <v>0.14930280960000003</v>
       </c>
       <c r="K107" s="2"/>
       <c r="L107" s="2">
@@ -23723,19 +24330,19 @@
       </c>
       <c r="X107" s="2"/>
       <c r="Y107" s="2">
-        <v>6.7336923600000015E-2</v>
+        <v>6.7336923599999973E-2</v>
       </c>
       <c r="Z107" s="2"/>
       <c r="AA107" s="2">
         <v>5.8966298999999995E-3</v>
       </c>
       <c r="AB107" s="2">
-        <v>2.7714697999999998E-3</v>
+        <v>2.7714698000000002E-3</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" s="2"/>
       <c r="AE107" s="2">
-        <v>0.24104739280000004</v>
+        <v>0.24104739280000001</v>
       </c>
     </row>
     <row r="108" spans="1:31" x14ac:dyDescent="0.25">
@@ -23743,25 +24350,25 @@
         <v>131</v>
       </c>
       <c r="B108" s="2">
-        <v>2.5096564792999998</v>
+        <v>2.5096564793000002</v>
       </c>
       <c r="C108" s="2">
         <v>0.38593559999999999</v>
       </c>
       <c r="D108" s="2">
-        <v>7.6094269899999983E-2</v>
+        <v>7.6094269899999997E-2</v>
       </c>
       <c r="E108" s="2">
-        <v>4.6978368785999995</v>
+        <v>4.6978368786000004</v>
       </c>
       <c r="F108" s="2">
-        <v>0.89445370989999995</v>
+        <v>0.89445370990000006</v>
       </c>
       <c r="G108" s="2">
-        <v>2.0722231492999996</v>
+        <v>2.0722231493000001</v>
       </c>
       <c r="H108" s="2">
-        <v>4.3039844189000007</v>
+        <v>4.3039844189000025</v>
       </c>
       <c r="I108" s="2">
         <v>2.6595699E-3</v>
@@ -23785,10 +24392,10 @@
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="P108" s="2">
-        <v>20.0968495937</v>
+        <v>20.096849593700004</v>
       </c>
       <c r="Q108" s="2">
-        <v>1.4394571097999997</v>
+        <v>1.4394571098</v>
       </c>
       <c r="R108" s="2">
         <v>0.31051675979999999</v>
@@ -23797,31 +24404,31 @@
         <v>0.14568527990000002</v>
       </c>
       <c r="T108" s="2">
-        <v>6.8436526397000002</v>
+        <v>6.8436526396999993</v>
       </c>
       <c r="U108" s="2">
         <v>1.0969614695000001</v>
       </c>
       <c r="V108" s="2">
-        <v>3.8720962798999996</v>
+        <v>3.8720962799</v>
       </c>
       <c r="W108" s="2">
-        <v>0.99706682870000007</v>
+        <v>0.9970668287000003</v>
       </c>
       <c r="X108" s="2">
         <v>1E-4</v>
       </c>
       <c r="Y108" s="2">
-        <v>0.70961261419999966</v>
+        <v>0.70961261419999988</v>
       </c>
       <c r="Z108" s="2">
         <v>1.426E-3</v>
       </c>
       <c r="AA108" s="2">
-        <v>1.2349703098</v>
+        <v>1.2349703097999998</v>
       </c>
       <c r="AB108" s="2">
-        <v>6.4870549900000005E-2</v>
+        <v>6.4870549899999991E-2</v>
       </c>
       <c r="AC108" s="2">
         <v>2.2431E-4</v>
@@ -23830,7 +24437,7 @@
         <v>1.9715999999999999E-4</v>
       </c>
       <c r="AE108" s="2">
-        <v>16.716837311199995</v>
+        <v>16.716837311199999</v>
       </c>
     </row>
     <row r="109" spans="1:31" x14ac:dyDescent="0.25">
@@ -23844,28 +24451,28 @@
         <v>0.67271874990000002</v>
       </c>
       <c r="D109" s="2">
-        <v>0.56355119989999991</v>
+        <v>0.56355119990000002</v>
       </c>
       <c r="E109" s="2">
-        <v>12.2575770487</v>
+        <v>12.257577048699998</v>
       </c>
       <c r="F109" s="2">
-        <v>1.4420222100000002</v>
+        <v>1.44202221</v>
       </c>
       <c r="G109" s="2">
-        <v>13.599364889</v>
+        <v>13.599364889000002</v>
       </c>
       <c r="H109" s="2">
-        <v>5.8482524195000005</v>
+        <v>5.8482524194999996</v>
       </c>
       <c r="I109" s="2">
         <v>8.294195E-2</v>
       </c>
       <c r="J109" s="2">
-        <v>5.5395596578999999</v>
+        <v>5.539559657899999</v>
       </c>
       <c r="K109" s="2">
-        <v>2.09818799E-2</v>
+        <v>2.0981879900000003E-2</v>
       </c>
       <c r="L109" s="2">
         <v>3.2933772699000001</v>
@@ -23878,19 +24485,19 @@
       </c>
       <c r="O109" s="2"/>
       <c r="P109" s="2">
-        <v>50.902238913799998</v>
+        <v>50.902238913799991</v>
       </c>
       <c r="Q109" s="2">
         <v>2.9099903197999999</v>
       </c>
       <c r="R109" s="2">
-        <v>1.2650178096</v>
+        <v>1.2650178096000002</v>
       </c>
       <c r="S109" s="2">
-        <v>0.1065389999</v>
+        <v>0.10653899990000001</v>
       </c>
       <c r="T109" s="2">
-        <v>9.9160820092000002</v>
+        <v>9.9160820091999984</v>
       </c>
       <c r="U109" s="2">
         <v>5.1299130896000005</v>
@@ -23899,22 +24506,22 @@
         <v>17.7356039296</v>
       </c>
       <c r="W109" s="2">
-        <v>15.8241498796</v>
+        <v>15.824149879600002</v>
       </c>
       <c r="X109" s="2">
         <v>1.0145E-2</v>
       </c>
       <c r="Y109" s="2">
-        <v>1.8697059138000007</v>
+        <v>1.8697059137999998</v>
       </c>
       <c r="Z109" s="2">
         <v>1.7019E-4</v>
       </c>
       <c r="AA109" s="2">
-        <v>0.98909154980000014</v>
+        <v>0.98909154980000002</v>
       </c>
       <c r="AB109" s="2">
-        <v>7.3265275295999999</v>
+        <v>7.3265275296000008</v>
       </c>
       <c r="AC109" s="2">
         <v>2.2160998999999999E-3</v>
@@ -23923,7 +24530,7 @@
         <v>0.5</v>
       </c>
       <c r="AE109" s="2">
-        <v>63.585152320399999</v>
+        <v>63.585152320400006</v>
       </c>
     </row>
     <row r="110" spans="1:31" x14ac:dyDescent="0.25">
@@ -23940,13 +24547,13 @@
         <v>2.3746740098999997</v>
       </c>
       <c r="E110" s="2">
-        <v>18.101094888000006</v>
+        <v>18.101094887999999</v>
       </c>
       <c r="F110" s="2">
-        <v>2.7011731796</v>
+        <v>2.7011731796000005</v>
       </c>
       <c r="G110" s="2">
-        <v>28.055478878599995</v>
+        <v>28.055478878599999</v>
       </c>
       <c r="H110" s="2">
         <v>10.904366849800001</v>
@@ -23955,7 +24562,7 @@
         <v>5.6418119900000001E-2</v>
       </c>
       <c r="J110" s="2">
-        <v>4.988294688299999</v>
+        <v>4.9882946882999999</v>
       </c>
       <c r="K110" s="2">
         <v>8.8044989900000009E-2</v>
@@ -23979,7 +24586,7 @@
         <v>1.2830309696</v>
       </c>
       <c r="R110" s="2">
-        <v>3.1578427090000001</v>
+        <v>3.1578427089999996</v>
       </c>
       <c r="S110" s="2">
         <v>8.2800989800000002E-2</v>
@@ -23988,25 +24595,25 @@
         <v>0.37280868950000001</v>
       </c>
       <c r="U110" s="2">
-        <v>7.8622929699999997E-2</v>
+        <v>7.862292970000001E-2</v>
       </c>
       <c r="V110" s="2">
-        <v>12.991646919200001</v>
+        <v>12.991646919199999</v>
       </c>
       <c r="W110" s="2">
-        <v>4.4442158596000008</v>
+        <v>4.4442158596000017</v>
       </c>
       <c r="X110" s="2">
-        <v>0.20809047999999999</v>
+        <v>0.20809048000000002</v>
       </c>
       <c r="Y110" s="2">
-        <v>2.5034657940000011</v>
+        <v>2.5034657939999998</v>
       </c>
       <c r="Z110" s="2">
         <v>3.030299E-4</v>
       </c>
       <c r="AA110" s="2">
-        <v>0.37291251980000001</v>
+        <v>0.37291251979999995</v>
       </c>
       <c r="AB110" s="2">
         <v>5.2992661893999999</v>
@@ -24024,7 +24631,7 @@
         <v>134</v>
       </c>
       <c r="B111" s="2">
-        <v>1.1333617697</v>
+        <v>1.1333617696999998</v>
       </c>
       <c r="C111" s="2">
         <v>0.89631024999999998</v>
@@ -24042,19 +24649,19 @@
         <v>10.0619224887</v>
       </c>
       <c r="H111" s="2">
-        <v>11.731190969499998</v>
+        <v>11.7311909695</v>
       </c>
       <c r="I111" s="2">
         <v>5.5333E-2</v>
       </c>
       <c r="J111" s="2">
-        <v>1.0005415778000002</v>
+        <v>1.0005415778</v>
       </c>
       <c r="K111" s="2">
-        <v>9.4723209799999999E-2</v>
+        <v>9.4723209800000013E-2</v>
       </c>
       <c r="L111" s="2">
-        <v>1.7938587298000002</v>
+        <v>1.7938587297999999</v>
       </c>
       <c r="M111" s="2">
         <v>8.9329959799999997E-2</v>
@@ -24066,34 +24673,34 @@
         <v>7.4599000000000004E-6</v>
       </c>
       <c r="P111" s="2">
-        <v>39.65177365249999</v>
+        <v>39.651773652499998</v>
       </c>
       <c r="Q111" s="2">
-        <v>3.5045785396000002</v>
+        <v>3.5045785395999998</v>
       </c>
       <c r="R111" s="2">
-        <v>1.0006790296000003</v>
+        <v>1.0006790296000001</v>
       </c>
       <c r="S111" s="2">
         <v>0.1787738797</v>
       </c>
       <c r="T111" s="2">
-        <v>2.5606531391999994</v>
+        <v>2.5606531391999998</v>
       </c>
       <c r="U111" s="2">
         <v>1.0874557998000001</v>
       </c>
       <c r="V111" s="2">
-        <v>11.886549478599999</v>
+        <v>11.886549478599997</v>
       </c>
       <c r="W111" s="2">
-        <v>4.2417172294999999</v>
+        <v>4.2417172295000007</v>
       </c>
       <c r="X111" s="2">
         <v>6.7949999999999998E-3</v>
       </c>
       <c r="Y111" s="2">
-        <v>2.1491516443000016</v>
+        <v>2.1491516442999976</v>
       </c>
       <c r="Z111" s="2">
         <v>5.4343999999999996E-4</v>
@@ -24111,7 +24718,7 @@
         <v>1.3847899999999999E-3</v>
       </c>
       <c r="AE111" s="2">
-        <v>27.484182400000002</v>
+        <v>27.484182399999998</v>
       </c>
     </row>
     <row r="112" spans="1:31" x14ac:dyDescent="0.25">
@@ -24122,25 +24729,25 @@
         <v>1.0217140897000001</v>
       </c>
       <c r="C112" s="2">
-        <v>6.5043974797999997</v>
+        <v>6.5043974798000006</v>
       </c>
       <c r="D112" s="2">
         <v>0.52745240999999998</v>
       </c>
       <c r="E112" s="2">
-        <v>3.6945644886000002</v>
+        <v>3.6945644885999998</v>
       </c>
       <c r="F112" s="2">
-        <v>4.1965709899999995E-2</v>
+        <v>4.1965709900000002E-2</v>
       </c>
       <c r="G112" s="2">
-        <v>11.790913559099996</v>
+        <v>11.7909135591</v>
       </c>
       <c r="H112" s="2">
-        <v>1.1048527398000003</v>
+        <v>1.1048527398000001</v>
       </c>
       <c r="I112" s="2">
-        <v>5.4248020000000001E-2</v>
+        <v>5.4248019999999994E-2</v>
       </c>
       <c r="J112" s="2">
         <v>1.8321259883999996</v>
@@ -24149,7 +24756,7 @@
         <v>0.22342341979999999</v>
       </c>
       <c r="L112" s="2">
-        <v>1.2727332994999998</v>
+        <v>1.2727332995</v>
       </c>
       <c r="M112" s="2">
         <v>6.660663E-2</v>
@@ -24167,28 +24774,28 @@
         <v>4.5575444996999996</v>
       </c>
       <c r="R112" s="2">
-        <v>2.6546592692999997</v>
+        <v>2.6546592693000002</v>
       </c>
       <c r="S112" s="2">
         <v>4.2404459800000002E-2</v>
       </c>
       <c r="T112" s="2">
-        <v>3.7475695992000002</v>
+        <v>3.7475695991999998</v>
       </c>
       <c r="U112" s="2">
         <v>0.96941356979999993</v>
       </c>
       <c r="V112" s="2">
-        <v>13.683405768500002</v>
+        <v>13.6834057685</v>
       </c>
       <c r="W112" s="2">
-        <v>10.998298199399999</v>
+        <v>10.998298199400001</v>
       </c>
       <c r="X112" s="2">
         <v>3.2468069999999995E-2</v>
       </c>
       <c r="Y112" s="2">
-        <v>1.2645985633000005</v>
+        <v>1.2645985632999992</v>
       </c>
       <c r="Z112" s="2">
         <v>1.3406499000000001E-3</v>
@@ -24197,7 +24804,7 @@
         <v>0.46019248979999999</v>
       </c>
       <c r="AB112" s="2">
-        <v>0.11799761959999999</v>
+        <v>0.11799761960000001</v>
       </c>
       <c r="AC112" s="2">
         <v>0.26443068990000002</v>
@@ -24221,23 +24828,23 @@
         <v>1.6000000000000001E-3</v>
       </c>
       <c r="E113" s="2">
-        <v>1.6522773781999998</v>
+        <v>1.6522773782</v>
       </c>
       <c r="F113" s="2">
         <v>8.60199E-5</v>
       </c>
       <c r="G113" s="2">
-        <v>0.1031850797</v>
+        <v>0.10318507969999999</v>
       </c>
       <c r="H113" s="2">
         <v>2.2065109999999999E-2</v>
       </c>
       <c r="I113" s="2"/>
       <c r="J113" s="2">
-        <v>3.05195181E-2</v>
+        <v>3.0519518099999997E-2</v>
       </c>
       <c r="K113" s="2">
-        <v>6.6482999000000006E-3</v>
+        <v>6.6482998999999997E-3</v>
       </c>
       <c r="L113" s="2">
         <v>5.6577097999999998E-3</v>
@@ -24250,7 +24857,7 @@
       </c>
       <c r="O113" s="2"/>
       <c r="P113" s="2">
-        <v>1.9003078649999994</v>
+        <v>1.9003078649999996</v>
       </c>
       <c r="Q113" s="2">
         <v>8.4460200000000003E-3</v>
@@ -24269,27 +24876,27 @@
         <v>2.4426099600000001E-2</v>
       </c>
       <c r="W113" s="2">
-        <v>7.8297139499999988E-2</v>
+        <v>7.8297139500000001E-2</v>
       </c>
       <c r="X113" s="2"/>
       <c r="Y113" s="2">
-        <v>0.18072428600000018</v>
+        <v>0.18072428599999998</v>
       </c>
       <c r="Z113" s="2">
         <v>1.1853000000000001E-4</v>
       </c>
       <c r="AA113" s="2">
-        <v>7.3607899999999999E-3</v>
+        <v>7.3607900000000007E-3</v>
       </c>
       <c r="AB113" s="2">
-        <v>1.2347349700000001E-2</v>
+        <v>1.2347349699999999E-2</v>
       </c>
       <c r="AC113" s="2">
         <v>2.2301799E-3</v>
       </c>
       <c r="AD113" s="2"/>
       <c r="AE113" s="2">
-        <v>0.4080009541000002</v>
+        <v>0.40800095409999998</v>
       </c>
     </row>
     <row r="114" spans="1:31" x14ac:dyDescent="0.25">
@@ -24317,7 +24924,7 @@
       </c>
       <c r="I114" s="2"/>
       <c r="J114" s="2">
-        <v>1.0460969399999999E-2</v>
+        <v>1.0460969400000002E-2</v>
       </c>
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
@@ -24337,7 +24944,7 @@
       </c>
       <c r="S114" s="2"/>
       <c r="T114" s="2">
-        <v>4.7083699999999999E-2</v>
+        <v>4.7083700000000006E-2</v>
       </c>
       <c r="U114" s="2">
         <v>4.2154399000000004E-3</v>
@@ -24370,7 +24977,7 @@
         <v>138</v>
       </c>
       <c r="B115" s="2">
-        <v>4.1718715696999995</v>
+        <v>4.1718715697000004</v>
       </c>
       <c r="C115" s="2">
         <v>4.9330698000000003E-3</v>
@@ -24379,13 +24986,13 @@
         <v>0.18359998979999997</v>
       </c>
       <c r="E115" s="2">
-        <v>1.9030036384000004</v>
+        <v>1.9030036384</v>
       </c>
       <c r="F115" s="2">
         <v>1.4166719899999999E-2</v>
       </c>
       <c r="G115" s="2">
-        <v>7.3240962696</v>
+        <v>7.3240962695999992</v>
       </c>
       <c r="H115" s="2">
         <v>0.28268344979999999</v>
@@ -24394,16 +25001,16 @@
         <v>4.8653498999999996E-3</v>
       </c>
       <c r="J115" s="2">
-        <v>0.94212681830000011</v>
+        <v>0.9421268183</v>
       </c>
       <c r="K115" s="2">
         <v>2.1589099E-3</v>
       </c>
       <c r="L115" s="2">
-        <v>0.95493683979999999</v>
+        <v>0.9549368398000001</v>
       </c>
       <c r="M115" s="2">
-        <v>2.3483739899999998E-2</v>
+        <v>2.3483739899999995E-2</v>
       </c>
       <c r="N115" s="2">
         <v>1.1590000000000001E-3</v>
@@ -24413,22 +25020,22 @@
         <v>15.813085364799999</v>
       </c>
       <c r="Q115" s="2">
-        <v>3.5419900194999991</v>
+        <v>3.5419900194999996</v>
       </c>
       <c r="R115" s="2">
-        <v>3.6475143194000008</v>
+        <v>3.6475143194000004</v>
       </c>
       <c r="S115" s="2">
-        <v>0.19353318990000001</v>
+        <v>0.19353318989999999</v>
       </c>
       <c r="T115" s="2">
         <v>1.9581311591000001</v>
       </c>
       <c r="U115" s="2">
-        <v>5.8971540394000002</v>
+        <v>5.8971540393999993</v>
       </c>
       <c r="V115" s="2">
-        <v>9.1594764796000021</v>
+        <v>9.1594764796000003</v>
       </c>
       <c r="W115" s="2">
         <v>4.3546414897999997</v>
@@ -24437,7 +25044,7 @@
         <v>4.5000000000000003E-5</v>
       </c>
       <c r="Y115" s="2">
-        <v>1.9936713545000004</v>
+        <v>1.9936713544999995</v>
       </c>
       <c r="Z115" s="2">
         <v>4.8655999999999998E-4</v>
@@ -24466,19 +25073,19 @@
         <v>4.4089374596000006</v>
       </c>
       <c r="C116" s="2">
-        <v>1.1544905099999998</v>
+        <v>1.15449051</v>
       </c>
       <c r="D116" s="2">
         <v>0.21959732979999999</v>
       </c>
       <c r="E116" s="2">
-        <v>2.8340743380000002</v>
+        <v>2.8340743380000006</v>
       </c>
       <c r="F116" s="2">
-        <v>4.4409935799999998</v>
+        <v>4.4409935800000007</v>
       </c>
       <c r="G116" s="2">
-        <v>17.608619569399998</v>
+        <v>17.608619569400002</v>
       </c>
       <c r="H116" s="2">
         <v>2.1314959997000003</v>
@@ -24487,16 +25094,16 @@
         <v>1.115909E-2</v>
       </c>
       <c r="J116" s="2">
-        <v>1.2647888485000003</v>
+        <v>1.2647888484999998</v>
       </c>
       <c r="K116" s="2">
         <v>1.4593398999999999E-3</v>
       </c>
       <c r="L116" s="2">
-        <v>6.1242180397000014</v>
+        <v>6.1242180396999997</v>
       </c>
       <c r="M116" s="2">
-        <v>0.53442169949999996</v>
+        <v>0.53442169950000007</v>
       </c>
       <c r="N116" s="2">
         <v>4.8697999999999998E-4</v>
@@ -24505,43 +25112,43 @@
         <v>0.15600999999999998</v>
       </c>
       <c r="P116" s="2">
-        <v>40.890752784100002</v>
+        <v>40.890752784100009</v>
       </c>
       <c r="Q116" s="2">
         <v>4.4633243696999996</v>
       </c>
       <c r="R116" s="2">
-        <v>4.0268172795000003</v>
+        <v>4.0268172794999995</v>
       </c>
       <c r="S116" s="2">
-        <v>0.37622475960000001</v>
+        <v>0.37622475960000007</v>
       </c>
       <c r="T116" s="2">
-        <v>3.5421008388999997</v>
+        <v>3.5421008389000002</v>
       </c>
       <c r="U116" s="2">
         <v>2.5056096797999996</v>
       </c>
       <c r="V116" s="2">
-        <v>23.694637568500003</v>
+        <v>23.694637568499999</v>
       </c>
       <c r="W116" s="2">
-        <v>4.3206386792999991</v>
+        <v>4.3206386793</v>
       </c>
       <c r="X116" s="2">
         <v>9.0015000000000008E-3</v>
       </c>
       <c r="Y116" s="2">
-        <v>9.5305304044000039</v>
+        <v>9.5305304043999968</v>
       </c>
       <c r="Z116" s="2">
         <v>1.46470399E-2</v>
       </c>
       <c r="AA116" s="2">
-        <v>5.6982490896000009</v>
+        <v>5.6982490896</v>
       </c>
       <c r="AB116" s="2">
-        <v>0.21192324959999997</v>
+        <v>0.2119232496</v>
       </c>
       <c r="AC116" s="2">
         <v>4.8664799999999994E-3</v>
@@ -24550,7 +25157,545 @@
         <v>0.13086400970000001</v>
       </c>
       <c r="AE116" s="2">
-        <v>58.529434948499997</v>
+        <v>58.529434948499983</v>
+      </c>
+    </row>
+    <row r="117" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>140</v>
+      </c>
+      <c r="B117" s="2">
+        <v>2.4249565095999999</v>
+      </c>
+      <c r="C117" s="2">
+        <v>2.2730884398000004</v>
+      </c>
+      <c r="D117" s="2">
+        <v>6.6615639800000001E-2</v>
+      </c>
+      <c r="E117" s="2">
+        <v>1.8550803674</v>
+      </c>
+      <c r="F117" s="2">
+        <v>0.77554355990000001</v>
+      </c>
+      <c r="G117" s="2">
+        <v>18.5775569993</v>
+      </c>
+      <c r="H117" s="2">
+        <v>2.2981995896999994</v>
+      </c>
+      <c r="I117" s="2">
+        <v>0.17071804999999998</v>
+      </c>
+      <c r="J117" s="2">
+        <v>4.2378244185000007</v>
+      </c>
+      <c r="K117" s="2">
+        <v>8.8948E-4</v>
+      </c>
+      <c r="L117" s="2">
+        <v>1.5976589097999998</v>
+      </c>
+      <c r="M117" s="2">
+        <v>0.13514408980000001</v>
+      </c>
+      <c r="N117" s="2">
+        <v>3.7877000000000001E-4</v>
+      </c>
+      <c r="O117" s="2">
+        <v>0.25136757990000003</v>
+      </c>
+      <c r="P117" s="2">
+        <v>34.665022403499997</v>
+      </c>
+      <c r="Q117" s="2">
+        <v>8.7242307397999994</v>
+      </c>
+      <c r="R117" s="2">
+        <v>5.3576997596</v>
+      </c>
+      <c r="S117" s="2">
+        <v>1.3229672497</v>
+      </c>
+      <c r="T117" s="2">
+        <v>4.677629949</v>
+      </c>
+      <c r="U117" s="2">
+        <v>5.2429506395999992</v>
+      </c>
+      <c r="V117" s="2">
+        <v>15.212640458300001</v>
+      </c>
+      <c r="W117" s="2">
+        <v>4.1994570090999996</v>
+      </c>
+      <c r="X117" s="2">
+        <v>0.19940906980000001</v>
+      </c>
+      <c r="Y117" s="2">
+        <v>14.987448524000003</v>
+      </c>
+      <c r="Z117" s="2">
+        <v>7.6535298999999999E-3</v>
+      </c>
+      <c r="AA117" s="2">
+        <v>6.4320158394000009</v>
+      </c>
+      <c r="AB117" s="2">
+        <v>0.39156755970000001</v>
+      </c>
+      <c r="AC117" s="2">
+        <v>2.2084998999999999E-3</v>
+      </c>
+      <c r="AD117" s="2">
+        <v>8.2585999999999998E-4</v>
+      </c>
+      <c r="AE117" s="2">
+        <v>66.758704687800005</v>
+      </c>
+    </row>
+    <row r="118" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>141</v>
+      </c>
+      <c r="B118" s="2">
+        <v>3.1846716895999996</v>
+      </c>
+      <c r="C118" s="2">
+        <v>0.62872975990000002</v>
+      </c>
+      <c r="D118" s="2">
+        <v>2.5661769900000003E-2</v>
+      </c>
+      <c r="E118" s="2">
+        <v>1.7990672481000001</v>
+      </c>
+      <c r="F118" s="2">
+        <v>0.38508512989999999</v>
+      </c>
+      <c r="G118" s="2">
+        <v>8.2126466693999998</v>
+      </c>
+      <c r="H118" s="2">
+        <v>3.3679871098</v>
+      </c>
+      <c r="I118" s="2">
+        <v>1.7524459999999999E-2</v>
+      </c>
+      <c r="J118" s="2">
+        <v>3.0730268883000003</v>
+      </c>
+      <c r="K118" s="2">
+        <v>4.6474997999999997E-3</v>
+      </c>
+      <c r="L118" s="2">
+        <v>2.3753682897000004</v>
+      </c>
+      <c r="M118" s="2">
+        <v>1.33431399E-2</v>
+      </c>
+      <c r="N118" s="2">
+        <v>2.6613990000000002E-4</v>
+      </c>
+      <c r="O118" s="2">
+        <v>1.7819999999999999E-5</v>
+      </c>
+      <c r="P118" s="2">
+        <v>23.0880436142</v>
+      </c>
+      <c r="Q118" s="2">
+        <v>1.7262058198000003</v>
+      </c>
+      <c r="R118" s="2">
+        <v>1.0451179098999999</v>
+      </c>
+      <c r="S118" s="2">
+        <v>3.1922522596</v>
+      </c>
+      <c r="T118" s="2">
+        <v>0.75632496970000007</v>
+      </c>
+      <c r="U118" s="2">
+        <v>1.6771042396000002</v>
+      </c>
+      <c r="V118" s="2">
+        <v>2.3218215296999993</v>
+      </c>
+      <c r="W118" s="2">
+        <v>11.9555273192</v>
+      </c>
+      <c r="X118" s="2">
+        <v>4.333E-3</v>
+      </c>
+      <c r="Y118" s="2">
+        <v>4.9648162521000012</v>
+      </c>
+      <c r="Z118" s="2">
+        <v>2.19916899E-2</v>
+      </c>
+      <c r="AA118" s="2">
+        <v>2.7449825095999998</v>
+      </c>
+      <c r="AB118" s="2">
+        <v>0.3186486295</v>
+      </c>
+      <c r="AC118" s="2">
+        <v>2.2066019800000003E-2</v>
+      </c>
+      <c r="AD118" s="2">
+        <v>1.6230476999999999</v>
+      </c>
+      <c r="AE118" s="2">
+        <v>32.374239848399995</v>
+      </c>
+    </row>
+    <row r="119" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>142</v>
+      </c>
+      <c r="B119" s="2">
+        <v>3.9797424395999998</v>
+      </c>
+      <c r="C119" s="2">
+        <v>3.0326020197000001</v>
+      </c>
+      <c r="D119" s="2">
+        <v>9.1755009700000015E-2</v>
+      </c>
+      <c r="E119" s="2">
+        <v>6.7601680280000007</v>
+      </c>
+      <c r="F119" s="2">
+        <v>0.87398166989999992</v>
+      </c>
+      <c r="G119" s="2">
+        <v>10.026497469499999</v>
+      </c>
+      <c r="H119" s="2">
+        <v>7.3240203799999977</v>
+      </c>
+      <c r="I119" s="2">
+        <v>5.56319E-3</v>
+      </c>
+      <c r="J119" s="2">
+        <v>2.4935459886000002</v>
+      </c>
+      <c r="K119" s="2">
+        <v>6.1733000000000003E-4</v>
+      </c>
+      <c r="L119" s="2">
+        <v>1.3239372598999999</v>
+      </c>
+      <c r="M119" s="2">
+        <v>8.7697019799999998E-2</v>
+      </c>
+      <c r="N119" s="2">
+        <v>1.04E-2</v>
+      </c>
+      <c r="O119" s="2">
+        <v>1.0499999999999999E-6</v>
+      </c>
+      <c r="P119" s="2">
+        <v>36.010528854699984</v>
+      </c>
+      <c r="Q119" s="2">
+        <v>2.7403005198999999</v>
+      </c>
+      <c r="R119" s="2">
+        <v>0.29240218979999999</v>
+      </c>
+      <c r="S119" s="2">
+        <v>0.5208472596</v>
+      </c>
+      <c r="T119" s="2">
+        <v>1.5808077787000001</v>
+      </c>
+      <c r="U119" s="2">
+        <v>0.34976723980000002</v>
+      </c>
+      <c r="V119" s="2">
+        <v>1.1962082494000001</v>
+      </c>
+      <c r="W119" s="2">
+        <v>2.0382081298000001</v>
+      </c>
+      <c r="X119" s="2">
+        <v>1.0449999999999999E-3</v>
+      </c>
+      <c r="Y119" s="2">
+        <v>0.87230686329999974</v>
+      </c>
+      <c r="Z119" s="2">
+        <v>4.0142179900000005E-2</v>
+      </c>
+      <c r="AA119" s="2">
+        <v>0.33674399979999997</v>
+      </c>
+      <c r="AB119" s="2">
+        <v>1.8411590495999997</v>
+      </c>
+      <c r="AC119" s="2">
+        <v>1.159089E-2</v>
+      </c>
+      <c r="AD119" s="2">
+        <v>8.3517299999999999E-3</v>
+      </c>
+      <c r="AE119" s="2">
+        <v>11.8298810796</v>
+      </c>
+    </row>
+    <row r="120" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>143</v>
+      </c>
+      <c r="B120" s="2">
+        <v>0.1226959297</v>
+      </c>
+      <c r="C120" s="2">
+        <v>6.757E-4</v>
+      </c>
+      <c r="D120" s="2">
+        <v>9.0969899999999998E-5</v>
+      </c>
+      <c r="E120" s="2">
+        <v>0.96665056849999997</v>
+      </c>
+      <c r="F120" s="2">
+        <v>1.9619E-4</v>
+      </c>
+      <c r="G120" s="2">
+        <v>8.07463296E-2</v>
+      </c>
+      <c r="H120" s="2">
+        <v>1.2235129999999999E-2</v>
+      </c>
+      <c r="I120" s="2"/>
+      <c r="J120" s="2">
+        <v>0.14371123899999999</v>
+      </c>
+      <c r="K120" s="2">
+        <v>1.1174900000000001E-3</v>
+      </c>
+      <c r="L120" s="2">
+        <v>6.7643797999999995E-3</v>
+      </c>
+      <c r="M120" s="2">
+        <v>4.3060899000000007E-3</v>
+      </c>
+      <c r="N120" s="2">
+        <v>1.11019E-3</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" s="2">
+        <v>1.3403002064</v>
+      </c>
+      <c r="Q120" s="2">
+        <v>1.7282280000000001E-2</v>
+      </c>
+      <c r="R120" s="2">
+        <v>2.9052039799999999E-2</v>
+      </c>
+      <c r="S120" s="2">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="T120" s="2">
+        <v>6.6810649799999997E-2</v>
+      </c>
+      <c r="U120" s="2">
+        <v>1.0649129800000001E-2</v>
+      </c>
+      <c r="V120" s="2">
+        <v>3.6853599699999996E-2</v>
+      </c>
+      <c r="W120" s="2">
+        <v>0.13227768980000001</v>
+      </c>
+      <c r="X120" s="2"/>
+      <c r="Y120" s="2">
+        <v>8.660572429999995E-2</v>
+      </c>
+      <c r="Z120" s="2">
+        <v>9.3256199999999997E-3</v>
+      </c>
+      <c r="AA120" s="2">
+        <v>9.3093198999999998E-3</v>
+      </c>
+      <c r="AB120" s="2">
+        <v>1.2477139800000002E-2</v>
+      </c>
+      <c r="AC120" s="2">
+        <v>5.35243E-3</v>
+      </c>
+      <c r="AD120" s="2"/>
+      <c r="AE120" s="2">
+        <v>0.41606562289999999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>144</v>
+      </c>
+      <c r="B121" s="2">
+        <v>8.6563000000000005E-3</v>
+      </c>
+      <c r="C121" s="2">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="D121" s="2">
+        <v>3.1817999999999999E-4</v>
+      </c>
+      <c r="E121" s="2">
+        <v>0.50897346939999988</v>
+      </c>
+      <c r="F121" s="2">
+        <v>1.4238E-4</v>
+      </c>
+      <c r="G121" s="2">
+        <v>1.5935849700000001E-2</v>
+      </c>
+      <c r="H121" s="2">
+        <v>4.3849398000000003E-3</v>
+      </c>
+      <c r="I121" s="2"/>
+      <c r="J121" s="2">
+        <v>7.8782592999999991E-3</v>
+      </c>
+      <c r="K121" s="2"/>
+      <c r="L121" s="2"/>
+      <c r="M121" s="2">
+        <v>1.73317E-3</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
+      <c r="P121" s="2">
+        <v>0.5483225481999997</v>
+      </c>
+      <c r="Q121" s="2">
+        <v>3.26669E-3</v>
+      </c>
+      <c r="R121" s="2">
+        <v>3.0783519599999996E-2</v>
+      </c>
+      <c r="S121" s="2"/>
+      <c r="T121" s="2">
+        <v>4.8706579799999997E-2</v>
+      </c>
+      <c r="U121" s="2">
+        <v>1.05770198E-2</v>
+      </c>
+      <c r="V121" s="2">
+        <v>2.7077739899999998E-2</v>
+      </c>
+      <c r="W121" s="2">
+        <v>0.11519347000000001</v>
+      </c>
+      <c r="X121" s="2"/>
+      <c r="Y121" s="2">
+        <v>7.7884295000000006E-2</v>
+      </c>
+      <c r="Z121" s="2"/>
+      <c r="AA121" s="2">
+        <v>8.9163799999999998E-3</v>
+      </c>
+      <c r="AB121" s="2">
+        <v>3.0604E-3</v>
+      </c>
+      <c r="AC121" s="2"/>
+      <c r="AD121" s="2"/>
+      <c r="AE121" s="2">
+        <v>0.32546609410000005</v>
+      </c>
+    </row>
+    <row r="122" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>145</v>
+      </c>
+      <c r="B122" s="2">
+        <v>3.4565984594000003</v>
+      </c>
+      <c r="C122" s="2">
+        <v>4.0530007899000005</v>
+      </c>
+      <c r="D122" s="2">
+        <v>9.7755990000000001E-2</v>
+      </c>
+      <c r="E122" s="2">
+        <v>7.3356065579999994</v>
+      </c>
+      <c r="F122" s="2">
+        <v>1.7080680000000001E-2</v>
+      </c>
+      <c r="G122" s="2">
+        <v>1.8812888993999997</v>
+      </c>
+      <c r="H122" s="2">
+        <v>4.5670779396999999</v>
+      </c>
+      <c r="I122" s="2">
+        <v>6.4868609999999993E-2</v>
+      </c>
+      <c r="J122" s="2">
+        <v>1.6700030388</v>
+      </c>
+      <c r="K122" s="2">
+        <v>5.9423700000000006E-3</v>
+      </c>
+      <c r="L122" s="2">
+        <v>1.0992869800000001E-2</v>
+      </c>
+      <c r="M122" s="2">
+        <v>2.2451529800000002E-2</v>
+      </c>
+      <c r="N122" s="2">
+        <v>3.1314400000000001E-3</v>
+      </c>
+      <c r="O122" s="2"/>
+      <c r="P122" s="2">
+        <v>23.185799174800003</v>
+      </c>
+      <c r="Q122" s="2">
+        <v>0.70061543989999986</v>
+      </c>
+      <c r="R122" s="2">
+        <v>5.2286210298999993</v>
+      </c>
+      <c r="S122" s="2">
+        <v>0.10363640989999999</v>
+      </c>
+      <c r="T122" s="2">
+        <v>1.0032564895</v>
+      </c>
+      <c r="U122" s="2">
+        <v>4.206613E-2</v>
+      </c>
+      <c r="V122" s="2">
+        <v>5.7828634597000006</v>
+      </c>
+      <c r="W122" s="2">
+        <v>1.2489245297</v>
+      </c>
+      <c r="X122" s="2">
+        <v>3.1203000000000002E-2</v>
+      </c>
+      <c r="Y122" s="2">
+        <v>0.16231829429999994</v>
+      </c>
+      <c r="Z122" s="2">
+        <v>9.0182598999999988E-3</v>
+      </c>
+      <c r="AA122" s="2">
+        <v>0.15598398989999998</v>
+      </c>
+      <c r="AB122" s="2">
+        <v>0.1225650097</v>
+      </c>
+      <c r="AC122" s="2">
+        <v>7.6397299000000004E-3</v>
+      </c>
+      <c r="AD122" s="2"/>
+      <c r="AE122" s="2">
+        <v>14.5987117723</v>
       </c>
     </row>
   </sheetData>
@@ -24560,7 +25705,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B8D9CE-6C58-4665-83B8-0D13D9F92D59}">
-  <dimension ref="A2:AE116"/>
+  <dimension ref="A2:AE122"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -34310,6 +35455,544 @@
         <v>36170</v>
       </c>
     </row>
+    <row r="117" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>140</v>
+      </c>
+      <c r="B117" s="2">
+        <v>822</v>
+      </c>
+      <c r="C117" s="2">
+        <v>32</v>
+      </c>
+      <c r="D117" s="2">
+        <v>8</v>
+      </c>
+      <c r="E117" s="2">
+        <v>379</v>
+      </c>
+      <c r="F117" s="2">
+        <v>19</v>
+      </c>
+      <c r="G117" s="2">
+        <v>268</v>
+      </c>
+      <c r="H117" s="2">
+        <v>230</v>
+      </c>
+      <c r="I117" s="2">
+        <v>9</v>
+      </c>
+      <c r="J117" s="2">
+        <v>284</v>
+      </c>
+      <c r="K117" s="2">
+        <v>9</v>
+      </c>
+      <c r="L117" s="2">
+        <v>38</v>
+      </c>
+      <c r="M117" s="2">
+        <v>72</v>
+      </c>
+      <c r="N117" s="2">
+        <v>8</v>
+      </c>
+      <c r="O117" s="2">
+        <v>3</v>
+      </c>
+      <c r="P117" s="2">
+        <v>2181</v>
+      </c>
+      <c r="Q117" s="2">
+        <v>5360</v>
+      </c>
+      <c r="R117" s="2">
+        <v>4254</v>
+      </c>
+      <c r="S117" s="2">
+        <v>33</v>
+      </c>
+      <c r="T117" s="2">
+        <v>4747</v>
+      </c>
+      <c r="U117" s="2">
+        <v>630</v>
+      </c>
+      <c r="V117" s="2">
+        <v>2678</v>
+      </c>
+      <c r="W117" s="2">
+        <v>6906</v>
+      </c>
+      <c r="X117" s="2">
+        <v>8</v>
+      </c>
+      <c r="Y117" s="2">
+        <v>11663</v>
+      </c>
+      <c r="Z117" s="2">
+        <v>16</v>
+      </c>
+      <c r="AA117" s="2">
+        <v>788</v>
+      </c>
+      <c r="AB117" s="2">
+        <v>15371</v>
+      </c>
+      <c r="AC117" s="2">
+        <v>11</v>
+      </c>
+      <c r="AD117" s="2">
+        <v>5</v>
+      </c>
+      <c r="AE117" s="2">
+        <v>52470</v>
+      </c>
+    </row>
+    <row r="118" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>141</v>
+      </c>
+      <c r="B118" s="2">
+        <v>831</v>
+      </c>
+      <c r="C118" s="2">
+        <v>30</v>
+      </c>
+      <c r="D118" s="2">
+        <v>8</v>
+      </c>
+      <c r="E118" s="2">
+        <v>356</v>
+      </c>
+      <c r="F118" s="2">
+        <v>15</v>
+      </c>
+      <c r="G118" s="2">
+        <v>206</v>
+      </c>
+      <c r="H118" s="2">
+        <v>180</v>
+      </c>
+      <c r="I118" s="2">
+        <v>27</v>
+      </c>
+      <c r="J118" s="2">
+        <v>269</v>
+      </c>
+      <c r="K118" s="2">
+        <v>11</v>
+      </c>
+      <c r="L118" s="2">
+        <v>47</v>
+      </c>
+      <c r="M118" s="2">
+        <v>49</v>
+      </c>
+      <c r="N118" s="2">
+        <v>6</v>
+      </c>
+      <c r="O118" s="2">
+        <v>1</v>
+      </c>
+      <c r="P118" s="2">
+        <v>2036</v>
+      </c>
+      <c r="Q118" s="2">
+        <v>7402</v>
+      </c>
+      <c r="R118" s="2">
+        <v>4351</v>
+      </c>
+      <c r="S118" s="2">
+        <v>55</v>
+      </c>
+      <c r="T118" s="2">
+        <v>5237</v>
+      </c>
+      <c r="U118" s="2">
+        <v>1000</v>
+      </c>
+      <c r="V118" s="2">
+        <v>2707</v>
+      </c>
+      <c r="W118" s="2">
+        <v>7355</v>
+      </c>
+      <c r="X118" s="2">
+        <v>4</v>
+      </c>
+      <c r="Y118" s="2">
+        <v>12357</v>
+      </c>
+      <c r="Z118" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA118" s="2">
+        <v>959</v>
+      </c>
+      <c r="AB118" s="2">
+        <v>5631</v>
+      </c>
+      <c r="AC118" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD118" s="2">
+        <v>6</v>
+      </c>
+      <c r="AE118" s="2">
+        <v>47100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>142</v>
+      </c>
+      <c r="B119" s="2">
+        <v>1354</v>
+      </c>
+      <c r="C119" s="2">
+        <v>21</v>
+      </c>
+      <c r="D119" s="2">
+        <v>7</v>
+      </c>
+      <c r="E119" s="2">
+        <v>267</v>
+      </c>
+      <c r="F119" s="2">
+        <v>14</v>
+      </c>
+      <c r="G119" s="2">
+        <v>372</v>
+      </c>
+      <c r="H119" s="2">
+        <v>214</v>
+      </c>
+      <c r="I119" s="2">
+        <v>9</v>
+      </c>
+      <c r="J119" s="2">
+        <v>342</v>
+      </c>
+      <c r="K119" s="2">
+        <v>4</v>
+      </c>
+      <c r="L119" s="2">
+        <v>36</v>
+      </c>
+      <c r="M119" s="2">
+        <v>59</v>
+      </c>
+      <c r="N119" s="2">
+        <v>2</v>
+      </c>
+      <c r="O119" s="2">
+        <v>2</v>
+      </c>
+      <c r="P119" s="2">
+        <v>2703</v>
+      </c>
+      <c r="Q119" s="2">
+        <v>9182</v>
+      </c>
+      <c r="R119" s="2">
+        <v>2723</v>
+      </c>
+      <c r="S119" s="2">
+        <v>27</v>
+      </c>
+      <c r="T119" s="2">
+        <v>5015</v>
+      </c>
+      <c r="U119" s="2">
+        <v>1272</v>
+      </c>
+      <c r="V119" s="2">
+        <v>3495</v>
+      </c>
+      <c r="W119" s="2">
+        <v>8166</v>
+      </c>
+      <c r="X119" s="2">
+        <v>3</v>
+      </c>
+      <c r="Y119" s="2">
+        <v>11875</v>
+      </c>
+      <c r="Z119" s="2">
+        <v>26</v>
+      </c>
+      <c r="AA119" s="2">
+        <v>865</v>
+      </c>
+      <c r="AB119" s="2">
+        <v>6330</v>
+      </c>
+      <c r="AC119" s="2">
+        <v>10</v>
+      </c>
+      <c r="AD119" s="2">
+        <v>3</v>
+      </c>
+      <c r="AE119" s="2">
+        <v>48992</v>
+      </c>
+    </row>
+    <row r="120" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>143</v>
+      </c>
+      <c r="B120" s="2">
+        <v>1374</v>
+      </c>
+      <c r="C120" s="2">
+        <v>14</v>
+      </c>
+      <c r="D120" s="2">
+        <v>2</v>
+      </c>
+      <c r="E120" s="2">
+        <v>163</v>
+      </c>
+      <c r="F120" s="2">
+        <v>10</v>
+      </c>
+      <c r="G120" s="2">
+        <v>224</v>
+      </c>
+      <c r="H120" s="2">
+        <v>172</v>
+      </c>
+      <c r="I120" s="2"/>
+      <c r="J120" s="2">
+        <v>233</v>
+      </c>
+      <c r="K120" s="2">
+        <v>6</v>
+      </c>
+      <c r="L120" s="2">
+        <v>17</v>
+      </c>
+      <c r="M120" s="2">
+        <v>49</v>
+      </c>
+      <c r="N120" s="2">
+        <v>4</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" s="2">
+        <v>2268</v>
+      </c>
+      <c r="Q120" s="2">
+        <v>88</v>
+      </c>
+      <c r="R120" s="2">
+        <v>3583</v>
+      </c>
+      <c r="S120" s="2">
+        <v>1</v>
+      </c>
+      <c r="T120" s="2">
+        <v>4404</v>
+      </c>
+      <c r="U120" s="2">
+        <v>856</v>
+      </c>
+      <c r="V120" s="2">
+        <v>2569</v>
+      </c>
+      <c r="W120" s="2">
+        <v>5858</v>
+      </c>
+      <c r="X120" s="2"/>
+      <c r="Y120" s="2">
+        <v>10129</v>
+      </c>
+      <c r="Z120" s="2">
+        <v>5</v>
+      </c>
+      <c r="AA120" s="2">
+        <v>655</v>
+      </c>
+      <c r="AB120" s="2">
+        <v>396</v>
+      </c>
+      <c r="AC120" s="2">
+        <v>3</v>
+      </c>
+      <c r="AD120" s="2"/>
+      <c r="AE120" s="2">
+        <v>28547</v>
+      </c>
+    </row>
+    <row r="121" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>144</v>
+      </c>
+      <c r="B121" s="2">
+        <v>178</v>
+      </c>
+      <c r="C121" s="2">
+        <v>1</v>
+      </c>
+      <c r="D121" s="2">
+        <v>1</v>
+      </c>
+      <c r="E121" s="2">
+        <v>58</v>
+      </c>
+      <c r="F121" s="2">
+        <v>6</v>
+      </c>
+      <c r="G121" s="2">
+        <v>93</v>
+      </c>
+      <c r="H121" s="2">
+        <v>145</v>
+      </c>
+      <c r="I121" s="2"/>
+      <c r="J121" s="2">
+        <v>180</v>
+      </c>
+      <c r="K121" s="2"/>
+      <c r="L121" s="2"/>
+      <c r="M121" s="2">
+        <v>34</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
+      <c r="P121" s="2">
+        <v>696</v>
+      </c>
+      <c r="Q121" s="2">
+        <v>55</v>
+      </c>
+      <c r="R121" s="2">
+        <v>3490</v>
+      </c>
+      <c r="S121" s="2"/>
+      <c r="T121" s="2">
+        <v>4176</v>
+      </c>
+      <c r="U121" s="2">
+        <v>755</v>
+      </c>
+      <c r="V121" s="2">
+        <v>2276</v>
+      </c>
+      <c r="W121" s="2">
+        <v>6102</v>
+      </c>
+      <c r="X121" s="2"/>
+      <c r="Y121" s="2">
+        <v>9271</v>
+      </c>
+      <c r="Z121" s="2"/>
+      <c r="AA121" s="2">
+        <v>644</v>
+      </c>
+      <c r="AB121" s="2">
+        <v>431</v>
+      </c>
+      <c r="AC121" s="2"/>
+      <c r="AD121" s="2"/>
+      <c r="AE121" s="2">
+        <v>27200</v>
+      </c>
+    </row>
+    <row r="122" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>145</v>
+      </c>
+      <c r="B122" s="2">
+        <v>1345</v>
+      </c>
+      <c r="C122" s="2">
+        <v>35</v>
+      </c>
+      <c r="D122" s="2">
+        <v>4</v>
+      </c>
+      <c r="E122" s="2">
+        <v>219</v>
+      </c>
+      <c r="F122" s="2">
+        <v>15</v>
+      </c>
+      <c r="G122" s="2">
+        <v>128</v>
+      </c>
+      <c r="H122" s="2">
+        <v>209</v>
+      </c>
+      <c r="I122" s="2">
+        <v>39</v>
+      </c>
+      <c r="J122" s="2">
+        <v>317</v>
+      </c>
+      <c r="K122" s="2">
+        <v>12</v>
+      </c>
+      <c r="L122" s="2">
+        <v>52</v>
+      </c>
+      <c r="M122" s="2">
+        <v>74</v>
+      </c>
+      <c r="N122" s="2">
+        <v>4</v>
+      </c>
+      <c r="O122" s="2"/>
+      <c r="P122" s="2">
+        <v>2453</v>
+      </c>
+      <c r="Q122" s="2">
+        <v>4776</v>
+      </c>
+      <c r="R122" s="2">
+        <v>3409</v>
+      </c>
+      <c r="S122" s="2">
+        <v>6</v>
+      </c>
+      <c r="T122" s="2">
+        <v>4608</v>
+      </c>
+      <c r="U122" s="2">
+        <v>792</v>
+      </c>
+      <c r="V122" s="2">
+        <v>2496</v>
+      </c>
+      <c r="W122" s="2">
+        <v>6326</v>
+      </c>
+      <c r="X122" s="2">
+        <v>7</v>
+      </c>
+      <c r="Y122" s="2">
+        <v>9654</v>
+      </c>
+      <c r="Z122" s="2">
+        <v>9</v>
+      </c>
+      <c r="AA122" s="2">
+        <v>762</v>
+      </c>
+      <c r="AB122" s="2">
+        <v>6829</v>
+      </c>
+      <c r="AC122" s="2">
+        <v>5</v>
+      </c>
+      <c r="AD122" s="2"/>
+      <c r="AE122" s="2">
+        <v>39679</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
